--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A296"/>
+  <dimension ref="A1:A273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,175 +445,175 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-cm-devendra-fadnavis-chairs-review-meeting-on-excessive-rainfall-at-mantralaya-video</t>
+          <t>https://www.msn.com/en-in/news/India/bal-thackeray-must-be-blessing-me-devendra-fadnavis-jibe-at-uddhav-raj/ar-AA1I1uNG?cvid=4abb379217d14469d8ca5b000d1b6962&amp;ocid=up97dhp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
+          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/bal-thackeray-must-be-blessing-me-devendra-fadnavis-jibe-at-uddhav-raj/ar-AA1I1uNG?cvid=4abb379217d14469d8ca5b000d1b6962&amp;ocid=up97dhp</t>
+          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
+          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan,-presents-him-book-of-shivaji-maharaj's-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/fadnavis-hails-maha-guvs-nomination-as-vice-presidential-candidate-1503473264.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
@@ -627,609 +627,609 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
+          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
+          <t>https://www.devdiscourse.com/article/politics/3545404-maharashtra-governor-radhakrishnan-a-voter-from-mumbai-and-ndas-vice-presidential-choice</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/video/mt-originals/manoj-jarange-alligation-on-devendra-fadnavis/videoshow/123365218.cms</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://www.lokmattimes.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/manoj-jarange-vs-devendra-fadnavis-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%98%E0%A5%87%E0%A4%A3-%E0%A4%B0%E0%A4%9A-%E0%A4%86%E0%A4%A1%E0%A4%B5-%E0%A4%AF%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%A6-%E0%A4%96%E0%A4%B5-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%87%E0%A4%B6-%E0%A4%B0/vi-AA1KJrkK?ocid=hpmsn</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-heavy-rainfall-lashes-maharashtra-schools-closed-cm-devendra-fadnavis-to-review-situation-1377933</t>
+          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
+          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/tn/838759/third-mumbai-new-city-announced-by-devendra-fadnavis</t>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/mumbai-rain-update-next-10-to-12-hours-are-important-for-mumbai-people-cm-devendra-fadnavis-warning-to-stay-safe-from-rain-aau85</t>
+          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/mumbai/mumbai-connectivity-coastal-road-atal-setu-worli-shivdi-link</t>
+          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-took-review-of-rain-situation-at-state-disaster-management-centre-in-the-ministry-963383.html</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/mumbai/will-mumbai-become-slum-free-what-is-the-chief-ministers-plan-for-rapid-redevelopment</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-heavy-rainfall-red-orange-alert-15-districts-cm-fadnavis-advisory-as80</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A7-%E0%A4%AC%E0%A4%A8-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A6-%E0%A4%A6-%E0%A4%97-%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1JMfla?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray-2/913299/</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/cloud-burst-types-rain-in-nanded-indian-army-called-for-rescue-cm-devendra-fadnavis-reacts/933262</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivaji-sawants-entry-into-bjp-confirmed-decision-announced-after-meeting-with-chief-minister-vd83</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%9B-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A2%E0%A4%BC-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8-%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%9C%E0%A4%A6%E0%A5%82%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87/ar-AA1JMr77?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/nanded-umri-tehsildar-suspended-for-singing-while-sitting-on-a-chair-uddhav-thackeray-shivsena-slams-chandrashekhar-bawankule-mention-devendra-fadnavis-wife/933459</t>
+          <t>https://www.msn.com/hi-in/news/other/indias-got-latent-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A4%E0%A4%95-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A5%87-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1yKIjb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/mumbai-rain-alert-cm-devendra-fadnavis-said-mumbai-schools-declared-holiday-on-tomorrow-bmc-to-decide-pvm91</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
+          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nanded-rain-news-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%87%E0%A4%A1%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A2%E0%A4%97%E0%A4%AB%E0%A5%81%E0%A4%9F-%E0%A4%B8%E0%A4%A6%E0%A5%83%E0%A4%B6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-cm-devendra-fadanvis-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A4%A6%E0%A4%A4-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%A8/vi-AA1KIk6k</t>
+          <t>https://vikalptimes.com/red-and-orange-alert-issued-in-many-districts-of-maharashtra-due-to-heavy-rains/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/nanded-rain-news-cloudburst-like-rain-in-mukhed-cm-devendra-fadnavis-issues-help-instructions-1070799.html</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-orders-agencies-to-be-alert-review-of-the-situation-across-the-state/</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/dada-bhuse-news-%E0%A4%85%E0%A4%A4-%E0%A4%B5%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%95-%E0%A4%A3%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9C-%E0%A4%B2%E0%A5%8D%E0%A4%B9%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2-%E0%A4%B6-%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%9C-%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A5%8D%E0%A4%AF-n18v/vi-AA1KKbyi?ocid=hpmsn</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-farmer-loan-waiver-soon-amidst-heavy-rain-and-crop-damage-minister-confirms-cm-devendra-fadnavis-announcement-1378070</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3545659-third-mumbai-initiative-sparks-new-wave-of-economic-growth-in-maharashtra</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3545353-mumbai-monsoon-mayhem-navigating-challenges-amid-torrential-rains</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/raghuji-bhosale-sword-inauguration-in-mumbai-by-cm-devendra-fadnavis/photoshow/123367923.cms</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html?ref_source=OI-MR&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://vikalptimes.com/red-and-orange-alert-issued-in-many-districts-of-maharashtra-due-to-heavy-rains/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A7-%E0%A4%AC%E0%A4%A8-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A6-%E0%A4%A6-%E0%A4%97-%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1JMfla?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%9B-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A2%E0%A4%BC-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8-%E0%A4%9A-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%9C%E0%A4%A6%E0%A5%82%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87/ar-AA1JMr77?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-reviews-rains-800-villages-affected-in-marathwada-red-alert-in-konkan-vidarbha/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/from-banda-to-chanda-there-is-chaos-everywhere-due-to-rain/</t>
+          <t>https://deshonnati.com/road-constructionvillagers-stage-protest-gangakhed-parbhani/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-rain-news-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B3%E0%A4%A7-%E0%A4%B0-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B5-%E0%A4%B9%E0%A4%A4%E0%A5%82%E0%A4%95-%E0%A4%95-%E0%A4%82%E0%A4%A1-%E0%A4%B2-%E0%A4%95-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B9-%E0%A4%B2/vi-AA1KI8VB?ocid=hpmsn</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3545404-maharashtra-governor-radhakrishnan-a-voter-from-mumbai-and-ndas-vice-presidential-choice</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chief-justice-bhushan-gavai-praised-shivendrasinghraje-bhosale-vd83</t>
+          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://aaplaawajnews.com/2025/34067/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-august-2025-mumbai-pune-rain-maharashtra-weather-update-imd-kokan-cm-devendra-fadnavis-stock-market-ajit-pawar-farmer-ahul-gandhi-us-president-donald-trump-supreme-court-railway-sports-entertainment-politics-finance-trending-viral-news-updates</t>
+          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/cp-radhakrishnan-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%B8-%E0%A4%A0-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%95-%E0%A4%AF-marathi-news-n18v/vi-AA1KKh8T</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
@@ -1243,91 +1243,91 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/india-news/maharashtra/mumbai-rains-city-on-red-alert-schools-and-colleges-closed-clouds-will-rain-for-5-days-id-465240/amp</t>
+          <t>https://www.msn.com/mr-in/news/other/nanded-heavy-rain-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%A1%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A2%E0%A4%97%E0%A4%AB%E0%A5%81%E0%A4%9F-%E0%A4%B8%E0%A4%A6%E0%A5%83%E0%A4%B6-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%87%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%AA-%E0%A4%9A-%E0%A4%9C%E0%A4%A3-%E0%A4%AC%E0%A5%87%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B8%E0%A5%88%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A4%B2-%E0%A4%B2-%E0%A4%AA-%E0%A4%9A-%E0%A4%B0%E0%A4%A3/ar-AA1KIAWQ</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/india-squad-asia-cup-2025-2025-08-18-1156798</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rain-news-all-government-semi-government-offices-in-mumbai-remain-closed-today-mumbai-local-tracks-under-water-amid-imd-red-alert-for-extremely-heavy-rainfall-maharashtra-news-mhs25081901225</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/abu-azmi-writes-to-cm-fadnavis-on-flood-situation-demands-urgent-assistance-125081900011_1.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/third-mumbai-will-be-settled-in-this-district-of-maharashtra-125081900017_1.html</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
+          <t>https://www.msn.com/en-in/news/India/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/ar-AA1KGGDd</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/ar-AA1KGGDd</t>
+          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
         </is>
       </c>
     </row>
@@ -1341,448 +1341,448 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>http://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/ajit-pawar-is-torturing-me-bjp-ram-shinde-big-statement-rohit-pawar/</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/water-supply-in-nagar-road-area-will-be-closed-on-thursday/</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/bmc-big-decision-holiday-declared-for-government-and-private-offices-heavy-rain-mumbai/</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/obscene-dance-premises-of-renowned-rayat-shikshan-sanstha-baramati/</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/nation/telecom-collapses-across-the-country-airtel-jio-vi-network-down/</t>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/crime/sister-i-need-your-help-a-10th-grade-girls-phone-call-and-the-sensitivity-of-the-police-saved-the-family/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/bawankule-advises-rahul-gandhi-to-get-workers-to-check-voter-list/</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/maharashtra/entrepreneur-salim-seth-ghaniwala-enters-bjp/</t>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34070/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/solapur-political-news-bjp-strengthens-in-solapur-as-40-sena-leaders-join-with-shivaji-sawant-bdk97</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrapur-bjp-mla-kishor-jorgewar-faces-setback-as-administration-demolishes-illegal-amma-memorial-construction-as11-rc70</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34067/</t>
+          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/eknath-shinde-big-announcement-ladki-soon-yojana-shiv-senato-implement-scheme/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray-2/913299/amp</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/08/19/nagpur-district-planning-committee-meeting-chaired-by-revenue-minister-chandrashekhar-bawankule-review-of-2025-26-annual-plan/</t>
+          <t>https://www.indiatv.in/video/sports/india-squad-asia-cup-2025-2025-08-18-1156798</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
+          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/heavy-rains-in-mumbai-limited-to-a-few-days-mumbai-print-news-amy-95-5313543/</t>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/areas-in-aarey-submerged-due-to-heavy-rains-mumbai-print-news-amy-95-5313545/</t>
+          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://www.indianewsstream.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
+          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bogus-teacher-scam-school-id-fraud-directors-property-to-be-seized-ng81</t>
+          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>http://www.msn.com/mr-in/news/other/maharashtra-politics-%E0%A4%AC-%E0%A4%8F%E0%A4%AE%E0%A4%B8-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%82%E0%A4%A1-%E0%A4%B5%E0%A4%B0-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A5%82%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%B2-%E0%A4%9F%E0%A4%AE%E0%A4%B8-%E0%A4%9F%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%9C-%E0%A4%97-%E0%A4%B5-%E0%A4%9F%E0%A4%AA-%E0%A4%A0%E0%A4%B0%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%AC%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%AD-%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1KCf0p?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/vote-chori-row-heats-up-election-commissions-presser-a-comedy-show-aaps-sanjay-singh-raps-ec/videoshow/123358629.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/vice-president-election-uddhav-thackeray-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-sanjay-raut-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-n18s/vi-AA1KIbM2</t>
+          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/best-election-news-%E0%A4%AE%E0%A4%A8%E0%A4%B8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-sandeep-deshpande-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%A7-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%97%E0%A4%82%E0%A4%AD-%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%AA-n18s/vi-AA1KIfwO</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/best-election-news-uddhav-thackeray-raj-thackeray-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B8-%E0%A4%9F-%E0%A4%9A-%E0%A4%A6-%E0%A4%B5%E0%A4%B8%E0%A4%AC-%E0%A4%9C-%E0%A4%AE-%E0%A4%B0%E0%A4%A3-%E0%A4%B0/vi-AA1KLt69</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/road-constructionvillagers-stage-protest-gangakhed-parbhani/</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A4%A3-%E0%A4%A4-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%9A-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A4%A3-%E0%A4%A4-%E0%A4%AE-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%9A-%E0%A4%B8%E0%A4%B2-%E0%A4%B5-%E0%A4%9C%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%B3-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF/ar-AA1I0OWR</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/maharashtra-politics-%E0%A4%AC-%E0%A4%8F%E0%A4%AE%E0%A4%B8-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%82%E0%A4%A1-%E0%A4%B5%E0%A4%B0-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A5%82%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%B2-%E0%A4%9F%E0%A4%AE%E0%A4%B8-%E0%A4%9F%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%9C-%E0%A4%97-%E0%A4%B5-%E0%A4%9F%E0%A4%AA-%E0%A4%A0%E0%A4%B0%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%AC%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%AD-%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1KCf0p?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://m.economictimes.com/markets/stocks/news/apollo-tyres-adani-ports-mrf-among-8-stocks-closed-crossing-above-vwap-on-august-18/supreme-industries/slideshow/123377083.cms</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/chandrashekhar-bawankule-check-the-voter-lists-now-chandrashekhar-bawankules-pinch-to-congress/</t>
+          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/supreme-court-reject-petition-on-maharashtra-assembly-elections-eci-reaction-9523295.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/cet-2025-announced-for-judicial-services-competitive-examination.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple,-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/nation/maharashtra-governor-radhakrishnan-is-the-candidate-from-nda-oppositions-dmk-card/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%B5-%E0%A4%B2-%E0%A4%A6-%E0%A4%82%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1KJ5pi</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/tiruchi-siva-will-india-aghadi-contest-the-vice-presidential-election-whose-name-is-in-the-lead/129400/</t>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/live-rahul-gandhi-tejashwi-yadav-at-voter-adhikar-rally-nawada-bihar/videoshow/123379809.cms</t>
+          <t>https://www.etvbharat.com/en/!state/mumbai-rains-update-august-19-govt-semi-govt-offices-shut-bmc-urges-wfh-for-pvt-employees-enn25081901231</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6%E0%A4%82%E0%A4%AD%E0%A5%82%E0%A4%B0-%E0%A4%9C-%E0%A4%A6%E0%A5%87%E0%A4%B8-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AC%E0%A4%9A%E0%A4%AA%E0%A4%A8-%E0%A4%B5-%E0%A4%B2-%E0%A4%B5%E0%A4%B9-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AC%E0%A4%82%E0%A4%97%E0%A4%B2-%E0%A4%AE-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%AD-%E0%A4%B5%E0%A5%81%E0%A4%95-%E0%A4%97%E0%A5%83%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1JRinD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
@@ -1796,707 +1796,546 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/uttarakhand-cm-dhamis-cabinet-decided-to-establish-closed-madarsa-system/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A4%A3-%E0%A4%A4-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%9A-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A4%A3-%E0%A4%A4-%E0%A4%AE-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%9A-%E0%A4%B8%E0%A4%B2-%E0%A4%B5-%E0%A4%9C%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%B3-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF/ar-AA1I0OWR</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/marathi-news-headlines-7-am-news18-lokmat-19-aug-2025-maharashtra-rain-update-mumbai-local/vi-AA1KLIwf?ocid=hpmsn</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bade-mudde-rahul-gandhi-vs-ec-news-%E0%A4%AC-%E0%A4%97%E0%A4%B8-%E0%A4%AE%E0%A4%A4%E0%A4%A6-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%A8%E0%A5%87-%E0%A4%AB%E0%A5%87%E0%A4%9F-%E0%A4%B3%E0%A4%B2/vi-AA1KKJ81?ocid=hpmsn</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%96-%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86-%E0%A4%B8%E0%A4%95%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%AE-%E0%A4%9D-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A4%B2-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%87%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%B2-%E0%A4%93%E0%A4%82-%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AA%E0%A5%88%E0%A4%B8%E0%A5%87/ar-AA1vsznB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-news-today-navi-mumbai-%E0%A4%9A%E0%A5%87-%E0%A4%B2-%E0%A4%95-dadar-station-%E0%A4%B2-%E0%A4%AF%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%85%E0%A4%A1%E0%A4%95%E0%A4%B2%E0%A5%87-n18s-shorts/vi-AA1KIFxI</t>
+          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/jalgoan-rain-update-%E0%A4%AA-%E0%A4%B0-%E0%A4%B3-%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AA-%E0%A4%95-%E0%A4%AA-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%9A%E0%A4%A8-%E0%A4%AE-%E0%A4%95%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%AE%E0%A4%A6%E0%A4%A4-%E0%A4%9A-%E0%A4%AE-%E0%A4%97%E0%A4%A3/vi-AA1KIgOa</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/body-weight-impact-%E0%A4%B2%E0%A4%A0%E0%A5%8D%E0%A4%A0-%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%AD%E0%A4%B0-%E0%A4%B5-%E0%A4%B2-%E0%A4%97%E0%A5%87%E0%A4%B2-%E0%A4%95%E0%A4%B0-%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A4-%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B2-%E0%A4%B5%E0%A4%B2-%E0%A4%9C-%E0%A4%A4-nw18s/vi-AA1KKrZe</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-rain-update-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B3%E0%A4%A7-%E0%A4%B0-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B6-%E0%A4%B3-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A4%B2-%E0%A4%AA%E0%A4%A3-%E0%A4%97%E0%A5%81%E0%A4%A1%E0%A4%98-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%8D%E0%A4%A5%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A4%B0-%E0%A4%9C-%E0%A4%AF%E0%A4%9A%E0%A4%82-%E0%A4%95%E0%A4%B8%E0%A4%82/vi-AA1KIDWr</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/thane-monsoon-update-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A8-%E0%A4%89%E0%A4%B6-%E0%A4%B0-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%A3-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A4%B3%E0%A4%A7-%E0%A4%B0-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%9A-%E0%A4%A0-%E0%A4%A3%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AB%E0%A4%9F%E0%A4%95/vi-AA1KIytZ</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/chembur-land-slide-video-%E0%A4%9A%E0%A5%87%E0%A4%82%E0%A4%AC%E0%A5%81%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AD-%E0%A4%82%E0%A4%A4-%E0%A4%95-%E0%A4%B8%E0%A4%B3%E0%A4%B2-7-%E0%A4%9D-%E0%A4%AA%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-news18-lokmat/vi-AA1KJ3O8</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-rain-update-%E0%A4%B8-%E0%A4%AF%E0%A4%A8%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B8-%E0%A4%9A%E0%A4%B2%E0%A4%82-%E0%A4%AA-%E0%A4%A3-%E0%A4%B8%E0%A4%95-%E0%A4%B3-1040%E0%A4%9A-%E0%A4%A6%E0%A5%83%E0%A4%B6%E0%A5%8D%E0%A4%AF%E0%A4%82/vi-AA1KHYOZ</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple,-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
+          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ajit-pawar-torturing-me-claims-ram-shinde/articleshow/123372969.cms</t>
+          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-rohit-pawar-alleges-5000-crore-land-scam-against-minister-sanjay-shirsat</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/minister-shirsat-accused-of-rs-5000-crore-land-scam-np88</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/third-mumbai-will-open-new-chapter-economic-development-maha-cm-441953</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/amp/?utm=relatedarticles</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6%E0%A4%82%E0%A4%AD%E0%A5%82%E0%A4%B0-%E0%A4%9C-%E0%A4%A6%E0%A5%87%E0%A4%B8-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AC%E0%A4%9A%E0%A4%AA%E0%A4%A8-%E0%A4%B5-%E0%A4%B2-%E0%A4%B5%E0%A4%B9-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AC%E0%A4%82%E0%A4%97%E0%A4%B2-%E0%A4%AE-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%AD-%E0%A4%B5%E0%A5%81%E0%A4%95-%E0%A4%97%E0%A5%83%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1JRinD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
+          <t>https://tennews.in/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
+          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/kamalabais-new-plan-allies-have-to-be-wiped-out-fadnavis-will-play-the-game-of-shinde-dada-till-2029/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.in/national/news/after-ladki-bahin-yojana-will-ladki-sunbai-yojana-be-an-2198473</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%96-%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86-%E0%A4%B8%E0%A4%95%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%AE-%E0%A4%9D-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A4%B2-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%87%E0%A4%A8-%E0%A4%AE%E0%A4%B9-%E0%A4%B2-%E0%A4%93%E0%A4%82-%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AA%E0%A5%88%E0%A4%B8%E0%A5%87/ar-AA1vsznB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/nanded-tehsildar-prashant-thorat-suspension-shiv-sena-ubt-criticism-sanjay-raut-devendra-fadnavis-jap93</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/urban-naxalites-campaign-to-defame-hindu-religious-places-karnataka-bjp-mla-harish-punja-alleges.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://thelivenagpur.com/2025/08/18/historic-sword-of-raghuji-bhonsle-returns-to-mumbai-to-be-unveiled-in-grand-ceremony/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://www.lokmat.com/pune/the-vande-bharat-train-from-nagpur-to-pune-which-started-a-week-ago-was-delayed-by-two-and-a-half-hours-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/paschim-maharashtra/statue-of-unity-style-memorial-in-maharashtra-soon</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://www.ptinews.com/story/national/monday-mayhem:-mumbai's-suburbs-recorded-over-100-mm-rainfall-in-12-hours,-says-imd/2834156</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/bus-catches-fire-on-mumbai-bangalore-highway-at-midnight-passengers-narrowly-escape/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/mumbai-on-red-alert-due-to-heavy-rain-schools-and-colleges-closed/</t>
+          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/noise-pollution-rules-violated-during-ganeshotsav-ngt-issues-notice-to-pune-police-and-pollution-board/</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/editorial/migration-of-billionaires/</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/08/05/satyapal-malik-pm-modi-former-governor-satyapal-malik-breaking-news/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-orders-agencies-to-be-alert-review-of-the-situation-across-the-state/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
+          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/public-trust-amendment-bill-introduced-in-lok-sabha.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/historic-sword-of-raghuji-bhonsle-returns-to-mumbai-to-be-unveiled-in-grand-ceremony/</t>
+          <t>https://www.msn.com/mr-in/news/other/marathi-news-headlines-7-am-news18-lokmat-19-aug-2025-maharashtra-rain-update-mumbai-rain/vi-AA1KLnMI?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
+          <t>https://m.economictimes.com/news/india/bmc-declares-holiday-for-mumbai-schools-colleges-on-august-19-as-city-braces-for-heavy-rain/articleshow/123366693.cms</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
+          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://www.hindustantimes.com/india-news/are-mumbai-schools-colleges-open-today-details-here-mumbai-rains-mumbai-weather-imd-red-alert-101755561079277.html</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
+          <t>https://www.thehindubusinessline.com/news/mumbai-weather-mumbai-rains-live-news-updates/article69946123.ece</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-august-2025-rahul-gandhi-election-commission-maharashtra-rain-mumabai-rain-local-body-election-nandani-elephant-vantara-gujarat-shravan-weather-update-imd-kokan-pune-mumbai-us-president-donald-trump-supreme-court-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C%E0%A4%A7-%E0%A4%A8-%E0%A4%A4-%E0%A4%AA-%E0%A4%B5%E0%A4%B8-%E0%A4%9A-%E0%A4%95%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%9A-%E0%A4%AA%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%A4%E0%A4%A1%E0%A4%95-%E0%A4%AB%E0%A4%A1%E0%A4%95-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1KKmSa</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+          <t>https://www.aninews.in/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune20250819111423/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
+          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-after-ladki-bahin-now-ladki-sunbai-yojana-announced-how-this-benefits-to-women-19873910</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/marathi-news-headlines-2-pm-news18-lokmat-18-aug-2025-maharashtra-rain-update-mumbai-rain/vi-AA1KIyNJ?ocid=hpmsn</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/chhatrapati-sambhajinagar/nanded-heavy-rain-over-200-stranded-after-heavy-rains-army-called-in-for-rescue-89509</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>https://hindi.etnownews.com/news/mumbai-rain-alert-delhi-yamuna-flood-imd-weather-forecast-heavy-rainfall-india-article-152485258</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>https://www.theindiadaily.com/india/mumbai-civic-body-declares-holiday-for-all-schools-and-colleges-on-august-19-amid-heavy-rain-forecast-news-90572</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>https://www.theindiadaily.com/india/maharashtra-mumbai-heavy-rain-in-several-cities-local-train-to-flight-affecting-imd-alert-for-next-coming-4-days-news-90608</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-rains-news-live-pune-weather-lake-levels-local-train-status-traffic-imd-forecast-waterlogging-schools-closed-red-alert-liveblog-152480215</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/bmc-declares-holiday-for-mumbai-schools-colleges-on-august-19-as-city-braces-for-heavy-rain/articleshow/123366693.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/india-news/maratha-general-raghuji-bhonsle-sword-brought-to-mumbai-maharashtra-government-acquired-in-auction-2025-08-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/cet-2025-announced-for-judicial-services-competitive-examination.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-holiday-in-mumbai-due-to-rain-heavy-rainfall-alert-for-the-next-48-hours/articleshow/123357322.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>https://kadwaghut.com/mumbai-rain-heavy-rains-in-mumbai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A289"/>
+  <dimension ref="A1:A301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,133 +445,133 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
+          <t>https://www.msn.com/en-in/news/India/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/ar-AA1KJ362</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://www.thehindubusinessline.com/news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/article69950172.ece</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Rain-fury-leaves-7-dead-in-Maharashtra--200-villagers-stranded/2834213</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
@@ -585,35 +585,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-metropolitan-region-development--fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/third-mumbai-to-boost-metropolitan-region-development-fadnavis-20250819T044623387Z?lang=en</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom20-mh-governor-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
+          <t>https://www.ptinews.com/story/national/Rain-fury-leaves-7-dead-in-Maharashtra--200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
@@ -627,1232 +627,1232 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://udayavani.com/national/third-mumbai-to-boost-metropolitan-region-development-fadnavis-20250819T044623387Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.onmanorama.com/news/india/2025/08/18/mumbai-rains-flooding-high-tide-warning-live.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://menafn.com/1109941619/Third-Mumbai-Will-Open-A-New-Chapter-Of-Economic-Development-Maha-CM</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
+          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A7-%E0%A4%AC%E0%A4%A8-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A6-%E0%A4%A6-%E0%A4%97-%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1JMfla?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/five-people-missing-many-people-stranded-due-to-heavy-rains-in-nanded-chief-minister-fadnavis/856679/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/indias-got-latent-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A4%E0%A4%95-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A5%87-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1yKIjb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://vikalptimes.com/red-and-orange-alert-issued-in-many-districts-of-maharashtra-due-to-heavy-rains/</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-torrential-rains-in-maharashtra-cause-havoc-seven-people-died/</t>
+          <t>https://www.msn.com/hi-in/news/other/indias-got-latent-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A4%E0%A4%95-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A5%87-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1yKIjb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/shinde-and-bjp-the-saga-continues/ar-AA1KHn3K</t>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
+          <t>https://www.ibc24.in/business/third-mumbai-will-lead-to-development-of-mmr-says-fadnavis-3213495.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sword-of-maratha-commander-raghuji-bhosale-returns-to-mumbai-to-be-unveiled-at-exhibition-by-cm-fadnavis-maharashtra-news-mhs25081803521</t>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/big-update-on-farmer-loan-waiver-cm-fadnavis-will-do-announcement-says-minister-sanjay-rathod-1472819.html</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-holiday-in-mumbai-due-to-rain-heavy-rainfall-alert-for-the-next-48-hours/articleshow/123357322.cms</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
+          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28165/</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://lokashanews.com/28165/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-is-making-every-effort-to-deal-with-the-flood-situation-the-chief-minister-appeals-to-people-to-be-careful-considering-the-risk-of-heavy-rains-maharashtra-news-mhs25081804221</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34070/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://www.msn.com/en-in/news/India/shinde-and-bjp-the-saga-continues/ar-AA1KHn3K</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-appeals-to-mumbaikars-after-review-of-rains-at-bmc-stay-at-house-during-mumbai-heavy-rains-1472440.html</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/new-minority-education-bill-to-be-introduced-in-uttarakhand-assembly.html</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://tripurachronicle.in/national-news/225-trapped-in-nanded-floods-army-ndrf-deployed-for-rescue-ops/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/new-minority-education-bill-to-be-introduced-in-uttarakhand-assembly.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/political-battle-over-nda-candidate-radhakrishnan-cm-fadnavis-seeks-support-from-uddhav-thackeray-and-sharad-pawar-1321873.html/amp</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
+          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
+          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-to-get-third-ring-road-with-land-acquisition-from-36-villages-vsb99</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/support-radhakrishnan-for-the-post-of-vice-president-who-talks-about-maharashtras-identity-fadnavis/856729/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
+          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-to-get-third-ring-road-with-land-acquisition-from-36-villages-vsb99</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/bihar-elections-rjd-leader-tejaswi-yadav-takes-on-pm-modi-over-bihar-polls-stop-fooling-981918</t>
+          <t>https://www.latestly.com/india/news/extremely-unfortunate-rajnath-singh-raps-opposition-for-stalling-special-discussion-in-parliament-on-astronaut-subhanshu-shuklas-space-mission-7064889.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
+          <t>https://www.ndtv.com/video/bihar-elections-rjd-leader-tejaswi-yadav-takes-on-pm-modi-over-bihar-polls-stop-fooling-981918</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/parliament-news-india-bloc-continues-protest-against-bihar-sir-at-parliament-982014</t>
+          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
+          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
+          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
+          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/shorts/national/vote-theft-row-escalates-opposition-mulls-impeachment-of-election-commissioner/</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://www.lokmat.com/shorts/national/vote-theft-row-escalates-opposition-mulls-impeachment-of-election-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
+          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
+          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/</t>
+          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
         </is>
       </c>
     </row>
@@ -1866,56 +1866,56 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6%E0%A4%82%E0%A4%AD%E0%A5%82%E0%A4%B0-%E0%A4%9C-%E0%A4%A6%E0%A5%87%E0%A4%B8-%E0%A4%88-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AC%E0%A4%9A%E0%A4%AA%E0%A4%A8-%E0%A4%B5-%E0%A4%B2-%E0%A4%B5%E0%A4%B9-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AC%E0%A4%82%E0%A4%97%E0%A4%B2-%E0%A4%AE-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%AD-%E0%A4%B5%E0%A5%81%E0%A4%95-%E0%A4%97%E0%A5%83%E0%A4%B9%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1JRinD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
@@ -1929,70 +1929,70 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
+          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation-9674122</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://www.patrika.com/national-news/heavy-rain-alert-in-mumbai-monsoon-gained-momentum-know-imd-weather-update-19874723</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
@@ -2006,49 +2006,49 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-sc-dismisses-plea-alleging-discrepancies-in-2024-maharashtra-assembly-polls-7065753.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/mah-plans-amnesty-scheme-to-recover-pending-transport-fines.html</t>
+          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maratha-commander-raghuji-bhosales-sword-brought-to-mumbai/856774/</t>
+          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
@@ -2062,392 +2062,476 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/amp/?utm=relatedarticles</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
+          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/states-and-uts/maharashtra/maha-govt-signs-mous-worth-rs-42000-crore-and-creation-of-28000-jobs</t>
+          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-imd-red-alert-mumbai-city-suburbs-schools-and-colleges-remain-closed-today-mumbai-university-exams-postponed-to-23-august-maharashtra-rain-news-today-maharashtra-news-mhs25081900792</t>
+          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/monday-mayhem:-mumbai's-suburbs-recorded-over-100-mm-rainfall-in-12-hours,-says-imd/2834156</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
+          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-live-press-on-mumbai-rain-update-red-alert-963319.html</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://www.ptinews.com/story/national/monday-mayhem:-mumbai's-suburbs-recorded-over-100-mm-rainfall-in-12-hours,-says-imd/2834156</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176009/</t>
+          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176143/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
+          <t>https://mahasamvad.in/176121/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-chief-ministers-eye-on-heavy-rains-in-nanded-district-instructions-to-the-administration/</t>
+          <t>https://mahasamvad.in/176009/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
+          <t>https://mahasamvad.in/176143/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
+          <t>https://www.tv9marathi.com/videos/maharashtras-major-decisions-police-recruitment-housing-projects-and-historical-artefact-return-1472726.html</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/bmc-declares-holiday-for-mumbai-schools-colleges-on-august-19-as-city-braces-for-heavy-rain/articleshow/123366693.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/are-mumbai-schools-colleges-open-today-details-here-mumbai-rains-mumbai-weather-imd-red-alert-101755561079277.html</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-reviews-rains-800-villages-affected-in-marathwada-red-alert-in-konkan-vidarbha/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
+          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
+          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!entertainment/trailer-of-the-film-dashavatar-which-brings-a-new-era-of-grandeur-to-marathi-cinema-is-released-maharashtra-news-mhs25081901382</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A301"/>
+  <dimension ref="A1:A296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
@@ -487,84 +487,84 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
+          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/ar-AA1KJ362</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/ar-AA1KJ362</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-'asmita'-should-support-radhakrishnan-for-vp-post:-fadnavis/2832772</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/article69950172.ece</t>
+          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
@@ -578,1596 +578,1596 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-metropolitan-region-development--fadnavis/2834902</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
+          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-mmr-development--says-fadnavis;-invites-pvt-sector-to-join-in-its-creation/2834267</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-metropolitan-region-development--fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom20-mh-governor-fadnavis.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Rain-fury-leaves-7-dead-in-Maharashtra--200-villagers-stranded/2834213</t>
+          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides/2832660</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/2833181</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/third-mumbai-to-boost-metropolitan-region-development-fadnavis-20250819T044623387Z?lang=en</t>
+          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.onmanorama.com/news/india/2025/08/18/mumbai-rains-flooding-high-tide-warning-live.html</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
+          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom21-mh-rains-mumbai-cm.html</t>
+          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278516795/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis</t>
+          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109941619/Third-Mumbai-Will-Open-A-New-Chapter-Of-Economic-Development-Maha-CM</t>
+          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://indiacsr.in/brillio-national-stem-challenge-empowers-2500-underserved-students-to-innovate-for-indias-future/</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250819/281994678584394</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://menafn.com/1109945394/Mumbai-Rains-Maharashtra-CM-Says-Observe-Precautions-Warns-Of-Heavy-Rainfall-High-Tide-Check-BMCs-Advisory</t>
+          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+          <t>https://www.ibc24.in/business/third-mumbai-will-lead-to-development-of-mmr-says-fadnavis-3213495.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
+          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://livevns.news/National/panic-in-maharashtra-due-to-heavy-rainphp/cid17258961.htm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/london-auction-historic-raghuji-bhosale-sword-brought-to-mumbai-devendra-fadnavis-says-indias-heritage-restored-2997814</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-sc-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AA%E0%A4%B0-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1IRMGx</t>
+          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/indias-got-latent-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A4%E0%A4%95-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A5%87-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1yKIjb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://lalluram.com/in-kolhapur-cji-gavai-praised-him-in-front-of-cm-and-deputy-cm-said-those-who-are-complaining-do-not-know-about-devendra-fadnavis-and-eknath-shinde/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/third-mumbai-will-lead-to-development-of-mmr-says-fadnavis-3213495.html</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
+          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
+          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
+          <t>https://lokashanews.com/28165/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-updates-18-august-heavy-rainfall-mumbai-navi-mumbai-kolhapur-raigad-sindhudurag-local-train-latest-updates-traffic-news-rak-94-5312079/</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/heavy-raincm-devendra-fadnavis-agencies-alert-heavy-rain-state/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/lowkey-launch-of-raghuji-bhonsle-s-sword-in-rain-lashed-city-101755543235713.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28165/</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/shinde-and-bjp-the-saga-continues/ar-AA1KHn3K</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
+          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/new-minority-education-bill-to-be-introduced-in-uttarakhand-assembly.html</t>
+          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://aaplaawajnews.com/2025/34070/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnvis-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A5%A7%E0%A5%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%AA%E0%A5%88%E0%A4%A0%E0%A4%A3-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1KKgDI</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
+          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD%E0%A4%AF-%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%8A%E0%A4%B8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A4-%E0%A4%A4%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%A7%E0%A4%B2-%E0%A4%B6%E0%A5%87%E0%A4%9C-%E0%A4%B0-%E0%A4%B2-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B6-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%85%E0%A4%A4-%E0%A4%B6%E0%A4%AF-%E0%A4%9A-%E0%A4%82%E0%A4%A4-%E0%A4%9C%E0%A4%A8%E0%A4%95/ar-AA1KJav3</t>
+          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-bjp-gives-setback-to-eknath-shinde-shiv-sena-before-civic-polls-19873589</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
+          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-excessive-screen-time-can-cause-heart-disease-in-children-2025-08-19-1156871</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-to-get-third-ring-road-with-land-acquisition-from-36-villages-vsb99</t>
+          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/extremely-unfortunate-rajnath-singh-raps-opposition-for-stalling-special-discussion-in-parliament-on-astronaut-subhanshu-shuklas-space-mission-7064889.html</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/bihar-elections-rjd-leader-tejaswi-yadav-takes-on-pm-modi-over-bihar-polls-stop-fooling-981918</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/teachers-planning-violent-protest-cops/articleshow/123350909.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
+          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/pm-modi-appeals-for-unanimous-election-of-radhakrishnan-as-vice-president</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://paliwalwani.com/maharastra/shiv-sena-eknath-shinde-faction-is-a-big-shock-shivaji-sawant-will-be-involved-in-bjp</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/shorts/national/vote-theft-row-escalates-opposition-mulls-impeachment-of-election-commissioner/</t>
+          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
+          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
+          <t>https://www.tribuneindia.com/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/radhakrishnan-should-be-supported-by-mps-from-all-parties-in-the-state/114185/</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%B5-%E0%A4%B2-%E0%A4%A6-%E0%A4%82%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1KJ5pi</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ajit-pawar-torturing-me-claims-ram-shinde/articleshow/123372969.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
+          <t>https://www.latestly.com/agency-news/india-news-sc-dismisses-plea-alleging-discrepancies-in-2024-maharashtra-assembly-polls-7065753.html</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/18/dcm62-biz-briefs-3.html</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-mmr-development-says-fadnavis-invites-pvt-sector-to-join-in-its-creation-9674122</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/heavy-rain-alert-in-mumbai-monsoon-gained-momentum-know-imd-weather-update-19874723</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
+          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
+          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
+          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/revenue-minister-bawankules-stance-4218277</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sindh-mukti-sangathan-holds-akhand-bharat-sankalp-diwas-programme/articleshow/123350984.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/two-bangladeshi-nationals-held-for-illegal-stay/articleshow/123350437.cms</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
+          <t>https://udayavani.com/national/heavy-rains-in-nanded-rescue-operations-on-as-5-go-missing-225-trapped-in-floodwaters-20250818T093308478Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-63-crore-people-have-spinal-injuries-how-will-cervical-and-sciatica-be-cured-2025-08-18-1156639</t>
         </is>
       </c>
     </row>
@@ -2181,357 +2181,322 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/ar-AA1KISQ7</t>
+          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/monday-mayhem:-mumbai's-suburbs-recorded-over-100-mm-rainfall-in-12-hours,-says-imd/2834156</t>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
+          <t>https://mahasamvad.in/176121/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
+          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176121/</t>
+          <t>https://mahasamvad.in/176009/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176009/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176143/</t>
+          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtras-major-decisions-police-recruitment-housing-projects-and-historical-artefact-return-1472726.html</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/mumbai-rain-cm-devendra-fadnavis-in-action-mode-administration-alert-due-to-rains-falling-across-the-state/</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
+          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
+          <t>https://www.informalnewz.com/rainfall-alert-all-schools-and-colleges-closed-due-to-heavy-rains-imd-issued-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
+          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/trailer-of-the-film-dashavatar-which-brings-a-new-era-of-grandeur-to-marathi-cinema-is-released-maharashtra-news-mhs25081901382</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/rain-wreaks-havoc-in-maharashtra-brings-mumbai-to-a-standstill/article69948564.ece</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/trailer-of-the-film-dashavatar-which-brings-a-new-era-of-grandeur-to-marathi-cinema-is-released-maharashtra-news-mhs25081901382</t>
+          <t>https://thelogicalindian.com/mumbai-on-red-alert-after-over-500mm-rain-in-84-hours-schools-shut-flights-delayed-traffic-paralyzed/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
+          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
+          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A296"/>
+  <dimension ref="A1:A299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,56 +438,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/business/third-mumbai-to-boost-mmrs-development-cm-devendra-fadnavis-says-101755577376569.html</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-seeks-opposition-backing-for-radhakrishnan-23590051</t>
+          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/india/devendra-fadnavis-first-reaction-to-raj-thackeray-s-reunion-with-uddhav-jibe/ar-AA1I1jzW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
         </is>
       </c>
     </row>
@@ -515,224 +515,224 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sword-of-raghuji-bhonsle-unveiled-in-mumbai-a-bridge-between-generations-says-cm-fadnavis/articleshow/123372524.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832772</t>
+          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/heavy-rains-ravage-state-cm-fadnavis-orders-relief-surveys-rain-hit-areas/articleshow/123372550.cms</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/ar-AA1KHNiH</t>
+          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-mmr-development--says-fadnavis;-invites-pvt-sector-to-join-in-its-creation/2834267</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/-third-mumbai--to-boost-metropolitan-region-development--fadnavis/2834902</t>
+          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-more-to-come-amid-high-tides/2832660</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322/</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rain-live-updates-heavy-rains-lashes-city-orange-alert-for-today-red-alert-in-pune-satara-ratnagiri-local-trains-delayed-traffic-jams-8017300/</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
+          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/heavy-rains-lash-nanded-five-missing-scores-stranded-says-cm-fadnavis-army-unit-deployed-9672306</t>
+          <t>https://thenewsmill.com/2025/08/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/paisa/business/third-mumbai-will-be-settled-in-raigad-district-of-maharashtra-chief-minister-devendra-fadnavis-told-the-important-points-of-the-project-2025-08-19-1156854</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
@@ -767,133 +767,133 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/maharashtra-cmdevendra-fadnavis-told-third-mumbai-mmr-will-develop-with-this-know-how-it-will-be-9112502</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-governor-radhakrishnan-gets-nda-backing-for-vice-president-post-devendra-fadnavis-uddhav-thackeray-sharad-pawar/articleshow/123371527.cms</t>
+          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%86%E0%A4%AA%E0%A4%95-%E0%A4%B5%E0%A4%B9-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%B2%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vljO5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%87%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A4%95-%E0%A4%98-%E0%A4%9F-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%AD-%E0%A4%B7-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%B9-%E0%A4%97/ar-AA1ImpaC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/raghuji-bhosale-historic-sword-will-arrive-in-mumbai-today-cm-fadnavis-will-welcome-it/2886138</t>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
+          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/third-mumbai-will-lead-to-development-of-mmr-says-fadnavis-3213495.html</t>
+          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-governments-master-plan-to-set-up-third-mumbai/cid17261301.htm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://livevns.news/National/panic-in-maharashtra-due-to-heavy-rainphp/cid17258961.htm</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis20250818145322</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-gets-support-from-congress-leader-nitin-raut-letter-goes-viral-1461146.html</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
@@ -956,21 +956,21 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
@@ -984,14 +984,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mahayuti-minister-gives-important-information-regarding-farmer-loan-waiver-devendra-fadnavis-soon/</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
@@ -1005,42 +1005,42 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28165/</t>
+          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://lokashanews.com/28165/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-mumbai-rain-alert-update-chief-minister-devendra-fadnavis-immediately-contacted-the-neighboring-states/933328</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
@@ -1068,924 +1068,924 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
+          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/tmc-identified-227-illegal-buildings-strict-action-will-be-taken-to-make-thane-a-well-planed-city-tmc-assures-bombay-high-court-maharashtra-news-mhs25081802854</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/lowkey-launch-of-raghuji-bhonsle-s-sword-in-rain-lashed-city-101755543235713.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rain-live-updates-red-alert-school-closed-heavy-rains-august-18-weather-waterlogging-borivali-thane-powai-bmc-101755498397210.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
+          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/waterlogging-in-thane-kalyan-dombivali-schools-closed-today-19-august/articleshow/123374806.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
+          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-in-the-meeting-of-president-trump-with-zelensky-and-european-leaders-an-agreement-was-reached-on-trilateral-talks-between-america-russia-2025-08-19-1156864</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%A1-%E0%A4%86%E0%A4%82%E0%A4%AC%E0%A5%87%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4%E0%A4%A8-%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1JMyQJ</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/crop-damage-on-two-lakh-hectares-in-vidarbha-rat16</t>
+          <t>https://ommcomnews.com/india-news/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
+          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/articleshow/123373035.cms</t>
+          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34070/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/declare-wet-drought-in-the-state-provide-assistance-of-rs-50000-per-acre-shashikant-shinde-97623/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
+          <t>https://hindi.oneindia.com/news/india/maharashtra-governor-cp-radhakrishnan-nda-vice-presidential-candidate-leaders-congratulate-1364687.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-politics-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A8-%E0%A4%98-%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%A6%E0%A5%81%E0%A4%AA%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%AE%E0%A4%9C-%E0%A4%B5/ar-AA1HHJp9</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/hakikat-kya-hai/haqiqat-kya-hai-2025-08-19-1156836</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
+          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/heavy-rains-damage-crops-on-4-lakh-hectares-cm-devendra-fadnaivs-reviews-situation-in-maharashtra/articleshow/123379831.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/a-blow-to-shindes-army-these-mla-brothers-left-the-party-97625/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nmc-pushes-ahead-with-land-acquisition-for-2-stps-amid-reluctance-from-vnit-pkv/articleshow/123372521.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/mbbs-admission-quota-in-unaided-colleges-cut-by-50-students-erupt/articleshow/123372541.cms</t>
+          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
+          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-19-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-19-1156865</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747/</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
+          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/08/19/308844/bharat/supreme-court-dismisses-plea-alleging-75-lakh-bogus-votes-in-maharashtra-assembly-polls/</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/sports/alcaraz-wins-the-cincinnati-open-after-sinner-retires-in-the-first-set-because-of-illness</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-defence-minister-rajnath-singh-reaches-out-to-dmk-tmc-bjd-for-consensus-for-cp-radhakrishnan/articleshow/123375990.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-dy-cm-eknath-shinde-launches-ladki-sun-surakshit-sun-campaign-to-protect-women-victims</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/teachers-planning-violent-protest-cops/articleshow/123350909.cms</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/slap-but-dont-make-video-raj-thackerays-blunt-advice-to-mns-workers-after-marathi-slapgate-case/ar-AA1I11OF</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-receives-over-200-mm-rainfall-in-24-hours-202405</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/sangh-centenary-is-a-time-of-review-and-foresight-sarsanghchalak-dr-mohanji-bhagwat.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://www.rokthoklekhani.com/article/43134/mumbai--heavy-rains-till-august-20--meteorological-department-issued-orange-alert</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple,-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/amit-shah-is-leader-of-maharashtra-corrupt-leader-says-sanjay-raut/</t>
+          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/'third-mumbai'-to-boost-metropolitan-region-development:-fadnavis/2834902</t>
+          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97-%E0%A4%A4-%E0%A4%B8%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%94%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%81%E0%A4%B5-%E0%A4%A7-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%95-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1KLMl6?ocid=finance-verthp-feeds</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/heavy-rains-in-maharashtra-flood-havoc-in-beed-latur-and-nanded-ndrf-and-army-deployed/articleshow/123370629.cms</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-heavy-rain-maharashtra-flood-situation-serious-ndrf-and-indian-army-deployed-in-marathwada/articleshow/123370824.cms</t>
+          <t>https://timesproperty.com/news/post/mumbai-to-get-238-new-ac-local-trains-in-three-yrs-blid10400</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://www.rokthoklekhani.com/article/43152/new-delhanew-delhi--supreme-court-strict-on-the-issue-of-disabled-military-cadets--center-should-consider-rehabilitation-plan-i-consider-supreme-court-strict-rehabilitation-scheme-on-the</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
+          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-approves-amendments-for-dharavi-project-land-transfer/ar-AA1G1ze9</t>
+          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ajit-pawar-torturing-me-claims-ram-shinde/articleshow/123372969.cms</t>
+          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%A8%E0%A4%A1-%E0%A4%8F%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B2-%E0%A4%AB-%E0%A4%AF%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1KJ7hd</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/cm-to-join-kawad-yatra-tv-center-chowk-shut-for-5-hours/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-sc-dismisses-plea-alleging-discrepancies-in-2024-maharashtra-assembly-polls-7065753.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
+          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
+          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
         </is>
       </c>
     </row>
@@ -1999,502 +1999,523 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/red-alert-issued-as-heavy-rain-batters-mumbai-schools-and-colleges-closed-due-to-waterlogging/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
+          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/jaipur/jaipur-abu-dhabi-flight-cancelled/articleshow/123350813.cms</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sindh-mukti-sangathan-holds-akhand-bharat-sankalp-diwas-programme/articleshow/123350984.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/two-bangladeshi-nationals-held-for-illegal-stay/articleshow/123350437.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/concrete-from-bengalurus-ejipura-flyover-slab-falls-on-autorickshaw-injures-driver/articleshow/123350812.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raisoni-college-of-business-management-hosts-nptel-awareness-workshop/articleshow/123351088.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/heavy-rains-in-nanded-rescue-operations-on-as-5-go-missing-225-trapped-in-floodwaters-20250818T093308478Z?lang=en</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/nashik-cops-start-e-meeting-with-police-commissioner-facility/articleshow/123351427.cms</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-63-crore-people-have-spinal-injuries-how-will-cervical-and-sciatica-be-cured-2025-08-18-1156639</t>
+          <t>https://udayavani.com/national/heavy-rains-in-nanded-rescue-operations-on-as-5-go-missing-225-trapped-in-floodwaters-20250818T093308478Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-63-crore-people-have-spinal-injuries-how-will-cervical-and-sciatica-be-cured-2025-08-18-1156639</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
+          <t>https://samacharnama.com/states/maharashtra-news/supreme-court-dismisses-plea-seeking-cancellation-of/cid17260970.htm</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
+          <t>https://www.etvbharat.com/mr/!state/anna-hazare-outburst-on-flex-boards-in-pune-maharashtra-news-mhs25081801191</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/articleshow/123368187.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/i-got-offer-to-remove-10000-names-from-voter-list-before-assembly-elections-bachchu-kadu-claim-maharashtra-news-mhs25081703006</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
+          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
+          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176121/</t>
+          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
+          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176009/</t>
+          <t>https://mahasamvad.in/176121/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
+          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+          <t>https://mahasamvad.in/176009/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
+          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
+          <t>https://mahasamvad.in/176143/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-ramesh-bidhuri-congratulated-radhakrishnan-said---he-will-prove-to-be-a-good-vice-president-news-hindi-1-745268-KKN.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/india-monsoon-live-mumbai-rains-yamuna-river-flood-alert-delhi-kashmir-cloudburst-updates-august-18/article69946105.ece</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.informalnewz.com/rainfall-alert-all-schools-and-colleges-closed-due-to-heavy-rains-imd-issued-red-alert/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
+          <t>https://www.etvbharat.com/mr/!bharat/krishna-janmashtami-2025-celebrations-procession-turn-tragic-in-hyderabad-five-devotees-electrocuted-to-death-after-chariot-comes-in-contact-electric-wire-maharashtra-news-mhs25081800993</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/trailer-of-the-film-dashavatar-which-brings-a-new-era-of-grandeur-to-marathi-cinema-is-released-maharashtra-news-mhs25081901382</t>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
+          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-heavy-rain-expected-by-imd-red-alert-heavy-rainfall-local-train-updates/articleshow/123376293.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/mumbai-rains-live-updates-mumbai-red-alert-issue-streets-inundated-and-hits-local-trains-lb-89483</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-rain-cm-fadnavis-reviews-situation-16-districts-on-red-alert/</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://thelogicalindian.com/mumbai-on-red-alert-after-over-500mm-rain-in-84-hours-schools-shut-flights-delayed-traffic-paralyzed/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
+        <is>
+          <t>https://panasiabiz.com/111088/cm-siddaramaiah-and-dycm-dk-shivakumar-inaugurate-%E2%82%B980-crore-hebbal-flyover-to-ease-bengaluru-traffic/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/18/bom51-mh-cm-third-mumbai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
         <is>
           <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A299"/>
+  <dimension ref="A1:A270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
+          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
         </is>
       </c>
     </row>
@@ -508,70 +508,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/ar-AA1KJ362</t>
+          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
+          <t>https://www.msn.com/en-in/news/India/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/ar-AA1KJ362</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/-Third-Mumbai--to-boost-metropolitan-region-development--Fadnavis/2834902</t>
+          <t>https://www.ptinews.com/story/business/-Third-Mumbai--to-boost-MMR-development--says-Fadnavis;-invites-pvt-sector-to-join-in-its-creation=/2834267</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
@@ -592,1932 +592,1729 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674-amp.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maratha-general-raghuji-bhonsle-s-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
+          <t>https://www.prameyanews.com/ndas-vice-presidential-candidate-cp-radhakrishnan-to-travel-to-delhi-today</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state-23590120</t>
+          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination/</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis-9672630</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
+          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-flights-status-airlines-issue-key-advisory-for-passengers/story</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-mangalore-9WWc/20250819/281947433944151</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharajs-letters-9672415</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded-9674070</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources/</t>
+          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/mumbai-news/heavy-rain-wreaks-havoc-in-mumbai-cm-devendra-fadnavis-calls-a-meeting-19874343</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://www.tv9hindi.com/india/raje-raghuji-bhosale-sword-history-maharashtra-cm-fadnavis-grand-welcome-3441860.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%85%E0%A4%AA%E0%A4%AE-%E0%A4%A8%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A6-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%9C%E0%A4%AE-%E0%A4%A8%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%96-%E0%A4%B0-%E0%A4%9C/ar-AA1Je80j?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://newstrack.com/india/third-mumbai-being-built-maharashtra-district-have-economic-development-know-full-details-534715</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+          <t>https://thenewsmill.com/2025/08/deliver-justice-in-spirit-of-shahu-maharajs-vision-cji-gavai-inaugurates-bombay-high-court-circuit-bench-at-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/maharashtra-bhari-barish-ke-baad-nanded-mein-rahat-bachav-karya-tez-jiladhikariyon-ke-sampark-mein-cm-fadnavis--20250818144516/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/declare-the-state-a-flood-disaster-call-a-special-session-ncp-state-president-made-a-demand-to-the-cm/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-governments-master-plan-to-set-up-third-mumbai/cid17261301.htm</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state/</t>
+          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://newslivetv.com/mumbai-rains-imd-issues-red-alert/</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-has-directed-all-agencies-to-be-on-alert-due-to-heavy-rains-in-the-maharashtra-mumbai-print-news-amy-95-5313479/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://lokashanews.com/28165/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-everyone-should-support-the-people-of-maharashtra-chief-minister-fadnavis-appeals-to-m-v-a-mps/</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/maharashtra-school-closed-tomorrow/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28165/</t>
+          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://www.etvbharat.com/mr/!state/tmc-identified-227-illegal-buildings-strict-action-will-be-taken-to-make-thane-a-well-planed-city-tmc-assures-bombay-high-court-maharashtra-news-mhs25081802854</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-shiv-sena-eknath-shinde-bjp-devendra-fadnavis-conflict-before-bmc-election-sdp-92-5314661/lite/</t>
+          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://www.etvbharat.com/mr/!spiritual/shravan-2025-fourth-shravan-somwar-horoscope-rashi-bhavishya-for-18-august-2025-in-marathi-mhs25081704098</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/tmc-identified-227-illegal-buildings-strict-action-will-be-taken-to-make-thane-a-well-planed-city-tmc-assures-bombay-high-court-maharashtra-news-mhs25081802854</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/mumbai-rains-schools-shut-as-mumbai-under-imd-red-alert-braces-for-another-day-of-heavy-rain-10-updates-101755564432674.html</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sword-of-raghuji-bhonsle-arrives-in-mumbai-and-will-be-on-display-till-aug-25/articleshow/123371745.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/live-news-updates-mumbai-rain-waterlogging-traffic-heavy-rain-orange-alert-125081800291_1.html</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-weather-red-alert-for-kolhapur-district-today-all-automatic-gates-of-radhanagari-dam-opened-for-the-first-time-in-the-season-1377818</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
+          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/cms-nod-for-new-terminal-bldg-at-nashik-airport-received-min/articleshow/123372835.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/articleshow/123354325.cms</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%B5-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zqXD8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/?amp</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+          <t>https://aaplaawajnews.com/2025/34070/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls20250819085747</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=bjp-man-accuses-trinamool-leaders-of-supporting-rohingyas-threatens-to-bulldoze-them-into-bangladesh</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-weather-forecast-imd-red-alert-for-mumbai-for-next-4-hours-extremely-important-for-mumbaikars-1473139.html/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/maharashtra-governor-cp-radhakrishnan-nda-vice-presidential-candidate-leaders-congratulate-1364687.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/fake-shalarth-id-recruitment-scam-nagpur-two-clerk-brothers-arrested-in-cheating-case-total-number-of-accused-arrested-in-reached-to-20-maharashtra-news-mhs25081800757</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
+          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-heavy-rains-in-the-state-800-villages-affected-170-mm-rain/</t>
+          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
+          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
+          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://www.lokmat.com/shorts/mumbai/best-credit-society-election-thackeray-brothers-unite-vs-bjp-results-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
+          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cp-radhakrishnan-vs-who-why-dmks-pushing-india-bloc-for-a-tamil-vs-tamil-contest-for-indias-v-p/2723136/</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
+          <t>https://www.rokthoklekhani.com/article/43138/mumbai--a-major-accident-was-averted-in-chira-bazaar--stairs-of-a-two-storey-old-building-suddenly-collapsed</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.rokthoklekhani.com/article/43136/mumbai--enthusiasm-of-ganesh-devotees-is-at-its-peak--mumbai-s-rain-has-no-effect</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
+          <t>https://www.rokthoklekhani.com/article/43134/mumbai--heavy-rains-till-august-20--meteorological-department-issued-orange-alert</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
+          <t>https://www.rokthoklekhani.com/article/43150/bangladeshi-woman-accused-who-escaped-from-jj-hospital-arrested-by-mumbai-police</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
+          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
+          <t>https://aninews.in/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune20250819111423</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://www.rokthoklekhani.com/article/43152/new-delhanew-delhi--supreme-court-strict-on-the-issue-of-disabled-military-cadets--center-should-consider-rehabilitation-plan-i-consider-supreme-court-strict-rehabilitation-scheme-on-the</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-receives-over-200-mm-rainfall-in-24-hours-202405</t>
+          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://english.varthabharati.in/karnataka/did-mahesh-shetty-timarodi-really-say-cm-siddaramaiah-killed-24-people-heres-the-truth</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/sangh-centenary-is-a-time-of-review-and-foresight-sarsanghchalak-dr-mohanji-bhagwat.html</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43134/mumbai--heavy-rains-till-august-20--meteorological-department-issued-orange-alert</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple,-crafted-by-shripad-shankar-nagarkar-jewellers-pune/2835628</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%A8%E0%A4%A1-%E0%A4%8F%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B2-%E0%A4%AB-%E0%A4%AF%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1KJ7hd</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/indias-7th-rank-in-us-scheme-for-children-sparks-fraud-concerns/articleshow/123350715.cms</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-jaipur/20250819/281681145971378</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/seven-people-died-due-to-heavy-rains-in-maharashtra-200-villagers-stranded/856903/</t>
+          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://www.amarujala.com/india-news/maratha-general-raghuji-bhonsle-sword-brought-to-mumbai-maharashtra-government-acquired-in-auction-2025-08-18</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/third-mumbai-in-raigad-district-to-boost-metropolitan-region-development-said-devendra-fadnavis-89724</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/heavy-rains-in-maharashtra-cause-huge-damage-to-farmers-after-crop-loss-and-land-submerged-in-water-1263471-2025-08-19</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/mrs-pragya-walkens-high-score-in-corruption-active-participation-in-anti-government-movement/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/amp/?utm=relatedarticles</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://timesproperty.com/news/post/mumbai-to-get-238-new-ac-local-trains-in-three-yrs-blid10400</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43152/new-delhanew-delhi--supreme-court-strict-on-the-issue-of-disabled-military-cadets--center-should-consider-rehabilitation-plan-i-consider-supreme-court-strict-rehabilitation-scheme-on-the</t>
+          <t>https://www.etnownews.com/news/mumbai-schools-colleges-to-be-closed-on-august-19-amid-heavy-rain-alert-article-152484704</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/heavy-rains-batter-mumbai-red-alert-issued-schools-and-colleges-closed-on-august-19-in-thane-and-palghar-998357</t>
+          <t>https://tennews.in/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.india.com/news/india/mumbai-rains-are-private-and-public-offices-shut-today-bmc-work-from-home-schools-colleges-devendra-fadnavis-markets-8019561/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107162/third-mumbai-will-open-a-new-chapter-of-economic-development-maha-cm</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://timesofindia.indiatimes.com/city/lucknow/poll-panel-needs-to-undergo-radical-changes-akhilesh/articleshow/123351446.cms</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%A8%E0%A4%A1-%E0%A4%8F%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B2-%E0%A4%AB-%E0%A4%AF%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1KJ7hd</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/mumbai-rain-live-updates-18-august-imd-red-alert-in-mumbai-weather-waterlogging-traffic-jam-local-train-train-latest-updates-in-marathi-933169</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/three-booked-for-assault-in-sec-49/articleshow/123350735.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/harish-ktr-slam-cong-govt-for-neglecting-farmers-scrapping-pharma-city/articleshow/123350210.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/goa/singapore-resident-arrested-for-cheating-siolim-woman-of-rs-1cr/articleshow/123350891.cms</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
+          <t>https://timesofindia.indiatimes.com/city/allahabad/79th-i-day-celebrated-with-patriotic-fervour/articleshow/123350254.cms</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/fines-of-around-rs-2500-crore-on-vehicles-in-the-state-government-to-introduce-a-lump-sum-repayment-scheme/</t>
+          <t>https://timesofindia.indiatimes.com/city/ludhiana/heavy-lifts-to-heavy-locks-sports-authority-of-indias-weightlifting-and-athletics-hub-in-ludhiana-weighed-down-by-neglect-/articleshow/123351362.cms</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/7-year-old-girl-found-dead-on-satna-street/articleshow/123351201.cms</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/over-2-crore-people-in-telangana-availed-esanjeevani-aid-since-2018/articleshow/123350599.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://timesofindia.indiatimes.com/city/goa/ngt-tells-green-authority-to-consider-concerns-over-proposed-xelvona-jetty/articleshow/123350970.cms</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
+          <t>https://www.eaajkaanand.com/Encyc/2025/8/18/vote.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://www.etvbharat.com/mr/!state/anna-hazare-outburst-on-flex-boards-in-pune-maharashtra-news-mhs25081801191</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
+          <t>https://www.etvbharat.com/mr/!state/i-got-offer-to-remove-10000-names-from-voter-list-before-assembly-elections-bachchu-kadu-claim-maharashtra-news-mhs25081703006</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/modi-govt-selling-dreams-of-2047-ignoring-present-rahul-gandhi-slams-centre-after-maharashtras-thane-train-tragedy/ar-AA1Gm3WY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://hindi.theprint.in/india/fadnavis-met-governor-radhakrishnan-presented-him-a-book-of-letters-of-shivaji-maharaj/856681/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-quantum-computing-initiative-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/those-who-speak-of-maharashtra--asmita--should-support-radhakrishnan-for-vp-post--fadnavis/2832772</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
+          <t>https://mahasamvad.in/176121/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
+          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/jaipur/jaipur-abu-dhabi-flight-cancelled/articleshow/123350813.cms</t>
+          <t>https://mahasamvad.in/176009/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
+          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/concrete-from-bengalurus-ejipura-flyover-slab-falls-on-autorickshaw-injures-driver/articleshow/123350812.cms</t>
+          <t>https://mahasamvad.in/176143/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/holiday-declared-for-schools-and-colleges-in-raigad-district-on-tuesday-due-to-heavy-rains-water-logging-on-mumbai-goa-highway-maharashtra-news-mhs25081806637</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/raisoni-college-of-business-management-hosts-nptel-awareness-workshop/articleshow/123351088.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/nashik-cops-start-e-meeting-with-police-commissioner-facility/articleshow/123351427.cms</t>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/heavy-rains-in-nanded-rescue-operations-on-as-5-go-missing-225-trapped-in-floodwaters-20250818T093308478Z?lang=en</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-63-crore-people-have-spinal-injuries-how-will-cervical-and-sciatica-be-cured-2025-08-18-1156639</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/maharashtra-news/supreme-court-dismisses-plea-seeking-cancellation-of/cid17260970.htm</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/amp/</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/anna-hazare-outburst-on-flex-boards-in-pune-maharashtra-news-mhs25081801191</t>
+          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/no-permission-for-worship-plenty-of-space-for-namaz-cpims-different-rules-for-hindus-and-muslims-in-kerala-the.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/i-got-offer-to-remove-10000-names-from-voter-list-before-assembly-elections-bachchu-kadu-claim-maharashtra-news-mhs25081703006</t>
+          <t>https://www.etvbharat.com/mr/!bharat/krishna-janmashtami-2025-celebrations-procession-turn-tragic-in-hyderabad-five-devotees-electrocuted-to-death-after-chariot-comes-in-contact-electric-wire-maharashtra-news-mhs25081800993</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/india/mumbai-rain-havoc-to-continue-for-next-4-days/story</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://hindi.moneycontrol.com/india/heavy-rains-in-maharashtra-nanded-leave-over-200-stranded-in-flood-waters-five-people-missing-article-2104052.html</t>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-maharashtra-in-developing-quantum-computing-initiative/</t>
+          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maratha-general-raghuji-bhonsle's-sword-brought-to-mumbai/2833930</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/mumbai-rains-live-updates-mumbai-red-alert-issue-streets-inundated-and-hits-local-trains-lb-89483</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-heavy-rainfall-batter-city-as-vihar-lake-overflows-23590062</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176121/</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/176009/</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/176143/</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!bharat/krishna-janmashtami-2025-celebrations-procession-turn-tragic-in-hyderabad-five-devotees-electrocuted-to-death-after-chariot-comes-in-contact-electric-wire-maharashtra-news-mhs25081800993</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/mumbai-rains-live-updates-mumbai-red-alert-issue-streets-inundated-and-hits-local-trains-lb-89483</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/holiday-for-schools-and-colleges-in-ratnagiri-due-to-heavy-rain-ratnagiri-district-administration-decision-orange-alert-weather-forecast-maharashtra-news-mhs25081806850</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
           <t>https://panasiabiz.com/111088/cm-siddaramaiah-and-dycm-dk-shivakumar-inaugurate-%E2%82%B980-crore-hebbal-flyover-to-ease-bengaluru-traffic/</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/18/bom51-mh-cm-third-mumbai.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/weather/mumbai-on-red-alert-for-second-consecutive-day-heavy-rain-disrupts-travel-shuts-educational-institutions/articleshow/123375296.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/over-%E2%82%B96-52-crore-medical-aid-distributed-to-5000-beneficiaries-in-pune-district/</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A270"/>
+  <dimension ref="A1:A271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,301 +473,301 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mns-morcha-raj-thackerays-party-workers-detained-cm-fadnavis-says-such-experiments-won-t-work-here/ar-AA1Iaint</t>
+          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/ar-AA1KJ362</t>
+          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
+          <t>https://www.ptinews.com/story/business/-Third-Mumbai--to-boost-MMR-development--says-Fadnavis;-invites-pvt-sector-to-join-in-its-creation=/2834267</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/-Third-Mumbai--to-boost-MMR-development--says-Fadnavis;-invites-pvt-sector-to-join-in-its-creation=/2834267</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.prameyanews.com/ndas-vice-presidential-candidate-cp-radhakrishnan-to-travel-to-delhi-today</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://www.prameyanews.com/ndas-vice-presidential-candidate-cp-radhakrishnan-to-travel-to-delhi-today</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination/</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
+          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3545060-ndas-vp-candidate-cp-radhakrishnan-heads-to-delhi-amid-criticism</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/third-mumbai-to-boost-metropolitan-region-development-fadnavis-9674858</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-7063782.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
+          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/fadnavis-said-third-mumbai-will-lead-to-development-of-mmr/856867/</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/mumbai-received-177-mm-of-rain-in-6-8-hours-fadnavis/856688/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
@@ -781,798 +781,798 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
+          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/raje-raghuji-bhosale-sword-history-maharashtra-cm-fadnavis-grand-welcome-3441860.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
+          <t>https://thenewsmill.com/2025/08/deliver-justice-in-spirit-of-shahu-maharajs-vision-cji-gavai-inaugurates-bombay-high-court-circuit-bench-at-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/deliver-justice-in-spirit-of-shahu-maharajs-vision-cji-gavai-inaugurates-bombay-high-court-circuit-bench-at-kolhapur/</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-asserts-that-the-work-of-connecting-the-new-generation-with-history-is-underway-mumbai-print-news-amy-95-5313830/</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
+          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28165/</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/mumbai/mumbai-heavy-rain-waterlogging-local-delays-school-shutdown/photoshow-at2tgam</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-of-india-election-2025-why-modi-of-tamil-nadu-cp-radhakrishnan-is-ndas-vice-presidential-pick-know-his-profile-from-tiruppur-roots-to-ndas-vice-presidential-candidate-maharashtra-news-mhs25081800641</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/rain-big-news-mukhed-cloudburst-nanded-rain-news-calling-out-the-army-maharashtra-rain-alert-9107388</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/tmc-identified-227-illegal-buildings-strict-action-will-be-taken-to-make-thane-a-well-planed-city-tmc-assures-bombay-high-court-maharashtra-news-mhs25081802854</t>
+          <t>https://www.patrika.com/en/state-news/patna-metro-testing-begins-this-week-passenger-services-targeted-for-september-19873149</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
+          <t>https://www.etvbharat.com/mr/!spiritual/shravan-2025-fourth-shravan-somwar-horoscope-rashi-bhavishya-for-18-august-2025-in-marathi-mhs25081704098</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!spiritual/shravan-2025-fourth-shravan-somwar-horoscope-rashi-bhavishya-for-18-august-2025-in-marathi-mhs25081704098</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-weather-red-alert-for-kolhapur-district-today-all-automatic-gates-of-radhanagari-dam-opened-for-the-first-time-in-the-season-1377818</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-weather-red-alert-for-kolhapur-district-today-all-automatic-gates-of-radhanagari-dam-opened-for-the-first-time-in-the-season-1377818</t>
+          <t>https://marathi.abplive.com/news/pune-imd-on-heavy-rainfall-know-why-is-mumbai-suddenly-getting-so-much-rain-wather-update-imd-alert-for-mumbai-thane-for-next-48-hours-1377940</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/mumbai-mumbai-heavy-rain-update-massive-traffic-jam-mumbai-local-train-5-to-10-minutes-delayed-latest-updates-marathi-news-1377845</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
+          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://ommcomnews.com/india-news/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/articleshow/123354325.cms</t>
+          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/articleshow/123354325.cms</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://thenewsmill.com/2025/08/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34070/</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maharashtra-politics-rain-flood-updates-election-commission-press-conference-thalak-batmya-sunday-17th-august-2025-1471433.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://hindi.oneindia.com/news/india/maharashtra-governor-cp-radhakrishnan-nda-vice-presidential-candidate-leaders-congratulate-1364687.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/fake-shalarth-id-recruitment-scam-nagpur-two-clerk-brothers-arrested-in-cheating-case-total-number-of-accused-arrested-in-reached-to-20-maharashtra-news-mhs25081800757</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-12-day-himachal-pradesh-assembly-session-opens-opposition-seeks-adjournment-on-disaster-7064955.html</t>
+          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-rajya-sabha-election-opposition-parties-may-support-nda-candidate-cp-radhakrishnan-24017212.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
+          <t>https://www.etvbharat.com/mr/!state/fake-shalarth-id-recruitment-scam-nagpur-two-clerk-brothers-arrested-in-cheating-case-total-number-of-accused-arrested-in-reached-to-20-maharashtra-news-mhs25081800757</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
+          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
+          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/eci-press-confrence-journalist-question/</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/shorts/mumbai/best-credit-society-election-thackeray-brothers-unite-vs-bjp-results-tomorrow/</t>
+          <t>https://www.indiatoday.in/india/law-news/story/chief-justice-of-india-inaugurates-new-bombay-high-court-circuit-bench-in-kolhapur-2772552-2025-08-18</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
+          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
+          <t>https://www.lokmat.com/shorts/mumbai/best-credit-society-election-thackeray-brothers-unite-vs-bjp-results-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/national-news/maharashtra-weather-red-alert-mumbai-pune-7-districts-281414/</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
+          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
+          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://thefocusindia.com/maharashtra-news/girish-mahajan-chagan-bhujbal-clash-nashik-guardian-minister-281360/amp/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
@@ -1586,329 +1586,329 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43138/mumbai--a-major-accident-was-averted-in-chira-bazaar--stairs-of-a-two-storey-old-building-suddenly-collapsed</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43136/mumbai--enthusiasm-of-ganesh-devotees-is-at-its-peak--mumbai-s-rain-has-no-effect</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-receives-over-200-mm-rainfall-in-24-hours-202405</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43134/mumbai--heavy-rains-till-august-20--meteorological-department-issued-orange-alert</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-rain-imd-red-alert-bmc-issues-holiday-amid-waterlogging-202287</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43150/bangladeshi-woman-accused-who-escaped-from-jj-hospital-arrested-by-mumbai-police</t>
+          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
+          <t>https://www.rokthoklekhani.com/article/43136/mumbai--enthusiasm-of-ganesh-devotees-is-at-its-peak--mumbai-s-rain-has-no-effect</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune20250819111423</t>
+          <t>https://www.rokthoklekhani.com/article/43138/mumbai--a-major-accident-was-averted-in-chira-bazaar--stairs-of-a-two-storey-old-building-suddenly-collapsed</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://www.rokthoklekhani.com/article/43134/mumbai--heavy-rains-till-august-20--meteorological-department-issued-orange-alert</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://www.rokthoklekhani.com/article/43150/bangladeshi-woman-accused-who-escaped-from-jj-hospital-arrested-by-mumbai-police</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://aninews.in/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune20250819111423</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
+          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43152/new-delhanew-delhi--supreme-court-strict-on-the-issue-of-disabled-military-cadets--center-should-consider-rehabilitation-plan-i-consider-supreme-court-strict-rehabilitation-scheme-on-the</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/karnataka/did-mahesh-shetty-timarodi-really-say-cm-siddaramaiah-killed-24-people-heres-the-truth</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/ports-and-shipping/maharashtra--singapore-review-progress-of-mega-container-port-project/77682</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://timesproperty.com/news/post/mumbai-to-get-238-new-ac-local-trains-in-three-yrs-blid10400</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%A8%E0%A4%A1-%E0%A4%8F%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B2-%E0%A4%AB-%E0%A4%AF%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1KJ7hd</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ahmedabad/indias-7th-rank-in-us-scheme-for-children-sparks-fraud-concerns/articleshow/123350715.cms</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
+          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maratha-general-raghuji-bhonsle-sword-brought-to-mumbai-maharashtra-government-acquired-in-auction-2025-08-18</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%A8%E0%A4%A1-%E0%A4%8F%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B2-%E0%A4%AB-%E0%A4%AF%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1KJ7hd</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/indias-7th-rank-in-us-scheme-for-children-sparks-fraud-concerns/articleshow/123350715.cms</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A4-%E0%A4%93%E0%A4%B2%E0%A4%BE-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95%E0%A4%BE%E0%A4%B3-%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80/114152/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/amp/?utm=relatedarticles</t>
+          <t>https://tennews.in/mumbai-set-to-honour-today-the-homecoming-of-raghuji-bhonsales-legendary-sword/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.etnownews.com/news/mumbai-schools-colleges-to-be-closed-on-august-19-amid-heavy-rain-alert-article-152484704</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://tennews.in/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
+          <t>https://www.etnownews.com/news/mumbai-schools-colleges-to-be-closed-on-august-19-amid-heavy-rain-alert-article-152484704</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Rain-fury--5-missing--200-stranded-in-Nanded;-local-trains--flights-hit-in-Mumbai/2832995</t>
+          <t>https://tennews.in/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/lucknow/poll-panel-needs-to-undergo-radical-changes-akhilesh/articleshow/123351446.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
         </is>
       </c>
     </row>
@@ -1922,329 +1922,329 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/three-booked-for-assault-in-sec-49/articleshow/123350735.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/harish-ktr-slam-cong-govt-for-neglecting-farmers-scrapping-pharma-city/articleshow/123350210.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/lucknow/poll-panel-needs-to-undergo-radical-changes-akhilesh/articleshow/123351446.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/goa/singapore-resident-arrested-for-cheating-siolim-woman-of-rs-1cr/articleshow/123350891.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/water-cut-in-parts-of-mulund-on-thursday/articleshow/123350558.cms</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/allahabad/79th-i-day-celebrated-with-patriotic-fervour/articleshow/123350254.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ludhiana/heavy-lifts-to-heavy-locks-sports-authority-of-indias-weightlifting-and-athletics-hub-in-ludhiana-weighed-down-by-neglect-/articleshow/123351362.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/lucknow/ashok-elected-prez-of-iit-alumni-body/articleshow/123351412.cms</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/7-year-old-girl-found-dead-on-satna-street/articleshow/123351201.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/goa/singapore-resident-arrested-for-cheating-siolim-woman-of-rs-1cr/articleshow/123350891.cms</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/over-2-crore-people-in-telangana-availed-esanjeevani-aid-since-2018/articleshow/123350599.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/natgrid-aids-cops-in-catching-four-minors-wanted-for-murder/articleshow/123350104.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/goa/ngt-tells-green-authority-to-consider-concerns-over-proposed-xelvona-jetty/articleshow/123350970.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/man-left-stranded-in-uganda-by-employer-wins-rs-3-lakh-dues-back/articleshow/123350843.cms</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/lucknow/1-48-crore-students-across-up-schools-celebrate-independence-day-event/articleshow/123351455.cms</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.eaajkaanand.com/Encyc/2025/8/18/vote.html</t>
+          <t>https://timesofindia.indiatimes.com/city/vijayawada/lokesh-in-delhi-to-secure-approvals-investments-for-ap-projects/articleshow/123349810.cms</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mumbai-rains-7-people-died-due-to-rain-water-flooded-on-roads-schools-and-colleges-closed-flights-also-affected/</t>
+          <t>https://timesofindia.indiatimes.com/city/goa/ngt-tells-green-authority-to-consider-concerns-over-proposed-xelvona-jetty/articleshow/123350970.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/anna-hazare-outburst-on-flex-boards-in-pune-maharashtra-news-mhs25081801191</t>
+          <t>https://timesofindia.indiatimes.com/city/varanasi/cargo-vessel-flags-new-chapter-in-varanasiwb-water-transport/articleshow/123351314.cms</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/i-got-offer-to-remove-10000-names-from-voter-list-before-assembly-elections-bachchu-kadu-claim-maharashtra-news-mhs25081703006</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/karnataka-forest-department-allows-ore-explorationin-chitradurga-reserve-forest/articleshow/123350404.cms</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
+          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/fadnavis-met-governor-radhakrishnan-presented-him-a-book-of-letters-of-shivaji-maharaj/856681/</t>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-18-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-18-1156628</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://www.eaajkaanand.com/Encyc/2025/8/18/vote.html</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-quantum-computing-initiative-in-maharashtra/</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/anna-hazare-outburst-on-flex-boards-in-pune-maharashtra-news-mhs25081801191</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://www.etvbharat.com/mr/!state/i-got-offer-to-remove-10000-names-from-voter-list-before-assembly-elections-bachchu-kadu-claim-maharashtra-news-mhs25081703006</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176121/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-quantum-computing-initiative-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB/</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176009/</t>
+          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
+          <t>https://mahasamvad.in/176121/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/in-mumbai-people-have-been-told-to-step-out-only-if-it-is-needed-says-cm-devendra-fadnavis/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176143/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/holiday-declared-for-schools-and-colleges-in-raigad-district-on-tuesday-due-to-heavy-rains-water-logging-on-mumbai-goa-highway-maharashtra-news-mhs25081806637</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
+          <t>https://mahasamvad.in/176009/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
+          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/19/bom3-mh-third-mumbai-cm.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/the-perks-and-costs-of-ladki-bahin-101755575344332.html</t>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
+          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/krishna-janmashtami-2025-celebrations-procession-turn-tragic-in-hyderabad-five-devotees-electrocuted-to-death-after-chariot-comes-in-contact-electric-wire-maharashtra-news-mhs25081800993</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
+          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
+          <t>https://www.etvbharat.com/mr/!bharat/krishna-janmashtami-2025-celebrations-procession-turn-tragic-in-hyderabad-five-devotees-electrocuted-to-death-after-chariot-comes-in-contact-electric-wire-maharashtra-news-mhs25081800993</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
@@ -2272,49 +2272,56 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/mumbai-rains-live-updates-mumbai-red-alert-issue-streets-inundated-and-hits-local-trains-lb-89483</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/mumbai-rains-live-updates-mumbai-red-alert-issue-streets-inundated-and-hits-local-trains-lb-89483</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
+          <t>https://civicmirror.in/nation/telecom-collapses-across-the-country-airtel-jio-vi-network-down/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://panasiabiz.com/111088/cm-siddaramaiah-and-dycm-dk-shivakumar-inaugurate-%E2%82%B980-crore-hebbal-flyover-to-ease-bengaluru-traffic/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/business/2025/08/18/bom51-mh-cm-third-mumbai.html</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A271"/>
+  <dimension ref="A1:A246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,1890 +438,1715 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/aurangzeb-tomb-row-vhp-s-statewide-protests-backed-by-rss-cm-devendra-fadnavis-calls-for-lawful-dismantling/ar-AA1Bfmct?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/107166/maha-cm-asks-agencies-to-be-on-alert-mode-after-heavy-rainfall-and-flash-floods</t>
+          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/industry/positive-about-bringing-a-law-to-protect-advocates-maharashtra-cm-fadnavis/123378199</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
+          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/real-estate/cannot-achieve-affordable-housing-with-business-as-usual-approach-maharashtra-cm-fadnavis-tells-realtors-13462328.html</t>
+          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-nominee-radhakrishnan-departs-for-delhi-maha-yuti-leaders-extend-support-3685392</t>
+          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
+          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/those-who-speak-of-maharashtra-asmita-should-support-radhakrishnan-for-vp-post-fadnavis/2832772</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/business/fadnavis-home</t>
+          <t>https://money.rediff.com/news/market/third-mumbai-fadnavis-boosts-mmr-development/32201020250818</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nda-vice-president-nominee-cp-radhakrishnan-expresses-gratitude-to-pm-modi-amit-shah-devendra-fadnavis-after-vp-nomination/ar-AA1KGvyO</t>
+          <t>https://www.ptinews.com/story/business/-Third-Mumbai--to-boost-MMR-development--says-Fadnavis;-invites-pvt-sector-to-join-in-its-creation=/2834267</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/public-safety-and-emergencies/health-and-safety-alerts/mumbai-aqi-dia-mirza-expresses-her-concern-with-cm-devendra-fadnavis-to-act-on-city-s-air-pollution/ar-AA1xZ0xs?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/red-alert-for-mumbai-mumbai-got-177mm-rain-in-just-6-8-hour-period-says-cm-fadnavis-more-to-come-amid-high-tides-23589990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-and-bjp-the-saga-continues-101755457833159.html</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/-Third-Mumbai--to-boost-MMR-development--says-Fadnavis;-invites-pvt-sector-to-join-in-its-creation=/2834267</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination20250818033912/</t>
+          <t>https://www.ptinews.com/story/national/Fadnavis-meets-Guv-Radhakrishnan--presents-him-book-of-Shivaji-Maharaj-s-letters/2832581</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra,-200-villagers-stranded/2834213</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/find-suitable-land-i-will-set-up-it-park-through-midc-in-solapur-fadnavis/articleshow/123351422.cms</t>
+          <t>https://www.ptinews.com/story/national/Rain-fury-leaves-7-dead-in-Maharashtra--200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-meets-guv-radhakrishnan-presents-him-book-of-shivaji-maharaj-s-letters/2832582</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination20250818081153</t>
+          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/city/third-mumbai-takes-shape-as-cm-fadnavis-unveils-mega-mmr-expansion-plan-article-13465350.html</t>
+          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom25-mh-governor-ld-fadnavis.html</t>
+          <t>https://www.prameyanews.com/ndas-vice-presidential-candidate-cp-radhakrishnan-to-travel-to-delhi-today</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/19/raghuji-bhonsles-sword-brought-to-india.html</t>
+          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/fadnavis-dedicates-goldman-sachs-new-mumbai-office-unveils-vision-for-third-mumbai-567845</t>
+          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom17-mh-rains-nanded.html</t>
+          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom50-mh-2nd-ldall-rains.html</t>
+          <t>https://english.newsnationtv.com/national/general-news/observe-precaution-maharashtra-cm-warns-about-severe-weather-conditions-in-state20250819025510</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.prameyanews.com/ndas-vice-presidential-candidate-cp-radhakrishnan-to-travel-to-delhi-today</t>
+          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pune-can-get-underground-road-network-to-beat-traffic-woes-1755566759073</t>
+          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.transcontinentaltimes.com/netherlands-yogasana-sports-nysa/</t>
+          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-7063782.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/vice-president-elections-2025-maharashtra-cm-devendra-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination-see-pics-7063864.html</t>
+          <t>https://thenewsmill.com/2025/08/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/india/news/devendra-fadnavis-says-third-mumbai-will-open-a-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/18/mumbai-c-p-radhakrishnan-departs-for-delhi-gallery/</t>
+          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3545060-ndas-vp-candidate-cp-radhakrishnan-heads-to-delhi-amid-criticism</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination/</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-patients-receive-over-rs-6-5-crore-in-medical-aid-under-chief-minister-devendra-fadnavis-initiative/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis-7064653.html</t>
+          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-7063782.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://panasiabiz.com/111091/cm-devendra-fadnavis-presents-rare-shivaji-maharaj-letters-to-governor-cp-radhakrishnan/</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/mumbai-received-177-mm-of-rain-in-just-6-8-hours-fadnavis-gave-instructions-to-take-precautions-11195</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/vice-president-election-2025-maharashtra-cm-devendra-fadnavis-request-uddhav-thackeray-and-sharad-pawar-2997542</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/cji-br-gavai-take-devendra-fadnavis-eknath-shinde-name-bombay-high-court-new-circuit-bench-in-kolhapur-9520456.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-maharashtra-rains-cm-and-managment-on-alert-hindi/</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-heavy-rainfall-flood-alert-red-and-orange-alerts-issued-relief-operations-mumbai-rain-ann-2997660</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A5-%E0%A4%AF%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B8/ar-AA1Jjy9z</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/chief-minister-devendra-fadnavis-congratulated-governor-radhakrishnan-on-his-candidature-for-the-post-of-vice-president-11180</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0-%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%A4-200-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AB%E0%A4%82%E0%A4%B8%E0%A5%87/ar-AA1KKl3K</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/heavy-rains-in-mumbai-schools-colleges-closed-7-deaths-in-maharashtra-5-missing-nanded-cm-fadnavis-emergency-meeting/articleshow/123366462.cms</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/mumbai-rain-news-rain-wreaked-havoc-in-mumbai-devendra-fadnavis-statement-came-4259449.html</t>
+          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/weather-mumbai-rains-local-train-cloudburst-nanded-alert-in-15-16-districts-in-maharashtra-cm-devendra-fadnavis-said-damage-to-crops-2997472</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%AD-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95-%E0%A4%B9-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE%E0%A4%9C-%E0%A4%B0-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1IRFiN</t>
+          <t>https://www.ptinews.com/story/national/rain-fury-leaves-7-dead-in-maharashtra-200-villagers-stranded/2834213</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/vice-presidential-election-cm-devendra-fadnavis-said-cp-radhakrishnan-is-a-mumbai-voter-support-him-1365243.html</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-manik-rao-kokate-successor-minister-dattatray-bharane-called-agriculture-ministry-is-a-headache-know-all/articleshow/123357471.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cji-br-gavai-said-our-dream-has-been-fulfilled-over-bombay-high-court-new-circuit-bench-at-kolhapur-mention-cm-fadnavis-name-know-all/articleshow/123350750.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/abu-azmi-ne-cm-devendra-fadnavis-ko-likha-patra-badh-prabhavit-ilakon-mein-rahat-pahunchane-ki-mang-ki--20250818191027/</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vice-president-nomination-4218433</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/raghuji-bhosale-historic-sword-returned-from-london-grand-welcome-in-mumbai-553050</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-dy-cm-shinde-congratulate-governor-cp-radhakrishnan-on-ndas-vp-nomination-23589945</t>
+          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/heavy-rainfall-causes-7-deaths-crop-loss-in-maharashtra-as-alerts-continue/ar-AA1KK6Zt</t>
+          <t>https://marathi.oneindia.com/maharashtra/maharashtra-cm-fadnavis-loan-waiver-announcement-035127.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/deliver-justice-in-spirit-of-shahu-maharajs-vision-cji-gavai-inaugurates-bombay-high-court-circuit-bench-at-kolhapur/</t>
+          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-review-mumbai-rain-says-next-12-hours-important-for-mumbai-and-mmr-region-1460967.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-mumbai-maharashtra-rain-today-visit-disaster-management-department-bmc-marathi-news-1377962</t>
+          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rains-lashed-the-state-chief-minister-devendra-fadnavis-took-stock-instructed-all-agencies-to-be-alert.html</t>
+          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-appeals-to-maharashtra-mps-to-support-cp-radhakrishnan-for-vice-president/913103/</t>
+          <t>https://lokashanews.com/28165/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-rain-update-cm-devendra-fadnavis-hold-meeting-with-district-administration-1460734.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/cm-devendra-fadnavis-will-soon-announce-loan-waiver-farmers-mahayuti-ministers-sanjay-rathod-gave-information-yavatmal-1377983</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/ravi-dubey-and-sargun-mehta-are-making-headlines-with-their-new-home-maharashtra-news-mhs25081802265</t>
+          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-mumbai-exhibition-of-nagpur-raghuji-raje-bhosle-historical-sword-marathi-news-1378075</t>
+          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/administrator-citizens-should-not-stay-home-chief-minister/</t>
+          <t>https://mahasamvad.in/176127/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/chief-minister-will-soon-announce-farmer-loan-waiver-shindes-ministers-claim/</t>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/cm-fadnavis-likely-to-announce-farm-loan-waiver-soon/</t>
+          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/big-relief-for-farmers-in-maharashtra-chief-minister-fadnavis-will-soon-announce-loan-waiver-125081900014_1.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-setback-for-eknath-shinde-in-solapur-leaders-leave-support/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.thodkyaat.com/it-park-in-solapur-announced-by-cm-devendra-fadnavis-boost-to-jobs-and-development/</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-urges-mps-to-support-radhakrishnan-targets-uddhav-thackeray-and-sharad-pawar-035137.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/goldman-sachs-new-mumbai-office-is-a-new-chapter-for-third-mumbai-devendra-fadnavis-89597</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-rain-news-chief-minister-devendra-fadnavis-gave-information-about-the-rainfall-situation-in-mumbai-9107883</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/cm-devendra-fadnavis-review-maharashtra-flood-135703334.html</t>
+          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/third-mumbai-will-open-a-new-chapter-of-economic-development-says-cm-devendra-fadnavis-9110192</t>
+          <t>https://www.latestly.com/agency-news/world-news-indian-diaspora-floods-new-york-streets-for-independence-day-celebrations-7063935.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mumbai-rains-update-next-12-hours-are-important-for-mumbai-7-people-died-across-state-in-2-days-cm-fadnavis-appeals-to-citizens-9109288</t>
+          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176127/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rains-in-latur-district-cause-flooding-in-many-rivers-cm-devendra-fadnavis-took-a-review-lendi-river-flood-maharashtra-news-mhs25081802447</t>
+          <t>https://www.etvbharat.com/mr/!spiritual/shravan-2025-fourth-shravan-somwar-horoscope-rashi-bhavishya-for-18-august-2025-in-marathi-mhs25081704098</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/rohit-pawar-accuses-sanjay-shirsat-of-5000-crores-of-corruption-big-demand-to-devendra-fadnavis-maharashtra-politics-marathi-news-1377888</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cloudburst-rain-in-mukhed-nanded-district-five-people-missing-chief-minister-devendra-fadnavis-gave-information/913157/</t>
+          <t>https://ilovenagar.com/mumbai-rain-alert-schools-declare-holiday-today/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/crops-affected-on-four-lakh-hectares-of-land-in-the-state-orders-to-conduct-crop-surveys/</t>
+          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/tanaji-sawant-brother-shivajirao-sawant-resign-eknath-shinde-sena-join-bjp-after-meet-fadnavis/913179/</t>
+          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-picks-cp-radhakrishnan-for-vice-president-post-cm-devendra-fadnavis-ask-uddhav-thackeray-for-support/articleshow/123362737.cms</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/great-news-for-youth-it-park-will-be-set-up-at-this-place-chief-ministers-announcement/08181712</t>
+          <t>https://mahasamvad.in/176229/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/unveiling-the-historic-sword-of-sardar-raghuji-raje-bhosale-in-mumbai-presence-of-chief-minister-devendra-fadnavis-know-history-of-raghuji-raje-sword-maharashtra-news-mhs25081900619</t>
+          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/vice-president-of-india-election-2025-why-modi-of-tamil-nadu-cp-radhakrishnan-is-ndas-vice-presidential-pick-know-his-profile-from-tiruppur-roots-to-ndas-vice-presidential-candidate-maharashtra-news-mhs25081800641</t>
+          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/heavy-rains-wreak-havoc-in-nanded-relief-work-intensified-under-the-supervision-of-chief-minister-fadnavis-125081800046_1.html</t>
+          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-hands-over-keys-to-new-police-housing/articleshow/123350974.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/state-news/patna-metro-testing-begins-this-week-passenger-services-targeted-for-september-19873149</t>
+          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/news/maharashtra-cm-devendra-fadnavis-says-third-mumbai-being-developed-in-raigad-district-will-open-new-chapter-of-economic-development-7064927.html</t>
+          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/15-maharashtra-districts-under-red-and-orange-alert-as-heavy-rains-continue-mumbai-records-177-mm-in-hours/</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/raghuji-bhosale-sword-to-arrive-in-mumbai-today-18-august-inauguration-ceremony-by-cm-devendra-fadnavis/articleshow/123353790.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-weather-red-alert-for-kolhapur-district-today-all-automatic-gates-of-radhanagari-dam-opened-for-the-first-time-in-the-season-1377818</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!spiritual/shravan-2025-fourth-shravan-somwar-horoscope-rashi-bhavishya-for-18-august-2025-in-marathi-mhs25081704098</t>
+          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/mumbai-rains-govt-declares-holiday-for-all-government-and-private-offices-amid-heavy-rainfall.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/super-100-today-india-alliance-can-announce-its-candidate-for-vice-presidential-election-2025-08-18-1156635</t>
+          <t>https://thenewsmill.com/2025/08/deliver-justice-in-spirit-of-shahu-maharajs-vision-cji-gavai-inaugurates-bombay-high-court-circuit-bench-at-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/states/maharashtra-mumbai-heavy-rainfall-waterlogging-imd-red-alert-local-train-delayed-photos-maharashtra-news-2997487</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%BE-508/</t>
+          <t>https://www.ibc24.in/maharashtra/five-people-missing-several-stranded-due-to-heavy-rains-in-nanded-cm-fadnavis-3212983.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176229/</t>
+          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/modi-aur-musalman-sir-2025-08-18-1156613</t>
+          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/news-bulletin/muqabla-rahul-gandhi-or-the-election-commission-who-wins-the-vote-theft-battle-2025-08-19-1156831</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/cm-devendra-fadnavis-inauguration-of-new-police-building-kolhapur-marathi-news/</t>
+          <t>https://www.aninews.in/news/national/general-news/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources20250818101908</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-18-political-news-in-marathi-933194</t>
+          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai-rain-news-update-red-alert-for-mumbai-thane-for-next-48-hours-imd-forecast-holiday-declared-for-schools-cm-devendra-fadnavis-reviews-flood-hit-areas-1377881</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/ahilyanagar-fire-news-massive-fire-breaks-out-at-furniture-shop-in-nevasa-several-dead-including-furniture-shop-owner-wife-two-his-kids-maharashtra-news-mhs25081800839</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-rains-updates-bmc-declared-holiday-today-for-afternoon-shift-for-all-schools-and-colleges-in-mumbai-amid-imd-red-alert-for-thane-raigad-navi-mumbai-maharashtra-news-mhs25081802005</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-weather-red-alert-for-kolhapur-district-today-all-automatic-gates-of-radhanagari-dam-opened-for-the-first-time-in-the-season-1377818</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune-imd-on-heavy-rainfall-know-why-is-mumbai-suddenly-getting-so-much-rain-wather-update-imd-alert-for-mumbai-thane-for-next-48-hours-1377940</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/articleshow/123354325.cms</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/mumbai-mumbai-heavy-rain-update-massive-traffic-jam-mumbai-local-train-5-to-10-minutes-delayed-latest-updates-marathi-news-1377845</t>
+          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/mumbai-gets-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert/amp_articleshow/123365291.cms</t>
+          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-rains-five-missing-several-stranded-as-heavy-rains-lash-nanded-rescue-operations-underway-2025-08-18-1004046</t>
+          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/upcoming-third-mumbai-will-spur-economic-growth-says-maharashtra-chief-minister/articleshow/123368667.cms</t>
+          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/video/maharashtra-crop-loss-4-lakh-hectares-cm-orders-panchanama</t>
+          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/heavy-rainfall-cm-devendra-fadnavis-instructs-to-remain-vigilant-in-places-where-red-alert-has-been-declared/</t>
+          <t>https://www.ndtv.com/travel/ladakh-government-plans-to-develop-siachen-and-galwan-as-major-tourist-hubs-9108322</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
+          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president/</t>
+          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ncp-must-get-nashik-guardian-minister-post-bhujbal-101755457413078.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Those-who-speak-of-Maharashtra--asmita--should-support-Radhakrishnan-for-VP-post--Fadnavis/2832772</t>
+          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-nda-vp-pick-in-delhi-to-meet-bjp-top-brass-opposition-yet-to-finalise-their-candidate-india-bloc-continues-attacking-ec-chief-over-sir-3685866</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/my-karyakarta-is-with-me-hitendra-thakur-shrugs-off-defections-ahead-of-civic-elections/articleshow/123354325.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-17-august-2025-earthquake-sikkim-rain-weather-mumbai-delhi-pm-modi-trump-putin-russia-israel-gaza-ukraine/liveblog/123340718.cms</t>
+          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/ndas-vice-president-nominee-cp-radhakrishnan-to-reach-delhi-today-sources/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-blow-to-eknath-shinde-big-leader-of-shiv-sena-shinde-group-will-join-bjp/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/solapur-shivaji-sawant-leaves-shiv-sena-and-bjp-entry-confirmed-devendra-fadnavis-bjp-attack-on-eknath-shinde-shiv-sena-in-solapur-1377928</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://policenama.com/congress-mohan-joshi-pune-dont-wait-for-bjps-event-open-the-flyover-former-mla-mohan-joshis-letter-to-the-municipal-commissioner/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/gangs-of-traitors-shindes-minister-targeted-by-rohit-pawar-97619/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/clean-image-and-cordial-relations-with-netas-across-political-parties-paves-maharashtra-governor-cp-radhakrishnans-path-to-vice-presidents-office/articleshow/123350030.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/fake-shalarth-id-recruitment-scam-nagpur-two-clerk-brothers-arrested-in-cheating-case-total-number-of-accused-arrested-in-reached-to-20-maharashtra-news-mhs25081800757</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/solapur/solapur-politics-over-shiv-sena-leader-shivaji-sawant-may-join-bjp/articleshow/123369493.cms</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-to-get-third-ring-road-with-land-acquisition-from-36-villages-vsb99</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/kurukshetra/coffee-par-kurukshetra-indi-2025-08-19-1156832</t>
+          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/maharashtra-governor-cp-radhakrishnan-nda-vice-presidential-candidate-leaders-congratulate-1364687.html</t>
+          <t>https://www.republicbharat.com/india/congress-angry-cp-radhakrishnan-nda-vice-presidential-candidate-opened-cards-on-indi-alliance-meeting</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/no-meeting-even-after-month-of-announcement-regarding-ethic-committee-mlas/articleshow/123356125.cms</t>
+          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/salim-ghaniwala-joins-bjp-big-blow-to-congress-in-daryapur-amravati-9106782</t>
+          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-18-august-2025-monday-latest-marathi-news-update-maharashtra-politics-marathi-news-1378004</t>
+          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/08/Ashish-Shelar-reviews-emergency-management.html</t>
+          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
+          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-infrastructure/nagpur-smart-city-projects-face-delay-7-projects-pending-completion/123360909</t>
+          <t>https://www.bignewsnetwork.com/news/278518718/destroying-constitutional-institutions-nishikant-dubey-slams-rahul-gandhi-as-sc-dismisses-plea-challenging-2024-maharashtra-polls</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/raghuji-bhonsles-sword-to-reach-mum-today-mudhoji-raje-to-attend-ceremony/articleshow/123351204.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/now-bachchu-kadu-claims-offer-to-delete-thousands-of-names-from-voters-list/articleshow/123351305.cms</t>
+          <t>https://www.saamana.com/file-affidavit-in-seven-days-or-apologise-eci-ultimatum-on-rahul-gandhi-vote-theft-allegations/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/owners-threaten-to-shut-bars-from-aug-25-over-high-taxes-on-liquor/articleshow/123351216.cms</t>
+          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/historic-sword-of-shrimant-raghuji-bhosle-back-in-mumbai.html</t>
+          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/nagpur-hit-and-run-accident-news-update-case-solved-with-the-help-of-ai-technology-first-experiment-in-the-state-driver-arrested-from-uttar-pradesh-1377914</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/seize-the-assets-of-directors-involved-in-the-school-id-scam.html</t>
+          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/fake-shalarth-id-recruitment-scam-nagpur-two-clerk-brothers-arrested-in-cheating-case-total-number-of-accused-arrested-in-reached-to-20-maharashtra-news-mhs25081800757</t>
+          <t>https://www.thodkyaat.com/big-setback-for-eknath-shinde-faction-as-senior-leader-shivaji-sawant-joins-bjp-ahead-of-local-body-polls/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/18-august-maharashtra-heavy-rain-update-monsoon-2025-mumbai-red-alert-1460576.html</t>
+          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/maharashtra-deputy-cm-ajit-pawar-visits-mantralaya-disaster-control-room-to-review-heavy-rain-situation-2732241.html</t>
+          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/sports/asia-cup-2025-2025-08-18-1156799</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/opposition-parties-likely-to-bring-impeachment-motion-notice-against-cec-over-vote-theft-maharashtra-news-mhs25081803712</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-receives-over-200-mm-rainfall-in-24-hours-202405</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://madrascourier.com/opinion/election-commission-of-india-the-politics-of-jugaad/</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-rain-imd-red-alert-bmc-issues-holiday-amid-waterlogging-202287</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/political-opinions-or-supreme-court-quashes-plea-challenging-validity-of-maharashtra-assembly-polls-3686244</t>
+          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/shiv-sena-ncp-support-maha-governors-nomination-for-vice-president</t>
+          <t>https://www.rokthoklekhani.com/article/43136/mumbai--enthusiasm-of-ganesh-devotees-is-at-its-peak--mumbai-s-rain-has-no-effect</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/law-news/story/chief-justice-of-india-inaugurates-new-bombay-high-court-circuit-bench-in-kolhapur-2772552-2025-08-18</t>
+          <t>https://www.rokthoklekhani.com/article/43144/latur--tehsildar-suspended-for-singing-bollywood-song-at-farewell-function-organized-after-transfer</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/rajnath-reaches-out-to-dmk-tmc-bjd-for-consensus-on-vp-nominee/ar-AA1KKGcl</t>
+          <t>https://www.rokthoklekhani.com/article/43150/bangladeshi-woman-accused-who-escaped-from-jj-hospital-arrested-by-mumbai-police</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/rahul-gandhi-takes-support-from-election-commission-to-save-party-minister-chandrashekhar-bawankule-criticizes.html</t>
+          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/shorts/mumbai/best-credit-society-election-thackeray-brothers-unite-vs-bjp-results-tomorrow/</t>
+          <t>https://aninews.in/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune20250819111423</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/vice-president-election-2025-sanjay-raut-says-elections-to-constitutional-posts-should-be-unopposed-maharashtra-news-mhs25081801506</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/congress-forgets-1987-kashmir-election-malpractices-rajiv-gandhi-ignores-opposition-allegations.html</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!bharat/maharashtra-is-poor-but-ministers-are-abroad-sanjay-raut-lashed-out-maharashtra-news-mhs25081801861</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/shivaji-sawants-admission-to-bjp-is-certain-281398/amp/</t>
+          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/girish-mahajan-chagan-bhujbal-clash-nashik-guardian-minister-281360/amp/</t>
+          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/potholes-persist-rekha-orders-fresh-campaign/articleshow/123349516.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-calls-bhind-rally-over-police-assault-on-journalists/articleshow/123350977.cms</t>
+          <t>https://www.transcontinentaltimes.com/steven-seagal-steamroller-hollywood/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/big-stir-in-solapur-politics-tanaji-sawants-brother-to-join-bjp/129377/</t>
+          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/serious-allegations-of-corruption-against-rohit-pawars-minister-sanjay-shirsat-see-what-he-said/129350/</t>
+          <t>https://www.rokthoklekhani.com/article/43152/new-delhanew-delhi--supreme-court-strict-on-the-issue-of-disabled-military-cadets--center-should-consider-rehabilitation-plan-i-consider-supreme-court-strict-rehabilitation-scheme-on-the</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/parties-reaction-to-nda-vice-presidential-candidate-cp-radhakrishnan/</t>
+          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A4%A6%E0%A4%BE%E0%A4%B0-%E0%A4%A4%E0%A4%BE%E0%A4%A8%E0%A4%BE%E0%A4%9C%E0%A5%80/</t>
+          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-receives-over-200-mm-rainfall-in-24-hours-202405</t>
+          <t>https://thelivenagpur.com/2025/08/18/nagpurs-councils-starved-again-pennies-for-a-region-in-ruin/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/mumbai-rain-imd-red-alert-bmc-issues-holiday-amid-waterlogging-202287</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-ncp-demands-after-heavy-rains-declaring-a-wet-drought-in-the-state-calling-a-special-session-shashikant-shinde-1377947</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/photo/initiative-of-msrtc-and-police-tribal-village-of-gadchiroli-gets-first-public-transport-1558</t>
+          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43136/mumbai--enthusiasm-of-ganesh-devotees-is-at-its-peak--mumbai-s-rain-has-no-effect</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%A8%E0%A4%A1-%E0%A4%8F%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B2-%E0%A4%AB-%E0%A4%AF%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1KJ7hd</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43138/mumbai--a-major-accident-was-averted-in-chira-bazaar--stairs-of-a-two-storey-old-building-suddenly-collapsed</t>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/indias-7th-rank-in-us-scheme-for-children-sparks-fraud-concerns/articleshow/123350715.cms</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43134/mumbai--heavy-rains-till-august-20--meteorological-department-issued-orange-alert</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/csmc-recovers-82cr-in-realty-tax-through-amnesty-scheme/articleshow/123351051.cms</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.rokthoklekhani.com/article/43150/bangladeshi-woman-accused-who-escaped-from-jj-hospital-arrested-by-mumbai-police</t>
+          <t>https://timesofindia.indiatimes.com/city/indore/farmers-intensify-protest-against-land-pool-scheme-in-ujjain-preventive-action-against-35/articleshow/123351223.cms</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/business/22-kg-golden-kalash-installed-at-sant-dnyaneshwar-temple-crafted-by-shripad-shankar-nagarkar-jewellers-pune20250819111423</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B2-%E0%A4%9F%E0%A4%B8-%E0%A4%B5%E0%A4%97%E0%A5%88%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A8-%E0%A4%B9-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%9F-%E0%A4%AF%E0%A4%97%E0%A4%B0-%E0%A4%A6-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%A1%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%98%E0%A4%A1%E0%A4%A4%E0%A4%82%E0%A4%AF/ar-AA1KKoUc</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/no-housing-society-on-govt-land-opts-for-self-redevelopment-in-mumbai/articleshow/123348139.cms</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/to-collect-outstanding-transportation-fines-the-mahagovernment-is-planning-an-amnesty-scheme-1588536</t>
+          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/18/cabinet-sends-back-note-regarding-gmr-with-multiple-queries.html</t>
+          <t>https://tennews.in/mumbai-set-to-honour-today-the-homecoming-of-raghuji-bhonsales-legendary-sword/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-historic-sword-of-maratha-general-raghuji-bhosale-i-repatriated-to-mumbai-201755537654676.html</t>
+          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/others/maharashtra-government-is-set-to-roll-out-an-amnesty-scheme-for-one-time-settlement-of-pending-traffic-challan/articleshow/123367444.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-government-will-build-airport-so-insist-on-compensation-sharad-pawar/</t>
+          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjA1NTQ=/mmrda-launches-sclr-bridge-metro-institute-and-flyovers-to-ease-city-commute</t>
+          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/ports-and-shipping/maharashtra--singapore-review-progress-of-mega-container-port-project/77682</t>
+          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://timesproperty.com/news/post/mumbai-to-get-238-new-ac-local-trains-in-three-yrs-blid10400</t>
+          <t>https://www.tribuneindia.com/news/business/credai-mchi-appoints-mr-sukhraj-nahar-as-18th-president-in-the-change-of-guard-ceremony-graced-by-maharashtra-cm-devendra-fadnavis/amp/?utm=relatedarticles</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-local-train-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%B2-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B6-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE%E0%A4%86%E0%A4%B0%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B8-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-15-000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5/ar-AA1KHzxV?ocid=finance-verthp-feeds</t>
+          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/business-expansion-investments-financial-news/32187520250818</t>
+          <t>https://www.millenniumpost.in/nation/third-mumbai-to-boost-metropolitan-region-development-fadnavis-623625</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-got-177mm-rain-in-6-8-hour-period-says-cm-all-agencies-asked-to-remain-alert-9673094</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-metro-running-smoothly-amid-heavy-rains-in-mumbai-cm-fadnavis-praised-news-hindi-1-745323-KKN.html</t>
+          <t>https://www.etnownews.com/news/mumbai-schools-colleges-to-be-closed-on-august-19-amid-heavy-rain-alert-article-152484704</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/maharashtra-cm-fadnavis-presents-shawl-to-cp-radhakrishnan-on-ndas-vp-nomination/</t>
+          <t>https://tennews.in/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/aaj-ki-baat/aaj-ki-baat-red-alert-for-rain-in-mumbai-be-careful-for-48-hours-2025-08-19-1156835</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/politics-heats-up-over-cidco-land-allocation-issue-pawar-attacks-shirsath/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%A8%E0%A4%A1-%E0%A4%8F%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0-%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AA%E0%A4%82%E0%A4%A4%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AD%E0%A4%B5-%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B2-%E0%A4%AB-%E0%A4%AF%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1KJ7hd</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ahmedabad/indias-7th-rank-in-us-scheme-for-children-sparks-fraud-concerns/articleshow/123350715.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sickle-cell-patients-await-bmt-as-govt-scheme-centres-yet-to-take-off-in-nagpur/articleshow/123351316.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/career/jobs-maharashtra-police-recruitment-2025-notification-for-more-than-15000-vacancy-mahapolice-gov-in-9518146.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/cji-gavai-infrastructure-for-judiciary/</t>
+          <t>https://timesofindia.indiatimes.com/city/lucknow/poll-panel-needs-to-undergo-radical-changes-akhilesh/articleshow/123351446.cms</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://tennews.in/mumbai-set-to-honour-today-the-homecoming-of-raghuji-bhonsales-legendary-sword/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-circuit-bench-inauguration-with-chief-justice-bhushan-gavai-marathi-news/</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/demand-to-declare-a-wet-drought-due-to-heavy-rains-in-the-state-is-strong/129359/</t>
+          <t>https://timesofindia.indiatimes.com/city/ahmedabad/ahmedabad-woman-accuses-in-laws-of-abuse-over-interfaith-marriage/articleshow/123350741.cms</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/maratha-commander-raghuji-bhonsle-s-sword-brought-to-mumbai-125081800027_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/tigers-rise-but-amarabad-struggles-with-encroachment-prey-loss/articleshow/123350744.cms</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/monsoon-update-red-and-orange-alert-in-15-to-16-districts-cm-devendra-fadnavis-said/129346/</t>
+          <t>https://timesofindia.indiatimes.com/city/guwahati/injured-by-arrow-wild-jumbo-tracked-to-goalpara-forest/articleshow/123350027.cms</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-office-bearers-of-mns-workers-organization-join-bjp/</t>
+          <t>https://timesofindia.indiatimes.com/city/goa/singapore-resident-arrested-for-cheating-siolim-woman-of-rs-1cr/articleshow/123350891.cms</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://trak.in/stories/pune-can-get-underground-road-network-to-beat-traffic-woes/</t>
+          <t>https://timesofindia.indiatimes.com/city/mysuru/historic-town-hall-crying-for-restoration-work-to-be-done/articleshow/123349504.cms</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!opinion/uttarkashi-floods-show-why-india-must-integrate-climate-risks-into-mountain-development-mhs25081806533</t>
+          <t>https://timesofindia.indiatimes.com/city/lucknow/1-48-crore-students-across-up-schools-celebrate-independence-day-event/articleshow/123351455.cms</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/rs-40kcr-of-investors-money-stuck-with-credit-societies-maharashtra-govt-to-announce-sop-for-recovery/articleshow/123367502.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/goa/ngt-tells-green-authority-to-consider-concerns-over-proposed-xelvona-jetty/articleshow/123350970.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.etnownews.com/news/mumbai-schools-colleges-to-be-closed-on-august-19-amid-heavy-rain-alert-article-152484704</t>
+          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://tennews.in/ncp-sp-targets-maha-minister-over-rs-5000-cr-scam-in-navi-mumbais-cidco-land-demands-his-resignation/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/tehsildar-sings-at-farewell-revenue-min-suspends-him-for-lack-of-decorum/articleshow/123350443.cms</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/dialogue-between-prime-minister-narendra-modi-and-vladimir-putin-indias-strong-support-for-peaceful-resolution.html</t>
+          <t>https://timesofindia.indiatimes.com/city/varanasi/private-hostel-owner-booked-for-harassing-dalit-girl-roommate/articleshow/123351311.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/publishing-books-on-diverse-topics-is-a-literary-movement-of-the-chaparak-author-abhiram-bhadkamkar-asserts.html</t>
+          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-18-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-18-1156628</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/school-9-a-side-hockey-league-begins-in-thane-76-teams-participate-enthusiastically.html</t>
+          <t>https://www.indiatv.in/video/yoga/yoga-with-swami-ramdev-63-crore-people-have-spinal-injuries-how-will-cervical-and-sciatica-be-cured-2025-08-18-1156639</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/rajannas-conspiracy-claim-pits-cm-supporters-against-dks-camp/articleshow/123348301.cms</t>
+          <t>https://www.eaajkaanand.com/Encyc/2025/8/18/vote.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/congress-vows-to-douse-fire-amid-rifts-within-party/articleshow/123350298.cms</t>
+          <t>https://samacharnama.com/states/maharashtra-news/supreme-court-dismisses-plea-seeking-cancellation-of/cid17260970.htm</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/industries-in-jalgaon-should-get-power-at-subsidised-rate-says-ajit-pawar/articleshow/123351430.cms</t>
+          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/lucknow/poll-panel-needs-to-undergo-radical-changes-akhilesh/articleshow/123351446.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/anna-hazare-outburst-on-flex-boards-in-pune-maharashtra-news-mhs25081801191</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/water-cut-in-parts-of-mulund-on-thursday/articleshow/123350558.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/one-held-for-friends-murder/articleshow/123350586.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/rss-and-its-contribution-to-freedom-narendra-modi-on-rss.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/lucknow/ashok-elected-prez-of-iit-alumni-body/articleshow/123351412.cms</t>
+          <t>https://www.communicationstoday.co.in/ibm-to-support-quantum-computing-initiative-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/three-of-seven-accused-arrested-in-journalist-attack-case/articleshow/123350718.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/goa/singapore-resident-arrested-for-cheating-siolim-woman-of-rs-1cr/articleshow/123350891.cms</t>
+          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/natgrid-aids-cops-in-catching-four-minors-wanted-for-murder/articleshow/123350104.cms</t>
+          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/man-left-stranded-in-uganda-by-employer-wins-rs-3-lakh-dues-back/articleshow/123350843.cms</t>
+          <t>https://mahasamvad.in/176121/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kanpur/two-more-suspects-held-in-jalaun-murder-case/articleshow/123350447.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/lucknow/1-48-crore-students-across-up-schools-celebrate-independence-day-event/articleshow/123351455.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/vijayawada/lokesh-in-delhi-to-secure-approvals-investments-for-ap-projects/articleshow/123349810.cms</t>
+          <t>https://mahasamvad.in/176009/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/goa/ngt-tells-green-authority-to-consider-concerns-over-proposed-xelvona-jetty/articleshow/123350970.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/raipur/uzbek-institute-to-collaborate-with-igkv-in-agri-research/articleshow/123350462.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/varanasi/cargo-vessel-flags-new-chapter-in-varanasiwb-water-transport/articleshow/123351314.cms</t>
+          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/karnataka-forest-department-allows-ore-explorationin-chitradurga-reserve-forest/articleshow/123350404.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
+          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/video/bhavishyawani/aaj-ka-rashifal-18-aug-2025-know-from-acharya-indu-prakash-ji-what-your-stars-are-saying-today-2025-08-18-1156628</t>
+          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.eaajkaanand.com/Encyc/2025/8/18/vote.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/8/18/nanded-flood-resues-continew.html</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/who-is-the-opposition-candidate-for-the-post-of-vice-president-events-in-delhi-are-gaining-momentum-what-decision-will-mallikarjun-kharge-take-gkt-96-5313155/</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-08-2025-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5-%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/anna-hazare-outburst-on-flex-boards-in-pune-maharashtra-news-mhs25081801191</t>
+          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/i-got-offer-to-remove-10000-names-from-voter-list-before-assembly-elections-bachchu-kadu-claim-maharashtra-news-mhs25081703006</t>
+          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolkata/controversy-mars-trailer-launch-of-bengal-files/articleshow/123339117.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/18/bom45-mh-maratha-ld-sword.html</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/what-happened-in-the-trump-putin-meeting-chandrashekhar-nene-maha-mtb.html</t>
+          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.communicationstoday.co.in/ibm-to-support-quantum-computing-initiative-in-maharashtra/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/cet-2025-announced-for-judicial-services-competitive-examination.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/mumbai-rains-heavy-showers-flood-roads-railway-tracks-bring-city-to-standstill-video/articleshow/123362740.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/photos/mumbai-rains-torrential-downpour-cripples-normal-life-train-services-hit-roads-flooded-see-pics-11755525808666.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://odishatv.in/news/national/rain-fury-5-missing-200-stranded-in-nanded-local-trains-flights-hit-in-mumbai-270189</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://newsroompost.com/india/indigo-airlines-issues-travel-advisory-for-passengers-flying-out-of-mumbai-due-to-heavy-rainfall-waterlogging-in-the-city/5347388.html</t>
+          <t>https://civicmirror.in/nation/telecom-collapses-across-the-country-airtel-jio-vi-network-down/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176121/</t>
+          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/-mumbai-maharashtra-government-third-mumbai-devendra-fadnavis-worli-shivdi.html</t>
+          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/19/the-chief-minister-is-continuously-reviewing-the-rainfall-in-mumbai.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-heavy-rains-in-the-state-7-people-died-cm-devendra-fadnavis-directs-all-agencies-to-be-alert-89603</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/176009/</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray/913004/</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-mumbai-next-48-hours-are-crucial-chief-minister-devendra-fadnavis-warns-citizens-to-be-alert/913099/</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/mumbai/navi-mumbais-successor-the-rise-of-third-mumbai-in-raigad-district-cm-devendra-fadnavis-pjp78</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-rain-update-heavy-rainfall-started-in-city-resulted-in-disruption-of-life-and-mumbai-local-cm-fadnavis-reviewed/articleshow/123363662.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>https://www.saamana.com/raghujiraje-bhosale-sword-a-legacy-of-bravery-is-open-to-history-lovers-in-mumbai-an-attempt-to-reclaim-the-legacy-of-the-maratha-empire-said-by-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/third-mumbai-a-new-chapter-in-economic-development-goldman-sachs-new-mumbai-office-inaugurated/129385/</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/cm-devendra-fadnavis-instructs-all-agencies-to-be-alert-in-the-wake-of-heavy-rains-in-the-state/129378/</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/business/3545330-transformative-leadership-sukhraj-nahar-steers-credai-mchi-towards-urban-revolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/civic/803-families-stranded-as-lokmanya-nagar-redevelopment-hits-political-roadblock/</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>https://www.latestly.com/india/politics/vice-president-elections-2025-shiv-sena-ncp-support-to-nomination-of-cp-radhakrishnan-as-nda-candidate-for-vp-polls-7064013.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!bharat/krishna-janmashtami-2025-celebrations-procession-turn-tragic-in-hyderabad-five-devotees-electrocuted-to-death-after-chariot-comes-in-contact-electric-wire-maharashtra-news-mhs25081800993</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>https://www.cnbctv18.com/india/are-mumbai-schools-colleges-open-or-close-on-august-19-19655564.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>https://auto.economictimes.indiatimes.com/news/industry/maharashtras-new-amnesty-scheme-settle-transport-fines-and-save-big/123364146</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/penal-action-will-be-taken-against-those-who-ignore-the-marathi-language-in-government-and-semi-government-offices-in-maharashtra-maharashtra-news-mhs25081803599</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/immediately-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-minister-makarand-jadhav-patil-directs.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/the-joy-of-working-in-social-work-is-immense-pandurang-chormale.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/18/student-felicitation-ceremony-during-the-schools-internal-parade.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/mumbai-rains-live-updates-mumbai-red-alert-issue-streets-inundated-and-hits-local-trains-lb-89483</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
           <t>https://www.etvbharat.com/mr/!state/minister-sanjay-shirsat-misuses-powers-rohit-pawar-alleges-rs-5000-crore-scam-mumbai-maharashtra-news-mhs25081804077</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/nation/telecom-collapses-across-the-country-airtel-jio-vi-network-down/</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/mahrashtra-mumbai-rain-latest-update-orange-alert-till-august-20-red-alert-issued-in-several-districts-963438.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/heavy-rain-in-raigad-district-savitri-river-flood-landslide-in-mangaon-maharashtra-news-mhs25081804820</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/fir-policy-leads-to-60-drop-in-citys-drunk-driving-cases/articleshow/123351105.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/08/18/bom51-mh-cm-third-mumbai.html</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A589"/>
+  <dimension ref="A1:A664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,4116 +438,4641 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/devendra-fadnavis-breaks-silence-over-ajit-pawar-ips-officer-issue-3719617</t>
+          <t>https://www.punjabnewsexpress.com/national/news/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi-297681</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-cm-devendra-fadnavis-signs-mous-with-tata-technologies-and-us-state-of-iowa/vi-AA1MsyFp</t>
+          <t>https://www.ndtv.com/india-news/devendra-fadnavis-shares-how-first-meeting-with-pm-modi-left-a-lasting-impression-9287347</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cm-lashes-out-at-karnataka-govt-for-decision-to-change-name-of-shivajinagar-metro-station-to-st-marys-station-in-bengaluru/articleshow/123836305.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/unacceptable-sharad-pawar-dials-devendra-fadnavis-over-bjp-mla-gopichand-padalkars-remarks-on-jayant-patils-parents-3735796</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.datacenterdynamics.com/en/news/indias-rovision-signs-mou-for-data-center-near-navi-mumbai/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-devendra-fadnavis-says-govt-will-create-corpus-fund-for-medical-treatments-that-cost-more-than-rs-5-lakh/articleshow/123905737.cms</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.jns.org/smotrich-visits-mumbai-meets-regional-leader-on-third-day-of-india-visit/</t>
+          <t>https://www.msn.com/en-gb/news/India/can-t-save-religion-when-deputy-cm-s-wife-busy-making-reels-kanhaiya-kumar-s-remarks-on-devendra-fadnavis-wife-amruta-sparks-row/ar-AA1u42XL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-will-lead-in-global-skilled-workforce-chief-minister-devendra-fadnavis-23593340</t>
+          <t>https://www.ndtv.com/india-news/on-rahul-gandhis-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-9306931</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/if-pakistan-funds-let-hq-reconstruction-india-must-devendra-fadnavis-994265</t>
+          <t>https://timesofindia.indiatimes.com/india/no-faith-in-constitution-fadnavis-targets-rahul-gandhi-over-gen-z-post-terms-him-urban-maoist/articleshow/123996897.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://ottumwaradio.com/2025/09/gov-reynolds-signs-partner-state-agreement-with-maharashtra-india/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-move-supreme-court-if-karnataka-goes-ahead-with-plan-to-increase-almatti-dams-height-cm-devendra-fadnavis-3732808</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-seeks-report-on-ajit-ips-officer-exchange-101757445183422.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-devendra-fadnavis-to-launch-railway-project-for-marathwada-3730637</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/minister-chhagan-bhujbal-writes-to-maharashtra-cm-devendra-fadnavis-seeks-changes-to-maratha-quota-rule/articleshow/123797597.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/next-mumbai-mayor-will-be-from-maha-yuti-says-devendra-fadnavis-as-bjp-launches-campaign-for-bmc-polls-3730927</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/cm-devendra-fadnavis-sanctions-10-crore-for-youth-policy-adds-opposition-members-to-panel/articleshow/123769739.cms</t>
+          <t>https://www.hindustantimes.com/india-news/only-rahul-gandhi-has-art-of-continuously-lying-devendra-fadnavis-101758224439191.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/time-to-play-biz-t-20-with-australia-says-maharashtra-cm-devendra-fadnavis/articleshow/123833319.cms</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/acharya-devvrat-takes-oath-as-maha-governor-in-sanskrit-in-the-presence-of-cm-devendra-fadnavis/videoshow/123896080.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/congress-insult-to-shivaji-maharashtra-cm-devendra-fadnavis-slams-karnataka-govt-for-renaming-bengaluru-metro-station/ar-AA1MoJ98</t>
+          <t>https://www.devdiscourse.com/article/politics/3631822-vote-theft-exposed-maharashtra-congress-demands-immediate-resignation-of-cm-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/autos/news/tesla-comes-to-india-maharashtra-cm-devendra-fadnavis-unveils-model-y-priced-at/ar-AA1IDJrP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-to-come-out-with-bamboo-industry-policy-cm-devendra-fadnavis-3735818</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/political-shockwaves-in-maharashtra-uddhav-thackeray-devendra-fadnavis-hold-30-minutes-meeting/ar-AA1IPa8l?cvid=f23a1cef36a544cedfc94adbc07bb2ec&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/pm-modi-to-inaugurate-mumbai-metro-3s-final-stretch-from-worli-to-cuffe-parade-on-sept-30-announces-chief-minister-devendra-fadnavis/articleshow/123928132.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/political-storm-in-karnataka-fadnavis-terms-renaming-metro-station-insult-to-shivaji-maharaj-opposition-leaders-join-chorus/articleshow/123830845.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/remove-requirement-of-non-agricultural-land-certificate-for-micro-and-small-enterprises-says-maharashtra-chief-minister-devendra-fadnavis/articleshow/123979505.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/insult-to-shivaji-maharaj-fadnavis-condemns-bengaluru-metro-station-name-change-3723874</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-will-move-sc-if-karnataka-goes-ahead-with-plan-to-raise-almatti-dam-height-fadnavis-101758133395229.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/stay-registration-of-homeopaths-with-mmc-until-hc-decides-matter-ima-urges-fadnavis/articleshow/123858932.cms</t>
+          <t>https://auto.economictimes.indiatimes.com/news/industry/chhatrapati-sambhajinagar-emerges-as-indias-ev-manufacturing-hub-declares-maharashtra-cm-fadnavis/123961856</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/chhagan-bhujbal-submits-memorandum-to-devendra-fadnavis-urges-to-withdraw-gr-on-obc-issue-3719401</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-fadnavis-reviews-security-and-preparedness-with-navy-and-army-officers/articleshow/124029075.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/sambhajinagar-hoarding-questions-why-only-fadnavis-targeted-over-maratha-quota/amp_articleshow/123874467.cms</t>
+          <t>https://www.devdiscourse.com/article/law-order/3634846-strengthening-maritime-military-ties-fadnavis-meets-armed-forces-leaders</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/minister-chhagan-bhujbal-writes-to-maharashtra-cm-devendra-fadnavis-seeks-changes-to-maratha-quota-rule/ar-AA1Meus3</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-pm-modi-a-visionary-global-statesman-on-his-75th-birthday-23594462</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mysuru/dcm-bats-for-bhadra-development-slams-fadnavis-on-water-issue/articleshow/123857186.cms</t>
+          <t>https://www.devdiscourse.com/article/law-order/3634606-harnessing-technology-for-next-level-policing?amp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.deshsewak.org/english/news/217828</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-lead-in-green-steel-manufacturing-cm-devendra-fadnavis-23594846</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/after-maratha-row-banjaras-demand-st-quota-in-maharashtra-101757816743870.html</t>
+          <t>https://www.devdiscourse.com/article/headlines/3634080-fadnavis-criticizes-rahul-gandhi-raises-brain-theft-allegations-amid-vote-theft-claims</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/not-all-countries-happy-with-india-s-progress-but-no-one-can-stop-us-says-fadnavis/2908702</t>
+          <t>https://www.deccanherald.com/india/congress-accuses-bjp-of-coming-to-power-in-maharashtra-by-rigging-votes-asks-fadnavis-to-quit-3734523</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/submit-wainganga-nalganaga-river-linking-dpr-by-oct-15-fadnavis-to-officials/2896018</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628667-fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir?amp</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/gadkari-fadnavis-to-inaugurate-rto-flyover-today/articleshow/123836339.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-signs-mou-with-cambridge-for-global-standard-education-cm-fadnavis/articleshow/123980116.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/maharashtra-best-destination-for-industries-investments-fadnavis/2905150</t>
+          <t>https://money.rediff.com/news/market/fadnavis-streamline-industry-approvals-in-maharashtra/33958120250919</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2165403</t>
+          <t>https://www.business-standard.com/industry/news/maha-govt-to-launch-skills-courses-for-gems-and-jewellery-sector-fadnavis-125091600501_1.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/services/property-/-cstruction/lodha-developers-signs-mou-with-fadnavis-govt-for-rs-30000-cr-worth-data-centre-park/articleshow/123834115.cms</t>
+          <t>https://www.devdiscourse.com/article/headlines/3632715-fadnavis-slams-rahul-gandhis-vote-theft-claims-as-baseless-propaganda?amp</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/residential-complex-for-muslims-in-mumbai-nhrc-issues-notice-to-fadnavis-govt-bjp-vs-rss-on-cards-2957165.html</t>
+          <t>https://www.ptinews.com/story/business/reduce-number-of-permissions-to-set-up-industries-speed-up-approval-time-fadnavis-to-officials/2930550</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-launches-e-samarth-to-monitor-annual-development-funds-allocated-to-mlas-101757530217737.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-fadnavis-defends-obc-reservation-policy-says-no-threat-to-communitys-rights/articleshow/123886921.cms</t>
+          <t>https://www.devdiscourse.com/article/politics/3628357-fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir?amp</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/st-mary-metro-station-talk-to-centre-cm-siddaramaiah-tells-fadnavis-3725854</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-devendra-fadnavis-23594442</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/cm-gives-nod-for-bmc-run-nursing-college-in-bandra/articleshow/123883610.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-for-tech-driven-policing-flags-ai-and-cybercrime-challenges-23594968</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-government-signs-mous-worth-rs-1-08-lakh-crore-move-will-create-47k-direct-jobs-says-cm/amp_articleshow/123832655.cms</t>
+          <t>https://m.economictimes.com/industry/indl-goods/svs/steel/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/articleshow/123999573.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/bengaluru/bengaluru-metro-row-siddaramaiahs-proposal-to-rename-shivajinagar-station-after-st-mary-sparks-outrage-article-152785620</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/congress-slams-cm-fadnavis-over-shivaji-posters-pasted-in-unhygienic-surroundings-near-prabhadevi-railway-station-in-mumbai/articleshow/123948554.cms</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-will-provide-skilled-manpower-to-overseas-industries-fadnavis/2902794</t>
+          <t>https://www.devdiscourse.com/article/law-order/3635039-harnessing-technology-maharashtras-policing-revolution</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-launches-online-college-approval-system-proposes-automated-scholarship-disbursement-23593354</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-cabinet-clears-avgc-xr-policy-draws-up-a-25-year-roadmap-101758043978392.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/karnataka-chief-minister-siddaramaiah-tells-fadnavis-to-approach-centre-on-metro-stations-name/amp_articleshow/123858132.cms</t>
+          <t>https://www.devdiscourse.com/article/politics/3630398-bjps-enduring-commitment-fadnavis-recollects-2017-political-maneuverings-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Submit-Wainganga-Nalganaga-river-linking-DPR-by-Oct-15-Fadnavis-to-officials/2896018</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/football-legend-lionel-messi-to-visit-mumbai-in-december-will-train-with-young-footballers-cm-fadnavis-23595113</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://yourstory.com/2025/09/fadnavis-inaugurates-cpris-testing-lab-nashik-boost-ev-industry</t>
+          <t>https://www.cnbctv18.com/infrastructure/pm-modi-to-inaugurate-mumbai-metro-3-on-september-30-says-devendra-fadnavis-19677024.htm</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/devendra-fadnavis-breaking-news-there-will-be-no-injustice-to-obc-devendra-fadnavis-1074271.html</t>
+          <t>https://www.ptinews.com/story/business/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/2930145</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/economy/news/maha-signs-mous-worth-1-08-trn-move-will-create-47k-direct-jobs-cm-125091101179_1.html</t>
+          <t>https://m.economictimes.com/news/india/fadnavis-pushes-officials-on-reforms-governance/amp_articleshow/124031684.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-discoms-get-a-rating/2903632</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/13/nagpur-to-be-hub-of-solar-panel-manufacturing-cm-fadnavis.amp.html</t>
+          <t>https://money.rediff.com/news/market/ev-capital-fadnavis-on-chhatrapati-sambhajinagar/33804020250917</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/devendra-fadnavis-on-obc-reservation-news-devendra-fadnavis-s-attack-on-supriya-sule-n18s-1074213.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharastra-cm-fadnavis-pushes-for-faster-industrial-approvals-ai-based-reforms-to-boost-investments-23594849</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/siddaramaiahs-move-to-rename-bengalurus-shivajinagar-metro-station-as-st-mary-sparks-political-row-1005532</t>
+          <t>https://www.mumbailive.com/en/politics/mumbai-congress-slams-fadnavis-for-'disrespecting'-shivaji-maharaj-in-billboard-row-90046</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://themachinemaker.com/news/maharashtra-government-allots-100-acres-to-rrp-electronics-ltd-a-leading-semiconductor-company/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168537</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/cm-fadnavis-should-address-anarchy-caused-by-maratha-obc-quota-issue-through-dialogue-raut/2911590</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mlas-remarks-about-ncp-sp-leader-23594821</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/news/west/administration-fadnavis-tribal-quota/3573106.html</t>
+          <t>https://www.ptinews.com/detail/national/Using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level-Fadnavis/2934307</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.sarkaritel.com/vision-maharashtra-document-2047-is-our-guiding-principle-cm-fadnavis/</t>
+          <t>https://lokmat.news18.com/short-videos/trending/gopichand-padalkar-news-first-reaction-after-cm-devendra-fadnavis-call-jayant-patil-n18s-1075363.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-distributes-seventh-instalment-of-namo-shetkari-mahasamman-kisan-yojana20250909155017</t>
+          <t>https://www.devdiscourse.com/article/politics/3631054-maharashtra-leaders-hail-pm-modis-visionary-leadership-on-75th-birthday?amp</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-govt-brings-widows-single-women-under-mission-vatsalyas-ambit-enn25091403141</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/sambhajinagar-becoming-ev-capital-of-country-fadnavis/articleshow/123952619.cms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/national/ganesh-festival-508-tonnes-of-floral-offerings-collected-in-post-immersion-drive/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628555-vast-growth-opportunities-in-fisheries-animal-husbandry-sectors-says-fadnavis-cites-aps-example</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278571243/maharashtra-signs-mou-with-iowa-to-boost-agriculture-technology</t>
+          <t>https://www.ptinews.com/editor-detail/fadnavis-leads-maharashtra-in-greeting-pm-modi-on-birthday;-calls-him-global-statesman--inspiration/2922857</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278576002/india-will-definitelty-demand-sanctions-maharashtra-cm-fadnavis-on-pakistan-funding-lashkar-e-taiba-hq-reconstruction</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-govt-dept-websites-landing-pages-to-be-in-marathi-101757962665589.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/09/12/315475/bharat/row-erupts-over-karnataka-congress-govts-decision-to-rename-bengalurus-shivajinagar-metro-station-to-st-mary/</t>
+          <t>https://www.ptinews.com/story/national/gst-reforms-to-speed-up-indias-economic-growth-says-fadnavis/2936669</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/in-touch-with-tourists-visiting-nepal-maharashtra-cm-fadnavis/</t>
+          <t>https://www.aninews.in/news/national/general-news/to-continuously-lie-is-an-art-that-only-rahul-gandhi-has-devendra-fadnavis-on-congress-mps-vote-theft-claims20250918223639?amp=1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/wainganga-nalganga-river-linking-project-cm-fadnavis-tells-officials-submit-dpr-oct-15-450051</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhi-speaks-like-an-urban-maoist-says-maharashtra-cm-fadnavis-on-congress-leaders-gen-z-post-23594827</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maharashtra-leads-providing-necessary-skilled-manpower-industries-abroad-cm-fadnavis-450889</t>
+          <t>https://www.ptinews.com/detail/national/No-case-of-honeytrap-in-state--CM-Fadnavis/2739248</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/ima-urges-cm-fadnavis-to-withdraw-decision-allowing-ccmp-doctors-registration-warns-of-statewide-strike/</t>
+          <t>https://lokmat.news18.com/short-videos/trending/sharad-pawar-on-devendra-fadnavis-rain-damage-saying-devabhau-pawar-s-big-demand-to-cm-n18s-1075195.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/shivajinagar-metro-station-name-change-row-fadnavis-slams-karnataka-cm-siddaramaiah-1799857</t>
+          <t>https://www.devdiscourse.com/article/health/3628551-fadnavis-calls-for-inclusive-cancer-care-policy-for-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://m.sakshipost.com/amp/news/maharashtra-best-state-investment-conducive-ecosystem-cm-fadnavis-451225</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/obcs-disrupt-cm-s-speech-holds-huge-rally-in-hingoli-101758137116445.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.apnnews.com/government-of-maharashtra-allots-100-acres-to-rrp-electronics-ltd-leading-semiconductor-player/</t>
+          <t>https://www.business-standard.com/india-news/next-phase-of-gst-reforms-will-boost-india-s-economic-growth-says-fadnavis-125092100781_1.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-cm-fadnavis-stresses-autonomy-for-higher-education-institutions-at-coep-event/</t>
+          <t>https://www.aninews.in/news/entertainment/out-of-box/hindi-films-fail-to-depict-the-true-heroism-of-mumbai-police-says-maharashtra-cm-fadnavis20250920135931</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/cm-fadnavis-calls-maharashtra-indias-most-industry-friendly-state/</t>
+          <t>https://www.ptinews.com/story/national/chhatrapati-sambhajinagar-will-become-country-s-ev-capital-fadnavis/2922165</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/proposal-rename-bengaluru-shivajinagar-metro-station-st-mary-fadnavis-terms-move-insult-to-shivaji-maharaj-135895191.html</t>
+          <t>https://www.aninews.in/news/national/general-news/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm20250919232605</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/good-news-for-farmers-in-maharashtra-as-cm-fadnavis-announces-decision-to-give-6000-rs-annually-under-namo-shetkari-yojana-135877472.html</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/sharad-pawar-calls-cm-over-bjp-mlas-remark/amp_articleshow/124003748.cms</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/maharashtra-will-provide-skilled-manpower-to-overseas-industries-fadnavis-10079630</t>
+          <t>https://www.ptinews.com/editor-detail/Rahul-Gandhi-speaks-like-an-urban-Maoist-Fadnavis-on-his-Gen-Z-post/2929933</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/entertainment/bollywood-amruta-fadnavis-10-beautiful-photos-devendra-fadnavis-wife-looks-like-a-bollywood-actress-3009276</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/18/no-cap-on-prices-of-cars-for-guv-cm-and-judges-in-maharashtra-vehicle-policy</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/favorable-environment-for-industries-cm-devendra-fadnavis-said-ease-of-doing-business-is-being-strengthened/articleshow/123845462.cms</t>
+          <t>https://www.mumbailive.com/en/politics/fadnavis-slams-rahul-gandhi-over-election-allegations-calls-him-a-habitual-liar-90060</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-sharad-pawar-devendra-fadnavis-engaged-in-a-war-of-words-over-maratha-obc-reservation-ws-l-9622419.html</t>
+          <t>https://money.rediff.com/amp/news/market/maharashtra-green-steel-leader-fadnavis-announces/33951620250919</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://awaazindiatv.com/?p=7373</t>
+          <t>https://www.mumbailive.com/en/politics/industrial-reforms-planned-under-cm-fadnavis-leadership-90070</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%A8%E0%A4%B6%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%A1%E0%A4%BC%E0%A4%B5-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%96%E0%A5%87%E0%A4%B2-%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%AF/ar-AA1M6krk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-to-storm-fadnavis-home-turf-rally-obcs-on-sept-18/articleshow/123929254.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/amruta-fadnavis-dress-issue-with-akshay-kumar-in-mumbai-juhu-beach-maharashtra-cm-wife-counter-attack/articleshow/123806648.cms</t>
+          <t>https://www.ptinews.com/editor-detail/maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop--fadnavis/2927696</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-trouble-for-devendra-fadnavis-obc-banjara-protest-against-maratha-reservation-maharashtra-politics-ws-ln-9621475.html</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628615-maharashtra-govt-will-create-corpus-fund-to-cover-treatments-costing-over-rs-5-lakh-fadnavis?amp</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%A6-%E0%A4%95%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%9A-%E0%A4%9F-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A5%88%E0%A4%A7-%E0%A4%96%E0%A4%A8%E0%A4%A8-%E0%A4%AE-%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6-%E0%A4%A6-%E0%A4%95-%E0%A4%86%E0%A4%88%E0%A4%AA-%E0%A4%8F%E0%A4%B8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%A0%E0%A4%A8/ar-AA1McHIL</t>
+          <t>https://www.ptinews.com/story/national/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal/2926755</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/chhatrapati-sambhajinagar-boy-anay-zanvar-made-devendra-fadnavis-photo-with-help-of-500-cubes-maharashtra-cm-lauds-his-talent-know-all/articleshow/123845638.cms</t>
+          <t>https://www.newsonair.gov.in/hyderabad-liberation-day-celebrated-with-flag-hoisting-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-fadnavis-big-orders-appoint-only-ias-officers-as-commissioners-in-municipal-body-after-mira-bhayandar-vasai-virar-corruption-row/articleshow/123844784.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3633546-streamlining-success-maharashtras-push-for-rapid-industrial-approvals?amp</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ips-anjana-krishna-and-ajit-pawar-controversy-cm-fadnavis-gives-clean-chit-to-deputy-cm/articleshow/123789864.cms</t>
+          <t>https://www.ptinews.com/editor-detail/GST-reforms-to-speed-up-India%E2%80%99s-economic-growth-says-Fadnavis/2936669</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%95-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%AB-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%9D%E0%A4%9F%E0%A4%95/ar-AA1M5pB5?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.tribuneindia.com/news/devendra-fadnavis/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-indian-racing-festival-finale</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%95-%E0%A4%95%E0%A4%AE-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%8F-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1La6Vu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/news/india-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-on-marathwada-liberation-day-107384/6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-how-mva-mps-did-cross-voting-in-vice-president-election-devendra-fadnavis-eknath-shinde-played-big-role-9604766.html</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe20250918053517/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-obc-reservation-ncp-minister-chhagan-bhujbal-meets-cm-devendra-fadnavis-201757408173289.html</t>
+          <t>https://www.ptinews.com/story/national/ladki-bahin-scheme-won%E2%80%99t-be-scrapped;-govt-committed-to-empowering-women-fadnavis=/2922760</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharshtra-co-guardian-ministers-gets-power-cm-fadnavis-said-said-they-also-solve-problems-know-all/articleshow/123869141.cms</t>
+          <t>https://www.ptinews.com/editor-detail/chhatrapati-sambhajinagar-will-become-country-s-ev-capital--fadnavis/2922163</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/in-review-meeting-of-developed-maharashtra-vision-2047-cm-fadnavis-said-we-are-moving-towards-making-maharashtra-developed-state/articleshow/123776908.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/vice-president-election-result-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B5-%E0%A4%B0-%E0%A4%A7-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%AF-%E0%A4%82-%E0%A4%85%E0%A4%AA%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%9F-%E0%A4%82-%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A4%9A-%E0%A4%AA-%E0%A4%88%E0%A4%82/ar-AA1McMGj</t>
+          <t>https://www.aninews.in/news/national/general-news/lifting-last-person-and-bringing-them-to-mainstream-development-reflects-pm-modis-working-approach-maharashtra-cm-fadnavis20250917223421</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/almatti-dam-karnataka-vs-maharashtra-dk-shivakumar-target-cm-devendra-fadnavis-9615427.html</t>
+          <t>https://aninews.in/news/national/general-news/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address20250921195926</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/cm-fadnavis-s-reply-to-the-opposition-said-obc-rights-will-not-be-affected-by-the-gr-of-maratha-reservation-2025-09-14</t>
+          <t>https://www.ptinews.com/story/national/oppn-ruling-parties-spar-over-rahuls-fresh-vote-chori-charges-cong-seeks-fadnavis-resignation/2927511</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-bengaluru-shivajinagar-metro-name-change-sparks-maharashtra-karnataka-clash-ws-ln-9610201.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-inks-nine-mous-for-industrial-projects-secures-investments-worth-rs-80962-crore-23594853</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/photo-gallery/education/amruta-fadnavis-education-know-top-institutes-where-maharashtra-cm-wife-studied-3010921</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal-23594647</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/cm-fadnavis-maharashtra-among-top-states-in-india-for-industry-and-investment/</t>
+          <t>https://www.ptinews.com/editor-detail/Oppn-ruling-parties-spar-over-Rahul-s-fresh-vote-chori-charges;-Cong-seeks-Fadnavis-resignation/2927028</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%95%E0%A5%9C%E0%A4%95-%E0%A4%95%E0%A5%88%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A4%A8-%E0%A4%AC%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A4%97%E0%A4%B0-%E0%A4%A8-%E0%A4%97%E0%A4%AE-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%AC-%E0%A4%B8-%E0%A4%B0%E0%A5%8D%E0%A4%AB-ias-%E0%A4%B9-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%9C-%E0%A4%A8-%E0%A4%B2-%E0%A4%9C-%E0%A4%8F-%E0%A4%B5%E0%A4%9C%E0%A4%B9/ar-AA1MoZu8</t>
+          <t>https://www.ptinews.com/editor-detail/oppn--ruling-parties-spar-over-rahul-s-fresh--vote-chori--charges;-cong-seeks-fadnavis--resignation/2927511</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-wife-amruta-fadnavis-first-public-video-naokda-bhairav-darshan-dham-program-after-dress-issue-with-akshay-kumar-in-mumbai/articleshow/123882728.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%82%E0%A4%AA-%E0%A4%95%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%AF-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AA-%E0%A4%8F%E0%A4%AE-%E0%A4%AE-%E0%A4%A6-%E0%A4%8F%E0%A4%95-%E0%A4%AE%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%85%E0%A4%AC-%E0%A4%95-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%A6%E0%A4%AC-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1M0lX5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/editor-detail/condition-of-getting-non-agricultural-land-nod-to-be-scrapped-for-micro--small-industries--fadnavis/2927545</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-leaders-meet-cm-speaker-over-vacant-lop-posts-in-assembly-and-council-2025-09-09</t>
+          <t>https://www.business-standard.com/industry/news/maharashtra-signs-mous-worth-80-962-cr-for-industrial-projects-40k-jobs-125091900956_1.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.starsamachar.com/bengaluru-shivajinagar-metro-station-name-change-controversy-devendra-fadnavis-bjp-shivsena-reaction</t>
+          <t>https://inshorts.com/en/amp_news/maharashtra-key-in-pm-s-mission-green-steel--cm-fadnavis-1758347491548</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%95-%E0%A4%A8-%E0%A4%9F-%E0%A4%87%E0%A4%A1-%E0%A4%A1%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%95%E0%A4%AE%E0%A5%87%E0%A4%82%E0%A4%9F-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2-%E0%A4%82-%E0%A4%95-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%95-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A8-%E0%A4%95-%E0%A4%9C%E0%A4%B5-%E0%A4%AC-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%AF-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F/ar-AA1MgjbQ</t>
+          <t>https://www.ptinews.com/story/national/condition-of-getting-non-agricultural-land-nod-to-be-scrapped-for-micro-small-industries-fadnavis/2927545</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/developed-maharashtra-by-2047-chief-minister-fadnavis-vision/articleshow/123771706.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%97%E0%A4%B0-%E0%A4%AD%E0%A5%81%E0%A4%9C%E0%A4%AC%E0%A4%B2-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%A4-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9B-%E0%A5%9C-%E0%A4%A6%E0%A5%87%E0%A4%82-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AC-%E0%A4%A4-%E0%A4%A4-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%B0%E0%A4%97%E0%A5%9C-%E0%A4%A8%E0%A4%AE%E0%A4%95-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%B9-%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%B6%E0%A4%A8/ar-AA1LVcCG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aninews.in/news/national/general-news/mumbai-union-minister-pralhad-joshi-maharashtra-cm-fadnavis-inaugurate-steel-mahakumbh20250919211944</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%A8%E0%A4%88-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-10-%E0%A4%95%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%95-%E0%A4%AE%E0%A4%82%E0%A4%9C%E0%A5%82%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%94%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B2-%E0%A4%8F%E0%A4%82-%E0%A4%AD-%E0%A4%B6-%E0%A4%AE-%E0%A4%B2/ar-AA1MeFbO</t>
+          <t>https://udayavani.com/national/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-419656?lang=en</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/mla-sanjay-khodke-met-cm-fadnavis-at-varsha-bungalow/</t>
+          <t>https://www.ptinews.com/detail/national/Only-eligible-applicants-will-receive-Kunbi-caste-certificates-Fadnavis/2925278</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.deshsewak.org/hindi/news/217831</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/metro-rail-and-railways-infrastructure/maharashtra-cm-fadnavis-inaugurates-new-amalner-beed-railway-line/78987</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/cm-devendra-fadnavis-played-a-game-by-ending-manoj-jaranges-fast-maratha-reservation-agitation-1381961.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114?ganesh-chaturthi-photos-breakingnews</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://bhasha.ptinews.com/detail/2909747</t>
+          <t>https://www.aninews.in/news/national/general-news/pm-modi-icon-of-fit-india-inspires-10-lakh-youth-to-join-largest-run-bjp-mp-tejasvi-surya20250921125145</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/job-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A8%E0%A5%87-1-08-%E0%A4%B2-%E0%A4%96-%E0%A4%95%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A5%87-mou-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%8F-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%B0-%E0%A4%95%E0%A4%B9-47-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%A8-%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%A6%E0%A4%B0%E0%A4%B5-%E0%A4%9C%E0%A5%87/ar-AA1MosNk?ocid=finance-verthp-feeds</t>
+          <t>https://www.aninews.in/news/national/general-news/delhi-cm-praises-pm-modi-for-gst-reforms-says-public-to-benefit-directly20250921223646</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hind-mazdoor-sabha-opposes-maharashtra-govt-rise-in-working-hours-decision-demand-for-roll-back-know-all/articleshow/123766205.cms</t>
+          <t>https://www.lokmattimes.com/maharashtra/rahul-gandhis-mind-has-been-stolen-maharashtra-cm-devendra-fadnavis-on-congress-mps-vote-theft-claims-a525/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/maharashtra-best-place-for-industries-and-investments-fadnavis/867304/</t>
+          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-cm-fadnavis-advertisement-created-a-ruckus-sanjay-raut-accused-him-of-spending-40-crore-1381167.html</t>
+          <t>https://www.socialnews.xyz/2025/09/16/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi/?nonamp=1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-may-see-maratha-obc-clash-how-own-people-increased-cm-fadnavis-tension-new-front-by-opposition-ruling-tie-up-201757394304554.html</t>
+          <t>https://www.lokmattimes.com/football/thank-you-for-gifting-me-signed-football-cm-fadnavis-confirms-lionel-messis-visit-to-maharashtra-on-december-14/amp/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/fadnavis-targeted-karnataka-government-over-st-marys-metro-station-said-this-is-an-insult-to-shivaji/867280/</t>
+          <t>https://newskarnataka.com/india/milind-soman-cm-fadnavis-flag-off-namo-yuva-run-in-mumbai/21092025</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/bengaluru-shivajinagar-metro-station-name-row-siddaramaiah-bjp-shivaji-maharaj-9610117.html</t>
+          <t>https://www.socialnews.xyz/2025/09/15/mumbai-acharya-devvrat-sworn-in-as-maharashtra-governor-gallery/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%94%E0%A4%B0-%E0%A4%A8-%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A5%8D%E0%A4%A5-%E0%A4%A8-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1MlBvB</t>
+          <t>https://www.lokmattimes.com/national/condition-about-obtaining-non-agricultural-land-license-should-be-removed-for-msmes-cm-fadnavis/amp/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/national-hindi-news/chief-minister-fadnavis-inaugurated-the-immersive-page-of-webdunia-hindi-and-marathi-125090900025_1.html</t>
+          <t>https://news.abplive.com/cities/maharashtra-mahayuti-mva-war-of-words-erupts-rahul-gandhi-vote-theft-congress-demands-devendra-fadnavis-resignation-1801046</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/vision-document-2047-will-serve-as-a-guiding-framework-for-key-policies-fadnavis/865810/</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/karnataka/bengaluru/bengaluru-shivajinagar-metro-to-named-st-mary-siddaramaiah-sparks-row-bjp-angry-maharashtra-cm-says-that-insult-shivaji-maharaj/articleshow/123830942.cms</t>
+          <t>https://m.sakshipost.com/amp/news/zero-tolerance-important-curb-drug-related-crimes-says-cm-fadnavis-454693</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/lalbaugcha-raja-immersed-during-lunar-eclipse-fishermen-committee-complaint-to-cm-devendra-fadnavis/articleshow/123770449.cms</t>
+          <t>https://www.punekarnews.in/cm-devendra-fadnavis-dcm-ajit-pawar-to-inaugurate-amalner-beed-new-railway-line-in-pune-division-on-september-17/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bjp-become-secular-conducting-vice-president-election-during-pitru-paksha-sanjay-raut-takes-a-jibe-19928195</t>
+          <t>https://www.punekarnews.in/bureaucratic-delays-stall-pune-khadki-cantonment-merger-despite-maharashtra-cms-nod/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/the-spread-of-hydro-ganja-is-dangerous/</t>
+          <t>https://www.sakshipost.com/news/maharashtra-cm-fadnavis-inaugurates-new-amalner-beed-railway-line-453629</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/devendra-fadnavis-hid-his-sins-else-ajit-pawar-would-have-been-in-jail-vijay-pandre-1757411989204</t>
+          <t>https://newsd.in/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://panchjanya.com/2025/09/13/435180/bharat/karnataka/karnataka-congress-government-is-changing-the-name-of-shivaji-nagar-metro-station-to-st-mary-devendra-fadnavis-opposed/</t>
+          <t>https://bhaskarlive.in/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/no-fake-person-will-be-included-in-obc-only-those-with-records-will-get-certificates-cm-fadnavis-reiterated-on-opposition-s-allegations-1757859745560</t>
+          <t>https://www.socialnews.xyz/2025/09/21/namo-yuva-run-in-mumbai-gallery/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/yavatmal/yavatmal-lack-of-basic-facilities-in-the-bandi-area-even-after-79-years-citizens-submitted-a-memorandum-to-chief-minister-devendra-fadnavis-1757321220265</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-shocked-bjp-leader-haresh-keni-joins-congress-panvel-municipal-election-maharashtra-politics/articleshow/124016475.cms</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://thevirallines.net/free-solar-electricity-to-every-farmer-by-2026</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-devendra-fadnavis-shares-story-of-first-meeting-with-pm-narendra-modi-ws-kl-9629275.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/maharashtra/instructions-to-submit-dpr-of-wainganga-nalganga-river-project-1757397931094</t>
+          <t>https://www.punjabkesari.com/india-news/maharashtra-cm-devendra-fadnavis-inaugurated-the-amalner-beed-railway-line-in-beed/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/tension-in-the-government-over-desired-posting-cms-order-shinde-faction-unhappy/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-big-attack-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava-bmc-election/articleshow/123926944.cms</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/bhujbals-warning-to-cm-reservation-gr-is-a-problem-for-the-government/</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-launched-various-csr-projects-of-hyundai-motor-india-ltd-in-mumbai-meeting-with-md-unsoo-kim-3013038</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/seventh-installment-of-namo-shetkari-yojana-distributed-rs-1892-61-crore-deposited-in-the-bank-accounts-of-91-lakh-65-thousand-156-farmers-of-the-state-1757413988181</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/others/maharashtra-cm-fadnavis-inaugurated-vtc-testing-lab-centre-announced-to-make-nashik-an-industrial-hub-4259072</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-devendra-fadnavis-compared-rahul-gandhi-to-hitlers-minister-saying-rahul-gandhis-hydrogen-bomb-is-a-dud/articleshow/123991146.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/i-am-in-touch-with-tourists-visiting-nepal-maharashtra-cm-fadnavis-4260634</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-shared-story-how-he-impressed-form-pm-narendra-modi-ahead-of-75th-birthday-rss-nagar-visit-know-all/articleshow/123913706.cms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/maharashtra-namo-shetkari-mahasamman-seventh-installment-devendra-fadnavis-farmers-1892-61-crores</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-solapur-air-service-will-begin-from-15th-october-2025-cm-devendra-fadnavis-on-flight-service-3016029/amp</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/politics/maharashtra-government-took-four-major-decisions-in-the-cabinet-meeting-2749874.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%97-%E0%A4%A8-%E0%A4%97-%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A4%B8-%E0%A4%A4%E0%A4%82%E0%A4%9C-%E0%A4%A4-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%90%E0%A4%B8-%E0%A4%89%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A6-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%A5/ar-AA1MJlsa</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%9C%E0%A5%80%E0%A4%A8%E0%A4%97%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%8B-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%B6%E0%A4%A8/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%95-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%AB-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%9D%E0%A4%9F%E0%A4%95/ar-AA1M5pB5?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/news-update/maharashtra-river-linking-project-cm-fadnavis-requests-central-funding/114609/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%95-%E0%A4%95%E0%A4%AE-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%8F-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1La6Vu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/cm-fadnavis-on-cp-radhakrishnan-win-opposition-failed/114761/</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-sharad-pawar-warn-devendra-fadnavis-over-farmers-suicide-said-look-what-happened-in-nepal-2025-09-16-1162916</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/siddaramaiah-asks-fadnavis-to-take-up-the-issue-of-naming-of-shivajinagar-metro-station-with-the-centre-3249584.html</t>
+          <t>https://www.msn.com/hi-in/news/other/devendra-fadnavis-%E0%A4%9C-%E0%A4%B8-%E0%A4%AD-%E0%A4%B7-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9A-%E0%A4%A8-%E0%A4%AA-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%B5%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%AB%E0%A4%9F%E0%A4%95-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC-%E0%A4%B2-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1JTdKS?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/raju-shetty-urges-gadkari-to-reduce-financial-burden-on-shaktipeeth-highway-4258724</t>
+          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/the-newly-appointed-governor-of-maharashtra-was-given-a-grand-welcome-at-the-raj-bhavan-and-was-given-a-guard-of-honour-acharya-devvrat-566579</t>
+          <t>https://www.lokmatnews.in/business/mumbai-financial-capital-chhatrapati-sambhajinagar-become-ev-electric-vehicle-capital-maharashtra-cm-devendra-fadnavis-said-14000-people-get-employment-latur-coach-factory-b507/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/ports-shipping/nashiks-transformation-into-a-port-led-growth-hub-insights-from-cm-fadnavis/123823527?utm_source=latest_news&amp;utm_medium=homepage</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-attacks-rahul-gandhi-accuses-him-of-being-urban-naxal-saying-his-brain-stolen/articleshow/123998386.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/cm-fadnavis-calls-maharashtra-indias-most-industry-friendly-state/</t>
+          <t>https://www.amarujala.com/india-news/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-hindi-news-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mysuru/dcm-bats-for-bhadra-development-slams-fadnavis-on-water-issue/amp_articleshow/123857186.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-fadnavis-announced-new-flight-between-solapur-to-mumbai-and-bengaluru-flight-from-15-october-know-all-details/articleshow/124016070.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-11-news-updates-live-updates-weather-update-mumbai-monsoon-18331419</t>
+          <t>https://www.livehindustan.com/maharashtra/sharad-pawar-calls-to-devendra-fadnavis-on-bjp-mla-gopichand-statement-201758271903306.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/cities/bengaluru/raise-shivajinagar-metro-station-renaming-issue-with-centre-1006273</t>
+          <t>https://www.msn.com/hi-in/news/other/devendra-fadnavis-%E0%A4%B5-%E0%A4%9F-%E0%A4%9A-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A6-%E0%A4%AE-%E0%A4%97-%E0%A4%9A-%E0%A4%B0-%E0%A4%B9-%E0%A4%97%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%81%E0%A4%B0-%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%AF-%E0%A4%A4-%E0%A4%96-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1MTRZn</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/obc-groups-plan-major-mumbai-protest-against-maratha-reservation-gr-23593602</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-baps-akshardham-temple-goyal-fadnavis-wish-mahant-swamiji-maharaj-on-92nd-birthday-9628582.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/elphinstone-bridge-closure-bridge-will-not-be-closed-until-written-assurance-from-cm-fadnavis-on-residents-rehabilitation-say-officials-23593544</t>
+          <t>https://www.amarujala.com/india-news/fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/opposition-could-not-save-their-own-votes-devendra-fadnavis-congratulates-radhakrishnan-on-winning-vice-presidential-election/</t>
+          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AA-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%A8-%E0%A4%97%E0%A4%B0-%E0%A4%95-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%AA%E0%A4%A4-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%96%E0%A4%AC%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%96-%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1DIcgm?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/vision-maharashtra-document-2047-our-guiding-principle-cm-fadnavis-449925</t>
+          <t>https://www.amarujala.com/video/india-news/rahul-gandhi-vote-theft-claim-cm-fond-of-rahul-gandhi-s-vote-theft-claims-gives-this-reply-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%86%E0%A4%A3-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%95-%E0%A4%A3%E0%A4%A4-%E0%A4%B9-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%B9-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/vi-AA1MtMSJ</t>
+          <t>https://www.msn.com/hi-in/news/other/nashik-kumbh-2027-%E0%A4%85%E0%A4%97%E0%A4%B2-%E0%A4%95%E0%A5%81%E0%A4%82%E0%A4%AD-%E0%A4%A8-%E0%A4%B8-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B2%E0%A4%97%E0%A5%87%E0%A4%97-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A5%9C-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AF-%E0%A4%97%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%B2%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97/ar-AA1Bu9g4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.bakharlive.com/maharashtra/devendra-fadnavis-and-shinde-ajit-pawar-clarified/</t>
+          <t>https://www.amarujala.com/entertainment/bollywood/maharashtra-cm-devendra-fadnavis-says-hindi-films-fail-to-depict-true-heroism-of-mumbai-police-2025-09-20?src=top-subnav</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/chartered-officers-in-d-class-municipalities-deputy-chief-minister-eknath-shinde-is-upset-with-this-decision-of-the-chief-minister-devendra-fadnavis/921168/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-mla-gopichand-padalkar-statement-sparked-uproar-in-maharashtra-devendra-fadnavis-calling-for-restraint/articleshow/124002748.cms</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/12/historic-mou-between-maharashtra-and-iowa-usa.html</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%B0-%E0%A4%AC-80-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A4%B2%E0%A5%87-%E0%A4%B8-%E0%A4%B2-%E0%A4%A6-%E0%A4%B8%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%A4%E0%A4%95-%E0%A4%AE%E0%A5%81%E0%A4%AB%E0%A5%8D%E0%A4%A4-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%AC-%E0%A4%9C%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%8F%E0%A4%B2-%E0%A4%A8/ar-AA1CPNKL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/devendra-fadnavis-reiterates-maratha-reservation-gr-legal-283884/</t>
+          <t>https://www.msn.com/hi-in/news/other/aditya-thackeray-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AE-%E0%A4%A1%E0%A4%BC-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%85%E0%A4%AC-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1IW0iz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/thackeray-brothers-meeting-cm-devendra-fadnavis-funny-reply/videoshow/123812966.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95-%E0%A4%9C%E0%A4%B5-%E0%A4%AC-%E0%A4%95%E0%A4%B9-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%95%E0%A5%87-%E0%A4%9C-%E0%A4%86%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%93%E0%A4%AC-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1MwFWu</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-one-sentence-reaction-after-shiv-sena-thackeray-faction-protests-over-india-pakistan-match/921462/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.bakharlive.com/maharashtra/devendra-fadnavis-targeted-among-the-12-maratha-chief-ministers/</t>
+          <t>https://www.patrika.com/mumbai-news/ncp-sharad-pawar-slams-devendra-fadnavis-government-claim-40-lakh-spent-on-cm-residence-19955838</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-read-out-the-list-saying-that-our-government-has-done-everything-for-the-obc-community/921468/</t>
+          <t>https://www.amarujala.com/india-news/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-hindi-news-2025-09-19?src=top-subnav</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-aadi-karmayogi-abhiyan-launched-in-yavatmal-with-devendra-fadnavis-inaugurating-335-crore-development-projects-for-tribal-welfare-1383634</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%AB-%E0%A4%B2%E0%A5%8D%E0%A4%AE-%E0%A4%9B-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%96%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1Al3WQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-mumbai-rain-best-co-operative-soc-election-live-maharashtra-update-political-rain-update-devendra-fadnavis-ajit-pawar-eknath-shinde-uddhav-thackeray-raj-thackeray-4/921353/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8%E0%A4%AC%E0%A5%82%E0%A4%A4-%E0%A4%A6%E0%A5%87%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%AD-%E0%A4%AD%E0%A5%8D%E0%A4%B0%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%B0%E0%A4%B9-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A4%97-%E0%A4%AF-%E0%A4%86%E0%A4%B0-%E0%A4%AA/ar-AA1KlkJI?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/cm-devendra-fadnavis-and-nitin-gadkari-meet-shrikant-jichkar-mother-in-nagpur-program/articleshow/123854763.cms</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/maharashtra-government-signs-mou-with-cambridge-university-press-and-assessment-india-to-improve-school-education-11676</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-slams-karnataka-congress-government-over-planning-of-rename-shivjainagar-metro-statation-as-sent-merij/articleshow/123828726.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97%E0%A4%AA%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B6-%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AB-%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%96%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%85%E0%A4%9F%E0%A4%95%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%A4%E0%A5%87%E0%A4%9C-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B2-%E0%A4%B0%E0%A4%B9-%E0%A4%B9%E0%A5%88/ar-AA1wZDM7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/chief-minister-devendra-fadnavis-41/</t>
+          <t>https://www.aajtak.in/india/news/story/sharad-pawar-ncp-sp-responded-to-bjp-devabhau-campaign-with-deva-tuch-saang-aid-ntc-rpti-2334011-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-slams-sharad-pawar-over-maratha-and-obc-reservation-statement/articleshow/123883048.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/fadnavis-on-congress-%E0%A4%B8%E0%A4%82%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%95-%E0%A4%A8%E0%A5%88%E0%A4%B0%E0%A5%87%E0%A4%9F-%E0%A4%B5-%E0%A4%A7%E0%A5%8D%E0%A4%B5%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%9D%E0%A5%82%E0%A4%A0-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%A6-%E0%A4%A8-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%9F-%E0%A4%95%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1txBPv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/minister-chhagan-bhujbal-and-cm-devendra-fadnavis-travel-together-in-same-plane/articleshow/123807391.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B2-%E0%A4%89%E0%A4%A1%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%B9-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A5%E0%A4%B2-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95-%E0%A4%A4%E0%A4%A8%E0%A5%87-%E0%A4%B9%E0%A4%9F-%E0%A4%8F-%E0%A4%97%E0%A4%8F/ar-AA1IstKE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/devendra-fadnavis-announces-whatsapp-services-citizens-283875/</t>
+          <t>https://www.mumbailive.com/hi/politics/fadnavis-slams-rahul-gandhi-over-election-allegations-calls-him-a-habitual-liar-90060</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/there-is-no-animosity-between-eknath-shinde-and-devendra-fadnavis-ajit-pawar/939011</t>
+          <t>https://hindi.webdunia.com/national-hindi-news/devendra-fadnavis-targeted-rahul-gandhi-125091900062_1.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/devendra-fadnavis-announces-in-nashik-that-maharashtra-will-soon-become-ev-hub/articleshow/123824796.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/police-recruitment-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%97%E0%A5%81%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A5%87-15000-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%A6-%E0%A4%AE%E0%A4%82%E0%A4%9C%E0%A5%82%E0%A4%B0/ar-AA1KnJ9O?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ncp-dhananjay-munde-letter-to-the-cm-devendra-fadnavis-demands-st-status-for-the-banjara-community/articleshow/123846090.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%85%E0%A4%AE%E0%A4%B0-%E0%A4%B5%E0%A4%A4-%E0%A4%B9%E0%A4%B5-%E0%A4%88-%E0%A4%85%E0%A4%A1%E0%A5%8D%E0%A4%A1%E0%A5%87-%E0%A4%95-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%98-%E0%A4%9F%E0%A4%A8/ar-AA1D2CP2?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/why-is-only-devendra-fadnavis-targeted-among-the-12-maratha-chief-ministers-of-maharashtra-questions-on-the-minds-of-maharashtra-on-the-banner-of-vaijapur-284041/</t>
+          <t>https://vocaltv.in/national/law-and-order-effective-implementation-cm-fadanviphp/cid17447208.htm</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/10/prepare-an-auto-system-model-for-students-to-get-scholarships-on-time-chief-minister-devendra-fadnavis-directs.html</t>
+          <t>https://www.livehindustan.com/maharashtra/obc-activists-show-black-flags-to-cm-devendra-fadnavis-attempt-self-immolation-in-front-of-deputy-cm-ajit-pawar-convoy-201758158508899.html</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/devendra-fadnavis-obc-reservation-statement-challenge-opponents-135919193.html</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%95%E0%A5%87-cm-devendra-fadnavis-%E0%A4%95-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-nep-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A3-%E0%A4%B2-%E0%A4%95-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%AF%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B9%E0%A5%88/ar-AA1BYWWq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/hingoli/news/bachchu-kadu-criticizes-devendra-fadnavis-ajit-pawar-government-135912072.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-directs-immediate-implementation-of-reforms-in-state-innovation-society/920428/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-s-politics-rises-due-to-rahul-s-claims-on-vote-theft-congress-says-fadnavis-should-resign-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-announce-process-to-benefits-of-government-services-and-schemes-on-whatsapp-1478023.html</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%9F-%E0%A4%9A-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%B8-%E0%A4%B0-%E0%A4%AF%E0%A4%B2-%E0%A4%B2-%E0%A4%AF%E0%A4%B0-%E0%A4%B9%E0%A5%88/ar-AA1L9M5X?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-mahayuti-rift-devendra-fadnavis-eknath-shinde-ajit-dada-lead-stable-maharashtra-alliance-amidst-discontent-rumors-unanimous-decisions-1383659</t>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-pm-modi-is-a-leader-who-prefers-simplicity-devendra-fadnavis-shared-a-special-video-news-hindi-1-753193-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-expressed-confidence-that-maharashtra-will-remain-at-the-forefront-in-providing-the-required-skilled-manpower-to-industries-abroad/920450/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/maharashtra-cm-devendra-fadnavis-signs-mous-with-tata-technologies-and-us-state-of-iowa/921194/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%B8%E0%A4%AE%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%89%E0%A4%A6-%E0%A4%B8-%E0%A4%A8-%E0%A4%B9%E0%A5%88-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1MzRC1</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-whatsapp-services-digital-devendra-fadnavis-135894490.html</t>
+          <t>https://www.amarujala.com/india-news/bjp-mla-s-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/aurangabad/news/devendra-fadnavis-maratha-reservation-banner-chhatrapati-sambhaji-nagar-135910399.html</t>
+          <t>https://hindi.theprint.in/india/chief-minister-fadnavis-should-resign-after-rahul-gandhis-revelation-of-vote-theft-in-maharashtra-sapkal/870326/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/vijay-wadettiwar-news-chhagan-bhujabal-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-cm-devendra-fadnavis-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%95-%E0%A4%A4%E0%A5%82%E0%A4%95-n18v/vi-AA1MlvQg?ocid=hpmsn</t>
+          <t>https://www.abplive.com/videos/news/maharashtra-cm-devendra-fadnavis-criticizes-bollywood-for-inaccurate-mumbai-police-portrayal-at-indian-police-foundation-2025-event-3016051/amp</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-cm-devendra-fadnavis-dycm-eknath-shinde-rift-ias-officer-appointments-135908162.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%B8%E0%A5%81%E0%A4%A7-%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%B5%E0%A5%83%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%95-%E0%A4%97%E0%A4%A4-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1N0XA9?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sanjay-raut-slams-cm-devendra-fadnavis-over-shiv-sena-ubt-cross-voting-accusation-in-vice-president-election/articleshow/123800398.cms</t>
+          <t>https://rajneetiguru.com/%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A5%80-%E0%A4%86%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%BF%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%9F%E0%A4%BF%E0%A4%AA%E0%A5%8D%E0%A4%AA/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/vice-president-election-result-cm-fadnavis-slams-opposition-could-not-save-their-own-votes-bjp-nda-283629/amp/</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/maharashtra-govt-issued-kunbi-certificates-in-five-marathwada-districts-on-liberation-day/articleshow/123961774.cms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chief-minister-fadnavis-gave-clarification-on-gr-of-maratha-reservation-slams-obc-leaders/articleshow/123829995.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/opinion-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A0%E0%A4%B9-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%97-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%B5-%E0%A4%B0-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%9B-%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95-%E0%A4%B9-%E0%A4%97-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%B0/ar-AA1w1TqU?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/mla-milind-narvekar-wrote-a-reminder-letter-to-chief-minister-devendra-fadnavis-regarding-what-happened-to-the-hospital-on-the-dumping-ground-in-mulund/921323/</t>
+          <t>https://mandalnews.com/amravati/banjara-community-should-be-included-in-st-category/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maratha-quota-row-cm-fadnavis-and-chhagan-bhujbal-travel-to-nashik-together-amidst-reservation-dispute-and-bhujbal-s-legal-threat-1383057</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/devendra-fadnavis-receives-phoenix-award-speech-135872067.html</t>
+          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maratha-and-obc-reservation-protest-congress-to-organize-marches-on-october-10-and-20-invites-ncp-chhagan-bhujbal/articleshow/123881511.cms</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/farmers-should-paid-some-money-uddhav-thakre.php</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-slams-india-alliance-after-cp-radhakrishnan-elected-as-new-vice-president-of-india/videoshow/123801905.cms</t>
+          <t>https://www.aajtak.in/amp/programmes/mumbai-metro/video/meena-tai-thackeray-memorial-vandalism-bmc-elections-frvd-2335927-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-comment-on-maratha-reservation-gr-regarding-kunbi-certificate-and-obc-leader-morcha-1477826.html</t>
+          <t>https://www.hindisaamana.com/the-battle-for-seats-in-the-mahagathbandhan-intensifies-vidarbha-is-not-the-fiefdom-of-bjp-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/supriya-sule-devendra-fadnavis-irrigation-scam-raakh-statement-maharashtra-135876550.html</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/reserve-bank-of-india-buys-land-in-nariman-point-for-rs-3472-crore-283849/</t>
+          <t>https://www.agniban.com/protests-erupt-in-maharashtra-over-reservation-issue-obc-activists-show-black-flags-to-fadnavis-attempt-suicide/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-eknath-shinde-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%85%E0%A4%B8%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A%E0%A4%82-%E0%A4%A8-%E0%A4%B5-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2%E0%A4%82/ar-AA1MsMVj</t>
+          <t>https://www.hindisaamana.com/former-mla-exposes-fadnaviss-transparent-work/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/ajit-pawar-explanation-on-ips-anjana-krishna-viral-video-call-135909921.html</t>
+          <t>https://www.prabhasakshi.com/national/ruckus-over-gen-z-statement-fadnavis-says-rahul-gandhi-given-evidence-of-urban-naxal-thinking</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/593-new-colleges-in-maharashtra-major-announcement-by-chief-minister-devendra-fadnavis/amp_articleshow/123815581.cms</t>
+          <t>https://www.bhaskarhindi.com/state/maharashtra/maharashtra-news-fadnavis-government-bjp-government-government-vehicles-cm-vehicles-governor-vehicles-gst-vehicle-tax-registration-fee-1188430</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/did-i-make-a-mistake-kishor-kadams-emotional-appeal-to-the-chief-minister-devendra-fadnavis-ws-l-1479941.html</t>
+          <t>https://lalluram.com/sharad-pawar-reminded-cm-fadnavis-of-rajdharma-appealed-for-complete-loan-waiver-of-farmers-warned-and-said-the-situation-should-not-become-like-nepal/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chhagan-bhujbal-wrote-letter-to-cm-devendra-fadanvis-over-maratha-reservation-gr-1476376.html</t>
+          <t>https://www.hindisaamana.com/mahayuti-government-trapped-in-the-maze-of-reservation/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/explainer-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%86%E0%A4%A3-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A4%E0%A4%A3-%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AD-%E0%A4%88-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%B5-%E0%A4%9A-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%9A-%E0%A4%B2%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%A4%E0%A4%B0-%E0%A4%95-%E0%A4%AF/ar-AA1MsMR7</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-expressed-gratitude-after-prime-minister-modis-speech-4277895</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ncp-sharad-pawar-campaign-deva-tuch-sang-against-bjp-devabhau-campaign-1479963.html</t>
+          <t>https://www.kisantak.in/news/trending/story/sharad-pawar-led-an-akrosh-morcha-in-nashik-demands-complete-loan-waiver-for-farmers-swm-1278008-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%A7%E0%A4%A8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%A1%E0%A5%87%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%95-%E0%A4%82%E0%A4%A1-%E0%A4%B9%E0%A5%88%E0%A4%A6%E0%A4%B0-%E0%A4%AC-%E0%A4%A6-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F-%E0%A4%AF%E0%A4%B0%E0%A4%AE%E0%A4%A7-%E0%A4%B2-%E0%A4%A4-%E0%A4%A8-%E0%A4%82%E0%A4%A6-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%A8%E0%A4%B5-%E0%A4%AE-%E0%A4%97%E0%A4%A3/ar-AA1MoXUd</t>
+          <t>https://jantaserishta.com/local/maharashtra/fadnavis-praised-pm-modis-working-style-4271099</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%86%E0%A4%AC-%E0%A4%B9%E0%A5%87-%E0%A4%87%E0%A4%AE-%E0%A4%A8%E0%A4%A6-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4%E0%A5%87-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%AB-%E0%A4%AF%E0%A4%A8%E0%A4%B2-%E0%A4%9A-%E0%A4%95%E0%A4%B6-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B2-%E0%A4%B5%E0%A4%B2/ar-AA1tfEKD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ibc24.in/business/chhatrapati-sambhajinagar-will-become-the-electric-vehicle-capital-of-the-country-fadnavis-3255721.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-government-vows-to-restore-27-political-quota-and-prevent-fake-beneficiaries-devendra-fadnavis-assures-obc-community-1384071</t>
+          <t>https://jantaserishta.com/others/rahul-gandhis-hydrogen-bomb-turned-out-to-be-a-dud-cm-fadnavis-4272872</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/cm-fadnavis-on-maratha-reservation-and-obc-reservation-in-mumbai/920662/</t>
+          <t>https://navyugsandesh.com/devendra-fadnavis-took-a-dig-at-rahul-gandhis-hydrogen-bomb-statement/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/mahayuti-maharashtra-co-gaurdian-minister-for-3-districts/920698/</t>
+          <t>https://indiagroundreport.com/mumbai-fadnavis-government-took-8-important-decisions-including-doubling-the-allowance-of-students/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sadabhau-khot-%E0%A4%86%E0%A4%AE%E0%A4%A6-%E0%A4%B0%E0%A4%95-%E0%A4%9A%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A1-%E0%A4%9F-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%A4-%E0%A4%A8-%E0%A4%96-%E0%A4%A4-%E0%A4%B9%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-n18s/vi-AA1Mvyst</t>
+          <t>https://indiagroundreport.com/maharashtra-should-become-a-best-model-for-new-industries/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/jaykumar-gore-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%82%E0%A4%A8-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8-%E0%A4%9C%E0%A4%AF%E0%A4%95%E0%A5%81%E0%A4%AE-%E0%A4%B0-%E0%A4%97-%E0%A4%B0%E0%A5%87/ar-AA1MjrmR</t>
+          <t>https://www.devdiscourse.com/article/politics/3633329-fadnavis-accuses-rahul-gandhi-of-urban-maoist-rhetoric?amp</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/8/submit-the-wainganga-nalganga-river-linking-project-report-by-october-15-chief-minister-devendra-fadnavis-inst.html</t>
+          <t>https://www.ptinews.com/story/national/using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level-fadnavis/2934307</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-ministry-meeting-decision-cm-devendra-fadnavis-relief-to-farmers/articleshow/123781255.cms</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharastra-cm-fadnavis-pushes-for-faster-industrial-approvals-ai-based-reforms-to-boost-investments-23594849</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%AD-%E0%A4%8A%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%A1%E0%A4%A8-%E0%A4%B5-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%90%E0%A4%B5%E0%A4%9C-%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%85%E0%A4%B8%E0%A4%A4%E0%A4%82-%E0%A4%A4%E0%A4%B0-%E0%A4%B8%E0%A4%A6-%E0%A4%AD-%E0%A4%8A-%E0%A4%96-%E0%A4%A4-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%82%E0%A4%A8-%E0%A4%89%E0%A4%A7-%E0%A4%A3/ar-AA1MtqCF</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3631374-controversy-surrounds-delayed-unveiling-of-swami-ramanand-tirtha-statue?amp</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/chhaggan-bhujbal-is-a-headache-for-the-government-if-he-is-unhappy-he-should-go-to-himalayas-mano-j-jarange-again-targets-bhujbal-283718/amp/</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mlas-remarks-about-ncp-sp-leader-23594821</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/only-those-with-kunbi-records-will-get-the-certificate-so-obcs-need-not-worry-says-cm-fadnavis/videoshow/123882300.cms</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/rahul-gandhi-speaks-like-an-urban-maoist-says-maharashtra-cm-fadnavis-on-congress-leaders-gen-z-post-23594827</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/vijay-pandhare-targets-ajit-pawar-devendra-fadnavis-and-narendra-modi-in-water-resources-irrigation-scam-case/919463/</t>
+          <t>https://www.ptinews.com/editor-detail/reduce-number-of-permissions-to-set-up-industries--speed-up-approval-time--fadnavis-to-officials/2930550</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-rejected-the-statement-of-manoj-jarange-patil-all-marathas-in-marathwada-will-get-kunbi-certificates-1475786.html</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A4%B9-%E0%A4%A8%E0%A4%97%E0%A4%B0%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%82%E0%A4%9A-%E0%A4%97-%E0%A4%AA-%E0%A4%B3%E0%A4%95-%E0%A4%B2-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B2%E0%A4%B5-%E0%A4%9F%E0%A4%B0/ar-AA1KGpcL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/editor-detail/Maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop-Fadnavis/2927696</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-govt-rs-22-crore-will-be-spent-for-sugarcane-workers-survey-work/articleshow/123880627.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/obcs-disrupt-cm-s-speech-holds-huge-rally-in-hingoli-101758137116445-amp.html</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/chief-minister-devendra-fadnavis-in-yavatmal-today/</t>
+          <t>https://orissadiary.com/aiifa-steelex-2025-maharashtra-chief-minister-devendra-fadnavis-and-union-minister-pralhad-joshi-inaugurate-the-steel-mahakumbh/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/there-will-be-a-radical-change-in-the-lives-of-tribals-devendra-fadnavis/</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bacchu-kadu-bosss-power-in-the-cabinet-devendra-fadnavis-is-the-big-boss/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114?news-breakingnews</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/state-government-help-loss-affected-farmers-cm-devendra-fadnavis/</t>
+          <t>https://www.devdiscourse.com/article/politics/3630398-bjps-enduring-commitment-fadnavis-recollects-2017-political-maneuverings-in-mumbai?amp</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://ebatmidar.com/%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5%E0%A4%BF%E0%A4%95-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%97%E0%A4%A4%E0%A5%80%E0%A4%A4/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628615-maharashtra-govt-will-create-corpus-fund-to-cover-treatments-costing-over-rs-5-lakh-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/brother-upset-by-cm-fadnavis-order-it-sparked-discussions-what-exactly-happened/</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/namo-yuva-run-held-nationwide-to-mark-pm-modi-s-75th-birthday-23595077</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/there-is-no-blanket-reservation-for-the-maratha-community/</t>
+          <t>https://www.aninews.in/news/national/general-news/acharya-devvrat-sworn-in-as-new-governor-of-maharashtra-succeeding-cp-radhakrishnan20250915124042</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/office-bearers-opposition-parties-cm-devendra-fadnavis/</t>
+          <t>https://www.punjabnewsexpress.com/health/news/maha-govt-approves-corpus-fund-for-health-treatment-of-over-rs-5-lakh-says-cm-fadnavis-297657</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawar-group-responds-to-devabhau-with-deva-tuch-sang-banners-are-displayed-in-yellow/</t>
+          <t>https://www.latestly.com/quickly/agency-news/acharya-devvrat-sworn-in-as-governor-of-maharashtra-in-presence-of-cm-devendra-fadnavis-7112162.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/there-will-be-a-radical-change-in-the-lives-of-tribals-in-the-next-3-years-cm-devendra-fadnavis-expressed-confidence/</t>
+          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cm-devendra-fadnavis-backs-mpsc-conducted-exams-to-tackle-recruitment-irregularities-commission-delegation-visits-kpsc-for-study-article-152799985</t>
+          <t>https://www.sakshipost.com/news/maharashtra-play-major-role-pms-mission-green-steel-cm-fadnavis-454325</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/but-i-wouldnt-be-surprised-sanjay-raut/</t>
+          <t>https://thenewsmill.com/2025/09/milind-soman-flags-off-namo-yuva-run-in-mumbai-says-its-pm-modis-dream-to-make-india-drug-free/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-governments-make-and-break-on-reservation-continues-vijay-vadettiwar-hits-out-at-fadnavis/</t>
+          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-online-system-based-on-ai-developed-for-obtaining-building-permits-required-by-industries-995520.html</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/many-times-people-thought-i-was-turning-into-ashes-and-what-did-chief-minister-devendra-fadnavis-actually-say/</t>
+          <t>https://zeenews.india.com/marathi/video/cm-devendra-fadnavis-media-brief/941116</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/chief-ministers-initiative-for-malaria-free-gadchiroli/</t>
+          <t>https://marathi.abplive.com/photo-gallery/sports/lionel-messi-gives-cm-devendra-fadnavis-a-special-gift-of-signed-footbal-will-also-come-to-mumbai-for-a-visit-1385826</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/proposal-to-rename-shivajinagar-station-in-karnataka-as-st-mary-fadnavis-said-this-is-an-insult-to-chhatrapati-shivaji-maharaj-congress-has-been-against-since-nehrus-time/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/cm-devendra-fadnavis-reaction-on-maratha-reservation-kunbi-certificates/articleshow/123993122.cms</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/there-have</t>
+          <t>https://marathi.indiatimes.com/maharashtra/chandrapur/shiv-sena-ubt-protest-in-chandrapur-over-place-of-banner-of-cm-devendra-fadnavis-and-chhatrapati-shivaji-maharaj/articleshow/124000637.cms</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/phoenix-award-cm-devendra-fadnavis-marathi-journalists/</t>
+          <t>https://thefocusindia.com/maharashtra-news/devendra-fadnavis-preached-gopichand-padalkar-over-his-controversial-statement-284593/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://ebatmidar.com/%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%B8-%E0%A5%A8%E0%A5%A6%E0%A5%A9%E0%A5%A6-%E0%A4%89%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%B5/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-talk-on-sharad-pawar-phone-call-about-gopchand-padalkar-statement/articleshow/123994142.cms</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-submit-report-on-wainganga-nalganga-river-linking-project-chief-minister-fadnavis-gave-instructions/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/gopichand-padalkar-clarification-on-his-statement-about-jayant-patil-after-receiving-a-call-from-cm-devendra-fadnavis/articleshow/123994231.cms</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/rauts-direct-challenge-to-cm-fadnavis-before-the-march-in-nashik-said-the-chief-minister-should-talk-to-the-opposition-leaders/</t>
+          <t>https://www.saamana.com/devendra-fadnavis-dreaming-of-becoming-prime-minister-says-harshwardhan-sapkal/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/sadabhau-khot-praised-devendra-fadnavis-in-sangali/</t>
+          <t>https://marathi.abplive.com/news/devendra-fadnavis-speech-at-chhatrapati-sambhajinagar-obc-activists-slogans-during-cm-speech-at-marathwada-mukti-sangram-din-program-marathi-news-1384714</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-rain-alert-beed-crime-ex-sarpanch-govind-barge-death-maratha-reservation-mumbai-pune-nagpur-breaking-news-pmw-88-5364723/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-advice-to-gopichand-padalkar-after-receiving-a-call-from-sharad-pawar-for-making-objectionable-comments-on-jayant-patil/923124/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%85%E0%A4%A8%E0%A5%87%E0%A4%95-%E0%A4%82%E0%A4%A8-%E0%A4%B5-%E0%A4%9F%E0%A4%B2%E0%A4%82-%E0%A4%AE-%E0%A4%9D-%E0%A4%B0-%E0%A4%96-%E0%A4%B9-%E0%A4%88%E0%A4%B2-%E0%A4%AA%E0%A4%A3-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A5%87%E0%A4%95%E0%A4%B5%E0%A5%87%E0%A4%B3-%E0%A4%AE-%E0%A4%AD%E0%A4%B0-%E0%A4%B0-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2%E0%A5%87%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1M9yXU</t>
+          <t>https://marathi.ndtv.com/cities/pm-modi-birthday-cm-fadnavis-reminisces-share-experienc-of-first-meeting-with-pm-modi-9291188</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/pune-news-%E0%A4%B6%E0%A4%A8-%E0%A4%B5-%E0%A4%B0%E0%A4%B5-%E0%A4%A1-%E0%A4%A4%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%B0%E0%A4%97%E0%A5%87%E0%A4%9F%E0%A4%A6%E0%A4%B0%E0%A4%AE%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%A6-%E0%A4%A8-%E0%A4%AD%E0%A5%81%E0%A4%AF-%E0%A4%B0-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%B5-%E0%A4%B9%E0%A4%A4%E0%A5%82%E0%A4%95-%E0%A4%95-%E0%A4%82%E0%A4%A1-%E0%A4%95%E0%A4%AE-%E0%A4%B9-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%AE%E0%A4%A6%E0%A4%A4-%E0%A4%95%E0%A4%B8-%E0%A4%95%E0%A5%81%E0%A4%A0%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97/ar-AA1MasBx?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/entrepreneurship-investment-agreement-worth-rs-1-lakh-9-thousand-crores-in-the-state/</t>
+          <t>https://news18marathi.com/maharashtra/manoj-jarange-admire-maharashtra-cm-devendra-fadnavis-after-maratha-reservation-protest-1481999.html</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ajit-pawar-dysp-krishna-anjana-video-viral-case-cm-devendra-fadnavis-unhappy-on-ajit-pawar-1476220.html</t>
+          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-directed-that-guidelines-should-be-issued-by-amending-the-criteria-of-the-solar-agricultural-pump-scheme-as-per-the-demands-of-the-farmers-local18-1483770.html</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178401/</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%A7%E0%A4%A1-%E0%A4%95%E0%A5%87%E0%A4%AC-%E0%A4%9C-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MDGd1</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178159/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/21/mumbaikars-run-towards-a-drug-free-india-namo-yuva-run-receives-overwhelming-response-will-intoxicate-our-yout.html</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/solapur-dysp-anjana-krishna-phone-case-chief-minister-devendra-fadnavis-angry-with-ajit-pawar/articleshow/123787842.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ncp-pune-city-president-prashant-jagtap-criticizes-bjp-mla-gopichand-padalkar/articleshow/123990567.cms</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-lashes-out-after-sharad-pawars-statement-regarding-reservation/921479/</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/television-news/devendra-fadnavis-watch-maharashtrachi-hasya-jatra-says-samir-choughule-in-mhj-unplugged/articleshow/123995979.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/devendra-fadnavis-banner-vaijapur-maharashtra-has-had-12-maratha-chief-ministers-so-for-maratha-reservation-manoj-jarange-patil-1383748/amp/amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/navi-mumbai/bjp-leader-haresh-keni-joins-congress-shocks-devendra-fadnavis-prashant-thakur-ahead-of-panvel-municipal-election/articleshow/124013605.cms</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/complaint-against-lalbaugcha-raja-mandal-by-fishermen-organization-calls-for-action-to-cm-devendra-fadnavis/articleshow/123768400.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-nashik-journalist-assault-cm-devendra-fadnavis-orders-strict-action-case-filing-process-initiated-against-assailants-1385488/amp</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178050/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-kamboj-allegations-sakkale-accuses-devendra-fadnavis-of-pm-ambition-empowering-mohit-kamboj-and-giving-mumbai-to-adani-1385640</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-led-maharashtra-goverment-cabinet-meeting-4-big-decisions-bhayandar-akola-chhatrapati-sambhajinagar-1476231.html</t>
+          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-inspects-nashik-and-surrounding-areas-in-the-backdrop-of-kumbh-mela-gives-important-instructions-local18-1483785.html</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/178405/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-reaction-on-rahul-gandhi-allegations-bogus-voting-in-chandrapur-rajura-1483022.html</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178479/</t>
+          <t>https://www.saamana.com/harshwardhan-sapkal-accuses-maharashtra-cm-devendra-fadnavis-of-election-fraud-calls-him-thief-cm-during-press-conference/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/obc-leaders-should-read-the-maratha-reservation-gr-carefully-no-injustice-to-obcs-cm-devendra-fadnavis-clarification-maharashtra-news-mhs25091105073</t>
+          <t>https://www.mymahanagar.com/maharashtra/farmer-scheme-cm-devendra-fadnavis-instructions-to-change-the-criteria-of-solar-agricultural-pump-scheme/923274/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/anjali-damania-shares-devendra-fadnavis-narendra-modi-video-about-ajit-pawar-pmw-88-5367477/lite/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/beed-news-chief-minister-devendra-fadnavis-and-deputy-chief-minister-ajit-pawar-visit-beed-dangerous-electrical-generator-covered-with-cloth-in-beed-1384811</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-news-live-%E0%A4%AE%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%A3-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%A4-%E0%A4%B8%E0%A5%81%E0%A4%A8-%E0%A4%B5%E0%A4%A3/ar-AA1MoyII</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/devendra-fadnavis-assures-on-hyderabad-liberation-day-marathwada-water-shortage-will-be-resolved/articleshow/123963714.cms</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/cm-devendra-fadnavis-says-maharashtra-best-for-investment-policies-for-14-sectors-announce-soon-zws-70-5366545/lite/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/devendra-fadnavis-is-messiah-of-obc-community-praises-minister-chhagan-bhujbal/articleshow/123987624.cms</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/congress-leaders-meet-chief-minister-devendra-fadnavis-283595/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AA-%E0%A4%9A%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A6%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%87-%E0%A4%8F%E0%A4%95-%E0%A4%A4%E0%A4%B0%E0%A5%82%E0%A4%A3/ar-AA1MSJPR</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/593-new-colleges-in-maharashtra-major-announcement-by-chief-minister-devendra-fadnavis/articleshow/123815581.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178345/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/congress-state-president-harshvardhan-sapkal-criticize-devendra-fadnavis-rss-narendra-modi/articleshow/124023628.cms</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-banner-in-kolhapur-%E0%A4%A6%E0%A5%88%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%AE-%E0%A4%A8%E0%A4%A4%E0%A4%B3-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%86%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%A4%E0%A4%B9-%E0%A4%A8-%E0%A4%A8-%E0%A4%B5-%E0%A4%AB%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%B8%E0%A4%B5%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%AD-%E0%A4%8A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%9F%E0%A4%B2%E0%A5%87/ar-AA1M5aoo</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bacchu-kadu-criticizes-on-prime-minister-narendra-modi-and-chief-minister-devendra-fadnavis-on-agriculture-issue-1385079</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/uttar-maharashtra/nashik/onion-prices-fall-nafed-nccf-buffer-stock-farmers-loss-consumers-benefit-nmk01</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-at-bjp-vijay-sankalp-melava/videoshow/123937912.cms</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%9A-%E0%A4%AE-%E0%A4%A5-%E0%A4%95%E0%A4%B6-%E0%A4%B8-%E0%A4%A0-%E0%A4%AD%E0%A4%A1%E0%A4%95%E0%A4%B5%E0%A4%A4-%E0%A4%96-%E0%A4%A4-%E0%A4%82%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%9C%E0%A4%AC%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A4%B5-%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%B2%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%89%E0%A4%AA%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%B5%E0%A4%B0-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%A8-%E0%A4%B9-%E0%A4%95/ar-AA1MtEY9</t>
+          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/mumbai/mumbai-infrastructure-news-devendra-fadnavis-government-clears-23487-cr-metro-line-11-project-sets-ticket-fare-structure-know-details-route-map-station-list-distance/938866/amp</t>
+          <t>http://marathi.factcrescendo.com/old-altered-video-viral-as-cm-fadnavis-did-not-believe-in-indian-constitution-democracy/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chief-minister-fadnavis-gave-clarification-on-gr-of-maratha-reservation-slams-obc-leaders/amp_articleshow/123829995.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/nana-patole-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE-%E0%A4%9D%E0%A5%87-%E0%A4%A6-%E0%A4%A8%E0%A4%9A-%E0%A4%AE-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A4%9C%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%A6%E0%A5%81%E0%A4%B8%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%A8-%E0%A4%A8-%E0%A4%AA%E0%A4%9F-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%B6%E0%A5%8D%E0%A4%95-%E0%A4%B2-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%AA%E0%A4%A3/ar-AA1sxB7K?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/devendra-fadnavis-recounts-history-congress-govt-changed-name-of-shivaji-metro-station-name-change-it-is-a-tradition-of-insulting-shivaji-maharaj-from-jawharlal-nehru-scj-81-5366379/lite/</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-cabinet-meeting-decision-for-farmers-electricity-bill-to-irrigation-check-here-details-1476261.html</t>
+          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-slam-gopichand-padalkar-over-his-controversial-statement-on-jayant-patil-special-report-1483793.html</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/clashes-between-devendra-fadnavis-amd-eknath-shinde-on-regarding-the-appointment-of-chartered-officers-in-municipalities/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-government-vows-to-restore-27-political-quota-and-prevent-fake-beneficiaries-devendra-fadnavis-assures-obc-community-1384071/amp</t>
+          <t>https://prahaar.in/2025/09/18/brand-vs-brandy-war-of-words-between-fadnavis-thackeray-faction-politics-heats-up/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B9-%E0%A4%AF-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B2%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9C-%E0%A4%98%E0%A4%A1-%E0%A4%AE-%E0%A4%A1-%E0%A4%9B%E0%A4%97%E0%A4%A8-%E0%A4%AD%E0%A5%81%E0%A4%9C%E0%A4%AC%E0%A4%B3-%E0%A4%86%E0%A4%A3-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5-%E0%A4%AE-%E0%A4%A8-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B8/ar-AA1Mgm5P</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%A6-%E0%A4%A8-%E0%A4%AE-%E0%A4%A0%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%86%E0%A4%A3%E0%A4%96-%E0%A4%A6-%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%A5-%E0%A4%A8%E0%A4%95%E0%A5%87/ar-AA1KW2te?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/9/once-again-the-corruption-of-officials-in-the-district-collectors-office-has-been-exposed-in-nashik.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-claim-that-milind-narvekar-phone-call-him-and-said-uddhav-thackeray-was-upset/articleshow/123927047.cms</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/7th-installment-of-namo-shetkari-yojana-released-in-maharashtra</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava/articleshow/123926617.cms</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maratha-obc-quota-cm-fadnavis-assures-obcs-says-only-those-with-kunbi-records-will-get-certificates-announces-80-professor-recruitment-soon-1384046/amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/vice-president-election-shiv-sena-ubt-mps-might-vote-for-nda-candidate-as-eknath-shinde-works-on-operation-tiger/articleshow/123785590.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-slams-uddhav-and-raj-thackeray-over-thackeray-brand/articleshow/123927266.cms</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/chief-minister-devendra-fadnavis-divided-the-powers-of-the-guardian-minister-125091300033_1.html</t>
+          <t>https://news18marathi.com/maharashtra/manoj-jarange-patil-warning-cm-devendra-fadanvis-regarding-kunbi-certificate-1484509.html</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/chief-minister-devendra-fadnavis-inaugurates-development-works-worth-rs-335-crore-in-yavatmal-125091400010_1.html</t>
+          <t>https://news18marathi.com/agriculture/what-is-the-new-decision-of-the-state-government-regarding-making-agricultural-land-na-1484003.html</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://maharashtramirror.com/mumbai-local-train-news-megablock-on-harbour-line-from-midnight-today-local-services-closed-for-14-30-hours/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-devendra-fadnavis-ek-1384548/amp</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Chief-Minister-Devendra-Fadnavis-big-announcement-on-professor-recruitment</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-political-tensions-sharad-pawar-calls-cm-devendra-fadnavis-over-bjp-mla-gopichand-padalkar-s-controversial-remarks-against-jayant-patil-in-maharashtra-1385192/amp</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/maharashtra-iowa-usa-partnership-will-open-new-doors-of-cooperation-in-various-sectors-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AC-%E0%A4%A1%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A7%E0%A4%A8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%A1%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%85%E0%A4%B8-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%96-%E0%A4%95-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%B8%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A4%E0%A5%87%E0%A4%AF-%E0%A4%A4%E0%A5%81%E0%A4%AB-%E0%A4%A8-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A/ar-AA1MJiC2</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/maharashtra-will-remain-at-the-forefront-in-providing-the-required-skilled-manpower-to-industries-abroad-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.mumbailive.com/amp/mr/politics/mumbai-congress-slams-fadnavis-for-'disrespecting'-shivaji-maharaj-in-billboard-row-90046</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cm-devendra-fadnavis-backs-mpsc-conducted-exams-to-tackle-recruitment-irregularities-commission-delegation-visits-kpsc-for-study-article-152799985/amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sharad-pawar-called-cm-devendra-fadnavis-about-gopichand-padalkar-controversial-statement-on-jayant-patil-in-sangli/articleshow/123992055.cms</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/maharashtra-cm-devendra-fadnavis-signs-mous-with-tata-technologies-and-us-state-of-iowa/vi-AA1MsyFp</t>
+          <t>https://www.nagpurtoday.in/modi-is-the-biggest-brand-in-the-world-chief-minister-fadnavis-statement/09171621</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/benefits-of-schemes-must-be-part-of-right-to-services-act-fadnavis/articleshow/123833973.cms</t>
+          <t>https://www.navarashtra.com/maharashtra/mahayuti-has-no-right-to-remain-in-power-fadnavis-should-immediately-give-rajnima-harshvardhan-sapkal-demands-994246.html</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/nashik-emerging-as-junction-for-port-led-development-cm/articleshow/123815800.cms</t>
+          <t>https://thefocusindia.com/maharashtra-news/cm-fadnavis-rebukes-padalkar-says-need-to-be-careful-while-aggressive-284632/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/drop-or-tweak-gr-on-obc-quota-says-chhagan-bhujbal/articleshow/123797714.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-for-giving-30-sara-projects-to-mohit-kamboj/921930/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/chhagan-bhujbal-takes-on-govt-over-maratha-reservation-benefits/amp_articleshow/123857694.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-chagan-bhujbal-sharad-pawar-obc-reservation-rain-update-friday-19-september-2025-1495763.html</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/amid-obc-unrest-bhujbal-tells-fadnavis-to-revisit-maratha-quota-gr-101757444768578.html</t>
+          <t>https://marathi.abplive.com/news/nagpur/ajit-pawar-advise-to-bjp-mla-gopichand-padalkar-on-jayant-patil-statement-maharashtra-politics-marathi-news-1385092</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3625905-naming-controversy-shivajinagar-metro-station-sparks-political-debate</t>
+          <t>https://news18marathi.com/mumbai/maharastra-cabinate-meeting-inside-story-ajit-pawar-makes-laughter-in-front-of-devendra-fadanvis-latest-marathi-news-1481676.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-fadnavis-defends-obc-reservation-policy-says-no-threat-to-communitys-rights/amp_articleshow/123886921.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/only-ias-officers-to-head-municipal-corporations-mandates-cm-101757530879984-amp.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/nashik-nationalist-party-sharad-pawar-group-aakrosh-morcha-mla-rohit-pawar-criticizes-chief-minister-devendra-fadnavis/articleshow/123919393.cms</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/rlys-announces-367-spl-services-for-ganpati-268-new-ac-trains/ar-AA1KOos6?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-prime-minister-narendra-modi-birthday-chhagan-bhujbal-obc-reservation-rain-alert-wednesday-17-september-2025-1494134.html</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://tennews.in/lives-of-tribals-will-undergo-radical-transformation-in-next-3-years-maha-cm-fadnavis/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/india-has-the-potential-to-become-a-global-leader-in-the-field-of-gems-and-jewellery-chief-minister-devendra-f.html</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/elphinstone-bridge-closure-bridge-will-not-be-closed-until-written-assurance-from-cm-fadnavis-on-residents-rehabilitation-say-officials-23593544</t>
+          <t>https://marathi.indiatimes.com/e-paper/pedeko-to-implement-dpar-on-intense-traffic-routes-will-be-presented-for-approval-to-the-chief-minister/articleshow/123971055.cms</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/maharashtra-tata-technologies-ink-rs-115-cr-pact-for-skill-hub-in-ramtek-571355</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%B5%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%AE%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF/ar-AA1uC6bt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/maharashtra-signs-mou-with-iowa-to-boost-agriculture-technology20250912161419-66621/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%B5-%E0%A4%B0-%E0%A4%A7-%E0%A4%A4-%E0%A4%A6-%E0%A4%A8-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87-%E0%A4%95-%E0%A4%A2%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A4-%E0%A4%B0%E0%A4%96%E0%A5%87%E0%A4%9A-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%AD%E0%A5%81%E0%A4%9C%E0%A4%AC%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%91%E0%A4%AB%E0%A4%B0/ar-AA1MvYll</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-108599-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%97%E0%A5%81%E0%A4%82%E0%A4%A4%E0%A4%B5%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%8F%E0%A4%95%E0%A4%9F%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%82%E0%A4%AC%E0%A4%B0%E0%A4%A8-%E0%A4%A5%E0%A4%B2-30000-%E0%A4%95-%E0%A4%9F-%E0%A4%AF-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-47000-jobs/ar-AA1Mp7tQ?ocid=finance-verthp-feeds</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/thousands-of-rupees-were-laundered-during-the-corona-period-devendra-fadnavis-criticizes-thackeray/videoshow/123926314.cms</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-cabinet-meeting-electricity-tariff-will-be-reduced-till-2027-cm-devendra-fadnavis-took-4-major-decisions-93644</t>
+          <t>https://www.mymahanagar.com/mahamumbai/uddhav-thackeray-in-power-the-mumbai-municipal-corporation-during-the-corona-period-committed-a-scam-in-the-body-bags-fadnavis-targets-thackeray/922227/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/namo-shetkari-samman-nidhi-yojana-seventh-installment-distribute-today-check-your-account-93564</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AB-%E0%A4%A8%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%B8%E0%A5%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%82-%E0%A4%AB-%E0%A4%B0%E0%A4%B2-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AB%E0%A4%9F%E0%A4%95-%E0%A4%B0%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%AC%E0%A4%A6%E0%A4%B2%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MSIyN</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/obc-demands-national-obc-federation-president-babanrao-taywade-to-meet-chief-minister-devendra-fadnavis-and-obc-development-minister-atul-save-possibility-of-issuing-gr-for-obc-demands/919737/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/maharashtra-cabinet-meeting-8-key-decisions-gaming-policy-hostel-allowance-increase-135933914.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/water-supply-to-be-disrupted-for-6-days-chhatrapati-sambhajinagar-citizens-to-face-difficulties/articleshow/123848235.cms</t>
+          <t>https://marathi.abplive.com/news/sangli/strict-shutdown-in-ishwarpur-and-ashta-to-protest-gopichand-padalkar-criticism-of-jayant-patil-marathi-news-update-1385432/amp</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-on-maratha-and-obc-reservation-and-challenges-cm-fadnavis/921173/</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-9/923517/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-government-cabinet-four-big-decision-today-extension-of-electricity-tariff-concession-till-march-2027-984595.html</t>
+          <t>https://thefocusindia.com/maharashtra-news/will-not-support-gopichand-padalkars-statement-fadnavis-clarifies-his-stance-284601/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-lawyer-yogesh-kedar-meets-minister-radhakrishna-vikhe-patil-for-maratha-reservation/amp_articleshow/123834187.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-thackeray-brand-controversy-sanjay-raut-slams-devendra-fadnavis-over-balasaheb-thackeray-s-legacy-and-brand-remarks-1384959</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-news-spark-of-discontent-between-chief-minister-fadnavis-and-eknath-shinde/</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-this-is-a-clove-cracker-chief-minister-devendra-fadnavis-reply/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/over-25-000-buildings-without-oc-in-mumbai-to-be-regularised-under-new-policy-minister-2025-09-11</t>
+          <t>https://www.dainikprabhat.com/implementation-of-law-and-order-will-lead-the-country-towards-becoming-a-superpower-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/maharashtra-australia-industry-round-table-conference-maharashtras-path-towards-global-partnership-283840/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-19-september-2025-125091900004_1.html</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/23-odias-rescued-from-violence-hit-nepal-says-odisha-cm-mohan-charan-majhi20250912060325</t>
+          <t>https://ahmednagarlive24.com/krushi/onion-rate-if-the-central-government-accepts-this-demand-of-chief-minister-devendra-fadnavis-onions-will-get-a-good-price/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/hindi/articles/c4g70gly2eqo</t>
+          <t>https://www.dainikprabhat.com/chaos-during-chief-minister-fadnavis-speech-protesters-allege-injustice-against-obcs/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-ahmednagar-railway-station-renamed-as-ahilyanagar-station-home-ministry-issued-notification-know-all/articleshow/123853954.cms</t>
+          <t>https://vishwanewsmarathi.com/so-my-dear-sisters-will-not-get-the-scheme-money/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/india-news/maharashtra-stuck-in-the-vortex-of-reservation-obc-organizations-are-angry-id-471400</t>
+          <t>https://www.dainikprabhat.com/milind-narvekar-got-a-call-and-cm-fadnavis-big-revelation-what-happened/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/obc-organizations-will-legally-challenge-the-government-order-regarding-maratha-reservation-wadettiwar/865906/</t>
+          <t>https://www.dainikprabhat.com/harshwardhan-sapkal-chief-minister-fadnavis-should-resign-congress-state-president-harshwardhan-sapkal-demanded/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-rrp-electronics-announces-fab-setup-in-navi-mumbai-worth-rs-12000-crore-ws-kl-9614687.html</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/cm-devendra-fadnavis-mou-between-the-state-government-and-cambridge/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://palpalindia.com/2025/09/14/Maharashtra-becomes-semiconductor-hub-Sachin-backed-RRP-Electronics-gets-100-acres-of-land.html</t>
+          <t>https://www.dainikprabhat.com/the-chief-ministers-first-reaction-to-gopichand-padalkars-controversial-statement-was-while-we-were-talking/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/quota-politics-mahayuti-govt-weakening-maharashtras-social-fabric-says-pawar/amp_articleshow/123883997.cms</t>
+          <t>https://www.dainikprabhat.com/big-news-sudden-resignation-of-the-states-advocate-general-chief-minister-fadnavis-gave-information-in-the-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.firstpost.com/web-stories/india/vice-presidential-elections-2025-fast-facts-on-cp-radhakrishnan-and-b-sudershan-reddy-25861.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-meeting-maharashtra-unveils-new-animation-vfx-and-gaming-policy-as-state-cabinet-approves-8-major-decisions-article-152829352</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/sena-ubt-announces-sindoor-protest-against-india-pak-cricket-match-101757758871756-amp.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-meeting-maharashtra-unveils-new-animation-vfx-and-gaming-policy-as-state-cabinet-approves-8-major-decisions-article-152829352/amp</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://themachinemaker.com/news/mahindra-tractors-and-maharashtra-government-join-hands-to-launch-skill-development-centre-in-gadchiroli/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-will-get-1-lakh-rupees-loan-without-interest-read-how-it-works-cm-devendra-fadnavis-tells-calculation-article-152844483</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-slams-congress-for-ignoring-obcs-3717135</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%9A-%E0%A4%97-%E0%A4%AA%E0%A4%A8-%E0%A4%AF-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%AC-%E0%A4%B9%E0%A5%87%E0%A4%B0-%E0%A4%AB-%E0%A4%A1%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%95-%E0%A4%B0%E0%A4%B5-%E0%A4%88-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AB-%E0%A4%A4%E0%A5%81%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A3-%E0%A4%9A-%E0%A4%87%E0%A4%B6-%E0%A4%B0/ar-AA1zk77g?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-signs-mous-worth-rs-1-09-lakh-cr-cm-claims-48k-direct-jobs-will-be-created/articleshow/123834356.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3627779-modis-development-push-in-bihar-a-double-engine-campaign?amp</t>
+          <t>https://www.msn.com/mr-in/news/other/pune-news-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%B9%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%AA-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%86%E0%A4%A3%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%A4-%E0%A4%8F%E0%A4%95-%E0%A4%B8-%E0%A4%AA-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%9F-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0/ar-AA1MS5wc</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.indiablooms.com/news/devendra-fadnavis-slams-siddaramaiah-govt-over-plan-to-rename-shivajinagar-metro-station-after-st-mary/details</t>
+          <t>https://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%A4%E0%A4%B0-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B2-%E0%A4%AD-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%88%E0%A4%B2-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87/ar-AA1yGbxE?cvid=095241392FF0412A82D481C439844DFB&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/eknath-shinde-unlikely-to-get-home-ministry-ajit-pawar-to-take-finance-ministry-big-scoop-on-maharashtra-cabinet-portfolios/ar-AA1vmwGF?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/cm-devendra-fadnavis-insured-maharashtra-state-government-to-introduce-new-bamboo-industry-policy-read-details/940426/amp</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/ahmednagar-railway-station-renamed-maharashtra-government-issues-notification-what-is-new-name/amp_articleshow/123852284.cms</t>
+          <t>https://marathi.abplive.com/photo-gallery/sports/lionel-messi-gives-cm-devendra-fadnavis-a-special-gift-of-signed-footbal-will-also-come-to-mumbai-for-a-visit-1385826/amp</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://english.bombaysamachar.com/national/india-pak-match-row-aaditya-thackeray-will-watch-india-pak-match-in-burqa-claims-bjps-nitesh-rane/</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-maharashtra-cm-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%98%E0%A5%87%E0%A4%A3-%E0%A4%B0/ar-AA1vePEI?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/economy/news/maha-signs-mous-worth-1-08-trn-move-will-create-47k-direct-jobs-cm-125091101179_1.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-leader-manoj-jarange-patil-big-announcement-about-delhi-visit/articleshow/123945687.cms</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/amp/en/!state/maharashtra-govt-brings-widows-single-women-under-mission-vatsalyas-ambit-enn25091403141</t>
+          <t>https://mahasamvad.in/179349/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.opindia.com/news-updates/karnataka-cm-siddaramaiah-says-shivaji-nagar-metro-station-will-be-named-after-saint-mary-dk-shivakumar-supports/</t>
+          <t>http://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AD%E0%A4%B0-%E0%A4%B8%E0%A4%AD-%E0%A4%97%E0%A5%83%E0%A4%B9-%E0%A4%A4-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%96%E0%A5%87%E0%A4%B3-%E0%A4%A1%E0%A5%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%A8-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%A8-%E0%A4%B5-%E0%A4%B0-%E0%A4%9F-%E0%A4%AE%E0%A4%97-%E0%A4%95-%E0%A4%A3/ar-AA1ABTLN?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278564140/opposition-could-not-save-their-own-votes-devendra-fadnavis-congratulates-radhakrishnan-on-winning-vice-presidential-election</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://m.sakshipost.com/amp/news/lives-tribals-will-undergo-radical-transformation-next-3-years-maha-cm-fadnavis-451985</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-live-breaking-news-17th-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-marathwada-vidarbha-rain-alert/liveblog/123933492.cms</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/deva-bhau-maharashtras-relentless-political-chess-master.html</t>
+          <t>https://mahasamvad.in/178525/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/karnataka/proposal-to-name-metro-station-after-st-mary-elicit-objections-from-bjp-some-sections</t>
+          <t>https://www.loksatta.com/maharashtra/mumbai-rain-latest-updates-maharashtra-weather-news-political-devendra-fadnavis-sanjay-raut-asc-95-5375148/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://therahnuma.com/maha-govt-launches-7th-instalment-of-namo-shetkari-yojana/</t>
+          <t>https://mahasamvad.in/178515/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/ajit-pawar-irrigation-scam-narendra-modi-devendra-fadnavis-video-anjali-damania-tweet-saamana-online-news/</t>
+          <t>https://www.instagram.com/p/DO3HFhNjGpE/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/vice-president-election-result-cm-fadnavis-slams-opposition-could-not-save-their-own-votes-bjp-nda-283629/</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AA-%E0%A4%A0-%E0%A4%82%E0%A4%AC-%E0%A4%95-%E0%A4%A6-%E0%A4%B2-%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A5%82%E0%A4%A8-%E0%A4%9F-%E0%A4%95%E0%A4%B2%E0%A5%87/ar-AA1u7Jyx?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/12/st-journey-of-reading-lovers-will-be-pleasant-initiatives-on-the-occasion-of-prime-minister-narendra-modis-75t.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/cm-devendra-fadnavis-directs-to-prepare-comprehensive-effective-policy-to-fight-cancer-maharashtra-health-marathi-news-1384411/amp</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/chhaggan-bhujbal-writes-8-page-letter-to-cm-devendra-fadnavis-over-maratha-reservation-gr-obc-protest-283634/</t>
+          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-attack-uddhav-thackeray-and-raj-thackeray-over-mumbai-mahapalika-bjp-vijay-melava-1481400.html</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/vice-president-election-shiv-sena-ubt-mps-might-vote-for-nda-candidate-as-eknath-shinde-works-on-operation-tiger/amp_articleshow/123785590.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/punepolice-force-1720-posts-will-soon-be-approved-by-the-high-powered-committee-headed-by-chief-minister-devendra-fadnavis/articleshow/124010529.cms</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-mumbai-rains-news-live-updates-in-marathi-manoj-jarange-patil-beed-ajit-pawar-sharad-pawar-rain-updates-monday-8th-september-2025-1487323.html</t>
+          <t>https://www.msn.com/mr-in/news/other/bmc-elections-2025-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%A4-%E0%A4%AD%E0%A4%97%E0%A4%B5-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%95%E0%A4%A3-%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-marathi-news/vi-AA1MFISF</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/anjali-damania-recalled-allegations-made-against-ajit-pawar-by-pm-modi-cm-fadnavis-regarding-irrigation-scam/920991/</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/namo-shetkari-yojana-seventh-installment-disbursed-rs-1892-crore-added-in-farmers-accounts-how-to-check-read-93694</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-informed-that-the-states-advocate-general-birendra-saraf-has-resigned/922000/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/ahmednagar/mla-amol-khatal-urges-unity-in-local-bodies-calls-for-collective-efforts-in-development-sdj87</t>
+          <t>https://www.mahasamvad.in/179466/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/11/after-nepal-now-france.html</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-nepal-protests-maratha-obc-reservation-wednesday-10-september-2025-1488818.html</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/television-news/devendra-fadnavis-watch-maharashtrachi-hasya-jatra-says-samir-choughule-in-mhj-unplugged/amp_articleshow/123995979.cms</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/8/the-repair-of-the-chinchoti-bhinwadi-route-which-has-been-in-constant-discussion-due-to-its-poor-condition-wil.html</t>
+          <t>https://marathi.abplive.com/news/politics/sanjay-raut-on-maharashtra-debt-burden-slams-devendra-fadnavis-eknath-shinde-ajit-pawar-says-state-situation-is-similar-to-nepal-marathi-news-1384489</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/supriya-sule-supports-anjana-krishna-scolds-ajit-pawar-283687/</t>
+          <t>https://marathi.indiatimes.com/e-paper/non-agricultural-land-certificates-compulsion-removed-for-micro-and-small-businesses/amp_articleshow/123988928.cms</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/mumbai/ramdas-athawale-expressed-confidence-that-the-republican-party-will-get-the-post-of-deputy-mayor-if-the-mahayuti-comes-to-power-in-the-mumbai-municipal-corporation/921439/amp/</t>
+          <t>https://www.tv9marathi.com/videos/cm-devendra-fadnavis-orders-immediate-action-after-attack-on-journalists-in-trimbakeshwar-nashik-1496889.html</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/13/inspector-zhende-a-suspense-thriller-from-the-80s-90s.html</t>
+          <t>https://www.loksatta.com/business/finance/chief-minister-devendra-fadnavis-steel-production-maharashtra-employment-vidarbha-marathwada-konkan-pune-print-eco-news-ssb-93-5384586/lite/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/8/ramchandra-keroba-kelvekars-90th-birthday-celebration-concluded-an-ideal-personality-who-lived-a-meaningful-li.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/sharad-pawar-criticizes-devendra-fadnavis-over-farmers-issues-from-aakrosh-morcha/921710/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/now-women-will-fly-drones-modi-government-approves-namo-drone-didi-scheme-125091400025_1.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/special-news/rahul-gandhi-said-on-pm-modis-visit-to-manipur-its-ok-but-main-issue-is-vote-theft/?noamp=mobile</t>
+          <t>https://www.navarashtra.com/videos/pimpri-chinchwad-allegation-that-shivaji-was-insulted-due-to-fadnavis-poster-case-registered-against-unknown-person-995542.html/amp</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/mumbai/bjp-organizes-grand-marathi-dandiya-in-mumbai-this-year-too/amp/</t>
+          <t>https://thefocusindia.com/maharashtra-news/90300-jobs-will-be-created-through-investment-of-%E2%82%B980962-crore-in-green-steel-in-the-state-cm-fadnavis-assures-284698/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/news/pm-modi-manipur-visit-i-can-never-forget-this-moment-why-did-modi-say-this-while-speaking-in-manipur-article-152793870/amp</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-pm-ambition-harshvardhan-sapkal-alleges-devendra-fadnavis-s-pm-dreams-mumbai-given-to-adani-rest-to-mohit-kamboj-political-row-in-maharashtra-1385667/amp</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/top-news/216251/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/sharad-pawar-phone-call-to-cm-devendra-fadnavis-registered-objection-over-mla-gopichand-padalkar-controversial-statement-about-jayant-patil/940436/amp</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://ilovenagar.com/amc-50/</t>
+          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-targets-devendra-fadnavis-over-marathwada-flood-situation/921688/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3623997-outcry-over-charlie-kirks-fatal-shooting-a-stark-reminder-of-political-violence?amp</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-advocate-general-birendra-saraf-resigns-for-personal-reasons-will-continue-till-january-on-government-s-request-amid-key-hearings-1384569/amp</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3624011-dire-decisions-life-amid-conflict-in-gaza-city?amp</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-flagged-off-the-first-train-service-from-beed-to-ahilyanagar-125091800006_1.html</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%A6-%E0%A4%95%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%9A-%E0%A4%9F-%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A5%88%E0%A4%A7-%E0%A4%96%E0%A4%A8%E0%A4%A8-%E0%A4%AE-%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6-%E0%A4%A6-%E0%A4%95-%E0%A4%86%E0%A4%88%E0%A4%AA-%E0%A4%8F%E0%A4%B8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%A0%E0%A4%A8/ar-AA1McHIL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://lokmanthan.com/hyundai-should-invest-more-and-more-in-the-state-and-increase-employment-generation-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/vice-president-election-2025-eknath-shinde-shiv-sena-leader-sanjay-nirupam-claims-uddhav-thackeray-five-mp-done-cross-voting-know-all/articleshow/123810931.cms</t>
+          <t>https://www.dainikprabhat.com/nashik-news-sharad-pawar-aggressive-on-farmers-issues-targets-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/shinde-group-again-committed-a-scam-of-rs-22-crores-cm-fadnavis-ordered-an-investigation/</t>
+          <t>https://lokmanthan.com/a-comprehensive-policy-should-be-prepared-for-cancer-treatment-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/topics/nagpur-railway-station/</t>
+          <t>https://lokmanthan.com/new-shetkari-bhavans-in-79-market-committees-across-the-state-provision-of-rs-132-crore-48-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/65-homes-eligible-in-dharavi-redevelopment-project-including-322-families/articleshow/123798304.cms</t>
+          <t>https://www.newsdanka.com/vishesh/how-was-the-first-meeting-between-devendra-fadnavis-and-narendra-modi/167384/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/conditional-bail-granted-by-special-court-in-25-kg-cannabis-case/articleshow/123800360.cms</t>
+          <t>https://pcbtoday.in/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1-13/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/farmers-granted-subsidy-on-lift-irrigation-electricity-rates-until-2027/articleshow/123800402.cms</t>
+          <t>https://www.loksatta.com/nagpur/another-train-between-nagpur-pune-ssb-93-5379462/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/malegaon-bomb-blast-case-victims-families-challenge-acquittal-of-sadhvi-pragya-singh-thakur/articleshow/123800199.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/demands-on-mulund-dumping-ground-land-grow-bjp-asks-for-golf-course-ubt-wants-hospital-and-now-dharavi-project-body-seeks-15-acres-for-casting-yard/articleshow/123904709.cms</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/msedcl-chief-honoured-withenergy-leadership-award-2025/articleshow/123788020.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/bmc-election-2025-%E0%A4%B2-%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%95%E0%A4%B0-%E0%A4%95-%E0%A4%B9-%E0%A4%B9-%E0%A4%9D-%E0%A4%B2%E0%A4%82-%E0%A4%A4%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B5%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0%E0%A4%AA%E0%A4%A6-%E0%A4%B5%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8/ar-AA1MFyqo</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/cm-pushes-for-self-reliant-gaushalas/articleshow/123772115.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-slams-thackeray-bjp-vijayi-sankalp-melava/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/bjp-slams-manoj-jarange-for-remarks-against-cm-fadnavis-mother/ar-AA1LaVWK?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-approves-joint-venture-for-5000-mw-capacity-renewable-energy-project/articleshow/123925535.cms</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mahayuti-govt-weakening-maharashtra-s-social-fabric-creating-divide-pawar-2025-09-14?src=tlh&amp;position=5</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633582-india-pushes-green-steel-revolution-at-aiifa-steelex-2025-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/sharad-pawar-comment-on-uddhav-thackeray-agitation-over-india-pakistan-asia-cup-2025-match/articleshow/123878851.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/smart-solar-bench-installed-at-st-xaviers-college-in-mumbai/articleshow/123905895.cms</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/congress-intensifies-efforts-for-leader-of-opposition-post-in-vidhan-parishad-uddhav-thackeray-and-sharad-pawars-roles-crucial/articleshow/123771641.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3633588-india-new-zealand-trade-talks-next-round-in-new-delhi?amp</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/maharashtra-government-repaying-the-favour-of-electoral-bond-donations-says-mla-rohit-pawar-in-jibe-at-chandrashekhar-bawankule/</t>
+          <t>https://www.devdiscourse.com/article/business/3633401-maharashtras-bold-step-towards-a-greener-steel-future</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/jitendra-awhad-supporter-puts-banner-as-strong-follower-amit-saraiyya-joins-bjp/articleshow/123776821.cms</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3628665-rs-1100-cr-allocated-for-repair-construction-of-roads-in-bengaluru-shivakumar?amp</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/advertisements-of-cm-fadnavis-by-anonymous-minister-rohit-pawar-criticized/</t>
+          <t>https://www.freepressjournal.in/amp/business/suzlon-group-bags-second-largest-order-of-838-mw-from-tata-power-for-solar-energy-project</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-08-september-2025-125090800003_1.html</t>
+          <t>https://www.devdiscourse.com/article/politics/3631932-rahul-gandhis-allegations-stir-controversy-over-voter-fraud</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/sharad-pawar-led-ncp-sp-faction-give-advertisement-to-counter-deva-bhau-ad-campaign-1479633.html</t>
+          <t>https://www.devdiscourse.com/article/politics/3632160-rahul-gandhi-sparks-political-storm-over-alleged-voter-fraud-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/bhujbals-last-breath-attended-the-cabinet-meeting-and-also-met-fadnavis-283566/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3632920-election-integrity-dispute-shinde-dismisses-gandhis-claims-as-baseless</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/ncp-leaders-blame-evms-for-defeat-in-chhagan-bhujbals-constituency-sd67</t>
+          <t>https://www.devdiscourse.com/article/politics/3632734-ajit-pawar-dismisses-rahul-gandhis-vote-theft-claims?amp</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-one-sentence-reaction-after-shiv-sena-thackeray-faction-protests-over-india-pakistan-match/921462/amp/</t>
+          <t>https://thenewsmill.com/2025/09/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm/</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-maratha-reservation-obc-leader-rain-updates-and-other-major-news-in-state-1490351.html</t>
+          <t>https://www.amarujala.com/video/india-news/asia-cup-2025-the-story-before-the-toss-has-come-to-light-revealing-the-handshake-controversy-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-read-out-the-list-saying-that-our-government-has-done-everything-for-the-obc-community/921468/amp/</t>
+          <t>https://www.devdiscourse.com/article/politics/3633167-sharad-pawar-denounces-derogatory-comments-by-bjp-mla</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/9/sharad-pawar-group-suffers-blow-in-jalgaon-district-former-mla-arun-patil-joins-bjp.html</t>
+          <t>https://www.ptinews.com/story/national/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm/2929801</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/sanjay-raut-attacks-eknath-shinde-maharashtra-political-crisis-1492096.html/amp</t>
+          <t>https://www.devdiscourse.com/article/politics/3633270-derogatory-remarks-stir-political-row-in-maharashtra?amp</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/vijay-wadettiwar-accuses-maharashtra-govt-inciting-social-conflict-obc-reservation-1492107.html/amp</t>
+          <t>https://www.devdiscourse.com/article/Newsalert/3633183-head-of-british-intelligence-says-there-is-absolutely-no-evidence-that-putin-wants-to-negotiate-peace-in-ukraine-reports-a?amp</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
+          <t>https://www.devdiscourse.com/article/politics/3633577-rift-in-maharashtra-controversy-erupts-over-padalkars-comments?amp</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/sanjay-raut-criticises-pm-modis-delayed-manipur-visit-shivsena-protest-tv9d-1491149.html/amp</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mla-s-remarks-on-ncp-sp-leader-kicks-up-row-101758309273108-amp.html</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/naresh-mhaske-responds-ganesh-naik-thane-political-conflict-1490365.html/amp</t>
+          <t>https://www.pratahkal.com/big-news/sharad-pawar-angered-over-bjp-mlas-controversial-statement-1519059</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/manoj-jarange-patils-powerful-response-maratha-reservation-poverty-fight-1490602.html/amp</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%AA-%E0%A4%8F%E0%A4%B8%E0%A4%AA-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%95-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%AA%E0%A4%A3-%E0%A4%B8%E0%A5%87-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AB-%E0%A4%A8-%E0%A4%95-%E0%A4%AF/ar-AA1MTEtV</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/supriya-sule-opposition-parties-are-denied-funds-in-the-state-but-this-does-not-happen-at-the-centre-supriya-sule-alleges/</t>
+          <t>https://hindi.theprint.in/india/fadnavis-government-is-indifferent-towards-the-problems-of-farmers-sharad-pawar/868925/?amp</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/technology/3625285-indias-tech-workforce-embraces-flexibility-and-purpose-in-career-choices?amp</t>
+          <t>https://www.livehindustan.com/maharashtra/shiv-sena-ubt-mp-sanjay-raut-says-many-mlas-because-of-vote-chori-in-maharashtra-201758358063004.html</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278576479/dhol-tasha-troupe-in-pune-launches-signature-campaign-for-dj-free-festivals</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%B8-%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9C-%E0%A4%97%E0%A4%B0-%E0%A4%B8-%E0%A4%A0-%E0%A4%B0-%E0%A4%9C%E0%A4%A7-%E0%A4%A8-%E0%A4%B8%E0%A4%9C%E0%A4%B2-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B8%E0%A5%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A5%81-%E0%A4%B9-%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B8-%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%AE%E0%A5%87%E0%A4%B2%E0%A4%A8-%E0%A4%B8-%E0%A4%A0-%E0%A4%B8%E0%A4%9C%E0%A5%8D%E0%A4%9C%E0%A4%A4/ar-AA1zpAh2?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/nhai-working-on-using-solid-waste-of-country-for-road-construction-by-2027-gadkari-13543973.html/amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/gopichand-padalkar-clarification-on-his-statement-about-jayant-patil-after-receiving-a-call-from-cm-devendra-fadnavis/amp_articleshow/123994231.cms</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/benefits-of-schemes-must-be-part-of-right-to-services-act-fadnavis/amp_articleshow/123833973.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/bjp-gopichand-padalkar-on-being-apology-to-jayant-patil-on-controversial-statement/923126/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-government-may-soon-allow-private-universities-to-offer-medical-education-courses/amp_articleshow/123815293.cms</t>
+          <t>https://deshbandhump.com/%E0%A4%9C%E0%A5%87%E0%A4%A8-%E0%A4%9C%E0%A5%80-%E0%A4%B5%E0%A4%BE%E0%A4%B2%E0%A4%BE-%E0%A4%AC%E0%A4%AF%E0%A4%BE%E0%A4%A8-%E0%A4%B0%E0%A4%BE%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97%E0%A4%BE%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/nitin-gadkari-express-opinion-about-backwardness-caste-politics-asj-82-5370190/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/cm-advises-padalkar-to-exercise-restraint-125092000048_1.html</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/shaktipith-highway-raju-shetti-news-make-ratnagiri-nagpur-national-highway-eight-lane-but-don-t-let-shaktipith-highway-be-built-on-the-back-of-the-people-raju-shetti-met-minister-nitin-gadkari-1382888</t>
+          <t>https://www.primetvindia.com/rahul-gandhis-new-allegations-and-his-gen-z-comment-have-caused-a-stir-in-politics/</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/uddhav-and-raj-thackeray-meet-for-second-time-in-two-weeks-amid-shiv-sena-ubt-mns-alliance-buzz-for-polls-3721939</t>
+          <t>https://www.marathijagran.com/maharashtra/nashik/sharad-pawar-criticizes-the-cm-devendra-fadnavis-by-calling-him-devabhau-warns-the-government-94901</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-politics-major-setback-for-bjp-in-ulhasnagar-as-omie-kalanis-team-joins-shiv-sena-shinde-faction-ahead-of-civic-polls</t>
+          <t>https://news18marathi.com/maharashtra/sharad-pawar-attack-cm-devendra-fadanvis-over-farmer-loan-waiver-and-crop-rate-issue-ncp-nashik-melava-1480406.html</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.eaajkaanand.com/Encyc/2025/9/11/hc.html</t>
+          <t>https://agrowon.esakal.com/video/sharad-pawar-criticizes-devendra-fadnavis-farm-loan-waiver-protest</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/what-s-in-a-name-bengaluru-metro-station-renaming-proposal-sparks-storm-maharashtra-cm-calls-it-insult-to-shivaji/ar-AA1MouAS</t>
+          <t>https://www.msn.com/mr-in/news/other/sharad-pawar-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%A8-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%9C-%E0%A4%AD-%E0%A4%98%E0%A4%B8%E0%A4%B0%E0%A4%B2-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AB-%E0%A4%B0%E0%A4%B5%E0%A4%B2-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AB-%E0%A4%A8-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MSu7q</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3627693-democracy-under-siege-ncp-leader-jayant-patil-slams-maharashtra-elections-delay?amp</t>
+          <t>https://marathi.abplive.com/news/politics/jayant-patil-first-reaction-on-gopichand-padalkar-criticism-anger-from-sharad-pawar-ncp-group-maharashtra-politics-marathi-news-1385191/amp</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3621474-udhayanidhi-stalin-champions-dravidian-model-of-progress-in-tamil-nadu?amp</t>
+          <t>https://thefocusindia.com/maharashtra-news/deva-bhau-you-take-the-name-of-shivaji-maharaj-but-you-dont-even-look-at-baliraja-what-sharad-pawar-said-in-his-speech-in-nashik-284196/amp/</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/bengaluru-s-shivajinagar-metro-to-be-named-st-mary-siddaramaiah-sparks-row/ar-AA1Mlbpz</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/gopichand-padalkar-asks-why-sharad-pawar-didnt-call-to-modi-when-congress-makes-ai-video-of-his-mother/940519/amp</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/amp/news/national/radhakrishnan-takes-oath-as-vice-president-1005902</t>
+          <t>https://www.dainikprabhat.com/padalkars-criticism-has-a-strong-impact-sharad-pawar-directly-calls-cm-fadnavis-says-to-those-who-make-absurd-statements/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3625026-controversial-induction-suraj-chavan-joins-youth-policy-panel?amp</t>
+          <t>https://dainikekmat.com/stop-those-who-make-absurd-statements/117875/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://madhyamamonline.com/amp/india/naming-bengalurus-shivaji-nagar-metro-station-after-st-mary-sparks-political-row-1446130</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/sanjay-raut-on-devendra-fadnavis-maratha-obc-reservation-clash-saamana-online-news/</t>
+          <t>https://www.devdiscourse.com/article/politics/3633220-political-tensions-rise-over-maratha-quota-resolution-in-maharashtra?amp</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/vice-president-election-cross-voting-jolts-india-bloc-bjp-gives-clear-message-to-maha-vikas-aghadi/articleshow/123805413.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/wadettiwar-accuses-mahayuti-ministers-of-pushing-fake-obc-certificates/articleshow/124020428.cms</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5%E0%A5%80%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D/116953/</t>
+          <t>https://www.msn.com/mr-in/news/other/sharad-pawar-on-devendra-fadnavis-%E0%A4%A8%E0%A5%87%E0%A4%AA-%E0%A4%B3-%E0%A4%B9-%E0%A4%8A-%E0%A4%A6%E0%A5%87%E0%A4%8A-%E0%A4%A8%E0%A4%95-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%AD-%E0%A4%8A%E0%A4%82%E0%A4%A8-%E0%A4%87%E0%A4%B6-%E0%A4%B0/ar-AA1MzkfC</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/news/news/maharashtra-is-best-state-for-investment-with-conducive-ecosystem-cm-fadnavis-297450</t>
+          <t>https://news18marathi.com/maharashtra/obc-activist-shouting-slogans-during-cm-devendra-fadnavis-speech-at-chhatrapati-sambhaji-nagar-1481714.html</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/maharashtra-israel-explore-deeper-collaboration-in-infrastructure-skilled-workforce-570848</t>
+          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-poetic-address-amidst-maharashtra-maratha-obc-reservation-disputes-1496046.html/amp</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/lifestyle/smart-living/government-of-maharashtra-allots-100-acres-to-rrp-electronics-ltd-a-leading-semiconductor-player/ar-AA1Mp2jp</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-fadnavis-reviews-security-and-preparedness-with-navy-and-army-officers/amp_articleshow/124029075.cms</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.tndindia.com/maharashtra-allots-land-to-rrp-electronics-for-semiconductor-fab-facility/</t>
+          <t>https://news.ssbcrack.com/viasat-selected-to-deliver-space-crypto-solution-for-u-s-space-force-space-systems-command/</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.manufacturingtodayindia.com/rrp-electronics-semiconductor-fab</t>
+          <t>https://news.ssbcrack.com/viasat-secures-contract-with-u-s-space-force-for-advanced-space-based-encryption-technology/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/14/govt-of-mah-allots-100-acres-to-rrp-electronics-ltd-to-set-up-semiconductor-facility.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/maharashtra-clears-rs-750-billion-urban-infra-projects/78507</t>
+          <t>https://www.msn.com/hi-in/news/other/exclusive-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AB%E0%A4%B0-%E0%A4%86%E0%A4%B8-%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%8F%E0%A4%97-%E0%A4%B5-%E0%A4%9F%E0%A4%B0-%E0%A4%9F%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%B8-%E0%A4%A8-%E0%A4%A4-%E0%A4%A8-%E0%A4%97%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8/ar-AA1MDmlO</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/cons-products/electronics/rrp-electronics-gets-100-acres-land-in-navi-mumbai-for-rs-12000-crore-semiconductor-project/amp_articleshow/123850737.cms</t>
+          <t>https://www.abplive.com/states/delhi-ncr/dhaula-kuan-to-manesar-pod-taxi-plan-for-ropeway-transport-says-nitin-gadkari-at-abp-reshaping-india-conclave-3013478/amp?utm_campaign=fullarticle&amp;utm_medium=referral&amp;utm_source=inshorts</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/government-policies/maharashtra-government-may-soon-allow-private-universities-to-offer-medical-education-courses/123829072</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%AC%E0%A4%82%E0%A4%9F%E0%A4%B5-%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A5%82%E0%A4%B2-%E0%A4%A4%E0%A4%AF-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95-%E0%A4%95-%E0%A4%A4%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6/ar-AA1vHycG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://telecom.economictimes.indiatimes.com/news/devices/rrp-electronics-gets-100-acres-land-in-navi-mumbai-for-12000-crore-semiconductor-project/123854406</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B5-%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%AD-%E0%A4%95-%E0%A4%B8%E0%A4%AE%E0%A4%9D%E0%A4%A6-%E0%A4%B0-%E0%A4%9C%E0%A4%A8%E0%A4%A4-%E0%A4%95-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%B2-%E0%A4%A1%E0%A4%B0%E0%A4%B6-%E0%A4%AA-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%B2-%E0%A5%87%E0%A4%95%E0%A4%B2-%E0%A4%AC-%E0%A4%A1-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%A8%E0%A4%B8-%E0%A4%AA-%E0%A4%95-%E0%A4%A6-%E0%A4%B5/ar-AA1MQAZG</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/12/mah-best-destination-for-industries-cm.html</t>
+          <t>https://www.etvbharat.com/mr/!state/no-question-of-pm-modis-retirement-increased-bjp-and-rss-bonding-ater-pm-modi-nagpur-visits-says-rss-researcher-dilip-devdhar-pm-modi-turns-75-today-75th-birthday-maharashtra-news-mhs25091700500</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3625538-gst-rate-cut-fuels-demand-surge-for-tvs-motors-new-scooter?amp</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/maharashtra-best-destination-for-industries-investments-fadnavis-10327195</t>
+          <t>http://www.msn.com/en-in/news/India/mahayuti-govt-wins-trust-vote-in-maharashtra-assembly-sena-ubt-boycotts-governor-address/ar-AA1vxGSA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A5%82%E0%A4%B2-%E0%A4%B5-%E0%A4%A4-%E0%A4%B5%E0%A4%B0%E0%A4%A3-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%88%E0%A4%9C-%E0%A4%91%E0%A4%AB-%E0%A4%A1%E0%A5%82%E0%A4%87%E0%A4%82%E0%A4%97-%E0%A4%AC-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A4%A8-%E0%A4%AF-%E0%A4%9C-%E0%A4%B0%E0%A4%B9-%E0%A4%AE%E0%A4%9C%E0%A4%AC%E0%A5%82%E0%A4%A4/ar-AA1MoX2r?ocid=finance-verthp-feeds</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maha-cong-chief-says-partys-symbol-didnt-reach-everywhere-after-joining-mva-rules-out-statewide-alliance-for-local-body-polls/articleshow/124019976.cms</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/favorable-environment-for-industries-cm-devendra-fadnavis-said-ease-of-doing-business-is-being-strengthened/amp_articleshow/123845462.cms</t>
+          <t>https://www.hindustantimes.com/india-news/didnt-do-so-for-power-but-ajit-pawar-on-why-he-split-with-sharad-pawar-101758292291397-amp.html</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-is-the-best-state-for-industry-and-investment-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%B2-%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AA%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%87%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%AB-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%86%E0%A4%88-%E0%A4%96%E0%A4%AC%E0%A4%B0/ar-AA1uIeu8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-cabinet-approved-822-crores-for-chhatrapati-sambhajinagar-water-issue-big-decision-before-mahapalika-election-1476429.html</t>
+          <t>https://www.hindisaamana.com/mahayutis-great-scam-200-forensic-labs-are-running-on-papers/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-ecosystem-a-new-era-will-begin-for-investors-in-the-state-what-is-the-governments-master-plan/</t>
+          <t>https://www.ndtv.com/video/on-rahul-gandhi-s-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-996639</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/uddhav-raj-meet-for-second-time-in-two-weeks-amid-sena-ubt-mns-alliance-buzz-for-polls</t>
+          <t>https://www.msn.com/en-in/news/India/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mla-s-remarks-about-ncp-sp-leader/ar-AA1MSMhG</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/sena-ubt-mns-protest-two-brothers-have-come-together-maharashtra-will-follow-says-sanjay-raut/amp_articleshow/123852578.cms</t>
+          <t>https://ianslive.in/saw-a-leader-who-valued-simplicity-over-luxury-service-over-status-devendra-fadnavis-recalls-memorable-modi-story--20250916110124</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/sena-ubt-mns-sound-poll-bugle-hold-joint-protest-march-in-nashik-against-govt-nmc/articleshow/123857047.cms</t>
+          <t>https://www.msn.com/en-in/health/health-news/maharashtra-govt-formation-bjp-cm-s-name-still-under-wraps-all-eyes-on-unwell-shinde-s-big-decision/ar-AA1v3aC9?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mahayuti-netas-from-maharashtra-congratulate-radhakrishnan-on-winning-vice-presidential-election/articleshow/123793427.cms</t>
+          <t>https://www.devdiscourse.com/article/politics/3632956-ncp-leader-dismisses-rahul-gandhis-vote-theft-allegations-as-childish?amp</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-promotes-investment-and-industry-ties-with-australia-at-business-forum/articleshow/123832837.cms</t>
+          <t>https://www.greaterkashmir.com/latest-news/namo-yuva-run-sees-nationwide-participation-leaders-call-for-nasha-mukt-bharat/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3627424-governor-devvrats-ceremonial-welcome-in-mumbai</t>
+          <t>https://www.etvbharat.com/mr/!state/it-is-everyones-responsibility-to-maintain-civility-in-politics-supriya-sule-is-aggressive-over-gopichand-padalkars-statement-in-mumbai-maharashtra-news-mhs25091903801</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3626665-maneka-gandhi-calls-for-reopening-of-mumbai-kabutarkhanas?amp</t>
+          <t>https://marathi.indiatimes.com/india-news/bjp-likely-to-make-next-president-from-brahmin-community-as-vp-election-changes-social-arithmetic-three-names-in-the-race/articleshow/123940423.cms</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/elphinstone-bridge-closure-bridge-will-not-be-closed-until-written-assurance-from-cm-fadnavis-say-officials-23593544</t>
+          <t>https://maharashtramirror.com/pune-news-placards-put-up-against-padalkar-in-pune-placards-saying-roadblock-leader-father-is-not-good-enough-to-perform-rituals-are-in-the-news/amp/</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-government-issues-notification-renaming-ahmednagar-railway-station-in-state-as-ahilyanagar-23593730</t>
+          <t>https://www.animationxpress.com/latest-news/maharashtra-government-approves-states-avgc-xr-policy-with-rs-3000-crore-plan/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/maharashtra-iowa-sign-partner-state-agreement-in-mumbai-10452582</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-cabinet-approves-eight-major-decisions-including-infrastructure-boost-labour-reforms-and-rural-development/ar-AA1Do4HZ?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-moves-to-decriminalise-6-state-acts</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3630825-chhatrapati-sambhajinagar-indias-emerging-ev-capital</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://sugermint.com/government-of-maharashtra-allots-100-acres-to-rrp-electronics/</t>
+          <t>https://m.economictimes.com/news/india/maharashtras-new-policy-to-promote-creative-tech-sector/amp_articleshow/123928891.cms</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.liveaaryaavart.com/2025/09/Devendra-fadnavis-mumbai%20.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/hi-tech-media-park-in-nagpur-with-rs3000cr-nod-to-avgc-xr/articleshow/123928752.cms</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/177895/</t>
+          <t>https://www.nagpurtoday.in/future-tech-hub-nagpur-to-host-dedicated-avgc-xr-park/09171239</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178444/</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-unveils-rs-3268-cr-avgc-xr-policy-to-create-2-lakh-jobs-23594327</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/9/cabinet-decisions-relief-for-farmers-these-important-decisions-were-taken-in-the-cabinet-meeting.html</t>
+          <t>https://www.devdiscourse.com/article/technology/3625253-when-help-hurts-proactive-ai-features-reduce-user-confidence-and-use?amp</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A%E0%A5%87-4-%E0%A4%AE-%E0%A4%A0%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8%E0%A4%B9-%E0%A4%AE-%E0%A4%B0-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%A6%E0%A4%B0-%E0%A4%85%E0%A4%95-%E0%A4%B2-%E0%A4%9B-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%A8%E0%A4%97%E0%A4%B0-%E0%A4%B0-%E0%A4%AF%E0%A4%97%E0%A4%A1%E0%A4%B8-%E0%A4%A0-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1Mankr</t>
+          <t>https://www.devdiscourse.com/article/business/3631286-rail-renaissance-marathwadas-transformation-through-strategic-investments</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/cabinet-decisions-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-%E0%A4%A6-%E0%A4%A8-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1MauJj?ocid=finance-verthp-feeds</t>
+          <t>https://www.mypunepulse.com/maharashtra-cabinet-approves-8-key-decisions-announces-new-animation-vfx-gaming-policy-2025/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chandrashekhar-bawankule-open-challenge-to-rohit-pawar-in-cm-fadnavis-advertisement-case/articleshow/123777163.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-cabinet-meeting-maharashtra-animation-gaming-policy-announced-government-takes-8-major-decisions-95140</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-expressed-confidence-that-maharashtra-will-remain-at-the-forefront-in-providing-the-required-skilled-manpower-to-industries-abroad/920450/amp/</t>
+          <t>https://news18marathi.com/maharashtra/what-is-gaming-policy-of-maharashtra-cabinet-approval-1481423.html</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/mr/civic/the-problems-of-those-living-in-buildings-without-occupancy-certificate-will-be-solved-soon-89959</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%B5-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97%E0%A4%B8-%E0%A4%A0-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1ME6vc</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/amp/mr/crime/bombay-high-court-premises-vacated-after-receiving-bomb-scare-89973</t>
+          <t>https://marathi.indiatimes.com/e-paper/4000-cctvs-to-be-installed-for-nashik-trimbakeshwars-simhastha-kumbhmela/articleshow/123994347.cms</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4/117060/</t>
+          <t>https://agrowon.esakal.com/agro-special/8-important-decisions-in-the-cabinet-meeting-132-crores-of-funds-for-farmers-buildings-and-extension-of-the-deadline-for-the-construction-of-a-modern-orange-center-rat16</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3624638-assassination-of-influential-conservative-activist-charlie-kirk-at-university-event-shocks-nation?amp</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-to-host-agrovision-2025-from-nov21-24/articleshow/123874742.cms</t>
+          <t>https://lokmanthan.com/maharashtra-has-great-opportunities-for-development-in-fisheries-and-animal-husbandry-sectors-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/09/11/australian-government-stands-firmly-with-migrants-says-country-s-high-commissioner-to-india.html</t>
+          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%82%E0%A4%97-2/117679/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/09/09/want-to-be-part-of-a-drama-club-or-sports-club-if-you-are-in-maharashtra-you-have-to-be-here-is-why.html</t>
+          <t>https://dainikekmat.com/%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%B6%E0%A4%B9%E0%A4%B0%E0%A4%BE%E0%A4%A4-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A5%AB-%E0%A4%AA%E0%A5%8B%E0%A4%B2%E0%A4%BF%E0%A4%B8-%E0%A4%A0/117370/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/statue-of-hindubhushan-to-get-historic-salute-with-3000-drums-in-pimpri-chinchwad-on-sept-14/</t>
+          <t>https://www.devdiscourse.com/article/politics/3631932-rahul-gandhis-allegations-stir-controversy-over-voter-fraud?amp</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-chhagan-bhujbal-vows-to-protect-obc-quota-after-youths-suicide-in-latur</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/rahul-gandhi-s-allegations-spark-fresh-vote-theft-debate-in-maha-101758223379409-amp.html</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/chhagan-bhujbal-criticised-maratha-community-mp-mla-about-maratha-obc-reservation/articleshow/123863294.cms</t>
+          <t>https://www.devdiscourse.com/article/headlines/3634080-fadnavis-criticizes-rahul-gandhi-raises-brain-theft-allegations-amid-vote-theft-claims?amp</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-gb/news/world/akshay-kumar-amruta-fadnavis-lead-juhu-beach-clean-up-after-ganesh-visarjan-2025/ar-AA1M7evX</t>
+          <t>https://xperttimes.com/rahul-gandhi-flags-electoral-roll-tampering-in-maharashtra-calls-for-urgent-electoral-reforms/</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/akshay-kumar-tries-to-win-hearts-by-cleaning-juhu-beach-post-ganesh-visarjan-gets-trolled-instead/ar-AA1M2CSx</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278571085/these-10-most-influential-social-activists-in-maharashtra-2025</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maha-cong-chief-says-partys-symbol-didnt-reach-everywhere-after-joining-mva-rules-out-statewide-alliance-for-local-body-polls/amp_articleshow/124019976.cms</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/after-ladki-bahin-question-mark-over-farmer-welfare-scheme-101757618315759.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://news24online.com/business/maharashtra-mukhyamantri-mazhi-ladki-bahin-yojana-1500-deposits-begin-when-will-you-get-august-installment-check-status/631076/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/perform-or-perish-ajit-pawar-warns-ncp-ministers-at-chintan-shivir/articleshow/124003932.cms</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/business/ladki-bahin-yojana-when-is-deposits-ladki-bahin-scheme-august-installment-big-update-93725</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-tri-bhasha-samiti-also-meets-uddhav-thackeray-raj-thackeray-amid-hindi-vs-marathi-row-in-state-know-all/articleshow/123948973.cms</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/when-will-the-august-installment-of-mukhyamantri-ladki-bahin-yojana-arrive-aditi-tatkare-gave-information-a-a941/</t>
+          <t>https://24city.news/ncp-chintan-camp-ajit-pawar-reveals-people-ask-why-i-leave-sharad-pawars-support/</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/11/women-and-child-development-minister-aditi-tatkare-should-provide-benefit-of-special-loan-policy-scheme-for-wo.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/declare-wet-drought-in-maha-waive-loans-of-affected-farmers-supriya/articleshow/123955405.cms</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/ladki-bahin-yojana-why-is-the-installment-of-ladki-bahin-yojana-delayed-aditi-tatkare-said/</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3630825-chhatrapati-sambhajinagar-indias-emerging-ev-capital?amp</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mahayuti-govt-weakening-maharashtra-s-social-fabric-creating-divide-pawar-2025-09-14</t>
+          <t>https://www.lokmattimes.com/aurangabad/drought-will-soon-be-a-thing-of-past-in-marathwada-cm/</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/maratha-reservation-sharad-pawar-mahayuti-govt-maharashtra-cm-devendra-fadnavis-9622532.html</t>
+          <t>https://www.satyahindi.com/india/abvp-wins-hyderabad-university-students-elections-credit-goes-to-gen-z-then-why-objection-to-rahuls-call-147944.html/amp</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://awaazindiatv.com/?p=7331</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://awajmaharashtracha.news/dentel/</t>
+          <t>https://www.moneycontrol.com/news/india/pm-modi-s-75th-birthday-celebrations-live-politicians-celebs-share-their-modi-story-on-eve-of-birthday-liveblog-13550965.html</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/4/?m=0</t>
+          <t>https://www.moneycontrol.com/news/india/pm-modi-s-75th-birthday-celebrations-live-politicians-celebs-share-their-modi-story-on-eve-of-birthday-13550965.html/amp</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/10/?m=0</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bom53-mh-meenatai-2ndld-statue.html</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/maharashtra-makes-governance-smarter-using-artificial-intelligence-992313</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382/1</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/09/12/government-of-maharashtra-allots-100-acres-to-rrp-electronics-ltd-a-leading-semiconductor-player/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/ahmednagar-railway-station-renamed-maharashtra-government-issues-notification-what-is-new-name/articleshow/123852284.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-mocks-uddhav-raj-thackeray-over-thackeray-brand-and-best-credit-society-poll-defeat-23594336</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/amp/news/railways/maharashtra-renames-ahmednagar-railway-station-to-ahilyanagar/123862509</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-for-tech-driven-policing-flags-ai-and-cybercrime-challenges-23594968</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://organiser.org/2025/09/13/315648/bharat/maharashtra-govt-issues-official-notification-to-rename-ahmednagar-railway-station-as-ahilyanagar/</t>
+          <t>https://www.ptinews.com/story/national/bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/2921301</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/maharashtra-government-signs-30000-cr-mou-with-lodha-green-data-centre-park-to-come-up-in-palava</t>
+          <t>https://www.aninews.in/news/entertainment/out-of-box/hindi-films-fail-to-depict-the-true-heroism-of-mumbai-police-says-maharashtra-cm-fadnavis20250920135931?amp=1</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2165472</t>
+          <t>https://sundayguardianlive.com/entertainment-news/milind-soman-flags-off-namo-yuva-run-in-mumbai-says-its-pm-modis-dream-to-make-india-drug-free20250921113302-144797/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-live-news-13th-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-local-train-block-uddhav-thackeray-cm-devendra-fadnavis/liveblog/123862426.cms</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/pm-modi-allocated-rs-21000-crore-for-rail-lines-in-marathwada-claims-cm-devendra-fadnavis-23594480</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-directs-immediate-implementation-of-reforms-in-state-innovation-society/920428/amp</t>
+          <t>https://inshorts.com/en/amp_news/hindi-films-fail-to-show-real-mumbai-police--maharashtra-cm-1758365200271</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/permission-for-private-universities-to-offer-medical-education-in-maharashtra-invest-seize-the-opportunity/articleshow/123842558.cms</t>
+          <t>https://m.economictimes.com/news/sports/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-in-december/articleshow/124011925.cms</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-vice-president-election-nepal-protests-genzs-revolt-maratha-obc-reservation-tuesday-9-september-2025-1488028.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-advocate-general-birendra-saraf-resigns-citing-personal-reasons-cm-fadnavis-accepts-resignation-23594290</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/tet-2025-maharashtra-teacher-eligibility-test-to-be-held-on-23-november-2025-vvg94</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe-23594597</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/14/the-99th-all-india-marathi-literature-conference-will-be-held-under-the-chairmanship-of-panipatkar-vishwas-pat.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cabinet-clears-animation-policy-2025-and-other-key-projects-23594299</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/investment-value-of-108599-crore-in-maharashtra-will-create-47100-jobs-details-of-various-memorandums-of-understanding/938695/amp</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-launch-skill-courses-to-boost-manpower-for-gems-and-jewellery-sector-devendra-fadnavis-23594288</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Implement-the-reforms-of-the-State-Innovation-Society-immediately.html</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/milind-soman-flags-off-namo-yuva-run-in-mumbai-says-its-pm-modis-dream-to-make-india-drug-free20250921113302</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Scholarship-distribution-on-auto-system.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/acharya-devvrat-takes-additional-charge-as-maharashtra-governor-101757923599184-amp.html</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/maharashtra/216436/</t>
+          <t>https://www.aninews.in/news/sports/others/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-indian-racing-festival-finale20250921191656</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-iowa-usa-partnership-will-open-new-doors-of-cooperation-in-various-sectors-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.devdiscourse.com/article/sports-games/3634664-mumbais-first-fia-grade-night-street-race-a-new-era-in-indian-motorsports?amp</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/ajit-pawar-cleared-devendra-fadnavis-and-eknath-shinde-clash/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/congress-mp-varsha-gaikwad-bjp-s-mohit-kamboj-spar-over-sra-projects-in-mumbai-23594189</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/politics/eknath-shinde-upset-on-devendra-fadnavis-maharashtra-politics-local-body-elections/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-23594141</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/4-important-decisions-in-maharashtra-cabinet-meeting-15368389</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/navi-mumbai-to-host-maharashtras-first-formula-street-race-in-the-indian-racing-festival-2025-23594957</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/9/loan-from-hudco-under-infrastructure-development-loan-scheme.html</t>
+          <t>https://inshorts.com/en/news/pm-modi-to-inaugurate-mumbai-metro-3-s-final-stretch-on-sept-30-1758118163968</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-politics-cm-dcm-dispute-municipal-officer-appointments-1491466.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-19-news-updates-live-updates-weather-update-mumbai-monsoon-18331427</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-11-political-news-in-marathi-938414</t>
+          <t>https://www.lokmattimes.com/maharashtra/to-continuously-lie-is-an-art-that-only-rahul-gandhi-has-devendra-fadnavis-on-congress-mps-vote-theft-claims-a510/</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/10/faster-approvals-for-maritime-board-projects-fisheries-and-ports-minister-nitesh-rane.html</t>
+          <t>https://news.abplive.com/cities/mumbai-balasaheb-thackeray-wife-meenatai-statue-defaced-1-arrested-1800879</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai/colaba/mumbai-demand-for-written-assurance-for-demolition-of-elphinstone-bridge-15381074</t>
+          <t>https://www.bhaskarenglish.in/amp/local/maharashtra/mumbai/news/varsha-bungalow-furniture-20-47-lakh-controversy-pwd-covers-multiple-bungalows-activists-point-to-crore-tenders-135952900.html</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/10/maternity-hospital-administration-not-responsible-for-girls-death-kdmc-clarifies.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-x-%E0%A4%AA%E0%A4%B0-%E0%A4%B2-%E0%A4%96-%E0%A4%A6-%E0%A4%B2-%E0%A4%95-%E0%A4%AC-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vn2ER?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/congress-claims-maharashtra-vidhan-parishad-leader-of-opposition-for-satej-patil/articleshow/123776446.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ima-doctors-threaten-to-go-on-24-hour-strike-in-maharashtra-including-mumbai-from-8-am-on-sep-18-devendra-cm-fadnavis-know-all/articleshow/123947629.cms</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/maharashtra/216368/</t>
+          <t>https://www.msn.com/mr-in/entertainment/bollywood/%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%A1%E0%A5%8D%E0%A4%B0%E0%A4%97%E0%A5%8D%E0%A4%9C-%E0%A4%9C-%E0%A4%A8-%E0%A4%85%E0%A4%AC%E0%A5%8D%E0%A4%B0-%E0%A4%B9%E0%A4%AE%E0%A4%B5%E0%A4%B0-%E0%A4%AD-%E0%A4%B3%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AD%E0%A4%B0-%E0%A4%B8%E0%A4%AD%E0%A5%87%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A4%82-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%82-%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%95/ar-AA1xaVLz?cvid=E5D2FC4919EC403B89F2CDD45BDCA942&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/what-did-eknath-shinde-say-at-the-meeting-of-developed-maharashtra-vision-document-2047-fulfilling-the-expectations-of-the-people/131638/</t>
+          <t>https://mahasamvad.in/179340/</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/athawale-hails-maharashtra-govt-s-decision-to-withdraw-orders-on-three-language-policy/ar-AA1HMp8g?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-no-matter-what-happens-the-mayor-will-be-from-the-mahayuti-chief-minister-criticizes-thackeray-brothers-from-bjps-vijay-sankalp-rally/922208/</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ncps-suraj-chavan-accused-in-activist-assault-case-made-special-invitee-on-youth-policy-panel/articleshow/123844397.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%B8-%E0%A4%B0%E0%A4%96-%E0%A4%AE%E0%A5%87%E0%A4%B2-%E0%A4%B9%E0%A5%87-%E0%A4%95%E0%A4%AB%E0%A4%A8%E0%A4%9A-%E0%A4%B0-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%95-%E0%A4%AF-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A4%A3-%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A4%A3-%E0%A4%98-%E0%A4%A4/ar-AA1MFObT</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3625045-turkeys-opposition-faces-critical-court-decision-on-leadership?amp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/19/maharashtra-will-be-number-one-in-the-green-steel-sector-chief-minister-devendra-fadnavis-iifa-2025-steel-maha.amp.html</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3625696-shashi-tharoor-advocates-for-simplified-gst-to-boost-economy?amp</t>
+          <t>https://marathi.ndtv.com/videos/mumbai-ahmedabad-highway-traffic-dcm-shinde-s-order-was-reversed-by-cm-fadnavis-997414</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/industry/mumbais-25000-buildings-to-get-occupation-certificates-under-new-policy/123842401</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-kamboj-allegations-sakkale-accuses-devendra-fadnavis-of-pm-ambition-empowering-mohit-kamboj-and-giving-mumbai-to-adani-1385640/amp</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/nda-appoints-shiv-sena-mp-shrikant-shinde-as-authorised-representative-for-vice-presidential-polls</t>
+          <t>https://marathi.abplive.com/tv-show/zero-hour/bmc-elections-bjp-s-khan-mayor-remark-sparks-hindu-muslim-debate-thackeray-brand-war-heats-up-in-mumbai-politics-1385074/amp</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-sant-shiromani-rajendraji-maharaj-passes-away-in-malad</t>
+          <t>https://indiagroundreport.com/maharashtra-should-become-a-best-model-for-new-industries/</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/positive-policy-changes-considering-workers-suggestions-maharashtra-labour-minister-akash-fundkar</t>
+          <t>https://bharatexpress.com/india/pm-modis-big-gift-to-mumbai-inauguration-of-underground-metro-from-worli-to-cuffe-parade-devendra-fadnavis-567660</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ncp-leader-suraj-chavan-becomes-special-member-of-youth-policy-committee-attacked-worker-in-latur-2025-09-12</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/gems-and-jewellery-exhibition-inaugurated-courses-to-be-started-for-skilled-manpower-cm-devendra-fadnavis/132720/</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/hindi/election/eager-to-come-together-in-bmc-elections-but-raj-thackeray-is-hesitantly-extending-his-hand-towards-uddhav-says-experts-241757864693921.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/kashmiri-pandit-student-alleges-harassment-at-book-event-in-pune/articleshow/123908215.cms</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbaikars-good-news-25000-buildings-without-oc-in-mumbai-urban-development-department-implement-new-policy-to-regularise/articleshow/123836698.cms</t>
+          <t>https://www.manufacturingtodayindia.com/maharashtra-seals-%E2%82%B980000-crore-mou-at-steelex-2025</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/9/extension-of-electricity-tariff-concession-for-upsa-irrigation-schemes-decision-in-cabinet-meeting-relief-for-.html</t>
+          <t>https://www.timesnownews.com/mumbai/formula-race-in-navi-mumbai-first-fia-approved-street-racing-circuit-to-be-unveiled-know-when-where-article-152865232</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pune-city/pune-mla-amit-gorkhe-appointed-invited-member-of-state-youth-policy-committee/</t>
+          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/chhatrapati-sambhajinagar-emerges-as-indias-ev-manufacturing-hub-declares-maharashtra-cm-fadnavis/123961856</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-%E0%A4%B2-%E0%A4%96-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B9%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%9A%E0%A4%82-%E0%A4%86%E0%A4%A3-%E0%A4%85%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%98%E0%A4%B0-25-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%82%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%87%E0%A4%AE-%E0%A4%B0%E0%A4%A4-%E0%A4%82%E0%A4%A8-oc-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%AE-%E0%A4%95%E0%A4%B3/ar-AA1Mpmwg?ocid=finance-verthp-feeds</t>
+          <t>https://energy.economictimes.indiatimes.com/amp/news/coal/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/123999906</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/amp/story/maharashtra/pune-university-faces-judicial-backlash-for-allowing-failed-students-into-next-year</t>
+          <t>https://m.economictimes.com/news/sports/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-in-december/amp_articleshow/124011925.cms</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/lifestyle/topstories/three-language-policy-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AD-%E0%A4%B7-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%A3-%E0%A4%B0-%E0%A4%A4%E0%A4%9C%E0%A5%8D%E0%A4%9C%E0%A5%8D%E0%A4%9E-%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%9C-%E0%A4%A7%E0%A4%B5-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%AA%E0%A4%A6-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF%E0%A4%AA%E0%A4%A6-%E0%A4%95-%E0%A4%A3-%E0%A4%95-%E0%A4%A3/ar-AA1LXBpv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aninews.in/news/sports/others/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-indian-racing-festival-finale20250921191656?amp=1</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://www.rprealtyplus.com/news-views/hudco-signs-rs-11300-cr-mou-in-nagpur-welcomes-govt-director-121646.html</t>
+          <t>https://udayavani.com/national/rahul-sonia-gandhi-arrive-in-wayanad-for-private-events-390635?lang=en</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/naveen-nagpur-coming-up-as-indias-next-global-financial-hub-mou-signed-3718512</t>
+          <t>https://news.ssbcrack.com/saturn-and-neptune-shine-brightest-this-week-a-celestial-spectacle-awaits/</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/ifc-maharashtra-govt-discuss-stronger-ppp-collaboration-to-drive-viksit-bharat-2047-570846</t>
+          <t>https://www.footboom1.com/en/news/football/2752001-lionel-messi-s-confirmed-visit-to-maharashtra-sparks-excitement</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/money/topstories/lodha-developers-signs-mou-with-fadnavis-govt-for-rs-30-000-cr-worth-data-centre-park/ar-AA1MmDCF</t>
+          <t>https://hastakshep.com/breaking-news/desh-duniya-ki-live-khabrein-17-september-2025-aaj-tak-live-268062</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-gets-rs268-crore-hudco-loan-for-sewage-projects-akola-irrigation-schemes-to-receive-rs9-crore/articleshow/123793226.cms</t>
+          <t>https://navbharattimes.indiatimes.com/breaking-news-in-hindi/liveblog/58166012.cms</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/adani-reliance-projects-to-bring-rs71500-crore-investment-to-nagpur/articleshow/123837089.cms</t>
+          <t>https://marathi.abplive.com/news/latur/latur-news-marathwada-mahadev-koli-community-hunger-strike-postponed-important-assurance-from-shivendraraje-bhosale-maharashtra-marathi-update-1384929</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/17-ac-e-buses-stuck-at-depot-due-to-charging-infra-delay/articleshow/123771704.cms</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3630451-mumbai-hosts-pioneering-international-bamboo-summit</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-biz-hub-to-take-shape-in-phased-manner-over-15-years/articleshow/123772865.cms</t>
+          <t>https://www.devdiscourse.com/article/headlines/3632259-maharashtras-bamboo-boom-a-green-revolution-in-the-making</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://www.dsij.in/dsijarticledetail/rs-11300-crore-infrastructure-projects-president-of-india-backed-financial-institution-signs-mou-with-nagpur-metropolitan-region-development-authority-nmrda-id001-52321</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633582-india-pushes-green-steel-revolution-at-aiifa-steelex-2025-in-mumbai?amp</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hails-signing-of-agreement-for-new-nagpur-development-project/09081753</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3631471-hollywood-stands-firm-against-free-speech-suppression?amp</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maharashtra-best-state-investment-conducive-ecosystem-cm-fadnavis-451225</t>
+          <t>https://www.devdiscourse.com/article/business/3633794-maharashtra-leads-charge-in-green-steel-revolution-with-massive-investment?amp</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/new-nagpur-smart-city-to-rise-on-1710-acres-promises-jobs-and-world-class-infrastructure/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3629927-maharashtras-renewable-energy-leap-a-new-joint-venture?amp</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/two-mous-signed-with-navratna-psus-for-new-nagpur-project-10061441</t>
+          <t>https://tathya.in/prabhakaran-on-green-steel/</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178292/</t>
+          <t>https://civicmirror.in/maharashtra/hyundai-should-invest-more-and-more-in-the-state-and-increase-employment-generation-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nagpur/important-mous-with-companies-for-the-development-of-new-nagpur-93565</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/18/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women.html</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/mumbai-news/approval-of-mumbai-metro-line-11-125091000010_1.html</t>
+          <t>https://www.studyiq.com/articles/mukhyamantri-majhi-ladki-bahin-yojana/</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://www.rprealtyplus.com/news-views/maharashtra-lodha-sign-rs-30000-crore-deal-for-data-centre-121676.html</t>
+          <t>https://www.latestly.com/socially/auto/raptee-hv-becomes-indias-first-high-voltage-ev-motorcycle-oem-backed-by-governments-technology-development-board-7119554.html/amp</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rs-4000-crore-bamboo-project-to-be-implemented-in-maharashtra-3717116</t>
+          <t>https://www.latestly.com/socially/india/news/pune-lift-collapse-elevator-with-6-including-child-crashes-in-maharashtras-wagholi-shocking-video-surfaces-7114317.html/amp</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/quota-politics-mahayuti-govt-weakening-maharashtras-social-fabric-says-pawar/articleshow/123883997.cms</t>
+          <t>https://news18marathi.com/photogallery/money/ladki-bahin-yojana-ekyc-government-makes-e-kyc-mandatory-check-details-in-marathi-1483416.html</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/india-inaugurates-largest-container-port-at-bmct-phase-ii/78631</t>
+          <t>https://mahasamvad.in/179428/</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/economy/news/maharashtra-govt-lodha-sign-rs-30000-cr-mou-for-data-centre-park-125091101321_1.html</t>
+          <t>https://www.tv9marathi.com/videos/ladki-bahin-yojana-big-update-e-kyc-mandatory-for-beneficiaries-in-maharashtra-minister-aditi-tatkare-announcement-1495890.html/amp</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://therahnuma.com/maha-govt-signs-mou-to-accelerate-digital-transformation-journey/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/19/e-kyc-mandatory-for-beloved-sisters-2-months-deadline.html</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/economy/vadhavan-port-maharashtra-to-join-worlds-top-10-deep-sea-ports-by-2028-id-471322</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/seventh-installment-of-1892-crore-under-mahasanmaan-yojana-direct-funds-to-91-million-farmers/articleshow/123806809.cms</t>
+          <t>https://tamil.getlokalapp.com/maharashtra-news/will-give-interest-free-loan-of-1-lakh-to-beloved-sisters-15420284</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/13/ubatha-group-should-implement-my-bin-laden-my-pakistan-campaign-navnath-bans-criticism.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-said-maharashtra-is-the-most-investor-friendly-state-125091200005_1.html</t>
+          <t>https://hindi.latestly.com/india/maharashtra-ladki-bahen-yojana-e-kyc-is-mandatory-here-are-the-new-update-2757688.html/amp</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maratha-quota-gr-will-not-affect-obc-rights-says-fadnavis-101757875654855.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-21-september-2025-125092100006_1.html</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://www.etnownews.com/companies/reliance-industries-to-invest-rs-1500-crore-in-this-state-article-152783844/amp</t>
+          <t>https://hindi.latestly.com/india/information/how-to-complete-e-kyc-for-the-chief-ministers-my-girlfriend-scheme-learn-the-step-by-step-process-in-simple-language-and-avoid-fake-websites-2759605.html/amp</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3625558-eu-tightens-grip-new-sanctions-target-shadow-fleet-and-banks?amp</t>
+          <t>https://dainikekmat.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%AD%E0%A5%8B%E0%A4%9C%E0%A4%A8-%E0%A4%A5%E0%A4%BE%E0%A4%B3%E0%A5%80-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%9A%E0%A4%BE%E0%A4%B2%E0%A4%95%E0%A4%BE/117563/</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/non-integration-of-99-services-stalls-implementation-of-right-to-services-act/articleshow/123859129.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/sharad-pawar-phone-call-to-cm-devendra-fadnavis-on-bjp-mla-gopichand-padalkar-remarks-3015443/amp</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-extends-electricity-subsidy-for-lift-irrigation-schemes-until-2027/articleshow/123793535.cms</t>
+          <t>https://www.aajtak.in/amp/india/news/story/sharad-pawar-ncp-sp-responded-to-bjp-devabhau-campaign-with-deva-tuch-saang-aid-ntc-rpti-2334011-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/devpt-projects-worth-rs335cr-launched-inaugurated-in-yavatmal/articleshow/123874708.cms</t>
+          <t>https://www.aajtak.in/amp/india/maharashtra/video/intensifying-verbal-conflict-in-maharashtra-pawars-complaint-to-the-cm-reprimanding-the-legislator-ytvd-2337563-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-signs-mou-with-iowa-to-boost-agriculture-technology/</t>
+          <t>https://www.ibc24.in/maharashtra/sharad-pawar-calls-fadnavis-calls-bjp-mlas-remarks-on-ncp-sp-leader-wrong-3259171.html/amp</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/implement-citizen-centric-aaple-sarkar-20-portal-get-benefits-govt-schemes-easily-cm-fadnavis</t>
+          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-launches-farm-access-roads-scheme-to-boost-agriculture-and-farmers-welfare</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-govt-dept-websites-landing-pages-to-be-in-marathi/ar-AA1MBOCR</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/amp/mumbai/maharashtra-minister-chhagan-bhujbal-vows-to-protect-obc-quota-after-youths-suicide-in-latur</t>
+          <t>https://www.devdiscourse.com/article/law-order/3634846-strengthening-maritime-military-ties-fadnavis-meets-armed-forces-leaders?amp</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/cm-devendra-fadnavis-directs-to-prepare-a-format-for-scholarship-distribution-on-auto-system/</t>
+          <t>https://www.business-standard.com/amp/industry/news/maha-govt-to-launch-skills-courses-for-gems-and-jewellery-sector-fadnavis-125091600501_1.html?isa=yes</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/lives-tribals-will-undergo-radical-transformation-next-3-years-maha-cm-fadnavis-451985</t>
+          <t>https://money.rediff.com/amp/news/market/maharashtra-govt-signs-rs-80-962-cr-investment-mous/33971920250919</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-sports-crime-national-international-entertainment-business-breaking-news-988442.html</t>
+          <t>https://www.newindianexpress.com/amp/story/sport/other/2025/Sep/19/sc-verdict-athletes-women-empowerment-in-aiff</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3622926-mota-launches-adi-sanskriti-a-digital-platform-for-tribal-heritage-livelihoods?amp</t>
+          <t>https://civicmirror.in/maharashtra/will-change-criteria-for-solar-agricultural-pump-scheme-if-requested-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/adi-karmayogi-abhiyaan-reflects-collective-resolve-to-build-inclusive-india-president-murmu/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B9-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%A8-%E0%A4%98-%E0%A4%B2-%E0%A4%B5-%E0%A4%9A-a-%E0%A4%9F%E0%A5%82-z-%E0%A4%9C-%E0%A4%86%E0%A4%B0/ar-AA1yUgvL?cvid=8A4346A7BD71407096C4EE24E5F4A00E&amp;ocid=nyl&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/maharashtra-government-signs-mou-with-iowa-to-promote-agriculture-and-technology-in-marathi/</t>
+          <t>https://thefocusindia.com/maharashtra-news/mou-between-maharashtra-government-and-naam-foundation-284511/</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-mou-with-the-state-of-iowa-us-both-work-together-on-agriculture</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/steel-mahakumbh-investment-worth-rs-80962-crores-will-come-to-maharashtra-90300-jobs-will-be-created-95899</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-maharashtra-iowa-partnership-opened-new-doors-in-various-fields/amp/</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-uss-iowa-sign-sister-state-agreement/articleshow/123855301.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-to-introduce-certification-courses-in-gold-and-jewelry-sector-at-skill-development-university/articleshow/123967156.cms</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-to-get-rs115cr-skill-development-centre-tata-signs-mou-with-state/articleshow/123869977.cms</t>
+          <t>https://ahmednagarlive24.com/maharashtra/cabinet-decision-fadnavis-governments-big-gift-for-farmers-and-students/</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/training-facility-for-3-thousand-students-skill-development-center-in-nagpur-by-tata-technology/132222/</t>
+          <t>https://mahabharti.in/pashusavardhan-vibhag-bharti-2025/</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/india/all-india/madhya-pradesh-government-to-audit-ladli-behna-beneficiaries-to-remove-ineligible-names-1903332</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%B5%E0%A4%B0-%E0%A4%B8%E0%A4%BE%E0%A4%A1%E0%A5%87%E0%A4%86%E0%A4%A0-%E0%A4%B2%E0%A4%BE%E0%A4%96-%E0%A4%95%E0%A5%8B%E0%A4%9F%E0%A5%80/117389/</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govts-move-to-raise-work-hours-snowballs-into-major-issue-3719241</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/acharya-devvrat-takes-oath-as-governor-of-maharashtra-94806</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/page/16?afdt=a8CllQrZd7MKEwihuYfauMCeAhUDOJwKHUYjqUoQBBgDIAAw35CMD1DfkIwP&amp;search</t>
+          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-illegal-building-demolition-halted-in-dombivli-as-urban-development-department-summons-kdmc-chief/articleshow/123789657.cms</t>
+          <t>https://civicmirror.in/maharashtra/the-countrys-path-towards-superpowerhood-is-being-paved-with-effective-implementation-of-law-and-order-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-directs-inclusion-of-koliwadas-in-mumbai-development-plan-within-60-days</t>
+          <t>https://civicmirror.in/maharashtra/ease-of-doing-business-reduce-the-time-required-for-new-industries-by-reducing-licenses-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/there-will-be-a-radical-change-in-the-lives-of-tribals-in-the-next-3-years-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.amp.html</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/educational/216349/</t>
+          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/kolhapur/kolhapur-north/kolhapur-teachers-tet-issue-to-be-discussed-with-chief-minister-15433332</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/centre-important-schemes-to-bring-tribal-community-into-mainstream-of-development-says-cm-devendra-fadnavis-zws-70-5370140/lite/</t>
+          <t>https://dainikekmat.com/a-committee-of-eight-secretaries-headed-by-the-chief-secretary-to-prepare-a-vision-document-for-a-developed-maharashtra-2047/117284/</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Maharashtra-is-a-leader-in-providing-skilled-manpower.html</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/13/nagpur-to-be-hub-of-solar-panel-manufacturing-cm-fadnavis.html</t>
+          <t>https://www.newindianexpress.com/amp/story/business/2025/Sep/19/rupee-recoups-early-losses-closes-higher-at-8810-even-as-dollar-rises</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178305/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3632182-maharashtra-unveils-industrial-and-social-policy-reforms</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/elphinstone-bridge-83-project-victims-will-get-houses-in-mhada-buildings-in-area/articleshow/123843252.cms</t>
+          <t>https://www.devdiscourse.com/article/politics/3628368-former-goa-cm-parsekar-says-he-could-return-to-bjp-this-year?amp</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178187/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/cabinet-approves-bhandara-to-gadchiroli-94-km-expressway.html</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-said-100-percent-farmers-will-get-free-electricity/amp/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628673-fmr-axis-mf-fund-manager-pays-rs-858-lakh-to-settle-market-rules-violation-case-with-sebi?amp</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/mahavitaran-ranks-first-in-the-performance-of-the-electricity-sector/</t>
+          <t>https://www.msn.com/mr-in/news/other/cm-devendra-fadnavis-on-obc-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A-%E0%A4%A8-%E0%A4%A4-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%93%E0%A4%AC-%E0%A4%B8-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9F-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%95-%E0%A4%B9-%E0%A4%9A-%E0%A4%95-%E0%A4%A2%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%B6%E0%A4%AC%E0%A5%8D%E0%A4%A6/ar-AA1M3dKu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/krushi/maharashtra-cabinet-decision-four-big-decisions-in-maharashtra-state-cabinet-meeting/</t>
+          <t>https://www.msn.com/mr-in/news/other/ev-%E0%A4%98%E0%A5%87%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-5-%E0%A4%B2-%E0%A4%96-%E0%A4%82%E0%A4%9A-%E0%A4%85%E0%A4%A4-%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%A7-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-9000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%B5%E0%A4%B0/ar-AA1MMJ2I?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-hits-back-at-oppn-targeting-cm-over-devabhau-advt/articleshow/123772690.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/cancer-treatment-policy-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A4%B0-%E0%A4%97-%E0%A4%B5%E0%A4%B0-%E0%A4%89%E0%A4%AA%E0%A4%9A-%E0%A4%B0-%E0%A4%B8-%E0%A4%A0-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%A4%E0%A4%AF-%E0%A4%B0-%E0%A4%95%E0%A4%B0/ar-AA1MBSNd</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>https://www.deshsewak.org/english/news/217484</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maha-govt-launches-7th-instalment-namo-shetkari-yojana-450404</t>
+          <t>https://marathi.indiatimes.com/e-paper/non-agricultural-land-certificates-compulsion-removed-for-micro-and-small-businesses/articleshow/123988928.cms</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/government-approves-rs-73-crore-91-lakh-43-thousand-assistance-for-crop-damage-caused-by-natural-calamities/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/wet-drought-declaring-a-wet-drought-in-maharashtra-congress-leader-nana-patole-demands-to-government-95184</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-govt-crores-of-rupees-rain-in-farmers-accounts-governments-big-decision/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-fadnavis-orders-to-build-a-cancer-hospital-on-behalf-of-the-sansthan-in-shirdi-prepare-a-policy-for-cancer-treatment/132544/</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/makarand-patil-announces-relief-for-rain-hit-farmers-ocd-94-5370643/lite/</t>
+          <t>https://www.constructionweekonline.in/business/mahindra-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-nepal-protest-solapur-crime-ex-deputy-sarpanch-govind-burge-ayush-komkar-manoj-jarange-patil-rain-maratha-obc-reservation-thursday-11-september-2025-1489566.html</t>
+          <t>https://www.manufacturingtodayindia.com/hyundai-rs-56-crore-csr-projects</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/uddhav-sena-mns-cadres-take-out-jan-akrosh-morcha-in-nashik-intensify-campaign-ahead-of-local-body-polls-3725190</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3631029-empowering-women-maharashtras-push-for-one-crore-lakhpati-didis</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3624602-shiv-sena-leader-demands-action-against-allegedly-anti-national-remarks?amp</t>
+          <t>https://mahasamvad.in/178604/</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/maharashtra-bamboo-mission-devendra-fadnavis-announcement-ocd-94-5382808/lite/</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/178828/</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nashik/plan-to-concrete-51-key-roads-in-nashik-city-at-rs3000-crore/articleshow/123981854.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/Newsalert/3630442-like-you-i-am-also-fully-committed-to-taking-india-us-partnership-to-new-heights-pm-modi-to-trump?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-cabinet-approves-rs931cr-for-bhandaragadchiroli-super-highway/articleshow/123928813.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>https://infra.economictimes.indiatimes.com/amp/news/railways/indias-bullet-train-project-tunnelling-to-begin-january-2026-as-tbm-arrives/124025478</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/gurgaon/monitor-infrastructure-projects-to-ensure-quality-union-minister-rao-narbir-singh-tells-gurgaon-residents/amp_articleshow/123954170.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/beed-gets-rail-connectivity-after-a-wait-of-3-generations/amp_articleshow/123955118.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>https://currentaffairs.adda247.com/statue-of-chhatrapati-shivaji-honoured-at-pimpri%E2%80%91chinchwad/</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-unveil-golden-data-of-citizens-move-to-help-detect-bogus-beneficiaries/amp_articleshow/124002889.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>https://www.businessworld.in/article/maharashtra-unveils-policy-reforms-to-boost-msmes-social-welfare-572212</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/national/general-news/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address20250921195926?amp=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/cm-devendra-fadnavis-directs-to-prepare-comprehensive-effective-policy-to-fight-cancer-maharashtra-health-marathi-news-1384411</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>https://www.saamana.com/shivsena-ubt-mp-sanjay-raut-press-conference-attack-on-bjp-on-corruption-and-debt-on-state-saamana-online-news/</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/business/3630001-maharashtra-advances-student-welfare-and-infrastructure-with-new-initiatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/19/people-propose-ai-powered-holographic-guides-cultural-tech-festivals-for-viksit-up-2047-vision</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/amp/india-news/maharashtra-mandates-e-kyc-for-ladki-bahin-beneficiaries-sets-deadline-125091900196_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>https://hindupost.in/society-culture/breaking-the-myth-of-equality-the-crisis-of-caste-in-bharatiya-christian-communities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/science-environment/3628578-maharashtra-rains-give-immediate-relief-of-rs-50k-per-hectare-to-affected-farmers-says-sapkal?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>https://www.thehansindia.com/amp/news/national/seva-pakhwada-pan-india-namo-yuva-run-instils-enthusiasm-patriotism-among-youth-1008611</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>https://indtoday.com/bjp-leader-slams-rahul-gandhi-for-remarks-on-gen-z-and-democracy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/amp/india/up-deputy-cm-keshav-maurya-directs-officials-to-work-in-team-spirit-during-bahraich-visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>https://indiaeducationdiary.in/hyundai-motor-india-foundation-commits-%E2%82%B956-crore-to-csr-initiatives-in-maharashtra/</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>https://newsmeto.com/tweet/pm-modi-75th-birthday-celebs-whose-wishes-took-everyone-by-surprise-modi-birthday-wishes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>https://www.liveaaryaavart.com/2025/09/Bihar-state-para-sports.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6-%E0%A4%A6-%E0%A4%A4-%E0%A4%9C-%E0%A4%B0-%E0%A4%AD%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AD-%E0%A4%88-%E0%A4%B8%E0%A4%A2%E0%A4%B3-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC%E0%A4%9C%E0%A5%87%E0%A4%9F%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%95%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%82%E0%A4%A8-%E0%A4%87%E0%A4%82%E0%A4%9F%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%86%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1wtpDt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>https://theclearnews.com/provide-a-fund-of-rs-500-crore-correct-the-caste-certificate-khadse-demands-in-a-letter-to-the-chief-minister/</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/madc-approves-220acre-land-for-solar-grps-defence-aerospace-projects/articleshow/124004510.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>https://sundayguardianlive.com/news/govt-to-set-up-adi-seva-kendras-to-solve-issues-of-tribal-people-tripura-cm20250916223512-139847/</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>https://kiow.com/2025/09/16/gov-reynolds-returns-from-india-trade-and-investment-mission/</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/kozhikode/tribal-kids-from-remote-wayanad-settlement-begin-their-schooling/articleshow/123928460.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/india-news/pm-modi-75th-birthday-2025-wishes-live-updates-quotes-messages-greetings-tweets-on-x-facebook/3980159/</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/179074/</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/178534/</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/2-year-extension-granted-for-modern-orange-processing-centres-in-vidarbha/articleshow/123928870.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>https://mandalnews.com/amravati/prime-minister-suryadhar-free-electricity-scheme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/mahayuti-cabinet-took-8-major-decisions-on-tuesday-mahayuti-cabinet-125091600058_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cm-devendra-fadnavis-says-will-make-changes-in-magel-tyala-saur-krushi-pump-yojana-article-152857154/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>https://www.berartimes.com/maharashtra/216617/</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>https://www.theindiadaily.com/india/maharashtra-to-launch-cleanliness-drive-on-pm-narendra-modi-s-birthday-cm-devendra-fadnavis-mangal-prabhat-lodha-iti-students-join-swachh-bharat-initiative-news-94108/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-congress-chief-harshawardhan-sapkal-attacks-state-govt-demands-special-package-for-rain-hit-farmers/articleshow/123904520.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/maharashtra-rains-give-immediate-relief-of-rs-50k-per-hectare-to-affected-farmers-says-sapkal/2917276</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-demands-rs50k/ha-relief-for-farmers/articleshow/123907918.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/Declare-%E2%80%98wet-drought%E2%80%99-in-Maharashtra-give-aid-of-Rs-50-000-per-hectare-to-farmers-Wadettiwar/2922992</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/Maharashtra-rains-Give-immediate-relief-of-Rs-50k-per-hectare-to-affected-farmers-says-Sapkal/2917276</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>https://www.afternoonvoice.com/wadettiwar-urges-maharashtra-to-declare-wet-drought-seeks-rs-50000-aid-per-hectare-for-farmers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/maharashtra-rains-give-immediate-relief-of-rs-50k-per-hectare-to-affected-farmers-says-sapkal-10467270</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/parbhani/maharashtra-government-gives-128-crore-rupees-funds-to-parbhani-for-rainfall-affected-farmers/articleshow/123980989.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%93%E0%A4%B2-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95-%E0%A4%B3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%95%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%B9%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-50-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7/ar-AA1MJhTF</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/178713/</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-slams-devendra-fadnavis-no-funds-for-loan-waiver-yet-40-lakh-spent-on-cms-residence-renovation-1384979</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/nanded-farmers-to-receive-rs-553-crore-dbt-relief-sai29</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/ncp-sharad-pawar-on-maharashtra-floods-farmers-distress-and-plea-for-government-aid-1495164.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AC%E0%A4%B3-%E0%A4%B0-%E0%A4%9C-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%93%E0%A4%B2-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95-%E0%A4%B3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%95%E0%A4%B0-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%83%E0%A4%A6%E0%A4%AF-%E0%A4%B2-%E0%A4%AA-%E0%A4%9D%E0%A4%B0-%E0%A4%95%E0%A4%B8-%E0%A4%AB%E0%A5%81%E0%A4%9F%E0%A4%A4-%E0%A4%A8-%E0%A4%B9/ar-AA1MPirq</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%AC%E0%A4%81%E0%A4%95-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%B8%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1MRkaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/179457/</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/nanded/maharashtra-sanctions-553-crore-relief-for-flood-hit-farmers-in-nanded-vsb99</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/ahilyanagar-rain-damage-vikhe-patil-orders-ocd-94-5377488/</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>https://www.athawadavishesh.com/39369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/agriculture/dattatray-bharne-went-to-the-washim-district-to-inspect-the-affected-crop/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>https://vishwanewsmarathi.com/sharad-pawars-main-indicator-but-wisdom-is-a-matter-of-learning/</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/flag-hoisting-by-cm-fadnavis-at-sambhajinagar-on-marathwada-liberation-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/social/agriculture-minister-dattatray-bharne-visits-washim-district-hoped-for-help-for-affected-farmers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%82%E0%A4%97%E0%A5%80/117572/</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/jayant-patil-heavy-rain-agriculture-news-declaring-a-wet-drought-in-the-state-jayant-patil-letter-to-chief-minister-devendra-fadnavis-in-sangli-1385048</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/kolhapur/maharashtra-government-sanctions-over-88-lakh-rupees-aid-for-kolhapur-sangli-and-dharashiv-farmers-hit-by-june-july-rains-rds-00-5381688/</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/a-fund-of-689-crores-has-been-approved-to-help-farmers-affected-by-heavy-rainfall-996353.html/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/maharashtra-dharashiv-flooding-causes-massive-soybean-crop-damage-1497495.html/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/agriculture/dattatray-bharne-went-to-the-washim-district-to-inspect-the-affected-crop/</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A664"/>
+  <dimension ref="A1:A682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,14 +438,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/national/news/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi-297681</t>
+          <t>https://www.ndtv.com/india-news/devendra-fadnavis-shares-how-first-meeting-with-pm-modi-left-a-lasting-impression-9287347</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/devendra-fadnavis-shares-how-first-meeting-with-pm-modi-left-a-lasting-impression-9287347</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/chhatrapati-sambhajinagar-will-become-countrys-ev-capital-maharashtra-cm-devendra-fadnavis/article70059920.ece</t>
         </is>
       </c>
     </row>
@@ -466,28 +466,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-gb/news/India/can-t-save-religion-when-deputy-cm-s-wife-busy-making-reels-kanhaiya-kumar-s-remarks-on-devendra-fadnavis-wife-amruta-sparks-row/ar-AA1u42XL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ndtv.com/india-news/on-rahul-gandhis-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-9306931</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/on-rahul-gandhis-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-9306931</t>
+          <t>https://indianmasterminds.com/news/cm-fadnavis-police-reform-technology-economy-ipf-2025-146277/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/no-faith-in-constitution-fadnavis-targets-rahul-gandhi-over-gen-z-post-terms-him-urban-maoist/articleshow/123996897.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-move-supreme-court-if-karnataka-goes-ahead-with-plan-to-increase-almatti-dams-height-cm-devendra-fadnavis-3732808</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-move-supreme-court-if-karnataka-goes-ahead-with-plan-to-increase-almatti-dams-height-cm-devendra-fadnavis-3732808</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/only-rahul-gandhi-has-art-of-continuously-lying-devendra-fadnavis-101758224439191.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/remove-requirement-of-non-agricultural-land-certificate-for-micro-and-small-enterprises-says-maharashtra-chief-minister-devendra-fadnavis/articleshow/123979505.cms</t>
         </is>
       </c>
     </row>
@@ -522,35 +522,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3631822-vote-theft-exposed-maharashtra-congress-demands-immediate-resignation-of-cm-fadnavis</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-strengthen-it-department-for-better-citizen-services-cm-fadnavis-23595276</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-to-come-out-with-bamboo-industry-policy-cm-devendra-fadnavis-3735818</t>
+          <t>https://www.hindustantimes.com/india-news/only-rahul-gandhi-has-art-of-continuously-lying-devendra-fadnavis-101758224439191.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/pm-modi-to-inaugurate-mumbai-metro-3s-final-stretch-from-worli-to-cuffe-parade-on-sept-30-announces-chief-minister-devendra-fadnavis/articleshow/123928132.cms</t>
+          <t>https://www.ap7am.com/en/109961/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-indias-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/remove-requirement-of-non-agricultural-land-certificate-for-micro-and-small-enterprises-says-maharashtra-chief-minister-devendra-fadnavis/articleshow/123979505.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-to-come-out-with-bamboo-industry-policy-cm-devendra-fadnavis-3735818</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-will-move-sc-if-karnataka-goes-ahead-with-plan-to-raise-almatti-dam-height-fadnavis-101758133395229.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-strenghten-it-dept-to-enhance-delivery-of-services-cm-fadnavis/articleshow/124053957.cms</t>
         </is>
       </c>
     </row>
@@ -571,728 +571,728 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3634846-strengthening-maritime-military-ties-fadnavis-meets-armed-forces-leaders</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/pm-modi-to-inaugurate-mumbai-metro-3s-final-stretch-from-worli-to-cuffe-parade-on-sept-30-announces-chief-minister-devendra-fadnavis/articleshow/123928132.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-pm-modi-a-visionary-global-statesman-on-his-75th-birthday-23594462</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-will-move-sc-if-karnataka-goes-ahead-with-plan-to-raise-almatti-dam-height-fadnavis-101758133395229.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3634606-harnessing-technology-for-next-level-policing?amp</t>
+          <t>https://www.devdiscourse.com/article/law-order/3634846-strengthening-maritime-military-ties-fadnavis-meets-armed-forces-leaders</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-lead-in-green-steel-manufacturing-cm-devendra-fadnavis-23594846</t>
+          <t>https://www.devdiscourse.com/article/politics/3633329-fadnavis-accuses-rahul-gandhi-of-urban-maoist-rhetoric</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3634080-fadnavis-criticizes-rahul-gandhi-raises-brain-theft-allegations-amid-vote-theft-claims</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628667-fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir?amp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/congress-accuses-bjp-of-coming-to-power-in-maharashtra-by-rigging-votes-asks-fadnavis-to-quit-3734523</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-pm-modi-a-visionary-global-statesman-on-his-75th-birthday-23594462</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628667-fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir?amp</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maratha-quota-gr-will-not-affect-obc-rights-says-fadnavis-101757875654855.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-signs-mou-with-cambridge-for-global-standard-education-cm-fadnavis/articleshow/123980116.cms</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168537</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/fadnavis-streamline-industry-approvals-in-maharashtra/33958120250919</t>
+          <t>https://www.deccanherald.com/india/congress-accuses-bjp-of-coming-to-power-in-maharashtra-by-rigging-votes-asks-fadnavis-to-quit-3734523</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/maha-govt-to-launch-skills-courses-for-gems-and-jewellery-sector-fadnavis-125091600501_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-signs-mou-with-cambridge-for-global-standard-education-cm-fadnavis/articleshow/123980116.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3632715-fadnavis-slams-rahul-gandhis-vote-theft-claims-as-baseless-propaganda?amp</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382/2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/reduce-number-of-permissions-to-set-up-industries-speed-up-approval-time-fadnavis-to-officials/2930550</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
+          <t>https://www.ptinews.com/story/business/reduce-number-of-permissions-to-set-up-industries-speed-up-approval-time-fadnavis-to-officials/2930550</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3628357-fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir?amp</t>
+          <t>https://money.rediff.com/news/market/fadnavis-streamline-industry-approvals-in-maharashtra/33958120250919</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-devendra-fadnavis-23594442</t>
+          <t>https://www.business-standard.com/industry/news/maha-govt-to-launch-skills-courses-for-gems-and-jewellery-sector-fadnavis-125091600501_1.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-for-tech-driven-policing-flags-ai-and-cybercrime-challenges-23594968</t>
+          <t>https://www.mid-day.com/news/india-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-on-marathwada-liberation-day-107384/1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/indl-goods/svs/steel/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/articleshow/123999573.cms</t>
+          <t>https://www.devdiscourse.com/article/technology/3636540-maharashtra-pushes-digital-transformation-with-it-department-revamp</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/congress-slams-cm-fadnavis-over-shivaji-posters-pasted-in-unhygienic-surroundings-near-prabhadevi-railway-station-in-mumbai/articleshow/123948554.cms</t>
+          <t>https://www.ptinews.com/editor-detail/Fadnavis-govt-apathetic-towards-farmers-woes-claims-Pawar;-warns-of-intensifying-stir/2916686</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3635039-harnessing-technology-maharashtras-policing-revolution</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-devendra-fadnavis-23594442</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-cabinet-clears-avgc-xr-policy-draws-up-a-25-year-roadmap-101758043978392.html</t>
+          <t>https://www.telegraphindia.com/india/bad-devendra-fadnavis-marg-youth-congress-targets-cm-as-potholes-expose-bmcs-failure-on-mumbai-roads/cid/2124363</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630398-bjps-enduring-commitment-fadnavis-recollects-2017-political-maneuverings-in-mumbai</t>
+          <t>https://www.ptinews.com/story/business/chhatrapati-sambhajinagar-will-become-countrys-ev-capital-fadnavis/2922163</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/football-legend-lionel-messi-to-visit-mumbai-in-december-will-train-with-young-footballers-cm-fadnavis-23595113</t>
+          <t>https://m.economictimes.com/tech/information-tech/maharashtra-govt-to-strengthen-it-dept-to-enhance-delivery-of-services-fadnavis/articleshow/124049221.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/infrastructure/pm-modi-to-inaugurate-mumbai-metro-3-on-september-30-says-devendra-fadnavis-19677024.htm</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-lead-in-green-steel-manufacturing-cm-devendra-fadnavis-23594846</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/2930145</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/fadnavis-pushes-officials-on-reforms-governance/amp_articleshow/124031684.cms</t>
+          <t>https://www.moneycontrol.com/news/india/ladki-bahin-scheme-to-continue-govt-committed-to-women-s-empowerment-devendra-fadnavis-13553696.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/ev-capital-fadnavis-on-chhatrapati-sambhajinagar/33804020250917</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/congress-slams-cm-fadnavis-over-shivaji-posters-pasted-in-unhygienic-surroundings-near-prabhadevi-railway-station-in-mumbai/articleshow/123948554.cms</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharastra-cm-fadnavis-pushes-for-faster-industrial-approvals-ai-based-reforms-to-boost-investments-23594849</t>
+          <t>https://www.cnbctv18.com/infrastructure/pm-modi-to-inaugurate-mumbai-metro-3-on-september-30-says-devendra-fadnavis-19677024.htm</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/politics/mumbai-congress-slams-fadnavis-for-'disrespecting'-shivaji-maharaj-in-billboard-row-90046</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhi-speaks-like-an-urban-maoist-says-maharashtra-cm-fadnavis-on-congress-leaders-gen-z-post-23594827</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168537</t>
+          <t>https://www.devdiscourse.com/article/politics/3630398-bjps-enduring-commitment-fadnavis-recollects-2017-political-maneuverings-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mlas-remarks-about-ncp-sp-leader-23594821</t>
+          <t>https://www.ptinews.com/editor-detail/using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level--fadnavis/2934307</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level-Fadnavis/2934307</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628555-vast-growth-opportunities-in-fisheries-animal-husbandry-sectors-says-fadnavis-cites-aps-example?amp</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/gopichand-padalkar-news-first-reaction-after-cm-devendra-fadnavis-call-jayant-patil-n18s-1075363.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-fadnavis-and-the-obcs-101757877151905.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3631054-maharashtra-leaders-hail-pm-modis-visionary-leadership-on-75th-birthday?amp</t>
+          <t>https://www.business-standard.com/india-news/maratha-quota-row-obc-other-groups-turn-up-heat-cm-urges-restraint-125091500006_1.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/sambhajinagar-becoming-ev-capital-of-country-fadnavis/articleshow/123952619.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628555-vast-growth-opportunities-in-fisheries-animal-husbandry-sectors-says-fadnavis-cites-aps-example</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modi-allocated-rs-21000-crore-for-rail-lines-in-marathwada-claims-cm-devendra-fadnavis-23594480</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/fadnavis-leads-maharashtra-in-greeting-pm-modi-on-birthday;-calls-him-global-statesman--inspiration/2922857</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-govt-to-strenghten-it-dept-to-enhance-delivery-of-services-fadnavis/2938775</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-govt-dept-websites-landing-pages-to-be-in-marathi-101757962665589.html</t>
+          <t>https://www.hindustantimes.com/india-news/acharya-devvrat-takes-oath-as-maharashtra-governor-101757915941969.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/gst-reforms-to-speed-up-indias-economic-growth-says-fadnavis/2936669</t>
+          <t>https://money.rediff.com/news/market/ev-capital-fadnavis-on-chhatrapati-sambhajinagar/33804020250917</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/to-continuously-lie-is-an-art-that-only-rahul-gandhi-has-devendra-fadnavis-on-congress-mps-vote-theft-claims20250918223639?amp=1</t>
+          <t>https://www.ptinews.com/story/business/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/2930145</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhi-speaks-like-an-urban-maoist-says-maharashtra-cm-fadnavis-on-congress-leaders-gen-z-post-23594827</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-leads-maharashtra-in-greeting-pm-modi-on-birthday-calls-him-global-statesman-inspiration/2922857</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/No-case-of-honeytrap-in-state--CM-Fadnavis/2739248</t>
+          <t>https://lokmat.news18.com/short-videos/trending/gopichand-padalkar-news-first-reaction-after-cm-devendra-fadnavis-call-jayant-patil-n18s-1075363.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/sharad-pawar-on-devendra-fadnavis-rain-damage-saying-devabhau-pawar-s-big-demand-to-cm-n18s-1075195.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-cabinet-clears-avgc-xr-policy-draws-up-a-25-year-roadmap-101758043978392.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/health/3628551-fadnavis-calls-for-inclusive-cancer-care-policy-for-maharashtra</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-govt-dept-websites-landing-pages-to-be-in-marathi-101757962665589.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/obcs-disrupt-cm-s-speech-holds-huge-rally-in-hingoli-101758137116445.html</t>
+          <t>https://www.ptinews.com/story/national/gst-reforms-to-speed-up-indias-economic-growth-says-fadnavis/2936669</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/next-phase-of-gst-reforms-will-boost-india-s-economic-growth-says-fadnavis-125092100781_1.html</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-lays-foundation-stone-for-aws-data-centre-in-mumbai-part-of-usd-8-3-billion-investment/2941290</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/out-of-box/hindi-films-fail-to-depict-the-true-heroism-of-mumbai-police-says-maharashtra-cm-fadnavis20250920135931</t>
+          <t>https://m.economictimes.com/industry/indl-goods/svs/steel/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/articleshow/123999573.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/chhatrapati-sambhajinagar-will-become-country-s-ev-capital-fadnavis/2922165</t>
+          <t>https://www.devdiscourse.com/article/politics/3636600-sanskriti-bachao-morcha-sparks-political-unrest-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm20250919232605</t>
+          <t>https://www.business-standard.com/india-news/next-phase-of-gst-reforms-will-boost-india-s-economic-growth-says-fadnavis-125092100781_1.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/sharad-pawar-calls-cm-over-bjp-mlas-remark/amp_articleshow/124003748.cms</t>
+          <t>https://www.devdiscourse.com/article/health/3628551-fadnavis-calls-for-inclusive-cancer-care-policy-for-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Rahul-Gandhi-speaks-like-an-urban-Maoist-Fadnavis-on-his-Gen-Z-post/2929933</t>
+          <t>https://lokmat.news18.com/short-videos/trending/sharad-pawar-on-devendra-fadnavis-rain-damage-saying-devabhau-pawar-s-big-demand-to-cm-n18s-1075195.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/18/no-cap-on-prices-of-cars-for-guv-cm-and-judges-in-maharashtra-vehicle-policy</t>
+          <t>https://infra.economictimes.indiatimes.com/news/railways/maharashtra-cm-fadnavis-inaugurates-new-amalner-beed-railway-line/123961961</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/politics/fadnavis-slams-rahul-gandhi-over-election-allegations-calls-him-a-habitual-liar-90060</t>
+          <t>https://www.mid-day.com/news/india-news/article/shiv-sena-ubt-targets-maharashtra-cm-devendra-for-not-unveiling-swami-ramanand-tirtha-statue-23594500</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/amp/news/market/maharashtra-green-steel-leader-fadnavis-announces/33951620250919</t>
+          <t>https://lokmat.news18.com/short-videos/trending/bajrang-sonawane-s-big-request-to-cm-devendra-fadnavis-directly-from-the-stage-n18s-1075017.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/politics/industrial-reforms-planned-under-cm-fadnavis-leadership-90070</t>
+          <t>https://www.devdiscourse.com/article/law-order/3636632-maharashtra-cm-fadnavis-acts-on-marathwada-rainfall-crisis</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-to-storm-fadnavis-home-turf-rally-obcs-on-sept-18/articleshow/123929254.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm20250919232605</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop--fadnavis/2927696</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004?button=next</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628615-maharashtra-govt-will-create-corpus-fund-to-cover-treatments-costing-over-rs-5-lakh-fadnavis?amp</t>
+          <t>https://www.deccanherald.com/india/maharashtra/drug-free-india-key-message-of-namo-yuva-run-bjp-mp-tejasvi-surya-3737765</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal/2926755</t>
+          <t>https://www.newsonair.gov.in/hyderabad-liberation-day-celebrated-with-flag-hoisting-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hyderabad-liberation-day-celebrated-with-flag-hoisting-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-to-storm-fadnavis-home-turf-rally-obcs-on-sept-18/articleshow/123929254.cms</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633546-streamlining-success-maharashtras-push-for-rapid-industrial-approvals?amp</t>
+          <t>https://www.msn.com/en-in/news/India/oppn-ruling-parties-spar-over-rahul-s-fresh-vote-chori-charges-cong-seeks-fadnavis-resignation/ar-AA1MOLDw</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/GST-reforms-to-speed-up-India%E2%80%99s-economic-growth-says-Fadnavis/2936669</t>
+          <t>https://www.ptinews.com/editor-detail/maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop--fadnavis/2927696</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/devendra-fadnavis/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-indian-racing-festival-finale</t>
+          <t>https://www.ptinews.com/editor-detail/gst-reforms-to-speed-up-india%E2%80%99s-economic-growth--says-fadnavis/2936669</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-on-marathwada-liberation-day-107384/6</t>
+          <t>https://www.ptinews.com/story/national/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal/2926755</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe20250918053517/</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-should-step-up-to-bridge-differences-among-communities-pawar-on-quota-row/2940731</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ladki-bahin-scheme-won%E2%80%99t-be-scrapped;-govt-committed-to-empowering-women-fadnavis=/2922760</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe20250918053517</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/chhatrapati-sambhajinagar-will-become-country-s-ev-capital--fadnavis/2922163</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004</t>
+          <t>https://www.ndtv.com/india-news/mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-cm-fadnavis-9322871</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/lifting-last-person-and-bringing-them-to-mainstream-development-reflects-pm-modis-working-approach-maharashtra-cm-fadnavis20250917223421</t>
+          <t>https://www.ptinews.com/editor-detail/Oppn-ruling-parties-spar-over-Rahul-s-fresh-vote-chori-charges;-Cong-seeks-Fadnavis-resignation/2927028</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address20250921195926</t>
+          <t>https://www.ptinews.com/story/national/oppn-ruling-parties-spar-over-rahul-s-fresh-vote-chori-charges;-cong-seeks-fadnavis-resignation/2927028</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/oppn-ruling-parties-spar-over-rahuls-fresh-vote-chori-charges-cong-seeks-fadnavis-resignation/2927511</t>
+          <t>https://www.ptinews.com/editor-detail/Cong-slams-Fadnavis-over-posters-featuring-Shivaji-Maharaj-pasted-at-train-station-with-filth-around/2923386</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-inks-nine-mous-for-industrial-projects-secures-investments-worth-rs-80962-crore-23594853</t>
+          <t>https://www.deccanherald.com/india/karnataka/dycm-shivakumar-dismisses-meeting-amit-shah-rumours-says-i-am-not-mad-3739304</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal-23594647</t>
+          <t>https://www.aninews.in/news/national/general-news/lifting-last-person-and-bringing-them-to-mainstream-development-reflects-pm-modis-working-approach-maharashtra-cm-fadnavis20250917223421</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Oppn-ruling-parties-spar-over-Rahul-s-fresh-vote-chori-charges;-Cong-seeks-Fadnavis-resignation/2927028</t>
+          <t>https://www.aninews.in/news/national/general-news/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address20250921195926</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/oppn--ruling-parties-spar-over-rahul-s-fresh--vote-chori--charges;-cong-seeks-fadnavis--resignation/2927511</t>
+          <t>https://www.ptinews.com/editor-detail/bjp-gave-up-claim-for-mumbai-mayor-s-post-in-2017-at-request-of-shinde--narvekar--says-cm-fadnavis/2921301</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal-23594647</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/condition-of-getting-non-agricultural-land-nod-to-be-scrapped-for-micro--small-industries--fadnavis/2927545</t>
+          <t>https://www.devdiscourse.com/article/business/3635703-gst-reforms-a-boost-to-indias-economic-growth-and-self-reliance</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/maharashtra-signs-mous-worth-80-962-cr-for-industrial-projects-40k-jobs-125091900956_1.html</t>
+          <t>https://zeenews.india.com/india/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-india-s-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt-2963047.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/amp_news/maharashtra-key-in-pm-s-mission-green-steel--cm-fadnavis-1758347491548</t>
+          <t>https://www.business-standard.com/industry/news/maharashtra-signs-mous-worth-80-962-cr-for-industrial-projects-40k-jobs-125091900956_1.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/condition-of-getting-non-agricultural-land-nod-to-be-scrapped-for-micro-small-industries-fadnavis/2927545</t>
+          <t>https://www.nagpurtoday.in/a-first-meeting-to-remember-for-a-lifetime-fadnavis-recalls-memory-on-pm-modis-75th-birthday/09171313</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
+          <t>https://www.ptinews.com/editor-detail/oppn--ruling-parties-spar-over-rahul-s-fresh--vote-chori--charges;-cong-seeks-fadnavis--resignation/2927511</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/mumbai-union-minister-pralhad-joshi-maharashtra-cm-fadnavis-inaugurate-steel-mahakumbh20250919211944</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-announces-pod-taxi-plan-to-ease-traffic-congestion-in-mumbai-23595266</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-419656?lang=en</t>
+          <t>https://zeenews.india.com/india/residential-complex-for-muslims-in-mumbai-nhrc-issues-notice-to-fadnavis-govt-bjp-2957165.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Only-eligible-applicants-will-receive-Kunbi-caste-certificates-Fadnavis/2925278</t>
+          <t>https://www.mid-day.com/news/india-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-on-marathwada-liberation-day-107384/7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/metro-rail-and-railways-infrastructure/maharashtra-cm-fadnavis-inaugurates-new-amalner-beed-railway-line/78987</t>
+          <t>https://www.aninews.in/news/national/general-news/mumbai-union-minister-pralhad-joshi-maharashtra-cm-fadnavis-inaugurate-steel-mahakumbh20250919211944</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114?ganesh-chaturthi-photos-breakingnews</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/pm-modi-icon-of-fit-india-inspires-10-lakh-youth-to-join-largest-run-bjp-mp-tejasvi-surya20250921125145</t>
+          <t>https://www.ptinews.com/detail/national/Mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-CM-Fadnavis/2938730</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/delhi-cm-praises-pm-modi-for-gst-reforms-says-public-to-benefit-directly20250921223646</t>
+          <t>https://www.ptinews.com/story/national/heavy-rains-in-solapur-marathwada-cm-asks-water-resources-dept-to-coordinate-with-collectors/2939011</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/rahul-gandhis-mind-has-been-stolen-maharashtra-cm-devendra-fadnavis-on-congress-mps-vote-theft-claims-a525/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/first-test-run-of-thane-metro-4-conducted-promises-to-ease-traffic-woes-23595193</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
+          <t>https://www.aninews.in/news/national/general-news/delhi-cm-praises-pm-modi-for-gst-reforms-says-public-to-benefit-directly20250921223646</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/16/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi/?nonamp=1</t>
+          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/football/thank-you-for-gifting-me-signed-football-cm-fadnavis-confirms-lionel-messis-visit-to-maharashtra-on-december-14/amp/</t>
+          <t>https://news.abplive.com/cities/maharashtra-mahayuti-mva-war-of-words-erupts-rahul-gandhi-vote-theft-congress-demands-devendra-fadnavis-resignation-1801046</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://newskarnataka.com/india/milind-soman-cm-fadnavis-flag-off-namo-yuva-run-in-mumbai/21092025</t>
+          <t>https://www.footboom1.com/en/news/football/2752001-lionel-messi-s-confirmed-visit-to-maharashtra-sparks-excitement</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/mumbai-acharya-devvrat-sworn-in-as-maharashtra-governor-gallery/</t>
+          <t>https://www.latestly.com/quickly/agency-news/acharya-devvrat-sworn-in-as-governor-of-maharashtra-in-presence-of-cm-devendra-fadnavis-7112162.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/condition-about-obtaining-non-agricultural-land-license-should-be-removed-for-msmes-cm-fadnavis/amp/</t>
+          <t>https://www.sakshipost.com/news/zero-tolerance-important-curb-drug-related-crimes-says-cm-fadnavis-454693</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/maharashtra-mahayuti-mva-war-of-words-erupts-rahul-gandhi-vote-theft-congress-demands-devendra-fadnavis-resignation-1801046</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://www.punekarnews.in/cm-devendra-fadnavis-dcm-ajit-pawar-to-inaugurate-amalner-beed-new-railway-line-in-pune-division-on-september-17/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://m.sakshipost.com/amp/news/zero-tolerance-important-curb-drug-related-crimes-says-cm-fadnavis-454693</t>
+          <t>https://www.punekarnews.in/bureaucratic-delays-stall-pune-khadki-cantonment-merger-despite-maharashtra-cms-nod/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/cm-devendra-fadnavis-dcm-ajit-pawar-to-inaugurate-amalner-beed-new-railway-line-in-pune-division-on-september-17/</t>
+          <t>https://www.latestly.com/quickly/agency-news/devendra-fadnavis-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane-7123779.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/bureaucratic-delays-stall-pune-khadki-cantonment-merger-despite-maharashtra-cms-nod/</t>
+          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maharashtra-cm-fadnavis-inaugurates-new-amalner-beed-railway-line-453629</t>
+          <t>https://www.punekarnews.in/cm-fadnavis-flags-poor-road-conditions-in-pune-raises-alarm-over-potholes/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://newsd.in/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/</t>
+          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://bhaskarlive.in/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi/</t>
+          <t>https://english.newsnationtv.com/national/general-news/mumbai-union-minister-pralhad-joshi-maharashtra-cm-fadnavis-inaugurate-steel-mahakumbh20250919211944</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/21/namo-yuva-run-in-mumbai-gallery/</t>
+          <t>https://english.publictv.in/acharya-devvrat-sworn-in-as-new-governor-of-maharashtra-succeeding-cp-radhakrishnan/</t>
         </is>
       </c>
     </row>
@@ -1306,14 +1306,14 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-devendra-fadnavis-shares-story-of-first-meeting-with-pm-narendra-modi-ws-kl-9629275.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-sharad-pawar-devendra-fadnavis-engaged-in-a-war-of-words-over-maratha-obc-reservation-ws-l-9622419.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/india-news/maharashtra-cm-devendra-fadnavis-inaugurated-the-amalner-beed-railway-line-in-beed/</t>
+          <t>https://www.msn.com/hi-in/news/other/mva-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%B0-%E0%A4%A8-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%AB%E0%A5%8D%E0%A4%A4-%E0%A4%B0-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%A5-sit-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%9C-%E0%A4%82%E0%A4%9A/ar-AA1ybCn1?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
@@ -1327,3752 +1327,3878 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-launched-various-csr-projects-of-hyundai-motor-india-ltd-in-mumbai-meeting-with-md-unsoo-kim-3013038</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%BF%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%A8-4/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-trouble-for-devendra-fadnavis-obc-banjara-protest-against-maratha-reservation-maharashtra-politics-ws-ln-9621475.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-devendra-fadnavis-compared-rahul-gandhi-to-hitlers-minister-saying-rahul-gandhis-hydrogen-bomb-is-a-dud/articleshow/123991146.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-launched-various-csr-projects-of-hyundai-motor-india-ltd-in-mumbai-meeting-with-md-unsoo-kim-3013038</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-shared-story-how-he-impressed-form-pm-narendra-modi-ahead-of-75th-birthday-rss-nagar-visit-know-all/articleshow/123913706.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-devendra-fadnavis-compared-rahul-gandhi-to-hitlers-minister-saying-rahul-gandhis-hydrogen-bomb-is-a-dud/articleshow/123991146.cms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-solapur-air-service-will-begin-from-15th-october-2025-cm-devendra-fadnavis-on-flight-service-3016029/amp</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-devendra-fadnavis-shares-story-of-first-meeting-with-pm-narendra-modi-ws-kl-9629275.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%97-%E0%A4%A8-%E0%A4%97-%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A4%B8-%E0%A4%A4%E0%A4%82%E0%A4%9C-%E0%A4%A4-%E0%A4%AD%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%90%E0%A4%B8-%E0%A4%89%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A6-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%A5/ar-AA1MJlsa</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-shared-story-how-he-impressed-form-pm-narendra-modi-ahead-of-75th-birthday-rss-nagar-visit-know-all/articleshow/123913706.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%95-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%AB-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95-%E0%A4%9D%E0%A4%9F%E0%A4%95/ar-AA1M5pB5?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-cm-devendra-fadnavis-wishi-pm-narendra-modi-on-75th-birthday-mumbai-3014251</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%95-%E0%A4%95%E0%A4%AE-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%8F-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1La6Vu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/cm-devendra-fadnavis-announces-metro-to-start-between-csmt-and-thane-date-announced/articleshow/124058765.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-sharad-pawar-warn-devendra-fadnavis-over-farmers-suicide-said-look-what-happened-in-nepal-2025-09-16-1162916</t>
+          <t>https://www.abplive.com/states/maharashtra/sharad-pawar-ncp-sp-claims-devendra-fadnavis-govt-apathetic-towards-farmers-warned-to-intensify-protests-3013235</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/devendra-fadnavis-%E0%A4%9C-%E0%A4%B8-%E0%A4%AD-%E0%A4%B7-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9A-%E0%A4%A8-%E0%A4%AA-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%B5%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%AB%E0%A4%9F%E0%A4%95-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC-%E0%A4%B2-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1JTdKS?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-shiv-sena-ubt-responds-to-cm-devendra-fadnavis-song-ahead-bmc-election-2025-ann-3014169</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AB-%E0%A4%B2%E0%A5%8D%E0%A4%AE-%E0%A4%9B-%E0%A4%B5-%E0%A4%95-%E0%A4%A4-%E0%A4%B0-%E0%A4%AB-%E0%A4%87%E0%A4%A4-%E0%A4%B9-%E0%A4%B8%E0%A4%95-%E0%A4%B0-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%89%E0%A4%A0-%E0%A4%8F-%E0%A4%B8%E0%A4%B5-%E0%A4%B2/ar-AA1AjRCP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/business/mumbai-financial-capital-chhatrapati-sambhajinagar-become-ev-electric-vehicle-capital-maharashtra-cm-devendra-fadnavis-said-14000-people-get-employment-latur-coach-factory-b507/</t>
+          <t>https://www.punjabkesari.com/india-news/maharashtra-cm-devendra-fadnavis-inaugurated-the-amalner-beed-railway-line-in-beed/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-attacks-rahul-gandhi-accuses-him-of-being-urban-naxal-saying-his-brain-stolen/articleshow/123998386.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-says-bala-saheb-thackeray-was-a-brand-but-uddhav-thackeray-cheated-with-bjp-ann-3013935</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-hindi-news-2025-09-19</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AA-%E0%A4%8F%E0%A4%AE-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%A6-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%95-%E0%A4%AC%E0%A4%A7-%E0%A4%88-%E0%A4%AB-%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%AF%E0%A5%87-%E0%A4%AC-%E0%A4%A4/ar-AA1MFO9P</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-fadnavis-announced-new-flight-between-solapur-to-mumbai-and-bengaluru-flight-from-15-october-know-all-details/articleshow/124016070.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/sharad-pawar-calls-to-devendra-fadnavis-on-bjp-mla-gopichand-statement-201758271903306.html</t>
+          <t>https://www.abplive.com/states/maharashtra/beed-amalner-railway-line-inauguration-by-maharashtra-cm-devendra-fadnavis-3014515</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/devendra-fadnavis-%E0%A4%B5-%E0%A4%9F-%E0%A4%9A-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A6-%E0%A4%AE-%E0%A4%97-%E0%A4%9A-%E0%A4%B0-%E0%A4%B9-%E0%A4%97%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%81%E0%A4%B0-%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%AF-%E0%A4%A4-%E0%A4%96-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1MTRZn</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-maharashtra-cm-reaction-on-pm-modi-address-to-nation-on-gst-reforms-3016450</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-baps-akshardham-temple-goyal-fadnavis-wish-mahant-swamiji-maharaj-on-92nd-birthday-9628582.html</t>
+          <t>https://www.amarujala.com/india-news/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-hindi-news-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir-2025-09-15</t>
+          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AA-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%A8-%E0%A4%97%E0%A4%B0-%E0%A4%95-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%AA%E0%A4%A4-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%96%E0%A4%AC%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%96-%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A4%B9-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1DIcgm?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.tv9hindi.com/videos/maharashtras-development-under-pm-modi-fadnavis-highlights-key-projects-3485056.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/rahul-gandhi-vote-theft-claim-cm-fond-of-rahul-gandhi-s-vote-theft-claims-gives-this-reply-2025-09-19</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-maharashtra-cm-on-trial-run-for-phase-i-of-metro-lines-4-and-4a-in-thane-also-attack-on-mva-3016842</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/nashik-kumbh-2027-%E0%A4%85%E0%A4%97%E0%A4%B2-%E0%A4%95%E0%A5%81%E0%A4%82%E0%A4%AD-%E0%A4%A8-%E0%A4%B8-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B2%E0%A4%97%E0%A5%87%E0%A4%97-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC%E0%A5%9C-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AF-%E0%A4%97%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%B2%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8-%E0%A4%B9-%E0%A4%97/ar-AA1Bu9g4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-attacks-rahul-gandhi-accuses-him-of-being-urban-naxal-saying-his-brain-stolen/articleshow/123998386.cms</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/entertainment/bollywood/maharashtra-cm-devendra-fadnavis-says-hindi-films-fail-to-depict-true-heroism-of-mumbai-police-2025-09-20?src=top-subnav</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-first-underground-metro-from-cuffe-parade-pm-narendra-modi-inugrate-cm-devendra-fadnavis-maharashtra-mmrc-3013836</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-mla-gopichand-padalkar-statement-sparked-uproar-in-maharashtra-devendra-fadnavis-calling-for-restraint/articleshow/124002748.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-nationalist-congress-party-ncp-president-ajit-pawar-cm-devendra-fadnavis-nitin-gadkari-maharashtra-local-poll-vidarbha-politics-9642156.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%B0-%E0%A4%AC-80-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%97%E0%A4%B2%E0%A5%87-%E0%A4%B8-%E0%A4%B2-%E0%A4%A6-%E0%A4%B8%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%A4%E0%A4%95-%E0%A4%AE%E0%A5%81%E0%A4%AB%E0%A5%8D%E0%A4%A4-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%AC-%E0%A4%9C%E0%A4%B2-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%8F%E0%A4%B2-%E0%A4%A8/ar-AA1CPNKL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/hi-in/news/other/devendra-fadnavis-%E0%A4%B5-%E0%A4%9F-%E0%A4%9A-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A6-%E0%A4%AE-%E0%A4%97-%E0%A4%9A-%E0%A4%B0-%E0%A4%B9-%E0%A4%97%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%81%E0%A4%B0-%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%AF-%E0%A4%A4-%E0%A4%96-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1MTRZn?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/aditya-thackeray-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AE-%E0%A4%A1%E0%A4%BC-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%87-%E0%A4%B8-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%9F-%E0%A4%AE-%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%85%E0%A4%AC-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1IW0iz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%B8%E0%A4%A8%E0%A4%B2-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AB-%E0%A4%95-%E0%A4%9B%E0%A5%81%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%9C-%E0%A4%82%E0%A4%9A-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1zIR9b?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95-%E0%A4%9C%E0%A4%B5-%E0%A4%AC-%E0%A4%95%E0%A4%B9-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%95%E0%A5%87-%E0%A4%9C-%E0%A4%86%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%93%E0%A4%AC-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1MwFWu</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-fadnavis-announced-new-flight-between-solapur-to-mumbai-and-bengaluru-flight-from-15-october-know-all-details/articleshow/124016070.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-2025-09-15</t>
+          <t>https://www.livehindustan.com/maharashtra/sharad-pawar-calls-to-devendra-fadnavis-on-bjp-mla-gopichand-statement-201758271903306.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/ncp-sharad-pawar-slams-devendra-fadnavis-government-claim-40-lakh-spent-on-cm-residence-19955838</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B5-%E0%A4%95-%E0%A4%AA-%E0%A4%A1-%E0%A4%AF-%E0%A4%AA%E0%A4%B0-%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%85%E0%A4%A8-%E0%A4%AA-%E0%A4%B6%E0%A4%A8-%E0%A4%AA-%E0%A4%95-%E0%A4%B8%E0%A4%A8%E0%A5%87-%E0%A4%B2-%E0%A4%96-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%AF-%E0%A4%B9%E0%A4%9F%E0%A4%B5-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1zhEO3?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-hindi-news-2025-09-19?src=top-subnav</t>
+          <t>https://www.msn.com/hi-in/news/other/bullet-train-project-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%85%E0%A4%B9%E0%A4%AE%E0%A4%A6-%E0%A4%AC-%E0%A4%A6-%E0%A4%AC%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%9F-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A4%AC-%E0%A4%B9-%E0%A4%97-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AC%E0%A5%9C-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1DPcCq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%AB-%E0%A4%B2%E0%A5%8D%E0%A4%AE-%E0%A4%9B-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%96%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1Al3WQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-baps-akshardham-temple-goyal-fadnavis-wish-mahant-swamiji-maharaj-on-92nd-birthday-9628582.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8%E0%A4%AC%E0%A5%82%E0%A4%A4-%E0%A4%A6%E0%A5%87%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%AD-%E0%A4%AD%E0%A5%8D%E0%A4%B0%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%B0%E0%A4%B9-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A4%97-%E0%A4%AF-%E0%A4%86%E0%A4%B0-%E0%A4%AA/ar-AA1KlkJI?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.lokmatnews.in/business/mumbai-financial-capital-chhatrapati-sambhajinagar-become-ev-electric-vehicle-capital-maharashtra-cm-devendra-fadnavis-said-14000-people-get-employment-latur-coach-factory-b507/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/maharashtra-government-signs-mou-with-cambridge-university-press-and-assessment-india-to-improve-school-education-11676</t>
+          <t>https://www.amarujala.com/india-news/fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97%E0%A4%AA%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B6-%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AB-%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%96%E0%A5%87%E0%A4%B2-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%85%E0%A4%9F%E0%A4%95%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%A4%E0%A5%87%E0%A4%9C-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B2-%E0%A4%B0%E0%A4%B9-%E0%A4%B9%E0%A5%88/ar-AA1wZDM7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.abplive.com/states/maharashtra/sharad-pawar-phone-call-to-cm-devendra-fadnavis-on-bjp-mla-gopichand-padalkar-remarks-3015443</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/story/sharad-pawar-ncp-sp-responded-to-bjp-devabhau-campaign-with-deva-tuch-saang-aid-ntc-rpti-2334011-2025-09-15</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/rahul-gandhi-vote-chori-controversy-maharashtra-fadnavis-resignation-congress-bjp-ntc-dskc-2336442-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/fadnavis-on-congress-%E0%A4%B8%E0%A4%82%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%95-%E0%A4%A8%E0%A5%88%E0%A4%B0%E0%A5%87%E0%A4%9F-%E0%A4%B5-%E0%A4%A7%E0%A5%8D%E0%A4%B5%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%9D%E0%A5%82%E0%A4%A0-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%A6-%E0%A4%A8-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%9F-%E0%A4%95%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%A4-%E0%A4%96-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1txBPv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/pm-modi-75th-birthday-devendra-fadnavis-shared-how-he-was-impressed-with-narendra-modi-in-1st-meetin-1387117.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B2-%E0%A4%89%E0%A4%A1%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%B9-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A5%E0%A4%B2-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95-%E0%A4%A4%E0%A4%A8%E0%A5%87-%E0%A4%B9%E0%A4%9F-%E0%A4%8F-%E0%A4%97%E0%A4%8F/ar-AA1IstKE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-mla-gopichand-padalkar-statement-sparked-uproar-in-maharashtra-devendra-fadnavis-calling-for-restraint/articleshow/124002748.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/fadnavis-slams-rahul-gandhi-over-election-allegations-calls-him-a-habitual-liar-90060</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/cm-fadnavis-joins-7000-people-in-namo-yuva-run-in-mumbai/articleshow/124030814.cms</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/national-hindi-news/devendra-fadnavis-targeted-rahul-gandhi-125091900062_1.html</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/ladki-behen-yojana-will-not-be-discontinued-committed-to-empowering-women-11648</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/police-recruitment-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%97%E0%A5%81%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A5%87-15000-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%A6-%E0%A4%AE%E0%A4%82%E0%A4%9C%E0%A5%82%E0%A4%B0/ar-AA1KnJ9O?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%85%E0%A4%AE%E0%A4%B0-%E0%A4%B5%E0%A4%A4-%E0%A4%B9%E0%A4%B5-%E0%A4%88-%E0%A4%85%E0%A4%A1%E0%A5%8D%E0%A4%A1%E0%A5%87-%E0%A4%95-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%98-%E0%A4%9F%E0%A4%A8/ar-AA1D2CP2?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/law-and-order-effective-implementation-cm-fadanviphp/cid17447208.htm</t>
+          <t>https://www.patrika.com/mumbai-news/sharad-pawar-called-devendra-fadnavis-complained-about-bjp-mla-19958470</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/obc-activists-show-black-flags-to-cm-devendra-fadnavis-attempt-self-immolation-in-front-of-deputy-cm-ajit-pawar-convoy-201758158508899.html</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/pod-taxis-to-run-in-mumbai-fadnavis-announces-11728</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%95%E0%A5%87-cm-devendra-fadnavis-%E0%A4%95-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-nep-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A3-%E0%A4%B2-%E0%A4%95-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%AF%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B9%E0%A5%88/ar-AA1BYWWq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aajtak.in/india/news/story/sharad-pawar-ncp-sp-responded-to-bjp-devabhau-campaign-with-deva-tuch-saang-aid-ntc-rpti-2334011-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B9-%E0%A4%AE%E0%A5%8D%E0%A4%AE%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%A4-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%95-%E0%A4%95%E0%A4%AC%E0%A5%8D%E0%A4%B0-%E0%A4%B9%E0%A4%9F-%E0%A4%93-%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%96-%E0%A4%93-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B9%E0%A5%81%E0%A4%B8%E0%A5%88%E0%A4%A8-%E0%A4%A6%E0%A4%B2%E0%A4%B5%E0%A4%88-%E0%A4%A8%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%9A%E0%A5%88%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9C/ar-AA1BqMnJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-s-politics-rises-due-to-rahul-s-claims-on-vote-theft-congress-says-fadnavis-should-resign-2025-09-18</t>
+          <t>https://hindi.webdunia.com/national-hindi-news/devendra-fadnavis-targeted-rahul-gandhi-125091900062_1.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%9F-%E0%A4%9A-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%B8-%E0%A4%B0-%E0%A4%AF%E0%A4%B2-%E0%A4%B2-%E0%A4%AF%E0%A4%B0-%E0%A4%B9%E0%A5%88/ar-AA1L9M5X?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%B8%E0%A4%8F%E0%A4%AE%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%A0-%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%B9-%E0%A4%97-%E0%A4%AE%E0%A5%87%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%A4-%E0%A4%B0-%E0%A4%96-%E0%A4%AD-%E0%A4%AC%E0%A4%A4-%E0%A4%A6/ar-AA1N5LIg?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-pm-modi-is-a-leader-who-prefers-simplicity-devendra-fadnavis-shared-a-special-video-news-hindi-1-753193-KKN.html</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-s-politics-rises-due-to-rahul-s-claims-on-vote-theft-congress-says-fadnavis-should-resign-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%97-%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A4%97%E0%A5%87%E0%A4%97-%E0%A4%AE%E0%A4%95-%E0%A4%95-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%95%E0%A4%B9-%E0%A4%9C-%E0%A4%A8-%E0%A4%B2-%E0%A4%9C-%E0%A4%8F/ar-AA1BkgKd?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%B8%E0%A4%AE%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%89%E0%A4%A6-%E0%A4%B8-%E0%A4%A8-%E0%A4%B9%E0%A5%88-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1MzRC1</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/fadnavis-promises-rehabilitation-plan-for-elphinstone-residents-11705</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/bjp-mla-s-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm-2025-09-19</t>
+          <t>https://www.livehindustan.com/maharashtra/obc-activists-show-black-flags-to-cm-devendra-fadnavis-attempt-self-immolation-in-front-of-deputy-cm-ajit-pawar-convoy-201758158508899.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/chief-minister-fadnavis-should-resign-after-rahul-gandhis-revelation-of-vote-theft-in-maharashtra-sapkal/870326/</t>
+          <t>https://vocaltv.in/national/law-and-order-effective-implementation-cm-fadanviphp/cid17447208.htm</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/videos/news/maharashtra-cm-devendra-fadnavis-criticizes-bollywood-for-inaccurate-mumbai-police-portrayal-at-indian-police-foundation-2025-event-3016051/amp</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%B8%E0%A5%81%E0%A4%A7-%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%B5%E0%A5%83%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%95-%E0%A4%97%E0%A4%A4-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1N0XA9?ocid=finance-verthp-feeds</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%A8-%E0%A4%B9-%E0%A4%97-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-cm-%E0%A4%9C-%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%9C-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A5%81%E0%A4%B2-%E0%A4%88-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%82-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95/ar-AA1uE4o5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://rajneetiguru.com/%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A5%80-%E0%A4%86%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%BF%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%9F%E0%A4%BF%E0%A4%AA%E0%A5%8D%E0%A4%AA/</t>
+          <t>https://www.amarujala.com/india-news/bjp-mla-s-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/maharashtra-govt-issued-kunbi-certificates-in-five-marathwada-districts-on-liberation-day/articleshow/123961774.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-cm-devendra-fadnavis-pod-taxi-last-mile-connectivity-transport-update-ann-3017094</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/opinion-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A0%E0%A4%B9-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%97-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%B5-%E0%A4%B0-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%9B-%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95-%E0%A4%B9-%E0%A4%97-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%B0/ar-AA1w1TqU?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/banjara-community-should-be-included-in-st-category/</t>
+          <t>https://mandalnews.com/amravati/dhangar-community-should-get-st-certificate-otherwise-hunger-strike/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
+          <t>https://hindi.theprint.in/india/maharashtra-government-will-create-a-fund-for-treatment-costing-more-than-rs-5-lakh-fadnavis/869009/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
+          <t>https://hindi.theprint.in/india/rahul-gandhi-speaks-like-an-urban-naxal-fadnavis/870800/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/farmers-should-paid-some-money-uddhav-thakre.php</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B2-%E0%A4%95%E0%A4%B2%E0%A5%81%E0%A4%AD-%E0%A4%B5%E0%A4%A8-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A5%82%E0%A4%82%E0%A4%9C-%E0%A4%A8-%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1Av3BQ?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/amp/programmes/mumbai-metro/video/meena-tai-thackeray-memorial-vandalism-bmc-elections-frvd-2335927-2025-09-18</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/metro-4-corridor-trial-run-starts-today-ghodbunder-road-commute-to-be-easier/articleshow/124031334.cms</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-battle-for-seats-in-the-mahagathbandhan-intensifies-vidarbha-is-not-the-fiefdom-of-bjp-fadnavis/</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-gopichand-padalkar-controversial-remark-on-jayant-patil-sharad-pawar-reaction-9642900.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
+          <t>https://hindi.business-standard.com/india-news/maharashtra/mumbai-people-will-get-relief-from-traffic-jam-soon-pod-taxi-service-will-start-id-473799</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/protests-erupt-in-maharashtra-over-reservation-issue-obc-activists-show-black-flags-to-fadnavis-attempt-suicide/</t>
+          <t>https://navbharattimes.indiatimes.com/lifestyle/fashion/maharashtra-cm-wife-amruta-fadnavis-beautiful-photos-in-peach-banarasi-tissue-silk-saree-at-screening/articleshow/124040076.cms</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/former-mla-exposes-fadnaviss-transparent-work/</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/maharashtra-govt-issued-kunbi-certificates-in-five-marathwada-districts-on-liberation-day/articleshow/123961774.cms</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/ruckus-over-gen-z-statement-fadnavis-says-rahul-gandhi-given-evidence-of-urban-naxal-thinking</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-bombay-high-court-hyderabad-gazette-gr-plea-reject-obc-reservation-sharad-pawar-suicide-nanded-clash-know-all/articleshow/123999053.cms</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/maharashtra/maharashtra-news-fadnavis-government-bjp-government-government-vehicles-cm-vehicles-governor-vehicles-gst-vehicle-tax-registration-fee-1188430</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%95-%E0%A4%AC%E0%A4%A7-%E0%A4%88-%E0%A4%A6-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%A6%E0%A5%82%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1MJ71H</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://lalluram.com/sharad-pawar-reminded-cm-fadnavis-of-rajdharma-appealed-for-complete-loan-waiver-of-farmers-warned-and-said-the-situation-should-not-become-like-nepal/</t>
+          <t>https://mandalnews.com/amravati/banjara-community-should-be-included-in-st-category/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/mahayuti-government-trapped-in-the-maze-of-reservation/</t>
+          <t>https://www.amarujala.com/india-news/51-students-from-maharashtra-will-visit-nasa-students-who-win-the-science-competition-will-get-a-chance-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-expressed-gratitude-after-prime-minister-modis-speech-4277895</t>
+          <t>https://www.patrika.com/mumbai-news/uddhav-thackeray-mother-meenatai-statue-colour-thrown-accused-upendra-pawaskar-held-19954266</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/sharad-pawar-led-an-akrosh-morcha-in-nashik-demands-complete-loan-waiver-for-farmers-swm-1278008-2025-09-15</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-government-changed-the-name-of-ahmednagar-railway-station-to-ahilyanagar-1387233.html</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/fadnavis-praised-pm-modis-working-style-4271099</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-doctors-strike-1-8-lakh-allopathic-doctors-protest-against-fadnavis-government-decision-1388823.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/chhatrapati-sambhajinagar-will-become-the-electric-vehicle-capital-of-the-country-fadnavis-3255721.html</t>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-cm-devendra-fadnavis-in-new-tension-over-quota-clash-maratha-vs-obc-banjara-vs-tribal-community-politics-201757910651491.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/others/rahul-gandhis-hydrogen-bomb-turned-out-to-be-a-dud-cm-fadnavis-4272872</t>
+          <t>https://hindi.theprint.in/india/western-naval-command-chief-meets-fadnavis-discusses-maritime-security-situation/871381/?amp</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://navyugsandesh.com/devendra-fadnavis-took-a-dig-at-rahul-gandhis-hydrogen-bomb-statement/</t>
+          <t>https://hindi.news18.com/news/nation/maratha-reservation-sharad-pawar-mahayuti-govt-maharashtra-cm-devendra-fadnavis-9622532.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-fadnavis-government-took-8-important-decisions-including-doubling-the-allowance-of-students/</t>
+          <t>https://www.bhaskarhindi.com/state/maharashtra/maharashtra-news-fadnavis-government-bjp-government-government-vehicles-cm-vehicles-governor-vehicles-gst-vehicle-tax-registration-fee-1188430</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/maharashtra-should-become-a-best-model-for-new-industries/?amp=1</t>
+          <t>https://24city.news/when-devendra-fadnavis-yaad-was-surprised-to-hear-this-of-narendra-modi-his-first-meeting/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3633329-fadnavis-accuses-rahul-gandhi-of-urban-maoist-rhetoric?amp</t>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-pm-modi-is-a-leader-who-prefers-simplicity-devendra-fadnavis-shared-a-special-video-news-hindi-1-753193-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level-fadnavis/2934307</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharastra-cm-fadnavis-pushes-for-faster-industrial-approvals-ai-based-reforms-to-boost-investments-23594849</t>
+          <t>https://raftaar.in/news/national/maharashtra-cm-devendra-fadnavis-took-a-dig-at-the-opposition-especially-the-shiv-sena-ubt-faction-by-singing-a-song</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3631374-controversy-surrounds-delayed-unveiling-of-swami-ramanand-tirtha-statue?amp</t>
+          <t>https://jantaserishta.com/local/maharashtra/all-phases-of-the-metro-will-be-open-for-passengers-by-the-end-of-2026-devendra-fadnavis-4279721</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mlas-remarks-about-ncp-sp-leader-23594821</t>
+          <t>https://lalluram.com/sharad-pawar-reminded-cm-fadnavis-of-rajdharma-appealed-for-complete-loan-waiver-of-farmers-warned-and-said-the-situation-should-not-become-like-nepal/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/rahul-gandhi-speaks-like-an-urban-maoist-says-maharashtra-cm-fadnavis-on-congress-leaders-gen-z-post-23594827</t>
+          <t>https://www.hindisaamana.com/the-public-has-no-food-there-is-no-money-in-the-treasury-the-chief-minister-has-a-bed-worth-rs-20-lakh/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/reduce-number-of-permissions-to-set-up-industries--speed-up-approval-time--fadnavis-to-officials/2930550</t>
+          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-expressed-gratitude-after-prime-minister-modis-speech-4277895</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004</t>
+          <t>https://hindi.latestly.com/quickly/india/devendra-fadnavis-on-pm-modi-pm-modi-is-a-leader-who-prefers-simplicity-devendra-fadnavis-shared-a-special-video-2755431.html</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop-Fadnavis/2927696</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/sharad-pawar-raging-on-the-issue-of-maharashtra-farmers/article-105258</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/obcs-disrupt-cm-s-speech-holds-huge-rally-in-hingoli-101758137116445-amp.html</t>
+          <t>https://joindia.co.in/news/sharad-pawar-calls-devendra-fadnavis-expresses-objection-to-controversial-statement/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/aiifa-steelex-2025-maharashtra-chief-minister-devendra-fadnavis-and-union-minister-pralhad-joshi-inaugurate-the-steel-mahakumbh/</t>
+          <t>https://www.hindisaamana.com/the-conflict-between-the-bjp-and-shinde-factions-escalates-in-thane-district/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114</t>
+          <t>https://hindi.latestly.com/india/video-ahead-of-bmc-polls-fadnavis-targets-uddhav-with-accha-sila-diya-jibe-2756036.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114?news-breakingnews</t>
+          <t>https://jantaserishta.com/local/maharashtra/fadnavis-praised-pm-modis-working-style-4271099</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630398-bjps-enduring-commitment-fadnavis-recollects-2017-political-maneuverings-in-mumbai?amp</t>
+          <t>https://hindi.latestly.com/india/pm-modi-to-inaugurate-mumbai-metro-3-worli-cuffe-parade-stretch-on-sept-30-2755975.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628615-maharashtra-govt-will-create-corpus-fund-to-cover-treatments-costing-over-rs-5-lakh-fadnavis</t>
+          <t>https://indiagroundreport.com/mumbai-fadnavis-government-took-8-important-decisions-including-doubling-the-allowance-of-students/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/namo-yuva-run-held-nationwide-to-mark-pm-modi-s-75th-birthday-23595077</t>
+          <t>https://up18news.com/free-solar-power-to-every-farmer-by-2026-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/acharya-devvrat-sworn-in-as-new-governor-of-maharashtra-succeeding-cp-radhakrishnan20250915124042</t>
+          <t>https://hindi.gyanhigyan.com/auto/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A4%B0%E0%A4%BF%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%A8%E0%A4%BE%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-21000-%E0%A4%95%E0%A4%B0%E0%A5%8B%E0%A4%A1%E0%A4%BC-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A4%BE/cid17430694.htm</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/health/news/maha-govt-approves-corpus-fund-for-health-treatment-of-over-rs-5-lakh-says-cm-fadnavis-297657</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114?news-breakingnews</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/acharya-devvrat-sworn-in-as-governor-of-maharashtra-in-presence-of-cm-devendra-fadnavis-7112162.html</t>
+          <t>https://www.punjabnewsexpress.com/health/news/maha-govt-approves-corpus-fund-for-health-treatment-of-over-rs-5-lakh-says-cm-fadnavis-297657</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/sambhajinagar-becoming-ev-capital-of-country-fadnavis/articleshow/123952619.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maharashtra-play-major-role-pms-mission-green-steel-cm-fadnavis-454325</t>
+          <t>https://sundayguardianlive.com/entertainment-news/hindi-films-fail-to-depict-the-true-heroism-of-mumbai-police-says-maharashtra-cm-fadnavis20250920135931-143844/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/milind-soman-flags-off-namo-yuva-run-in-mumbai-says-its-pm-modis-dream-to-make-india-drug-free/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/cm-devendra-fadnavis-online-system-based-on-ai-developed-for-obtaining-building-permits-required-by-industries-995520.html</t>
+          <t>https://www.financialexpress.com/india-news/maharashtra-to-appoint-new-advocate-general-as-birendra-saraf-resigns-citing-personal-reasons/3979732/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/cm-devendra-fadnavis-media-brief/941116</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480/6</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/sports/lionel-messi-gives-cm-devendra-fadnavis-a-special-gift-of-signed-footbal-will-also-come-to-mumbai-for-a-visit-1385826</t>
+          <t>https://www.dailypioneer.com/2025/india/congress-demands-apology-from-fadnavis-for-shivaji-poster.html</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/cm-devendra-fadnavis-reaction-on-maratha-reservation-kunbi-certificates/articleshow/123993122.cms</t>
+          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/chandrapur/shiv-sena-ubt-protest-in-chandrapur-over-place-of-banner-of-cm-devendra-fadnavis-and-chhatrapati-shivaji-maharaj/articleshow/124000637.cms</t>
+          <t>https://thenewsmill.com/2025/09/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/devendra-fadnavis-preached-gopichand-padalkar-over-his-controversial-statement-284593/</t>
+          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-talk-on-sharad-pawar-phone-call-about-gopchand-padalkar-statement/articleshow/123994142.cms</t>
+          <t>https://news.abplive.com/cities/mumbai-balasaheb-thackeray-wife-meenatai-statue-defaced-1-arrested-1800879</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/gopichand-padalkar-clarification-on-his-statement-about-jayant-patil-after-receiving-a-call-from-cm-devendra-fadnavis/articleshow/123994231.cms</t>
+          <t>https://thenewsmill.com/2025/09/milind-soman-flags-off-namo-yuva-run-in-mumbai-says-its-pm-modis-dream-to-make-india-drug-free/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/devendra-fadnavis-dreaming-of-becoming-prime-minister-says-harshwardhan-sapkal/</t>
+          <t>http://marathi.factcrescendo.com/old-altered-video-viral-as-cm-fadnavis-did-not-believe-in-indian-constitution-democracy/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/devendra-fadnavis-speech-at-chhatrapati-sambhajinagar-obc-activists-slogans-during-cm-speech-at-marathwada-mukti-sangram-din-program-marathi-news-1384714</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashatra-news-live-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A4%B9-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%85%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1MRBRN</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-advice-to-gopichand-padalkar-after-receiving-a-call-from-sharad-pawar-for-making-objectionable-comments-on-jayant-patil/923124/</t>
+          <t>https://marathi.ndtv.com/cities/pm-modi-birthday-cm-fadnavis-reminisces-share-experienc-of-first-meeting-with-pm-modi-9291188</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/pm-modi-birthday-cm-fadnavis-reminisces-share-experienc-of-first-meeting-with-pm-modi-9291188</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://zeenews.india.com/marathi/video/cm-devendra-fadnavis-media-brief/941116</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/manoj-jarange-admire-maharashtra-cm-devendra-fadnavis-after-maratha-reservation-protest-1481999.html</t>
+          <t>https://www.msn.com/mr-in/news/other/kunbi-certificate-%E0%A4%96-%E0%A4%A1-%E0%A4%96-%E0%A4%A1-%E0%A4%95-%E0%A4%97%E0%A4%A6%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A7-%E0%A4%B0%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%A6-%E0%A4%96%E0%A4%B2%E0%A5%87-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A4%B0%E0%A4%A3/ar-AA1MMluT?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-directed-that-guidelines-should-be-issued-by-amending-the-criteria-of-the-solar-agricultural-pump-scheme-as-per-the-demands-of-the-farmers-local18-1483770.html</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%A7%E0%A4%A1-%E0%A4%95%E0%A5%87%E0%A4%AC-%E0%A4%9C-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MDXwL</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%A7%E0%A4%A1-%E0%A4%95%E0%A5%87%E0%A4%AC-%E0%A4%9C-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MDGd1</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/gopichand-padalkar-clarification-on-his-statement-about-jayant-patil-after-receiving-a-call-from-cm-devendra-fadnavis/articleshow/123994231.cms</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/21/mumbaikars-run-towards-a-drug-free-india-namo-yuva-run-receives-overwhelming-response-will-intoxicate-our-yout.html</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%B5-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97%E0%A4%B8-%E0%A4%A0-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1ME6vc</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ncp-pune-city-president-prashant-jagtap-criticizes-bjp-mla-gopichand-padalkar/articleshow/123990567.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/aurangabad/beed/news/beed-railway-ignoration-cm-devendra-fadnavis-speech-135942485.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/television-news/devendra-fadnavis-watch-maharashtrachi-hasya-jatra-says-samir-choughule-in-mhj-unplugged/articleshow/123995979.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B2%E0%A4%9A-%E0%A4%B2-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9C%E0%A4%B5%E0%A4%B3%E0%A4%9A%E0%A5%87-3-%E0%A4%AC%E0%A4%A1%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%B2/ar-AA1yK0Ky?cvid=6B345CC548B8475D94F9EB8EE0C8C751&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/navi-mumbai/bjp-leader-haresh-keni-joins-congress-shocks-devendra-fadnavis-prashant-thakur-ahead-of-panvel-municipal-election/articleshow/124013605.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-slams-raj-uddhav-thackeray-mumbai-bmc-election-narendra-modi-brand-maharashtra-politics-1384645</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-nashik-journalist-assault-cm-devendra-fadnavis-orders-strict-action-case-filing-process-initiated-against-assailants-1385488/amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-claim-that-milind-narvekar-phone-call-him-and-said-uddhav-thackeray-was-upset/articleshow/123927047.cms</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-kamboj-allegations-sakkale-accuses-devendra-fadnavis-of-pm-ambition-empowering-mohit-kamboj-and-giving-mumbai-to-adani-1385640</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava/articleshow/123926617.cms</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-inspects-nashik-and-surrounding-areas-in-the-backdrop-of-kumbh-mela-gives-important-instructions-local18-1483785.html</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-called-devendra-fadnavis-and-complained-about-gopichand-padalkar-jayant-patil-maharashtra-politics-marathi-news-1385183</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-reaction-on-rahul-gandhi-allegations-bogus-voting-in-chandrapur-rajura-1483022.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/harshwardhan-sapkal-accuses-maharashtra-cm-devendra-fadnavis-of-election-fraud-calls-him-thief-cm-during-press-conference/</t>
+          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/farmer-scheme-cm-devendra-fadnavis-instructions-to-change-the-criteria-of-solar-agricultural-pump-scheme/923274/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/cm-devendra-fadnavis-reaction-on-maratha-reservation-kunbi-certificates/articleshow/123993122.cms</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/beed-news-chief-minister-devendra-fadnavis-and-deputy-chief-minister-ajit-pawar-visit-beed-dangerous-electrical-generator-covered-with-cloth-in-beed-1384811</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-slams-uddhav-and-raj-thackeray-over-thackeray-brand/articleshow/123927266.cms</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/devendra-fadnavis-assures-on-hyderabad-liberation-day-marathwada-water-shortage-will-be-resolved/articleshow/123963714.cms</t>
+          <t>https://news18marathi.com/maharashtra/manoj-jarange-admire-maharashtra-cm-devendra-fadnavis-after-maratha-reservation-protest-1481999.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/devendra-fadnavis-is-messiah-of-obc-community-praises-minister-chhagan-bhujbal/articleshow/123987624.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AA-%E0%A4%9A%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A6%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%87-%E0%A4%8F%E0%A4%95-%E0%A4%A4%E0%A4%B0%E0%A5%82%E0%A4%A3/ar-AA1MSJPR</t>
+          <t>https://prahaar.in/2025/09/18/brand-vs-brandy-war-of-words-between-fadnavis-thackeray-faction-politics-heats-up/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-talk-on-sharad-pawar-phone-call-about-gopchand-padalkar-statement/articleshow/123994142.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/congress-state-president-harshvardhan-sapkal-criticize-devendra-fadnavis-rss-narendra-modi/articleshow/124023628.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%A3%E0%A4%A4-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%AE%E0%A4%A6-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%B7-%E0%A4%B5%E0%A4%B0-%E0%A4%96%E0%A4%B2%E0%A4%AC%E0%A4%A4%E0%A4%82/ar-AA1IC7SW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bacchu-kadu-criticizes-on-prime-minister-narendra-modi-and-chief-minister-devendra-fadnavis-on-agriculture-issue-1385079</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AA-%E0%A4%9A%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%B8%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%A8-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AB-%E0%A4%A8/ar-AA1MSNkK</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-at-bjp-vijay-sankalp-melava/videoshow/123937912.cms</t>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-recalled-the-demand-declaring-a-wet-drought-made-by-devendra-fadnavis-and-ajit-pawar-when-they-were-the-leader-of-opposition-1386183</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/</t>
+          <t>https://marathi.abplive.com/news/devendra-fadnavis-speech-at-chhatrapati-sambhajinagar-obc-activists-slogans-during-cm-speech-at-marathwada-mukti-sangram-din-program-marathi-news-1384714</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>http://marathi.factcrescendo.com/old-altered-video-viral-as-cm-fadnavis-did-not-believe-in-indian-constitution-democracy/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ncp-pune-city-president-prashant-jagtap-criticizes-bjp-mla-gopichand-padalkar/articleshow/123990567.cms</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nana-patole-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AE-%E0%A4%9D%E0%A5%87-%E0%A4%A6-%E0%A4%A8%E0%A4%9A-%E0%A4%AE-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A4%9C%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%A6%E0%A5%81%E0%A4%B8%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%A8-%E0%A4%A8-%E0%A4%AA%E0%A4%9F-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%B6%E0%A5%8D%E0%A4%95-%E0%A4%B2-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%AA%E0%A4%A3/ar-AA1sxB7K?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-for-giving-30-sara-projects-to-mohit-kamboj/921930/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-slam-gopichand-padalkar-over-his-controversial-statement-on-jayant-patil-special-report-1483793.html</t>
+          <t>https://marathi.abplive.com/news/beed/devendra-fadnavis-beed-railway-inaguration-programme-train-dedicated-to-gopinath-munde-marathi-1384797</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-kamboj-allegations-sakkale-accuses-devendra-fadnavis-of-pm-ambition-empowering-mohit-kamboj-and-giving-mumbai-to-adani-1385640</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/18/brand-vs-brandy-war-of-words-between-fadnavis-thackeray-faction-politics-heats-up/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/nashik-nationalist-party-sharad-pawar-group-aakrosh-morcha-mla-rohit-pawar-criticizes-chief-minister-devendra-fadnavis/articleshow/123919393.cms</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%A6-%E0%A4%A8-%E0%A4%AE-%E0%A4%A0%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%86%E0%A4%A3%E0%A4%96-%E0%A4%A6-%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%A5-%E0%A4%A8%E0%A4%95%E0%A5%87/ar-AA1KW2te?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-said-that-devendra-fadnavis-does-not-know-history-has-no-social-knowledge-and-rss-was-not-involved-in-freedom-struggle-but-muslims-were-involved-and-they-were-part-of-the-social-fabric-mah/922681/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-claim-that-milind-narvekar-phone-call-him-and-said-uddhav-thackeray-was-upset/articleshow/123927047.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/india-has-the-potential-to-become-a-global-leader-in-the-field-of-gems-and-jewellery-chief-minister-devendra-f.html</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava/articleshow/123926617.cms</t>
+          <t>https://marathi.abplive.com/photo-gallery/sports/lionel-messi-gives-cm-devendra-fadnavis-a-special-gift-of-signed-footbal-will-also-come-to-mumbai-for-a-visit-1385826</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
+          <t>https://www.tv9marathi.com/videos/cm-devendra-fadnavis-attacks-on-thackeray-brand-and-brothers-accuses-them-of-mishandling-best-elections-1495102.html</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-slams-uddhav-and-raj-thackeray-over-thackeray-brand/articleshow/123927266.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/thousands-of-rupees-were-laundered-during-the-corona-period-devendra-fadnavis-criticizes-thackeray/videoshow/123926314.cms</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/manoj-jarange-patil-warning-cm-devendra-fadanvis-regarding-kunbi-certificate-1484509.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-advice-to-gopichand-padalkar-after-receiving-a-call-from-sharad-pawar-for-making-objectionable-comments-on-jayant-patil/923124/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/what-is-the-new-decision-of-the-state-government-regarding-making-agricultural-land-na-1484003.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-devendra-fadnavis-ek-1384548/amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-leader-manoj-jarange-patil-big-announcement-about-delhi-visit/articleshow/123945687.cms</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-political-tensions-sharad-pawar-calls-cm-devendra-fadnavis-over-bjp-mla-gopichand-padalkar-s-controversial-remarks-against-jayant-patil-in-maharashtra-1385192/amp</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-20-political-news-in-marathi-940632</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AC-%E0%A4%A1%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A7%E0%A4%A8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%A1%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%85%E0%A4%B8-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%96-%E0%A4%95-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%85%E0%A4%B8%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%A4%E0%A5%87%E0%A4%AF-%E0%A4%A4%E0%A5%81%E0%A4%AB-%E0%A4%A8-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A/ar-AA1MJiC2</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/22/indias-longest-elevated-metro-corridor-in-mumbai-information-from-chief-minister-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/amp/mr/politics/mumbai-congress-slams-fadnavis-for-'disrespecting'-shivaji-maharaj-in-billboard-row-90046</t>
+          <t>https://www.mymahanagar.com/mahamumbai/uddhav-thackeray-in-power-the-mumbai-municipal-corporation-during-the-corona-period-committed-a-scam-in-the-body-bags-fadnavis-targets-thackeray/922227/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sharad-pawar-called-cm-devendra-fadnavis-about-gopichand-padalkar-controversial-statement-on-jayant-patil-in-sangli/articleshow/123992055.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/why-cant-they-be-removed-from-the-unruly-gopichand-padalkar-anjali-damania-lashed-out-at-cm-devendra-fadnavis-1385414</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/modi-is-the-biggest-brand-in-the-world-chief-minister-fadnavis-statement/09171621</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mahayuti-has-no-right-to-remain-in-power-fadnavis-should-immediately-give-rajnima-harshvardhan-sapkal-demands-994246.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AB-%E0%A4%A8%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%B8%E0%A5%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%82-%E0%A4%AB-%E0%A4%B0%E0%A4%B2-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AB%E0%A4%9F%E0%A4%95-%E0%A4%B0%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%AC%E0%A4%A6%E0%A4%B2%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MSIyN</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/cm-fadnavis-rebukes-padalkar-says-need-to-be-careful-while-aggressive-284632/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-majhi-ladki-bahin-yojana-ekyc-update-women-beneficiaries-last-date-135957916.html</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-for-giving-30-sara-projects-to-mohit-kamboj/921930/</t>
+          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-criticized-jayant-patil-in-dirty-words-devendra-fadnavis-phone-call-to-gopichand-padalkars-1385221</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-chagan-bhujbal-sharad-pawar-obc-reservation-rain-update-friday-19-september-2025-1495763.html</t>
+          <t>https://marathi.abplive.com/news/politics/devendra-fadnavis-on-uddhav-thackeray-mumbai-municipal-corporation-will-have-a-mahayuti-mayor-write-it-down-fadnavis-sang-song-achha-sila-diya-tune-1384650</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur/ajit-pawar-advise-to-bjp-mla-gopichand-padalkar-on-jayant-patil-statement-maharashtra-politics-marathi-news-1385092</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-boosts-aid-for-organ-transplant-treatment-to-over-lakh-announces-cm-devendra-fadanvis-maharashtra-news-mhs25091505789</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/maharastra-cabinate-meeting-inside-story-ajit-pawar-makes-laughter-in-front-of-devendra-fadanvis-latest-marathi-news-1481676.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/akola/buldhana/news/97-gram-panchayats-from-khamgaon-taluka-participate-in-samruddhi-panchayat-raj-abhiyan-135924229.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-prime-minister-narendra-modi-birthday-chhagan-bhujbal-obc-reservation-rain-alert-wednesday-17-september-2025-1494134.html</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/nashik-nationalist-party-sharad-pawar-group-aakrosh-morcha-mla-rohit-pawar-criticizes-chief-minister-devendra-fadnavis/articleshow/123919393.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-prime-minister-narendra-modi-birthday-chhagan-bhujbal-obc-reservation-rain-alert-wednesday-17-september-2025-1494134.html</t>
+          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/india-has-the-potential-to-become-a-global-leader-in-the-field-of-gems-and-jewellery-chief-minister-devendra-f.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/pedeko-to-implement-dpar-on-intense-traffic-routes-will-be-presented-for-approval-to-the-chief-minister/articleshow/123971055.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%B5%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%AE%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF/ar-AA1uC6bt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.etvbharat.com/mr/!state/comforting-news-for-the-maratha-community-the-benefits-of-annasaheb-patil-corporations-schemes-will-reach-the-villages-directly-maharashtra-news-mhs25091901865</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%B5-%E0%A4%B0-%E0%A4%A7-%E0%A4%A4-%E0%A4%A6-%E0%A4%A8-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87-%E0%A4%95-%E0%A4%A2%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A4-%E0%A4%B0%E0%A4%96%E0%A5%87%E0%A4%9A-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%AD%E0%A5%81%E0%A4%9C%E0%A4%AC%E0%A4%B3-%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%91%E0%A4%AB%E0%A4%B0/ar-AA1MvYll</t>
+          <t>https://marathi.abplive.com/news/thane/thane-metro-railway-exciting-news-for-thane-residents-trial-run-date-announced-when-will-the-first-phase-begin-1385724</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/thousands-of-rupees-were-laundered-during-the-corona-period-devendra-fadnavis-criticizes-thackeray/videoshow/123926314.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-criticizes-devendra-fadnavis-for-not-unveiling-the-statue-of-swami-ramanand-tirtha-despite-coming-to-chhatrapati-sambhajinagar/922378/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/uddhav-thackeray-in-power-the-mumbai-municipal-corporation-during-the-corona-period-committed-a-scam-in-the-body-bags-fadnavis-targets-thackeray/922227/</t>
+          <t>https://www.saamana.com/harshwardhan-sapkal-accuses-maharashtra-cm-devendra-fadnavis-of-election-fraud-calls-him-thief-cm-during-press-conference/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AB-%E0%A4%A8%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%B8%E0%A5%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%82-%E0%A4%AB-%E0%A4%B0%E0%A4%B2-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AB%E0%A4%9F%E0%A4%95-%E0%A4%B0%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%AC%E0%A4%A6%E0%A4%B2%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MSIyN</t>
+          <t>https://news18marathi.com/maharashtra/chhatrapati-sambhaji-nagar/chhatrapati-sambhajinagar-80-year-old-sunanda-shinde-write-letter-to-cm-devendra-fadnavis-on-adarsh-bank-scam-local18-1481471.html</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/maharashtra-cabinet-meeting-8-key-decisions-gaming-policy-hostel-allowance-increase-135933914.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-19-september-2025-125091900004_1.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/strict-shutdown-in-ishwarpur-and-ashta-to-protest-gopichand-padalkar-criticism-of-jayant-patil-marathi-news-update-1385432/amp</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-this-is-a-clove-cracker-chief-minister-devendra-fadnavis-reply/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-9/923517/</t>
+          <t>https://www.dainikprabhat.com/big-news-sudden-resignation-of-the-states-advocate-general-chief-minister-fadnavis-gave-information-in-the-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/will-not-support-gopichand-padalkars-statement-fadnavis-clarifies-his-stance-284601/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-22-september-2025-125092200004_1.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thackeray-brand-controversy-sanjay-raut-slams-devendra-fadnavis-over-balasaheb-thackeray-s-legacy-and-brand-remarks-1384959</t>
+          <t>https://www.dainikprabhat.com/implementation-of-law-and-order-will-lead-the-country-towards-becoming-a-superpower-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-this-is-a-clove-cracker-chief-minister-devendra-fadnavis-reply/</t>
+          <t>https://vishwanewsmarathi.com/sharad-pawars-main-indicator-but-wisdom-is-a-matter-of-learning/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/implementation-of-law-and-order-will-lead-the-country-towards-becoming-a-superpower-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.dainikprabhat.com/nashik-news-sharad-pawar-aggressive-on-farmers-issues-targets-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-19-september-2025-125091900004_1.html</t>
+          <t>https://www.dainikprabhat.com/harshwardhan-sapkal-chief-minister-fadnavis-should-resign-congress-state-president-harshwardhan-sapkal-demanded/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/krushi/onion-rate-if-the-central-government-accepts-this-demand-of-chief-minister-devendra-fadnavis-onions-will-get-a-good-price/</t>
+          <t>https://thodkyaat.com/maharashtra-cm-announces-%E2%82%B91-lakh-interest-free-loan-for-women-plans-to-make-1-crore-lakhpati-didis/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/chaos-during-chief-minister-fadnavis-speech-protesters-allege-injustice-against-obcs/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%9A-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%B2-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%8A-%E0%A4%A8%E0%A4%AF%E0%A5%87-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8/ar-AA1MDxgy</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/so-my-dear-sisters-will-not-get-the-scheme-money/</t>
+          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-inspects-nashik-and-surrounding-areas-in-the-backdrop-of-kumbh-mela-gives-important-instructions-local18-1483785.html</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/milind-narvekar-got-a-call-and-cm-fadnavis-big-revelation-what-happened/</t>
+          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/harshwardhan-sapkal-chief-minister-fadnavis-should-resign-congress-state-president-harshwardhan-sapkal-demanded/</t>
+          <t>https://marathi.ndtv.com/politics/political-news-file-a-case-against-sharad-pawar-gopichand-padalkar-demands-markadwadi-solapur-9294330</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/cm-devendra-fadnavis-mou-between-the-state-government-and-cambridge/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/the-chief-ministers-first-reaction-to-gopichand-padalkars-controversial-statement-was-while-we-were-talking/</t>
+          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-attack-uddhav-thackeray-and-raj-thackeray-over-mumbai-mahapalika-bjp-vijay-melava-1481400.html</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-news-sudden-resignation-of-the-states-advocate-general-chief-minister-fadnavis-gave-information-in-the-cabinet-meeting/</t>
+          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-meeting-maharashtra-unveils-new-animation-vfx-and-gaming-policy-as-state-cabinet-approves-8-major-decisions-article-152829352</t>
+          <t>https://news18marathi.com/maharashtra/obc-activist-shouting-slogans-during-cm-devendra-fadnavis-speech-at-chhatrapati-sambhaji-nagar-1481714.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cabinet-meeting-maharashtra-unveils-new-animation-vfx-and-gaming-policy-as-state-cabinet-approves-8-major-decisions-article-152829352/amp</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-bmc-election-%E0%A4%B2-%E0%A4%B9%E0%A5%82%E0%A4%A3-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0-%E0%A4%B9-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%9A-bjp-melava/vi-AA1MFmSp?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-will-get-1-lakh-rupees-loan-without-interest-read-how-it-works-cm-devendra-fadnavis-tells-calculation-article-152844483</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-at-bjp-vijay-sankalp-melava/videoshow/123937912.cms</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%9A-%E0%A4%97-%E0%A4%AA%E0%A4%A8-%E0%A4%AF-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%AC-%E0%A4%B9%E0%A5%87%E0%A4%B0-%E0%A4%AB-%E0%A4%A1%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%95-%E0%A4%B0%E0%A4%B5-%E0%A4%88-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AB-%E0%A4%A4%E0%A5%81%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A3-%E0%A4%9A-%E0%A4%87%E0%A4%B6-%E0%A4%B0/ar-AA1zk77g?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-thackeray-brand-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%A5%E0%A5%87%E0%A4%9F%E0%A4%9A-%E0%A4%9F-%E0%A4%B2%E0%A5%87%E0%A4%AC-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82-marathi-news/vi-AA1MI8n0?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8-%E0%A4%AE%E0%A5%82%E0%A4%B9-%E0%A4%95-%E0%A4%95-%E0%A4%AA-%E0%A4%86%E0%A4%A2%E0%A4%B3%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%A4-%E0%A4%B0%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%95%E0%A4%B0-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A4%A1%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%B5-%E0%A4%88%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1yRhpX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/pune-news-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%B9%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%AA-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%86%E0%A4%A3%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%A4-%E0%A4%8F%E0%A4%95-%E0%A4%B8-%E0%A4%AA-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%9F-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0/ar-AA1MS5wc</t>
+          <t>https://mahasamvad.in/178525/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%A4%E0%A4%B0-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B2-%E0%A4%AD-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%88%E0%A4%B2-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A4%9A-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87/ar-AA1yGbxE?cvid=095241392FF0412A82D481C439844DFB&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AA-%E0%A4%9A%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A6%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%87-%E0%A4%8F%E0%A4%95-%E0%A4%A4%E0%A4%B0%E0%A5%82%E0%A4%A3/ar-AA1MSJPR</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/cm-devendra-fadnavis-insured-maharashtra-state-government-to-introduce-new-bamboo-industry-policy-read-details/940426/amp</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-reaction-on-rahul-gandhi-allegations-bogus-voting-in-chandrapur-rajura-1483022.html</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/sports/lionel-messi-gives-cm-devendra-fadnavis-a-special-gift-of-signed-footbal-will-also-come-to-mumbai-for-a-visit-1385826/amp</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-maharashtra-cm-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A4-%E0%A4%AA-%E0%A4%B5%E0%A4%B0%E0%A4%AB%E0%A5%81%E0%A4%B2-%E0%A4%96%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%B5%E0%A4%B0-%E0%A4%AC%E0%A4%B8%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%A4-%E0%A4%AA%E0%A4%97-%E0%A4%B0-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A7-%E0%A4%95-%E0%A4%AA%E0%A4%97-%E0%A4%B0/ar-AA1vigKI?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-maharashtra-cm-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%98%E0%A5%87%E0%A4%A3-%E0%A4%B0/ar-AA1vePEI?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/news/maharashtra/beed-news-chief-minister-devendra-fadnavis-and-deputy-chief-minister-ajit-pawar-visit-beed-dangerous-electrical-generator-covered-with-cloth-in-beed-1384811</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-leader-manoj-jarange-patil-big-announcement-about-delhi-visit/articleshow/123945687.cms</t>
+          <t>https://www.lokmat.com/mumbai/modi-is-the-biggest-brand-in-the-world-chief-minister-devendra-fadnavis-bjp-is-the-party-that-created-the-brand-of-its-workers-a-a941/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179349/</t>
+          <t>https://mahasamvad.in/178515/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AD%E0%A4%B0-%E0%A4%B8%E0%A4%AD-%E0%A4%97%E0%A5%83%E0%A4%B9-%E0%A4%A4-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%96%E0%A5%87%E0%A4%B3-%E0%A4%A1%E0%A5%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%A8-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%A8-%E0%A4%B5-%E0%A4%B0-%E0%A4%9F-%E0%A4%AE%E0%A4%97-%E0%A4%95-%E0%A4%A3/ar-AA1ABTLN?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://mahasamvad.in/178649/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://news18marathi.com/agriculture/when-will-river-linking-project-in-marathwada-start-chief-minister-fadnavis-has-given-information-about-this-1482614.html</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-live-breaking-news-17th-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-marathwada-vidarbha-rain-alert/liveblog/123933492.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/cm-devendra-fadnavis-directs-to-prepare-comprehensive-effective-policy-to-fight-cancer-maharashtra-health-marathi-news-1384411</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178525/</t>
+          <t>https://mahasamvad.in/178530/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/mumbai-rain-latest-updates-maharashtra-weather-news-political-devendra-fadnavis-sanjay-raut-asc-95-5375148/</t>
+          <t>https://marathi.abplive.com/news/politics/ajit-pawar-in-nagpur-refusal-to-accept-that-vidarbha-is-the-stronghold-of-bjp-and-devendra-fadnavis-maharashtra-politics-marathi-news-1385133</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178515/?amp=1</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DO3HFhNjGpE/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A4%B8%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8%E0%A4%B5-%E0%A4%A7%E0%A4%AE-%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%A6%E0%A4%B0-%E0%A4%AC-%E0%A4%A6-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F%E0%A4%B5%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B6%E0%A5%87%E0%A4%B5%E0%A4%9F%E0%A4%9A-%E0%A4%85%E0%A4%B2%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%87%E0%A4%9F/ar-AA1MXK2J</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AA-%E0%A4%A0-%E0%A4%82%E0%A4%AC-%E0%A4%95-%E0%A4%A6-%E0%A4%B2-%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A5%82%E0%A4%A8-%E0%A4%9F-%E0%A4%95%E0%A4%B2%E0%A5%87/ar-AA1u7Jyx?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/cm-devendra-fadnavis-insured-maharashtra-state-government-to-introduce-new-bamboo-industry-policy-read-details/940426</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/cm-devendra-fadnavis-directs-to-prepare-comprehensive-effective-policy-to-fight-cancer-maharashtra-health-marathi-news-1384411/amp</t>
+          <t>https://www.navarashtra.com/india/top-marathi-news-today-live-marathi-news-breaking-news-live-update-national-news-live-news-992561.html</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-attack-uddhav-thackeray-and-raj-thackeray-over-mumbai-mahapalika-bjp-vijay-melava-1481400.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/maharashtra-devendra-fadnavis-pm-ambitions-rss-modi-resignation-claim-harshvardhan-sapkal-135967771.html</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/punepolice-force-1720-posts-will-soon-be-approved-by-the-high-powered-committee-headed-by-chief-minister-devendra-fadnavis/articleshow/124010529.cms</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ncp-counters-devendra-fadnavis-devabhavu-campaign-1492671.html</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bmc-elections-2025-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%A4-%E0%A4%AD%E0%A4%97%E0%A4%B5-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%95%E0%A4%A3-%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-marathi-news/vi-AA1MFISF</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://marathi.abplive.com/news/ahmednagar/rohit-pawar-reply-to-chhagan-bhujbal-on-jalna-antarwali-sarathi-lathicharge-on-maratha-protest-1385305</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-informed-that-the-states-advocate-general-birendra-saraf-has-resigned/922000/</t>
+          <t>https://news18marathi.com/mumbai/maharastra-cabinate-meeting-inside-story-ajit-pawar-makes-laughter-in-front-of-devendra-fadanvis-latest-marathi-news-1481676.html</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/179466/</t>
+          <t>https://marathi.abplive.com/news/thane/thane-metro-4-and-metro-4a-35-km-long-how-many-stations-trial-run-by-devendra-fadnavis-eknath-shinde-see-details-in-marathi-1385959</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/punepolice-force-1720-posts-will-soon-be-approved-by-the-high-powered-committee-headed-by-chief-minister-devendra-fadnavis/articleshow/124010529.cms</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/television-news/devendra-fadnavis-watch-maharashtrachi-hasya-jatra-says-samir-choughule-in-mhj-unplugged/amp_articleshow/123995979.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-activist-waves-black-flag-and-raise-slogans-against-devendra-fadnavis/videoshow/123936572.cms</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sanjay-raut-on-maharashtra-debt-burden-slams-devendra-fadnavis-eknath-shinde-ajit-pawar-says-state-situation-is-similar-to-nepal-marathi-news-1384489</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-ias-officer-transfer-order-cabinet-meeting-devendra-fadanvis-ws-a-1481304.html</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/non-agricultural-land-certificates-compulsion-removed-for-micro-and-small-businesses/amp_articleshow/123988928.cms</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/cm-devendra-fadnavis-orders-immediate-action-after-attack-on-journalists-in-trimbakeshwar-nashik-1496889.html</t>
+          <t>https://mahasamvad.in/179466/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/business/finance/chief-minister-devendra-fadnavis-steel-production-maharashtra-employment-vidarbha-marathwada-konkan-pune-print-eco-news-ssb-93-5384586/lite/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-to-introduce-certification-courses-in-gold-and-jewelry-sector-at-skill-development-university/articleshow/123967156.cms</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sharad-pawar-criticizes-devendra-fadnavis-over-farmers-issues-from-aakrosh-morcha/921710/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-informed-that-the-states-advocate-general-birendra-saraf-has-resigned/922000/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-cm-bungalow-sofa-kitchen-renovation-40-lakh-expense-controversy-135949649.html</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/pimpri-chinchwad-allegation-that-shivaji-was-insulted-due-to-fadnavis-poster-case-registered-against-unknown-person-995542.html/amp</t>
+          <t>https://agrowon.esakal.com/agro-special/8-important-decisions-in-the-cabinet-meeting-132-crores-of-funds-for-farmers-buildings-and-extension-of-the-deadline-for-the-construction-of-a-modern-orange-center-rat16</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/90300-jobs-will-be-created-through-investment-of-%E2%82%B980962-crore-in-green-steel-in-the-state-cm-fadnavis-assures-284698/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/devendra-fadnavis-dreams-of-becoming-pm-claims-congress-state-president-harshvardhan-sapkal-135973533.html</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-pm-ambition-harshvardhan-sapkal-alleges-devendra-fadnavis-s-pm-dreams-mumbai-given-to-adani-rest-to-mohit-kamboj-political-row-in-maharashtra-1385667/amp</t>
+          <t>https://news18marathi.com/maharashtra/beed-railway-inaugurate-by-ajit-pawar-and-cm-devendra-fadnavis-maharashtra-news-1481857.html</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/sharad-pawar-phone-call-to-cm-devendra-fadnavis-registered-objection-over-mla-gopichand-padalkar-controversial-statement-about-jayant-patil/940436/amp</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chagan-bhujbal-questions-kunbi-certificates-fadnavis-clarifies-135944637.html</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-targets-devendra-fadnavis-over-marathwada-flood-situation/921688/</t>
+          <t>https://marathi.abplive.com/news/politics/sanjay-raut-on-maharashtra-debt-burden-slams-devendra-fadnavis-eknath-shinde-ajit-pawar-says-state-situation-is-similar-to-nepal-marathi-news-1384489</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-advocate-general-birendra-saraf-resigns-for-personal-reasons-will-continue-till-january-on-government-s-request-amid-key-hearings-1384569/amp</t>
+          <t>https://marathi.abplive.com/news/nagpur/ajit-pawar-advise-to-bjp-mla-gopichand-padalkar-on-jayant-patil-statement-maharashtra-politics-marathi-news-1385092</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-flagged-off-the-first-train-service-from-beed-to-ahilyanagar-125091800006_1.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-ajit-doval-criticism-anjali-damania-gopichand-padalkar-controversy-mcoca-removal-update-135966330.html</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/hyundai-should-invest-more-and-more-in-the-state-and-increase-employment-generation-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-9/923517/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/nashik-news-sharad-pawar-aggressive-on-farmers-issues-targets-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.esakal.com/desh/maharashtra-marathi-live-news-23-september-2025-navratri-festival-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/a-comprehensive-policy-should-be-prepared-for-cancer-treatment-chief-minister-devendra-fadnavis/</t>
+          <t>https://agrowon.esakal.com/agro-special/the-drought-history-of-marathwada-will-be-compiled-rat16</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/new-shetkari-bhavans-in-79-market-committees-across-the-state-provision-of-rs-132-crore-48-lakhs/</t>
+          <t>https://marathi.indiatimes.com/e-paper/non-agricultural-land-certificates-compulsion-removed-for-micro-and-small-businesses/articleshow/123988928.cms</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/how-was-the-first-meeting-between-devendra-fadnavis-and-narendra-modi/167384/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/sharad-pawar-says-farmer-lives-are-in-trouble-devevendra-fadnavis-taking-the-name-of-shivaji-maharaj-and-not-looking-at-baliraja-1384307</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1-13/</t>
+          <t>https://civicmirror.in/maharashtra/new-gst-reforms-will-give-new-impetus-to-indias-economic-development-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/another-train-between-nagpur-pune-ssb-93-5379462/</t>
+          <t>https://marathi.abplive.com/news/politics/pm-modi-birthday-special-cm-devendra-fadnavis-and-dcm-ekanth-shinde-wrote-articles-praises-modi-leadership-1384692</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/demands-on-mulund-dumping-ground-land-grow-bjp-asks-for-golf-course-ubt-wants-hospital-and-now-dharavi-project-body-seeks-15-acres-for-casting-yard/articleshow/123904709.cms</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bmc-election-2025-%E0%A4%B2-%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%95%E0%A4%B0-%E0%A4%95-%E0%A4%B9-%E0%A4%B9-%E0%A4%9D-%E0%A4%B2%E0%A4%82-%E0%A4%A4%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B5%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0%E0%A4%AA%E0%A4%A6-%E0%A4%B5%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8/ar-AA1MFyqo</t>
+          <t>https://www.mymahanagar.com/maharashtra/sharad-pawar-criticizes-devendra-fadnavis-over-farmers-issues-from-aakrosh-morcha/921710/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-slams-thackeray-bjp-vijayi-sankalp-melava/</t>
+          <t>https://www.saamana.com/shivsena-ubt-mp-sanjay-raut-press-conference-attack-on-bjp-on-corruption-and-debt-on-state-saamana-online-news/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-approves-joint-venture-for-5000-mw-capacity-renewable-energy-project/articleshow/123925535.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-targets-devendra-fadnavis-over-marathwada-flood-situation/921688/</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633582-india-pushes-green-steel-revolution-at-aiifa-steelex-2025-in-mumbai</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-chaired-a-review-meeting-of-the-information-technology-department-125092200052_1.html</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/smart-solar-bench-installed-at-st-xaviers-college-in-mumbai/articleshow/123905895.cms</t>
+          <t>https://maharashtramirror.com/maharashtra-news-political-turmoil-in-the-state-differences-between-shinde-fadnavis-over-ias-appointment-to-d-class-municipalities/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633588-india-new-zealand-trade-talks-next-round-in-new-delhi?amp</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-flagged-off-the-first-train-service-from-beed-to-ahilyanagar-125091800006_1.html</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633401-maharashtras-bold-step-towards-a-greener-steel-future</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-will-become-a-global-gaming-hub-fadnavis-cabinet-approves-125091700028_1.html</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3628665-rs-1100-cr-allocated-for-repair-construction-of-roads-in-bengaluru-shivakumar?amp</t>
+          <t>https://www.dainikprabhat.com/pune-news-governments-make-and-break-on-reservation-continues-vijay-vadettiwar-hits-out-at-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/amp/business/suzlon-group-bags-second-largest-order-of-838-mw-from-tata-power-for-solar-energy-project</t>
+          <t>https://www.dainikprabhat.com/devendra-fadanvis-pod-taxi-service-will-be-started-soon-in-mumbai-chief-minister-fadnavis-gave-information/</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3631932-rahul-gandhis-allegations-stir-controversy-over-voter-fraud</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3632160-rahul-gandhi-sparks-political-storm-over-alleged-voter-fraud-in-maharashtra</t>
+          <t>https://www.dainikprabhat.com/devendra-fadanvis-provision-of-corpus-fund-for-treatment-worth-more-than-5-lakhs-chief-minister-fadnavis-announcement/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3632920-election-integrity-dispute-shinde-dismisses-gandhis-claims-as-baseless</t>
+          <t>https://maharashtramirror.com/mumbai-local-train-news-megablock-on-harbour-line-from-midnight-today-local-services-closed-for-14-30-hours/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3632734-ajit-pawar-dismisses-rahul-gandhis-vote-theft-claims?amp</t>
+          <t>https://marathi.oneindia.com/maharashtra/mumbai-metro-4-project-inauguration-cm-fadnavis-blames-previous-mva-government-for-project-delay-037837.html</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm/</t>
+          <t>https://www.dainikprabhat.com/pimpri-news-devabhaus-poster-disfigures-the-city-allegations-that-chhatrapati-is-being-desecrated/</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/asia-cup-2025-the-story-before-the-toss-has-come-to-light-revealing-the-handshake-controversy-2025-09-19</t>
+          <t>https://www.dainikprabhat.com/pune-news-now-the-chief-minister-has-a-complaint-about-potholes-roads-are-being-cleaned-complaints-are-pouring-in-fadnavis-is-upset-with-the-management-of-the-municipality/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3633167-sharad-pawar-denounces-derogatory-comments-by-bjp-mla</t>
+          <t>https://www.newsdanka.com/vishesh/how-was-the-first-meeting-between-devendra-fadnavis-and-narendra-modi/167384/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm/2929801</t>
+          <t>https://lokmanthan.com/new-shetkari-bhavans-in-79-market-committees-across-the-state-provision-of-rs-132-crore-48-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3633270-derogatory-remarks-stir-political-row-in-maharashtra?amp</t>
+          <t>https://www.dainikprabhat.com/fadnavis-made-a-big-announcement-saying-that-the-ladki-bahin-scheme-will-not-be-closed/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/Newsalert/3633183-head-of-british-intelligence-says-there-is-absolutely-no-evidence-that-putin-wants-to-negotiate-peace-in-ukraine-reports-a?amp</t>
+          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3633577-rift-in-maharashtra-controversy-erupts-over-padalkars-comments?amp</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-18-september-2025-125091800004_1.html</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mla-s-remarks-on-ncp-sp-leader-kicks-up-row-101758309273108-amp.html</t>
+          <t>https://pcbtoday.in/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1-13/</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.pratahkal.com/big-news/sharad-pawar-angered-over-bjp-mlas-controversial-statement-1519059</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%AA-%E0%A4%8F%E0%A4%B8%E0%A4%AA-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%95-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%AA%E0%A4%A3-%E0%A4%B8%E0%A5%87-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AB-%E0%A4%A8-%E0%A4%95-%E0%A4%AF/ar-AA1MTEtV</t>
+          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%BE%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%80-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%9C%E0%A5%8D%E0%A4%9E%E0%A4%BE%E0%A4%A8-%E0%A4%B5%E0%A4%BF%E0%A4%AD%E0%A4%BE%E0%A4%97%E0%A4%BE/118336/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/fadnavis-government-is-indifferent-towards-the-problems-of-farmers-sharad-pawar/868925/?amp</t>
+          <t>https://timesofindia.indiatimes.com/india/no-faith-in-constitution-fadnavis-targets-rahul-gandhi-over-gen-z-post-terms-him-urban-maoist/articleshow/123996897.cms</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/shiv-sena-ubt-mp-sanjay-raut-says-many-mlas-because-of-vote-chori-in-maharashtra-201758358063004.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%B8-%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9C-%E0%A4%97%E0%A4%B0-%E0%A4%B8-%E0%A4%A0-%E0%A4%B0-%E0%A4%9C%E0%A4%A7-%E0%A4%A8-%E0%A4%B8%E0%A4%9C%E0%A4%B2-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B8%E0%A5%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A5%81-%E0%A4%B9-%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B8-%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%AE%E0%A5%87%E0%A4%B2%E0%A4%A8-%E0%A4%B8-%E0%A4%A0-%E0%A4%B8%E0%A4%9C%E0%A5%8D%E0%A4%9C%E0%A4%A4/ar-AA1zpAh2?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.punjabnewsexpress.com/national/news/fadnavis-calls-rahul-gandhi-%E2%80%98urban-naxal-then-what-about-indias-foreign-policy-leaning-towards-%E2%80%98maoism-asks-shiv-se-299178</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/gopichand-padalkar-clarification-on-his-statement-about-jayant-patil-after-receiving-a-call-from-cm-devendra-fadnavis/amp_articleshow/123994231.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/congress-slams-maharashtra-cm-fadnavis-over-posters-featuring-shivaji-maharaj-pasted-at-train-station-with-filth-around-3732307</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/bjp-gopichand-padalkar-on-being-apology-to-jayant-patil-on-controversial-statement/923126/</t>
+          <t>https://sundayguardianlive.com/news/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe20250918053517-141254/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%9C%E0%A5%87%E0%A4%A8-%E0%A4%9C%E0%A5%80-%E0%A4%B5%E0%A4%BE%E0%A4%B2%E0%A4%BE-%E0%A4%AC%E0%A4%AF%E0%A4%BE%E0%A4%A8-%E0%A4%B0%E0%A4%BE%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97%E0%A4%BE%E0%A4%82/</t>
+          <t>https://www.business-standard.com/india-news/govt-committed-to-empowering-women-ladki-bahin-to-continue-cm-fadnavis-125091700582_1.html</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/cm-advises-padalkar-to-exercise-restraint-125092000048_1.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharastra-cm-fadnavis-pushes-for-faster-industrial-approvals-ai-based-reforms-to-boost-investments-23594849</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.primetvindia.com/rahul-gandhis-new-allegations-and-his-gen-z-comment-have-caused-a-stir-in-politics/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nashik/sharad-pawar-criticizes-the-cm-devendra-fadnavis-by-calling-him-devabhau-warns-the-government-94901</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-devendra-fadnavis-23594442?button=next</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/sharad-pawar-attack-cm-devendra-fadanvis-over-farmer-loan-waiver-and-crop-rate-issue-ncp-nashik-melava-1480406.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-govt-signs-mou-with-cambridge-to-elevate-school-education-101758482430602.html</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/video/sharad-pawar-criticizes-devendra-fadnavis-farm-loan-waiver-protest</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-sign-mous-to-boost-steel-production-3736498</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sharad-pawar-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%A8-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%9C-%E0%A4%AD-%E0%A4%98%E0%A4%B8%E0%A4%B0%E0%A4%B2-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AB-%E0%A4%B0%E0%A4%B5%E0%A4%B2-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AB-%E0%A4%A8-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MSu7q</t>
+          <t>https://inshorts.com/en/news/marathwada-got--21-000-cr-investment-in-past-10-years--fadnavis-1758179070896</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/jayant-patil-first-reaction-on-gopichand-padalkar-criticism-anger-from-sharad-pawar-ncp-group-maharashtra-politics-marathi-news-1385191/amp</t>
+          <t>https://www.businessworld.in/article/hyundai-maharashtra-discuss-new-investments-jobs-571636</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/deva-bhau-you-take-the-name-of-shivaji-maharaj-but-you-dont-even-look-at-baliraja-what-sharad-pawar-said-in-his-speech-in-nashik-284196/amp/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-fadnavis-defends-obc-reservation-policy-says-no-threat-to-communitys-rights/articleshow/123886921.cms</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/gopichand-padalkar-asks-why-sharad-pawar-didnt-call-to-modi-when-congress-makes-ai-video-of-his-mother/940519/amp</t>
+          <t>https://www.ptinews.com/detail/national/Maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop-Fadnavis/2927696</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/padalkars-criticism-has-a-strong-impact-sharad-pawar-directly-calls-cm-fadnavis-says-to-those-who-make-absurd-statements/</t>
+          <t>https://www.ptinews.com/detail/national/CM-Fadnavis-must-resign-after-Rahul-Gandhi-exposed-vote-theft-in-Maharashtra-Sapkal/2926755</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/stop-those-who-make-absurd-statements/117875/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-reviews-pod-taxi-project-to-tackle-bkc-congestion-23595308</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
+          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3633220-political-tensions-rise-over-maratha-quota-resolution-in-maharashtra?amp</t>
+          <t>https://www.lokmattimes.com/aurangabad/drought-will-soon-be-a-thing-of-past-in-marathwada-cm/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/wadettiwar-accuses-mahayuti-ministers-of-pushing-fake-obc-certificates/articleshow/124020428.cms</t>
+          <t>https://www.mypunepulse.com/mumbai-to-get-pod-taxi-service-for-seamless-last-mile-connectivity-says-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sharad-pawar-on-devendra-fadnavis-%E0%A4%A8%E0%A5%87%E0%A4%AA-%E0%A4%B3-%E0%A4%B9-%E0%A4%8A-%E0%A4%A6%E0%A5%87%E0%A4%8A-%E0%A4%A8%E0%A4%95-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%AD-%E0%A4%8A%E0%A4%82%E0%A4%A8-%E0%A4%87%E0%A4%B6-%E0%A4%B0/ar-AA1MzkfC</t>
+          <t>https://www.sakshipost.com/news/mou-cambridge-new-phase-world-class-education-maha-cm-fadnavis-454046</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/obc-activist-shouting-slogans-during-cm-devendra-fadnavis-speech-at-chhatrapati-sambhaji-nagar-1481714.html</t>
+          <t>https://thenewsmill.com/2025/09/awakened-feeling-of-patriotism-in-every-person-says-amruta-fadnavis-after-watching-mera-desh-pehle-the-untold-story-of-shri-narendra-modi/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-poetic-address-amidst-maharashtra-maratha-obc-reservation-disputes-1496046.html/amp</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/varsha-bungalow-furniture-20-47-lakh-controversy-pwd-covers-multiple-bungalows-activists-point-to-crore-tenders-135952900.html</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-fadnavis-reviews-security-and-preparedness-with-navy-and-army-officers/amp_articleshow/124029075.cms</t>
+          <t>https://www.newsdrum.in/national/cm-couldnt-spare-even-15-minutes-to-unveil-swami-ramanand-tirthas-statue-oppn-targets-fadnavis-10473538</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://news.ssbcrack.com/viasat-selected-to-deliver-space-crypto-solution-for-u-s-space-force-space-systems-command/</t>
+          <t>https://www.newsband.in/article_detail/controversy-eruptsover-naming-ofambernaththeatre</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://news.ssbcrack.com/viasat-secures-contract-with-u-s-space-force-for-advanced-space-based-encryption-technology/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/padalkars-jibe-at-jayant-patil-sparks-protests-comment-inappropriate-says-cm/articleshow/124003830.cms</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row/articleshow/124004724.html</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/exclusive-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%AB%E0%A4%B0-%E0%A4%86%E0%A4%B8-%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%8F%E0%A4%97-%E0%A4%B5-%E0%A4%9F%E0%A4%B0-%E0%A4%9F%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%B8-%E0%A4%A8-%E0%A4%A4-%E0%A4%A8-%E0%A4%97%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8/ar-AA1MDmlO</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/delhi-ncr/dhaula-kuan-to-manesar-pod-taxi-plan-for-ropeway-transport-says-nitin-gadkari-at-abp-reshaping-india-conclave-3013478/amp?utm_campaign=fullarticle&amp;utm_medium=referral&amp;utm_source=inshorts</t>
+          <t>https://timesofindia.indiatimes.com/city/thiruvananthapuram/concerned-over-controversies-surrounding-sabarimala-tdb-chief/articleshow/123928370.cms</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%AC%E0%A4%82%E0%A4%9F%E0%A4%B5-%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A5%82%E0%A4%B2-%E0%A4%A4%E0%A4%AF-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95-%E0%A4%95-%E0%A4%A4%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6/ar-AA1vHycG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B5-%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%AD-%E0%A4%95-%E0%A4%B8%E0%A4%AE%E0%A4%9D%E0%A4%A6-%E0%A4%B0-%E0%A4%9C%E0%A4%A8%E0%A4%A4-%E0%A4%95-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%B2-%E0%A4%A1%E0%A4%B0%E0%A4%B6-%E0%A4%AA-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%B2-%E0%A5%87%E0%A4%95%E0%A4%B2-%E0%A4%AC-%E0%A4%A1-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%A8%E0%A4%B8-%E0%A4%AA-%E0%A4%95-%E0%A4%A6-%E0%A4%B5/ar-AA1MQAZG</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/feeding-into-the-debate-pigeon-spots-near-sgnp-ruffle-feathers/articleshow/123906843.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/no-question-of-pm-modis-retirement-increased-bjp-and-rss-bonding-ater-pm-modi-nagpur-visits-says-rss-researcher-dilip-devdhar-pm-modi-turns-75-today-75th-birthday-maharashtra-news-mhs25091700500</t>
+          <t>https://www.lokmattimes.com/national/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
+          <t>https://www.mypunepulse.com/political-posters-without-permission-stir-controversy-in-pimpri-chinchwad/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/mahayuti-govt-wins-trust-vote-in-maharashtra-assembly-sena-ubt-boycotts-governor-address/ar-AA1vxGSA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.afternoonvoice.com/maharashtra-doctors-stage-strike-over-govt-nod-to-register-homeopaths.html</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/maha-cong-chief-says-partys-symbol-didnt-reach-everywhere-after-joining-mva-rules-out-statewide-alliance-for-local-body-polls/articleshow/124019976.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-tri-bhasha-samiti-also-meets-uddhav-thackeray-raj-thackeray-amid-hindi-vs-marathi-row-in-state-know-all/articleshow/123948973.cms</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/didnt-do-so-for-power-but-ajit-pawar-on-why-he-split-with-sharad-pawar-101758292291397-amp.html</t>
+          <t>https://hindi.theprint.in/india/bjp-mlas-remarks-on-ncp-sp-leader-sparks-row-pawar-calls-cm/870777/</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%B2-%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AA%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%87%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%AB-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%86%E0%A4%88-%E0%A4%96%E0%A4%AC%E0%A4%B0/ar-AA1uIeu8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.theprint.in/india/ajit-pawar-downplayed-the-controversy-with-the-woman-ips-officer/870095/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/mahayutis-great-scam-200-forensic-labs-are-running-on-papers/</t>
+          <t>https://www.msn.com/hi-in/news/other/amit-shah-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B0-%E0%A4%AF%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%A6-%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5-%E0%A4%9C-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%AA-%E0%A4%A4-%E0%A4%95-%E0%A4%AA%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%AA-%E0%A4%82%E0%A4%9C%E0%A4%B2/ar-AA1CM0er?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/on-rahul-gandhi-s-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-996639</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-investigation-going-on-hindi-news-1390995.html</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mla-s-remarks-about-ncp-sp-leader/ar-AA1MSMhG</t>
+          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://ianslive.in/saw-a-leader-who-valued-simplicity-over-luxury-service-over-status-devendra-fadnavis-recalls-memorable-modi-story--20250916110124</t>
+          <t>https://www.amarujala.com/video/india-news/rahul-gandhi-vote-theft-claim-cm-fond-of-rahul-gandhi-s-vote-theft-claims-gives-this-reply-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/health/health-news/maharashtra-govt-formation-bjp-cm-s-name-still-under-wraps-all-eyes-on-unwell-shinde-s-big-decision/ar-AA1v3aC9?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharatlive.com/maharashtra/wardha/teachers-strike-against-tet-decision-wrote-letter-to-cm-in-blood-ministers-degrees-1356071.html</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3632956-ncp-leader-dismisses-rahul-gandhis-vote-theft-allegations-as-childish?amp</t>
+          <t>https://www.loksatta.com/nagpur/another-train-between-nagpur-pune-ssb-93-5379462/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/latest-news/namo-yuva-run-sees-nationwide-participation-leaders-call-for-nasha-mukt-bharat/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/demands-on-mulund-dumping-ground-land-grow-bjp-asks-for-golf-course-ubt-wants-hospital-and-now-dharavi-project-body-seeks-15-acres-for-casting-yard/articleshow/123904709.cms</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/it-is-everyones-responsibility-to-maintain-civility-in-politics-supriya-sule-is-aggressive-over-gopichand-padalkars-statement-in-mumbai-maharashtra-news-mhs25091903801</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-slams-thackeray-bjp-vijayi-sankalp-melava/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/bjp-likely-to-make-next-president-from-brahmin-community-as-vp-election-changes-social-arithmetic-three-names-in-the-race/articleshow/123940423.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-approves-joint-venture-for-5000-mw-capacity-renewable-energy-project/articleshow/123925535.cms</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://maharashtramirror.com/pune-news-placards-put-up-against-padalkar-in-pune-placards-saying-roadblock-leader-father-is-not-good-enough-to-perform-rituals-are-in-the-news/amp/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/smart-solar-bench-installed-at-st-xaviers-college-in-mumbai/articleshow/123905895.cms</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.animationxpress.com/latest-news/maharashtra-government-approves-states-avgc-xr-policy-with-rs-3000-crore-plan/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3632920-election-integrity-dispute-shinde-dismisses-gandhis-claims-as-baseless</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-cabinet-approves-eight-major-decisions-including-infrastructure-boost-labour-reforms-and-rural-development/ar-AA1Do4HZ?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mlas-remarks-about-ncp-sp-leader-23594821</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3630825-chhatrapati-sambhajinagar-indias-emerging-ev-capital</t>
+          <t>https://www.ptinews.com/story/national/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm/2929801</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtras-new-policy-to-promote-creative-tech-sector/amp_articleshow/123928891.cms</t>
+          <t>https://www.msn.com/en-in/sports/cricket/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm/ar-AA1MU0lT</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/hi-tech-media-park-in-nagpur-with-rs3000cr-nod-to-avgc-xr/articleshow/123928752.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%AA-%E0%A4%8F%E0%A4%B8%E0%A4%AA-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%95-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%AA%E0%A4%A3-%E0%A4%B8%E0%A5%87-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AB-%E0%A4%A8-%E0%A4%95-%E0%A4%AF/ar-AA1MTEtV</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/future-tech-hub-nagpur-to-host-dedicated-avgc-xr-park/09171239</t>
+          <t>https://www.livehindustan.com/maharashtra/shiv-sena-ubt-mp-sanjay-raut-says-many-mlas-because-of-vote-chori-in-maharashtra-201758358063004.html</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-unveils-rs-3268-cr-avgc-xr-policy-to-create-2-lakh-jobs-23594327</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/sharad-pawar-criticized-cm-devendra-fadnavis-at-nashik-baliraja-aakrosh-morcha/articleshow/123911615.cms</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/technology/3625253-when-help-hurts-proactive-ai-features-reduce-user-confidence-and-use?amp</t>
+          <t>https://www.loksatta.com/maharashtra/sharad-pawar-on-asking-pm-modi-to-retire-at-75-says-he-has-no-moral-right-watch-video-rak-94-5382190/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3631286-rail-renaissance-marathwadas-transformation-through-strategic-investments</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-news-scj-81-5380824/</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-cabinet-approves-8-key-decisions-announces-new-animation-vfx-gaming-policy-2025/</t>
+          <t>https://www.loksatta.com/nagpur/nagpur-ajit-pawar-silent-on-chhagan-bhujbal-allegation-against-sharad-pawars-role-in-antarwali-sarati-lathi-charge-rds-00-5382824/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-cabinet-meeting-maharashtra-animation-gaming-policy-announced-government-takes-8-major-decisions-95140</t>
+          <t>https://www.loksatta.com/photos/trending-gallery/5382357/why-do-snakes-fight-with-mongooses-science-explained-spl-93/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/what-is-gaming-policy-of-maharashtra-cabinet-approval-1481423.html</t>
+          <t>https://www.loksatta.com/nagpur/hindutva-certificate-nagpur-rakesh-tikait-comment-amravati-ssb-93-5382390/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%B5-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97%E0%A4%B8-%E0%A4%A0-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1ME6vc</t>
+          <t>https://www.loksatta.com/desh-videsh/bjp-fuming-on-shahid-afridis-positive-mindset-comment-on-rahul-gandhi-kvg-85-5377194/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/4000-cctvs-to-be-installed-for-nashik-trimbakeshwars-simhastha-kumbhmela/articleshow/123994347.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/bjp-gopichand-padalkar-on-being-apology-to-jayant-patil-on-controversial-statement/923126/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/8-important-decisions-in-the-cabinet-meeting-132-crores-of-funds-for-farmers-buildings-and-extension-of-the-deadline-for-the-construction-of-a-modern-orange-center-rat16</t>
+          <t>https://www.loksatta.com/photos/news/5382946/pomp-pageantry-and-politics-king-charles-royal-state-banquet-for-donlad-trump-in-photos-fehd-import-scj-81/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+          <t>https://www.loksatta.com/thane/truck-bike-accident-on-mumbai-nashik-highway-bhiwandi-ocd-94-5383014/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/maharashtra-has-great-opportunities-for-development-in-fisheries-and-animal-husbandry-sectors-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.loksatta.com/photos/entertainment-gallery/5380988/manasi-naik-shared-sakal-tar-hou-dya-movie-shoot-bts-photos-jahaz-mahal-mp-subodh-bhave-spl-93/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%82%E0%A4%97-2/117679/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/cm-advises-padalkar-to-exercise-restraint-125092000048_1.html</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87-%E0%A4%B6%E0%A4%B9%E0%A4%B0%E0%A4%BE%E0%A4%A4-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A5%AB-%E0%A4%AA%E0%A5%8B%E0%A4%B2%E0%A4%BF%E0%A4%B8-%E0%A4%A0/117370/</t>
+          <t>https://marathi.oneindia.com/maharashtra/shivaji-wategaonkar-attack-on-gopichand-padalkar-jayant-patil-and-rajarambapu-patil-controversial-re-037671.html</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3631932-rahul-gandhis-allegations-stir-controversy-over-voter-fraud?amp</t>
+          <t>https://www.marathijagran.com/maharashtra/nashik/sharad-pawar-criticizes-the-cm-devendra-fadnavis-by-calling-him-devabhau-warns-the-government-94901</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/rahul-gandhi-s-allegations-spark-fresh-vote-theft-debate-in-maha-101758223379409-amp.html</t>
+          <t>https://news18marathi.com/maharashtra/sharad-pawar-attack-cm-devendra-fadanvis-over-farmer-loan-waiver-and-crop-rate-issue-ncp-nashik-melava-1480406.html</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3634080-fadnavis-criticizes-rahul-gandhi-raises-brain-theft-allegations-amid-vote-theft-claims?amp</t>
+          <t>https://agrowon.esakal.com/video/sharad-pawar-criticizes-devendra-fadnavis-farm-loan-waiver-protest</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://xperttimes.com/rahul-gandhi-flags-electoral-roll-tampering-in-maharashtra-calls-for-urgent-electoral-reforms/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/chitra-wagh-slams-sharad-pawar-for-criticising-questioning-cm-devendra-fadnavis-over-farmers-issues-in-maharashtra/939621</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
+          <t>https://www.loksatta.com/nashik/sharad-pawar-criticizes-government-over-increase-in-farmer-suicides-amy-95-5374958/</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/maha-cong-chief-says-partys-symbol-didnt-reach-everywhere-after-joining-mva-rules-out-statewide-alliance-for-local-body-polls/amp_articleshow/124019976.cms</t>
+          <t>https://marathi.abplive.com/news/politics/jayant-patil-first-reaction-on-gopichand-padalkar-criticism-anger-from-sharad-pawar-ncp-group-maharashtra-politics-marathi-news-1385191</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
+          <t>https://thefocusindia.com/maharashtra-news/deva-bhau-you-take-the-name-of-shivaji-maharaj-but-you-dont-even-look-at-baliraja-what-sharad-pawar-said-in-his-speech-in-nashik-284196/amp/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/perform-or-perish-ajit-pawar-warns-ncp-ministers-at-chintan-shivir/articleshow/124003932.cms</t>
+          <t>https://thefocusindia.com/maharashtra-news/bjp-slams-sharad-pawar-farmers-politics-284281/</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-tri-bhasha-samiti-also-meets-uddhav-thackeray-raj-thackeray-amid-hindi-vs-marathi-row-in-state-know-all/articleshow/123948973.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/devendra-fadnavis-is-messiah-of-obc-community-praises-minister-chhagan-bhujbal/articleshow/123987624.cms</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://24city.news/ncp-chintan-camp-ajit-pawar-reveals-people-ask-why-i-leave-sharad-pawars-support/</t>
+          <t>https://agrowon.esakal.com/agro-special/sangli-ncp-sp-morcha-against-gopichand-padalkar-ddb79</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/declare-wet-drought-in-maha-waive-loans-of-affected-farmers-supriya/articleshow/123955405.cms</t>
+          <t>https://www.dainikprabhat.com/padalkars-criticism-has-a-strong-impact-sharad-pawar-directly-calls-cm-fadnavis-says-to-those-who-make-absurd-statements/</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3630825-chhatrapati-sambhajinagar-indias-emerging-ev-capital?amp</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/drought-will-soon-be-a-thing-of-past-in-marathwada-cm/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/obcs-disrupt-cm-s-speech-holds-huge-rally-in-hingoli-101758137116445.html</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://www.satyahindi.com/india/abvp-wins-hyderabad-university-students-elections-credit-goes-to-gen-z-then-why-objection-to-rahuls-call-147944.html/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/wadettiwar-accuses-mahayuti-ministers-of-pushing-fake-obc-certificates/articleshow/124020428.cms</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
+          <t>https://www.marathijagran.com/maharashtra/chhatrapati-sambhajinagar/obc-activists-create-ruckus-during-devendra-fadnavis-speech-at-the-main-event-of-marathwada-liberation-day-95358</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/pm-modi-s-75th-birthday-celebrations-live-politicians-celebs-share-their-modi-story-on-eve-of-birthday-liveblog-13550965.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/chhatrapati-sambhajinagar-cm-devendra-fadnavis-choas-police-arrested/922375/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/pm-modi-s-75th-birthday-celebrations-live-politicians-celebs-share-their-modi-story-on-eve-of-birthday-13550965.html/amp</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-solapur-crime-ex-deputy-sarpanch-govind-burge-death-case-maratha-reservation-mumbai-rain-sharad-pawar-ajit-pawar-manoj-jarange-patil-rain-maratha-obc-rese-1492609.html</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bom53-mh-meenatai-2ndld-statue.html</t>
+          <t>https://www.marathi.hindusthanpost.com/social/marathwada-mukti-sangram-din-2025-confusion-during-speech-cm-fadanvis/</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382/1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382</t>
+          <t>https://www.business-standard.com/india-news/pm-to-inaugurate-3-day-armed-forces-commanders-conference-in-kolkata-today-125091500085_1.html</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-mocks-uddhav-raj-thackeray-over-thackeray-brand-and-best-credit-society-poll-defeat-23594336</t>
+          <t>https://www.abplive.com/states/maharashtra/nitin-gadkari-exclusive-on-mumbai-water-taxi-sea-planes-roro-rides-in-abp-reshaping-india-conclave-3013493</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-for-tech-driven-policing-flags-ai-and-cybercrime-challenges-23594968</t>
+          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/2921301</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maha-cong-chief-says-partys-symbol-didnt-reach-everywhere-after-joining-mva-rules-out-statewide-alliance-for-local-body-polls/articleshow/124019976.cms</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/out-of-box/hindi-films-fail-to-depict-the-true-heroism-of-mumbai-police-says-maharashtra-cm-fadnavis20250920135931?amp=1</t>
+          <t>https://www.hindisaamana.com/mahayutis-great-scam-200-forensic-labs-are-running-on-papers/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/entertainment-news/milind-soman-flags-off-namo-yuva-run-in-mumbai-says-its-pm-modis-dream-to-make-india-drug-free20250921113302-144797/</t>
+          <t>https://www.khabarwala24.com/national/mumbai-mahapalika-sahit-anya-nagarpalikaon-mein-mahayuti-ka-bhagwa-jhanda-lahraega-eknath-shinde/104161/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/pm-modi-allocated-rs-21000-crore-for-rail-lines-in-marathwada-claims-cm-devendra-fadnavis-23594480</t>
+          <t>https://www.ndtv.com/video/on-rahul-gandhi-s-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-996639</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/amp_news/hindi-films-fail-to-show-real-mumbai-police--maharashtra-cm-1758365200271</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ncps-nagpur-declaration-speaks-about-strengthening-ties-with-bjp-hails-modis-leadership-3736829</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/sports/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-in-december/articleshow/124011925.cms</t>
+          <t>https://english.newstrack.com/uttar-pradesh/namo-yuva-run-inspires-india-youth-unite-for-a-drug-free-and-healthy-future-542936</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-advocate-general-birendra-saraf-resigns-citing-personal-reasons-cm-fadnavis-accepts-resignation-23594290</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-gets-shocker-as-pune-former-ncp-leader-bapu-bhegade-joins-bjp-bala-bhegade-vs-sunil-shelke/articleshow/123892833.cms</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe-23594597</t>
+          <t>https://ebatmidar.com/%E0%A4%9C%E0%A4%B3%E0%A4%97%E0%A4%BE%E0%A4%B5%E0%A4%BE%E0%A4%A4-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%AF%E0%A5%81%E0%A4%B5%E0%A4%BE-%E0%A4%B0%E0%A4%A8-%E0%A4%AD%E0%A4%B5%E0%A5%8D/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cabinet-clears-animation-policy-2025-and-other-key-projects-23594299</t>
+          <t>https://www.msn.com/mr-in/news/other/pm-modi-birthday-%E0%A4%AA%E0%A4%82%E0%A4%9A-%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%9D-%E0%A4%B2-%E0%A4%AA%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A4%82-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE-%E0%A4%A6-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87%E0%A4%9A-%E0%A4%B0-%E0%A4%B9%E0%A4%A3-%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A5%87%E0%A4%A4/ar-AA1MI1L2</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-launch-skill-courses-to-boost-manpower-for-gems-and-jewellery-sector-devendra-fadnavis-23594288</t>
+          <t>https://www.saamana.com/bjp-leader-hate-statement-pollutes-the-atmosphere-mahavikas-aghadi-save-maharashtra-sankruti-march-in-sangli/</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/bollywood/milind-soman-flags-off-namo-yuva-run-in-mumbai-says-its-pm-modis-dream-to-make-india-drug-free20250921113302</t>
+          <t>https://www.animationxpress.com/latest-news/maharashtra-government-approves-states-avgc-xr-policy-with-rs-3000-crore-plan/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/acharya-devvrat-takes-additional-charge-as-maharashtra-governor-101757923599184-amp.html</t>
+          <t>https://www.electronicsforyou.biz/industry-buzz/rrp-electronics-gets-land-for-semiconductor-fab-in-navi-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/sports/others/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-indian-racing-festival-finale20250921191656</t>
+          <t>https://m.economictimes.com/news/india/maharashtras-new-policy-to-promote-creative-tech-sector/articleshow/123928891.cms</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/sports-games/3634664-mumbais-first-fia-grade-night-street-race-a-new-era-in-indian-motorsports?amp</t>
+          <t>https://www.tribuneindia.com/news/business/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/congress-mp-varsha-gaikwad-bjp-s-mohit-kamboj-spar-over-sra-projects-in-mumbai-23594189</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/hi-tech-media-park-in-nagpur-with-rs3000cr-nod-to-avgc-xr/articleshow/123928752.cms</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-23594141</t>
+          <t>https://www.ptinews.com/story/entertainment/maharashtra-cabinet-clears-animation-visual-effects-policy-with-roadmap-till-2050/2920262</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/navi-mumbai-to-host-maharashtras-first-formula-street-race-in-the-indian-racing-festival-2025-23594957</t>
+          <t>https://www.mypunepulse.com/maharashtra-cabinet-approves-8-key-decisions-announces-new-animation-vfx-gaming-policy-2025/</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pm-modi-to-inaugurate-mumbai-metro-3-s-final-stretch-on-sept-30-1758118163968</t>
+          <t>https://www.sakshipost.com/news/maharashtra-clears-avgc-xr-policy-2025-eyes-rs-50000-crore-investment-and-2-lakh-jobs-453114</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-19-news-updates-live-updates-weather-update-mumbai-monsoon-18331427</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-cabinet-meeting-maharashtra-animation-gaming-policy-announced-government-takes-8-major-decisions-95140</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/to-continuously-lie-is-an-art-that-only-rahul-gandhi-has-devendra-fadnavis-on-congress-mps-vote-theft-claims-a510/</t>
+          <t>https://news18marathi.com/maharashtra/what-is-gaming-policy-of-maharashtra-cabinet-approval-1481423.html</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/mumbai-balasaheb-thackeray-wife-meenatai-statue-defaced-1-arrested-1800879</t>
+          <t>https://marathi.indiatimes.com/e-paper/4000-cctvs-to-be-installed-for-nashik-trimbakeshwars-simhastha-kumbhmela/articleshow/123994347.cms</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/amp/local/maharashtra/mumbai/news/varsha-bungalow-furniture-20-47-lakh-controversy-pwd-covers-multiple-bungalows-activists-point-to-crore-tenders-135952900.html</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%85%E0%A4%AE%E0%A5%83%E0%A4%A4-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-x-%E0%A4%AA%E0%A4%B0-%E0%A4%B2-%E0%A4%96-%E0%A4%A6-%E0%A4%B2-%E0%A4%95-%E0%A4%AC-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AF%E0%A5%87-%E0%A4%B5-%E0%A4%A6/ar-AA1vn2ER?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://lokmanthan.com/maharashtra-has-great-opportunities-for-development-in-fisheries-and-animal-husbandry-sectors-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ima-doctors-threaten-to-go-on-24-hour-strike-in-maharashtra-including-mumbai-from-8-am-on-sep-18-devendra-cm-fadnavis-know-all/articleshow/123947629.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/18/bom20-mh-rahul-ec-reax.html</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/entertainment/bollywood/%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%A1%E0%A5%8D%E0%A4%B0%E0%A4%97%E0%A5%8D%E0%A4%9C-%E0%A4%9C-%E0%A4%A8-%E0%A4%85%E0%A4%AC%E0%A5%8D%E0%A4%B0-%E0%A4%B9%E0%A4%AE%E0%A4%B5%E0%A4%B0-%E0%A4%AD-%E0%A4%B3%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AD%E0%A4%B0-%E0%A4%B8%E0%A4%AD%E0%A5%87%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A4%82-%E0%A4%85%E0%A4%AD-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%82-%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%95/ar-AA1xaVLz?cvid=E5D2FC4919EC403B89F2CDD45BDCA942&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://thenewsmill.com/2025/09/this-is-a-childish-statement-ncp-mp-sunil-tatkare-slams-rahul-gandhi-over-vote-theft-allegations/</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179340/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar-3735776</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-no-matter-what-happens-the-mayor-will-be-from-the-mahayuti-chief-minister-criticizes-thackeray-brothers-from-bjps-vijay-sankalp-rally/922208/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/perform-or-perish-ajit-pawar-warns-ncp-ministers-at-chintan-shivir/articleshow/124003932.cms</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%B8-%E0%A4%B0%E0%A4%96-%E0%A4%AE%E0%A5%87%E0%A4%B2-%E0%A4%B9%E0%A5%87-%E0%A4%95%E0%A4%AB%E0%A4%A8%E0%A4%9A-%E0%A4%B0-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%95-%E0%A4%AF-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A4%A3-%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A4%A3-%E0%A4%98-%E0%A4%A4/ar-AA1MFObT</t>
+          <t>https://www.hindisaamana.com/did-not-get-a-place-in-the-summit-committee-of-simhastha-kumbh-mela-saints-protest-against-the-mahayuti-government/</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/19/maharashtra-will-be-number-one-in-the-green-steel-sector-chief-minister-devendra-fadnavis-iifa-2025-steel-maha.amp.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/declare-wet-drought-in-maha-waive-loans-of-affected-farmers-supriya/articleshow/123955405.cms</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/mumbai-ahmedabad-highway-traffic-dcm-shinde-s-order-was-reversed-by-cm-fadnavis-997414</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-kamboj-allegations-sakkale-accuses-devendra-fadnavis-of-pm-ambition-empowering-mohit-kamboj-and-giving-mumbai-to-adani-1385640/amp</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/zero-hour/bmc-elections-bjp-s-khan-mayor-remark-sparks-hindu-muslim-debate-thackeray-brand-war-heats-up-in-mumbai-politics-1385074/amp</t>
+          <t>https://www.devdiscourse.com/article/law-order/3629565-life-sentence-for-afghan-national-in-mannheim-stabbing?amp</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/maharashtra-should-become-a-best-model-for-new-industries/</t>
+          <t>https://www.moneycontrol.com/news/india/pm-modi-s-75th-birthday-celebrations-live-politicians-celebs-share-their-modi-story-on-eve-of-birthday-liveblog-13550965.html</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/pm-modis-big-gift-to-mumbai-inauguration-of-underground-metro-from-worli-to-cuffe-parade-devendra-fadnavis-567660</t>
+          <t>https://www.pressreader.com/india/hindustan-times-st-mumbai/20250921/281668261136708</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/gems-and-jewellery-exhibition-inaugurated-courses-to-be-started-for-skilled-manpower-cm-devendra-fadnavis/132720/</t>
+          <t>https://www.msn.com/en-in/news/india/amit-shah-visits-lalbaugcha-raja-ganesh-mandal-cm-s-house-in-mumbai-holds-meeting-with-dycm-shinde/ar-AA1Lxp5d?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/kashmiri-pandit-student-alleges-harassment-at-book-event-in-pune/articleshow/123908215.cms</t>
+          <t>https://www.msn.com/en-in/news/India/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week/ar-AA1MYNtP</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://www.manufacturingtodayindia.com/maharashtra-seals-%E2%82%B980000-crore-mou-at-steelex-2025</t>
+          <t>https://www.thehansindia.com/news/national/mumbai-to-introduce-pod-taxi-services-for-last-mile-connectivity-maha-cm-1008907</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/formula-race-in-navi-mumbai-first-fia-approved-street-racing-circuit-to-be-unveiled-know-when-where-article-152865232</t>
+          <t>https://m.economictimes.com/news/sports/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-in-december/articleshow/124011925.cms</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/amp/news/industry/chhatrapati-sambhajinagar-emerges-as-indias-ev-manufacturing-hub-declares-maharashtra-cm-fadnavis/123961856</t>
+          <t>https://inshorts.com/en/news/hindi-films-fail-to-show-real-mumbai-police--maharashtra-cm-1758365200271</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://energy.economictimes.indiatimes.com/amp/news/coal/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/123999906</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/acharya-devvrat-takes-additional-charge-as-maharashtra-governor-101757923599184-amp.html</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/sports/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-in-december/amp_articleshow/124011925.cms</t>
+          <t>https://curlytales.com/india/trending/mumbai-metro-all-you-need-to-know-about-its-routes-features/</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/sports/others/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-indian-racing-festival-finale20250921191656?amp=1</t>
+          <t>https://www.aninews.in/news/sports/others/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-indian-racing-festival-finale20250921191656</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/rahul-sonia-gandhi-arrive-in-wayanad-for-private-events-390635?lang=en</t>
+          <t>https://curlytales.com/india/trending/pm-modi-to-inaugurate-mumbai-metro-three-final-stretch-on-sept-heres-all-about-it/</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://news.ssbcrack.com/saturn-and-neptune-shine-brightest-this-week-a-celestial-spectacle-awaits/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-22-news-updates-live-updates-weather-update-mumbai-monsoon-18331430</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://www.footboom1.com/en/news/football/2752001-lionel-messi-s-confirmed-visit-to-maharashtra-sparks-excitement</t>
+          <t>https://inshorts.com/en/news/pm-modi-to-inaugurate-mumbai-metro-3-s-final-stretch-on-sept-30-1758118163968</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://hastakshep.com/breaking-news/desh-duniya-ki-live-khabrein-17-september-2025-aaj-tak-live-268062</t>
+          <t>https://orissadiary.com/gjcs-8th-edition-of-india-gem-jewellery-show-gjs2025-opens-with-grand-inauguration-by-our-cm-shri-devendra-fadnavisji-at-jio-world-convention-centre-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/breaking-news-in-hindi/liveblog/58166012.cms</t>
+          <t>https://www.sakshipost.com/news/metro-line-connecting-thane-mumbai-be-operational-2026-end-says-cm-fadnavis-455400</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/latur/latur-news-marathwada-mahadev-koli-community-hunger-strike-postponed-important-assurance-from-shivendraraje-bhosale-maharashtra-marathi-update-1384929</t>
+          <t>https://www.socialnews.xyz/2025/09/21/namo-yuva-run-in-mumbai-gallery/</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3630451-mumbai-hosts-pioneering-international-bamboo-summit</t>
+          <t>https://gallinews.com/lodha-developers-mein-85-crore-ka-dhokhadhadi-rajendra-n-lodha-ko-mumbai-police-ne-pakda/</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3632259-maharashtras-bamboo-boom-a-green-revolution-in-the-making</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633582-india-pushes-green-steel-revolution-at-aiifa-steelex-2025-in-mumbai?amp</t>
+          <t>https://www.msn.com/hi-in/video/news/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%88-%E0%A4%96-%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%9C-%E0%A4%8F-%E0%A4%A4-bjp-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%AF-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%A6-%E0%A4%AC%E0%A4%AF-%E0%A4%A8/vi-AA1MHnOc</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3631471-hollywood-stands-firm-against-free-speech-suppression?amp</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%B8%E0%A5%8D%E0%A4%A5-%E0%A4%AA-%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AE%E0%A4%A4-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%96%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%AE-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%95%E0%A4%B9/ar-AA1MUpqj?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633794-maharashtra-leads-charge-in-green-steel-revolution-with-massive-investment?amp</t>
+          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-no-matter-what-happens-the-mayor-will-be-from-the-mahayuti-chief-minister-criticizes-thackeray-brothers-from-bjps-vijay-sankalp-rally/922208/</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3629927-maharashtras-renewable-energy-leap-a-new-joint-venture?amp</t>
+          <t>https://mahasamvad.in/179340/</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://tathya.in/prabhakaran-on-green-steel/</t>
+          <t>https://mahasamvad.in/179233/</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/hyundai-should-invest-more-and-more-in-the-state-and-increase-employment-generation-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%95%E0%A4%AC%E0%A5%81%E0%A4%A4%E0%A4%B0%E0%A4%96-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%86%E0%A4%A4-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%85%E0%A4%9F-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1JVxWD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/18/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women.html</t>
+          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://www.studyiq.com/articles/mukhyamantri-majhi-ladki-bahin-yojana/</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-podtaxi-solution-to-mumbai-traffic-congestion-pod-taxis-will-come-last-mile-connectivity-for-mumbaikars-1386065</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/socially/auto/raptee-hv-becomes-indias-first-high-voltage-ev-motorcycle-oem-backed-by-governments-technology-development-board-7119554.html/amp</t>
+          <t>https://mahasamvad.in/178607/</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/socially/india/news/pune-lift-collapse-elevator-with-6-including-child-crashes-in-maharashtras-wagholi-shocking-video-surfaces-7114317.html/amp</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-incident-of-throwing-paint-on-the-effigy-of-meenatai-thackeray-has-sparked-a-political-storm-uddhav-and-raj-thackeray-are-outraged-1188096</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/photogallery/money/ladki-bahin-yojana-ekyc-government-makes-e-kyc-mandatory-check-details-in-marathi-1483416.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/21/mumbaikars-run-towards-a-drug-free-india-namo-yuva-run-receives-overwhelming-response-will-intoxicate-our-yout.html</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179428/</t>
+          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-slams-thackeray-bandhu-over-best-election-2025-result-and-brand-defeat-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ladki-bahin-yojana-big-update-e-kyc-mandatory-for-beneficiaries-in-maharashtra-minister-aditi-tatkare-announcement-1495890.html/amp</t>
+          <t>https://marathi.ndtv.com/cities/pod-taxis-will-run-in-bandra-kurla-complex-chief-minister-devendra-fadnavis-has-instructed-9324651</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/19/e-kyc-mandatory-for-beloved-sisters-2-months-deadline.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/mohit-kamboj-special-for-bjp-and-sra-project-prof-mp-varsha-gaikwad-allegations-on-bjp-mohit-kamboj/921878/</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://tamil.getlokalapp.com/maharashtra-news/will-give-interest-free-loan-of-1-lakh-to-beloved-sisters-15420284</t>
+          <t>https://prahaar.in/2025/09/18/brand-vs-brandy-war-of-words-between-fadnavis-thackeray-faction-politics-heats-up/amp/</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://marathi.ndtv.com/videos/mumbai-ahmedabad-highway-traffic-dcm-shinde-s-order-was-reversed-by-cm-fadnavis-997414</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/maharashtra-ladki-bahen-yojana-e-kyc-is-mandatory-here-are-the-new-update-2757688.html/amp</t>
+          <t>https://civicmirror.in/maharashtra/varsha-gaikwad-big-statement-on-mohit-kamboj-sra-scam-mumbai-devendra-fadnavis-orders-to-exchange-juhu-land-reservation-bmc/</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-21-september-2025-125092100006_1.html</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/mumbai-on-september-30-pm-modi-will-give-underground-metro/article-105817</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/information/how-to-complete-e-kyc-for-the-chief-ministers-my-girlfriend-scheme-learn-the-step-by-step-process-in-simple-language-and-avoid-fake-websites-2759605.html/amp</t>
+          <t>https://lalluram.com/case-of-balasaheb-thackerays-wife-being-painted-uddhav-thackeray-says-conspiracy-to-incite-riots-in-mumbai-cm-fadnavis-orders-strict-action-against-the-culprits/</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%AD%E0%A5%8B%E0%A4%9C%E0%A4%A8-%E0%A4%A5%E0%A4%BE%E0%A4%B3%E0%A5%80-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%9A%E0%A4%BE%E0%A4%B2%E0%A4%95%E0%A4%BE/117563/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sharad-pawar-phone-call-to-cm-devendra-fadnavis-on-bjp-mla-gopichand-padalkar-remarks-3015443/amp</t>
+          <t>https://www.marathiebatmya.com/mumbai/varsha-gaikwad-alleges-the-government-is-kind-to-devendra-fadnavis-builder-friend/</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/amp/india/news/story/sharad-pawar-ncp-sp-responded-to-bjp-devabhau-campaign-with-deva-tuch-saang-aid-ntc-rpti-2334011-2025-09-15</t>
+          <t>https://www.marathiebatmya.com/mumbai/chief-minister-fadnavis-said-the-next-step-in-transport-service-is-pod-taxi/</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/amp/india/maharashtra/video/intensifying-verbal-conflict-in-maharashtra-pawars-complaint-to-the-cm-reprimanding-the-legislator-ytvd-2337563-2025-09-20</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/gems-and-jewellery-exhibition-inaugurated-courses-to-be-started-for-skilled-manpower-cm-devendra-fadnavis/132720/</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/sharad-pawar-calls-fadnavis-calls-bjp-mlas-remarks-on-ncp-sp-leader-wrong-3259171.html/amp</t>
+          <t>https://www.dainikprabhat.com/harshwardhan-sapkal-farmers-in-the-state-are-in-dire-straits-harshwardhan-sapkals-criticism/</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
+          <t>https://dainikekmat.com/%E0%A4%95%E0%A4%BE%E0%A4%B9%E0%A5%80%E0%A4%B9%E0%A5%80-%E0%A4%9D%E0%A4%BE%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A4%B0%E0%A5%80-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%9A%E0%A4%BE-%E0%A4%AA/117487/</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-govt-dept-websites-landing-pages-to-be-in-marathi/ar-AA1MBOCR</t>
+          <t>https://www.punjabnewsexpress.com/national/news/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi-297681</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3634846-strengthening-maritime-military-ties-fadnavis-meets-armed-forces-leaders?amp</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/kashmiri-pandit-student-alleges-harassment-at-book-event-in-pune/articleshow/123908215.cms</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/industry/news/maha-govt-to-launch-skills-courses-for-gems-and-jewellery-sector-fadnavis-125091600501_1.html?isa=yes</t>
+          <t>https://www.manufacturingtodayindia.com/maharashtra-seals-%E2%82%B980000-crore-mou-at-steelex-2025</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/amp/news/market/maharashtra-govt-signs-rs-80-962-cr-investment-mous/33971920250919</t>
+          <t>https://www.deccanherald.com/india/messi-set-to-dazzle-mumbai-with-his-magic-on-indian-turf-this-december-3738198</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/amp/story/sport/other/2025/Sep/19/sc-verdict-athletes-women-empowerment-in-aiff</t>
+          <t>https://www.timesnownews.com/mumbai/formula-race-in-navi-mumbai-first-fia-approved-street-racing-circuit-to-be-unveiled-know-when-where-article-152865232</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/will-change-criteria-for-solar-agricultural-pump-scheme-if-requested-chief-minister-devendra-fadnavis/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B9-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%A8-%E0%A4%98-%E0%A4%B2-%E0%A4%B5-%E0%A4%9A-a-%E0%A4%9F%E0%A5%82-z-%E0%A4%9C-%E0%A4%86%E0%A4%B0/ar-AA1yUgvL?cvid=8A4346A7BD71407096C4EE24E5F4A00E&amp;ocid=nyl&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://infra.economictimes.indiatimes.com/amp/news/urban-transportation/maharashtra-deputy-cm-calls-for-enhanced-coordination-on-pune-metro-and-elevated-highway-projects/124040274</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/mou-between-maharashtra-government-and-naam-foundation-284511/</t>
+          <t>https://curlytales.com/india/trending/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-dates-venue-celeb-owners-more/</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/steel-mahakumbh-investment-worth-rs-80962-crores-will-come-to-maharashtra-90300-jobs-will-be-created-95899</t>
+          <t>https://everythingexperiential.com/article/stars-leaders-and-icons-unite-for-manoj-muntashir-shuklas-mera-desh-pahle-premiere-in-mumbai-572708</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
+          <t>https://www.passionateinmarketing.com/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-the-indian-racing-festival-finale/</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-to-introduce-certification-courses-in-gold-and-jewelry-sector-at-skill-development-university/articleshow/123967156.cms</t>
+          <t>https://currentaffairs.adda247.com/statue-of-chhatrapati-shivaji-honoured-at-pimpri%E2%80%91chinchwad/</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/maharashtra/cabinet-decision-fadnavis-governments-big-gift-for-farmers-and-students/</t>
+          <t>https://www.msn.com/en-in/news/india/breaking-pm-modi-turns-75-nation-celebrates-with-prayers-art-global-greetings-and-tributes/vi-AA1MIflJ</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://mahabharti.in/pashusavardhan-vibhag-bharti-2025/</t>
+          <t>https://marathi.abplive.com/news/latur/latur-news-marathwada-mahadev-koli-community-hunger-strike-postponed-important-assurance-from-shivendraraje-bhosale-maharashtra-marathi-update-1384929</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%B5%E0%A4%B0-%E0%A4%B8%E0%A4%BE%E0%A4%A1%E0%A5%87%E0%A4%86%E0%A4%A0-%E0%A4%B2%E0%A4%BE%E0%A4%96-%E0%A4%95%E0%A5%8B%E0%A4%9F%E0%A5%80/117389/</t>
+          <t>https://indiaeducationdiary.in/hyundai-motor-india-foundation-commits-%E2%82%B956-crore-to-csr-initiatives-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/acharya-devvrat-takes-oath-as-governor-of-maharashtra-94806</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168588</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
+          <t>https://civicmirror.in/maharashtra/hyundai-should-invest-more-and-more-in-the-state-and-increase-employment-generation-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/the-countrys-path-towards-superpowerhood-is-being-paved-with-effective-implementation-of-law-and-order-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/18/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women.html</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/ease-of-doing-business-reduce-the-time-required-for-new-industries-by-reducing-licenses-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.marathijagran.com/maharashtra/chhatrapati-sambhajinagar/ladki-bahin-yojana-will-be-closed-cm-devendra-fadnavis-gave-clarification-95422</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.amp.html</t>
+          <t>https://marathi.abplive.com/business/ladki-bahin-yojana-scheme-1500-rs-stop-due-to-new-rules-e-kyc-women-get-angry-on-cm-devendra-fadnavis-at-hinogli-1386139</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/kolhapur/kolhapur-north/kolhapur-teachers-tet-issue-to-be-discussed-with-chief-minister-15433332</t>
+          <t>https://mahasamvad.in/179428/</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/a-committee-of-eight-secretaries-headed-by-the-chief-secretary-to-prepare-a-vision-document-for-a-developed-maharashtra-2047/117284/</t>
+          <t>https://news18marathi.com/photogallery/money/ladki-bahin-yojana-ekyc-government-makes-e-kyc-mandatory-check-details-in-marathi-1483416.html</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/amp/story/business/2025/Sep/19/rupee-recoups-early-losses-closes-higher-at-8810-even-as-dollar-rises</t>
+          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3632182-maharashtra-unveils-industrial-and-social-policy-reforms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3628368-former-goa-cm-parsekar-says-he-could-return-to-bjp-this-year?amp</t>
+          <t>https://www.loksatta.com/maharashtra/mumbai-rain-latest-updates-maharashtra-weather-news-political-devendra-fadnavis-sanjay-raut-asc-95-5375148/</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/cabinet-approves-bhandara-to-gadchiroli-94-km-expressway.html</t>
+          <t>https://www.marathijagran.com/maharashtra/chhatrapati-sambhajinagar/ladki-bahin-yojana-women-get-angry-on-mahayuti-government-at-hinogli-due-to-new-e-kyc-rules-96333</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628673-fmr-axis-mf-fund-manager-pays-rs-858-lakh-to-settle-market-rules-violation-case-with-sebi?amp</t>
+          <t>https://www.mymahanagar.com/maharashtra/chief-minister-devendra-fadnavis-resolved-to-make-one-crore-women-in-the-state-lakhpati-didi-on-the-occasion-of-marathwada-mukti-din/922549/</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/cm-devendra-fadnavis-on-obc-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A-%E0%A4%A8-%E0%A4%A4-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%93%E0%A4%AC-%E0%A4%B8-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9F-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%95-%E0%A4%B9-%E0%A4%9A-%E0%A4%95-%E0%A4%A2%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%B6%E0%A4%AC%E0%A5%8D%E0%A4%A6/ar-AA1M3dKu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-will-get-1-lakh-rupees-loan-without-interest-read-how-it-works-cm-devendra-fadnavis-tells-calculation-article-152844483</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ev-%E0%A4%98%E0%A5%87%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-5-%E0%A4%B2-%E0%A4%96-%E0%A4%82%E0%A4%9A-%E0%A4%85%E0%A4%A4-%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%A7-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-9000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%B5%E0%A4%B0/ar-AA1MMJ2I?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-21-september-2025-125092100006_1.html</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/cancer-treatment-policy-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A4%B0-%E0%A4%97-%E0%A4%B5%E0%A4%B0-%E0%A4%89%E0%A4%AA%E0%A4%9A-%E0%A4%B0-%E0%A4%B8-%E0%A4%A0-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%A4%E0%A4%AF-%E0%A4%B0-%E0%A4%95%E0%A4%B0/ar-AA1MBSNd</t>
+          <t>https://www.msn.com/mr-in/news/other/ladki-bahin-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%9D%E0%A4%9F%E0%A4%95-%E0%A4%B5%E0%A4%AF-%E0%A4%9A-%E0%A4%B0%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A4%9F-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%98%E0%A4%B0-%E0%A4%A4-%E0%A4%B2-%E0%A4%A4-%E0%A4%A8-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%A4%E0%A4%B0/ar-AA1MWw0i</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
+          <t>https://marathi.asianetnews.com/maharashtra/cidco-lottery-2025-navi-mumbai-affordable-homes-22000-dream-houses/photoshow-s99l5v8</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/non-agricultural-land-certificates-compulsion-removed-for-micro-and-small-businesses/articleshow/123988928.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/wet-drought-declaring-a-wet-drought-in-maharashtra-congress-leader-nana-patole-demands-to-government-95184</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/namo-yuva-run-2025-bjp-organizes-namo-yuva-run-marathon-in-navi-mumbai/133277/</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/cm-fadnavis-orders-to-build-a-cancer-hospital-on-behalf-of-the-sansthan-in-shirdi-prepare-a-policy-for-cancer-treatment/132544/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/18/no-cap-on-prices-of-cars-for-guv-cm-and-judges-in-maharashtra-vehicle-policy</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>https://www.constructionweekonline.in/business/mahindra-maharashtra</t>
+          <t>https://m.thewire.in/article/ptiprnews/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>https://www.manufacturingtodayindia.com/hyundai-rs-56-crore-csr-projects</t>
+          <t>https://www.adgully.com/post/6810/ficci-frames-2025-silver-jubilee-brings-stars-and-global-leaders-together</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3631029-empowering-women-maharashtras-push-for-one-crore-lakhpati-didis</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bes3-mh-fadnavis-jewellery-sector.html</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178604/</t>
+          <t>https://m.economictimes.com/news/india/maharashtras-new-policy-to-promote-creative-tech-sector/amp_articleshow/123928891.cms</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-bamboo-mission-devendra-fadnavis-announcement-ocd-94-5382808/lite/</t>
+          <t>https://startupnews.fyi/2025/09/22/maharashtra-govt-to-strengthen-it-dept-to-enhance-delivery-of-services-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178828/</t>
+          <t>https://www.sakshipost.com/news/maha-cabinet-clears-animation-policy-2025-renewable-energy-projects-452983</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/plan-to-concrete-51-key-roads-in-nashik-city-at-rs3000-crore/articleshow/123981854.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/Newsalert/3630442-like-you-i-am-also-fully-committed-to-taking-india-us-partnership-to-new-heights-pm-modi-to-trump?amp</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-cabinet-approves-rs931cr-for-bhandaragadchiroli-super-highway/articleshow/123928813.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/magel-tyala-saur-krushi-pump-yojana-%E0%A4%AE-%E0%A4%97%E0%A5%87%E0%A4%B2-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%B8-%E0%A4%B0-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AA%E0%A4%82%E0%A4%AA-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%95%E0%A4%B7-%E0%A4%A4-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MUDTy</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/amp/news/railways/indias-bullet-train-project-tunnelling-to-begin-january-2026-as-tbm-arrives/124025478</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-advocate-general-birendra-saraf-resigns-will-continue-his-work-till-january/</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/gurgaon/monitor-infrastructure-projects-to-ensure-quality-union-minister-rao-narbir-singh-tells-gurgaon-residents/amp_articleshow/123954170.cms</t>
+          <t>https://civicmirror.in/maharashtra/the-countrys-path-towards-superpowerhood-is-being-paved-with-effective-implementation-of-law-and-order-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/beed-gets-rail-connectivity-after-a-wait-of-3-generations/amp_articleshow/123955118.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/mahatet-exam-2025-mandatory-exam-confusion-for-senior-teachers-application-process-begins-from-15-september/articleshow/123893618.cms</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-mbbs-admissions-2025-new-schedule-released-for-second-round-what-is-the-date-for-the-third-round/articleshow/123914817.cms</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/statue-of-chhatrapati-shivaji-honoured-at-pimpri%E2%80%91chinchwad/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-govt-to-launch-cleanliness-drive-in-750-villages-on-sep-17-to-mark-pm-modis-birthday-95099</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-unveil-golden-data-of-citizens-move-to-help-detect-bogus-beneficiaries/amp_articleshow/124002889.cms</t>
+          <t>https://marathi.oneindia.com/maharashtra/marathwada-muktisangram-din-2025-devendra-fadanvis-speech-chhatrapati-sambhajinagar-today-037431.html</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/maharashtra-unveils-policy-reforms-to-boost-msmes-social-welfare-572212</t>
+          <t>https://www.berartimes.com/maharashtra/216617/</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address20250921195926?amp=1</t>
+          <t>https://awajmaharashtracha.news/waff-bord/</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
+          <t>https://ahmednagarlive24.com/spacial/maharashtra-railway-another-rs-150-crore-fund-approved-for-this-railway-line-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/cm-devendra-fadnavis-directs-to-prepare-comprehensive-effective-policy-to-fight-cancer-maharashtra-health-marathi-news-1384411</t>
+          <t>https://dainikekmat.com/a-committee-of-eight-secretaries-headed-by-the-chief-secretary-to-prepare-a-vision-document-for-a-developed-maharashtra-2047/117284/</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/shivsena-ubt-mp-sanjay-raut-press-conference-attack-on-bjp-on-corruption-and-debt-on-state-saamana-online-news/</t>
+          <t>https://civicmirror.in/maharashtra/will-change-criteria-for-solar-agricultural-pump-scheme-if-requested-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3630001-maharashtra-advances-student-welfare-and-infrastructure-with-new-initiatives</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/acharya-devvrat-takes-oath-as-governor-of-maharashtra-94806</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/19/people-propose-ai-powered-holographic-guides-cultural-tech-festivals-for-viksit-up-2047-vision</t>
+          <t>https://www.msn.com/mr-in/news/other/pahalgam-terror-attack-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%B2-500-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%9F%E0%A4%95-%E0%A4%86%E0%A4%A4-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%A6-%E0%A4%96%E0%A4%B2/ar-AA1Dy1rF?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/india-news/maharashtra-mandates-e-kyc-for-ladki-bahin-beneficiaries-sets-deadline-125091900196_1.html</t>
+          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>https://hindupost.in/society-culture/breaking-the-myth-of-equality-the-crisis-of-caste-in-bharatiya-christian-communities/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.amp.html</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3628578-maharashtra-rains-give-immediate-relief-of-rs-50k-per-hectare-to-affected-farmers-says-sapkal?amp</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%AF%E0%A4%A8-%E0%A4%A7%E0%A4%B0%E0%A4%A3-%E0%A4%AA-%E0%A4%AF%E0%A4%A5-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A4%97%E0%A5%83%E0%A4%B9-%E0%A4%B8-%E0%A4%A0-862-29-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A4%E0%A4%B0%E0%A4%A4%E0%A5%82%E0%A4%A6-%E0%A4%87%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%9C%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%9A%E0%A5%87-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF/ar-AA1HlaXX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/amp/news/national/seva-pakhwada-pan-india-namo-yuva-run-instils-enthusiasm-patriotism-among-youth-1008611</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>https://indtoday.com/bjp-leader-slams-rahul-gandhi-for-remarks-on-gen-z-and-democracy/</t>
+          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/amp/india/up-deputy-cm-keshav-maurya-directs-officials-to-work-in-team-spirit-during-bahraich-visit</t>
+          <t>https://www.devdiscourse.com/article/law-order/3632182-maharashtra-unveils-industrial-and-social-policy-reforms</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/hyundai-motor-india-foundation-commits-%E2%82%B956-crore-to-csr-initiatives-in-maharashtra/</t>
+          <t>https://www.nagpurtoday.in/future-tech-hub-nagpur-to-host-dedicated-avgc-xr-park/09171239</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>https://newsmeto.com/tweet/pm-modi-75th-birthday-celebs-whose-wishes-took-everyone-by-surprise-modi-birthday-wishes/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/cabinet-approves-bhandara-to-gadchiroli-94-km-expressway.html</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>https://www.liveaaryaavart.com/2025/09/Bihar-state-para-sports.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/the-government-is-kind-to-devendra-fadnavis-builder-friend-juhu-800-crore-municipal-plot-is-in-the-builders-throat-congress-mp-varsha-gaikwad/924065/</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6-%E0%A4%A6-%E0%A4%A4-%E0%A4%9C-%E0%A4%B0-%E0%A4%AD%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AD-%E0%A4%88-%E0%A4%B8%E0%A4%A2%E0%A4%B3-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC%E0%A4%9C%E0%A5%87%E0%A4%9F%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%95%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%82%E0%A4%A8-%E0%A4%87%E0%A4%82%E0%A4%9F%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%86%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1wtpDt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://puneprimenews.com/state/marathwada/tuljai-kala-kendra-polices-big-decision-regarding-tuljai-kala-kendra-the-administration-of-the-art-center-is-being-violated-by-flouting-the-rules/</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/provide-a-fund-of-rs-500-crore-correct-the-caste-certificate-khadse-demands-in-a-letter-to-the-chief-minister/</t>
+          <t>https://www.msn.com/mr-in/news/other/ev-%E0%A4%98%E0%A5%87%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-5-%E0%A4%B2-%E0%A4%96-%E0%A4%82%E0%A4%9A-%E0%A4%85%E0%A4%A4-%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%A7-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-9000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%B5%E0%A4%B0/ar-AA1MMJ2I?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/madc-approves-220acre-land-for-solar-grps-defence-aerospace-projects/articleshow/124004510.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/wet-drought-declaring-a-wet-drought-in-maharashtra-congress-leader-nana-patole-demands-to-government-95184</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/govt-to-set-up-adi-seva-kendras-to-solve-issues-of-tribal-people-tripura-cm20250916223512-139847/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-fadnavis-orders-to-build-a-cancer-hospital-on-behalf-of-the-sansthan-in-shirdi-prepare-a-policy-for-cancer-treatment/132544/</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>https://kiow.com/2025/09/16/gov-reynolds-returns-from-india-trade-and-investment-mission/</t>
+          <t>https://www.manufacturingtodayindia.com/hyundai-rs-56-crore-csr-projects</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kozhikode/tribal-kids-from-remote-wayanad-settlement-begin-their-schooling/articleshow/123928460.cms</t>
+          <t>https://indiaeducationdiary.in/mahindra-tractors-and-maharashtra-govt-partner-to-launch-skill-development-centre-in-gadchiroli/</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/india-news/pm-modi-75th-birthday-2025-wishes-live-updates-quotes-messages-greetings-tweets-on-x-facebook/3980159/</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
+          <t>https://mahasamvad.in/178828/</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179074/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/plan-to-concrete-51-key-roads-in-nashik-city-at-rs3000-crore/articleshow/123981854.cms</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178534/</t>
+          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/2-year-extension-granted-for-modern-orange-processing-centres-in-vidarbha/articleshow/123928870.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-cabinet-approves-rs931cr-for-bhandaragadchiroli-super-highway/articleshow/123928813.cms</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/prime-minister-suryadhar-free-electricity-scheme/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/urban-transportation/maharashtra-deputy-cm-calls-for-enhanced-coordination-on-pune-metro-and-elevated-highway-projects/124040274</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/mahayuti-cabinet-took-8-major-decisions-on-tuesday-mahayuti-cabinet-125091600058_1.html</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-unveil-golden-data-of-citizens-move-to-help-detect-bogus-beneficiaries/articleshow/124002889.cms</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cm-devendra-fadnavis-says-will-make-changes-in-magel-tyala-saur-krushi-pump-yojana-article-152857154/amp</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/parshuram-economic-development-corporation-chairman-ashish-damle-to-get-ministerial-status-says-maharashtra-govt-23594308?button=next</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/maharashtra/216617/</t>
+          <t>https://www.businessworld.in/article/maharashtra-unveils-policy-reforms-to-boost-msmes-social-welfare-572212</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>https://www.theindiadaily.com/india/maharashtra-to-launch-cleanliness-drive-on-pm-narendra-modi-s-birthday-cm-devendra-fadnavis-mangal-prabhat-lodha-iti-students-join-swachh-bharat-initiative-news-94108/amp</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-congress-chief-harshawardhan-sapkal-attacks-state-govt-demands-special-package-for-rain-hit-farmers/articleshow/123904520.cms</t>
+          <t>https://www.loksatta.com/mumbai/bombay-hc-grants-quashed-case-against-chamankar-brothers-in-maharashtra-sadan-scam-mumbai-print-news-zws-70-5378793/</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-rains-give-immediate-relief-of-rs-50k-per-hectare-to-affected-farmers-says-sapkal/2917276</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/pandit-deendayal-upadhyay-employment-fair-organized.html</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-demands-rs50k/ha-relief-for-farmers/articleshow/123907918.cms</t>
+          <t>https://lokmanthan.com/a-comprehensive-policy-should-be-prepared-for-cancer-treatment-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Declare-%E2%80%98wet-drought%E2%80%99-in-Maharashtra-give-aid-of-Rs-50-000-per-hectare-to-farmers-Wadettiwar/2922992</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%B5%E0%A4%B0-%E0%A4%B8%E0%A4%BE%E0%A4%A1%E0%A5%87%E0%A4%86%E0%A4%A0-%E0%A4%B2%E0%A4%BE%E0%A4%96-%E0%A4%95%E0%A5%8B%E0%A4%9F%E0%A5%80/117389/</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Maharashtra-rains-Give-immediate-relief-of-Rs-50k-per-hectare-to-affected-farmers-says-Sapkal/2917276</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-mandates-e-kyc-for-ladki-bahin-beneficiaries-sets-deadline-125091900196_1.html</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/wadettiwar-urges-maharashtra-to-declare-wet-drought-seeks-rs-50000-aid-per-hectare-for-farmers.html</t>
+          <t>https://hindupost.in/society-culture/breaking-the-myth-of-equality-the-crisis-of-caste-in-bharatiya-christian-communities/</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/maharashtra-rains-give-immediate-relief-of-rs-50k-per-hectare-to-affected-farmers-says-sapkal-10467270</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom30-mh-obc-committee-certificates.html</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/parbhani/maharashtra-government-gives-128-crore-rupees-funds-to-parbhani-for-rainfall-affected-farmers/articleshow/123980989.cms</t>
+          <t>https://www.studyiq.com/articles/mukhyamantri-majhi-ladki-bahin-yojana/</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%93%E0%A4%B2-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95-%E0%A4%B3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%95%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%B9%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-50-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7/ar-AA1MJhTF</t>
+          <t>https://www.liveaaryaavart.com/2025/09/Bihar-state-para-sports.html</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178713/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/madc-approves-220acre-land-for-solar-grps-defence-aerospace-projects/articleshow/124004510.cms</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/rohit-pawar-slams-devendra-fadnavis-no-funds-for-loan-waiver-yet-40-lakh-spent-on-cms-residence-renovation-1384979</t>
+          <t>https://www.latestly.com/agency-news/india-news-govt-to-set-up-adi-seva-kendras-to-solve-issues-of-tribal-people-tripura-cm-7114924.html</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/amp/</t>
+          <t>https://kiow.com/2025/09/16/gov-reynolds-returns-from-india-trade-and-investment-mission/</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/nanded-farmers-to-receive-rs-553-crore-dbt-relief-sai29</t>
+          <t>https://timesofindia.indiatimes.com/city/kozhikode/tribal-kids-from-remote-wayanad-settlement-begin-their-schooling/articleshow/123928460.cms</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ncp-sharad-pawar-on-maharashtra-floods-farmers-distress-and-plea-for-government-aid-1495164.html</t>
+          <t>https://www.financialexpress.com/india-news/pm-modi-75th-birthday-2025-wishes-live-updates-quotes-messages-greetings-tweets-on-x-facebook/3980159/</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AC%E0%A4%B3-%E0%A4%B0-%E0%A4%9C-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%93%E0%A4%B2-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95-%E0%A4%B3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%95%E0%A4%B0-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%83%E0%A4%A6%E0%A4%AF-%E0%A4%B2-%E0%A4%AA-%E0%A4%9D%E0%A4%B0-%E0%A4%95%E0%A4%B8-%E0%A4%AB%E0%A5%81%E0%A4%9F%E0%A4%A4-%E0%A4%A8-%E0%A4%B9/ar-AA1MPirq</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%AC%E0%A4%81%E0%A4%95-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%B8%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1MRkaw</t>
+          <t>https://mahasamvad.in/179074/</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179457/</t>
+          <t>https://mahasamvad.in/178534/</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/nanded/maharashtra-sanctions-553-crore-relief-for-flood-hit-farmers-in-nanded-vsb99</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/2-year-extension-granted-for-modern-orange-processing-centres-in-vidarbha/articleshow/123928870.cms</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ahilyanagar-rain-damage-vikhe-patil-orders-ocd-94-5377488/</t>
+          <t>https://mandalnews.com/amravati/prime-minister-suryadhar-free-electricity-scheme/</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>https://www.athawadavishesh.com/39369/</t>
+          <t>https://www.loksatta.com/mumbai/five-thousand-mw-renewable-energy-projects-in-maharashtra-state-mumbai-news-amy-95-5377726/</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/agriculture/dattatray-bharne-went-to-the-washim-district-to-inspect-the-affected-crop/amp/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/pm-suryaghar-yojana-443-mw-of-electricity-generated-in-vidarbha-1364448.html</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/sharad-pawars-main-indicator-but-wisdom-is-a-matter-of-learning/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/mahayuti-cabinet-took-8-major-decisions-on-tuesday-mahayuti-cabinet-125091600058_1.html</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/flag-hoisting-by-cm-fadnavis-at-sambhajinagar-on-marathwada-liberation-day/</t>
+          <t>https://www.theindiadaily.com/india/maharashtra-to-launch-cleanliness-drive-on-pm-narendra-modi-s-birthday-cm-devendra-fadnavis-mangal-prabhat-lodha-iti-students-join-swachh-bharat-initiative-news-94108</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/agriculture-minister-dattatray-bharne-visits-washim-district-hoped-for-help-for-affected-farmers/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-congress-chief-harshawardhan-sapkal-attacks-state-govt-demands-special-package-for-rain-hit-farmers/articleshow/123904520.cms</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%82%E0%A4%97%E0%A5%80/117572/</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-rains-give-immediate-relief-of-rs-50k-per-hectare-to-affected-farmers-says-sapkal/2917276</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/jayant-patil-heavy-rain-agriculture-news-declaring-a-wet-drought-in-the-state-jayant-patil-letter-to-chief-minister-devendra-fadnavis-in-sangli-1385048</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-demands-rs50k/ha-relief-for-farmers/articleshow/123907918.cms</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/amp</t>
+          <t>https://www.ptinews.com/story/national/rain-havoc-in-marathwada-8-dead-houses-and-crops-damaged/2941151</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/maharashtra-government-sanctions-over-88-lakh-rupees-aid-for-kolhapur-sangli-and-dharashiv-farmers-hit-by-june-july-rains-rds-00-5381688/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%93%E0%A4%B2-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95-%E0%A4%B3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%95%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%B9%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-50-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7/ar-AA1MJhTF?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/a-fund-of-689-crores-has-been-approved-to-help-farmers-affected-by-heavy-rainfall-996353.html/amp</t>
+          <t>https://mahasamvad.in/178713/</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-dharashiv-flooding-causes-massive-soybean-crop-damage-1497495.html/amp</t>
+          <t>https://www.tv9marathi.com/videos/ncp-sharad-pawar-on-maharashtra-floods-farmers-distress-and-plea-for-government-aid-1495164.html</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/agriculture/dattatray-bharne-went-to-the-washim-district-to-inspect-the-affected-crop/</t>
+          <t>https://www.loksatta.com/kolhapur/maharashtra-government-sanctions-over-88-lakh-rupees-aid-for-kolhapur-sangli-and-dharashiv-farmers-hit-by-june-july-rains-rds-00-5381688/</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
+          <t>https://agrowon.esakal.com/agro-special/nanded-farmers-to-receive-rs-553-crore-dbt-relief-sai29</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/rohit-pawar-slams-devendra-fadnavis-no-funds-for-loan-waiver-yet-40-lakh-spent-on-cms-residence-renovation-1384979</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%AC%E0%A4%81%E0%A4%95-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%B8%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1MRkaw?cvid=68ccf74848e64225b263c6b454dae318&amp;ocid=hpmsn</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/bacchu-kadu-has-strongly-criticized-on-state-government-on-the-agricultural-issue-farmers-heavy-rain-in-solapur-1384615</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/heavy-rain-damages-crops-in-nanded-agriculture-minister-assures-support-sai29</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/jayant-patil-heavy-rain-agriculture-news-declaring-a-wet-drought-in-the-state-jayant-patil-letter-to-chief-minister-devendra-fadnavis-in-sangli-1385048</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-farmers-crop-damage-relief-dattatray-bharne-announcement/41253</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-government-sanctions-128-crore-aid-for-flood-hit-farmers-in-parbhani-rds-00-5382862/</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-farmers-flood-compensation-2025-dattatray-bharane-statement-135991809.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/a-fund-of-689-crores-has-been-approved-to-help-farmers-affected-by-heavy-rainfall-996353.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/beed-farmers-worried-due-to-cloudburst-like-rain-in-ashti-taluka-farmers-demands-state-government-compensation-mla-suresh-dhas-says-government-with-you-watch-video-maharashtra-news-mhs25091803910</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/ahilyanagar-rain-damage-vikhe-patil-orders-ocd-94-5377488/</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/parbhani-immediate-assistance-provided-to-farmers-affected-by-heavy-rains-says-meghna-sakore-bordikar-css-98-5379203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>https://www.athawadavishesh.com/39369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>https://breakingmaharashtra.in/?p=40301</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/agriculture/dattatray-bharne-went-to-the-washim-district-to-inspect-the-affected-crop/</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/social/agriculture-minister-dattatray-bharne-visits-washim-district-hoped-for-help-for-affected-farmers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%82%E0%A4%97%E0%A5%80/117572/</t>
         </is>
       </c>
     </row>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A682"/>
+  <dimension ref="A1:A563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/chhatrapati-sambhajinagar-will-become-countrys-ev-capital-maharashtra-cm-devendra-fadnavis/article70059920.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/pm-modi-to-inaugurate-mumbai-metro-3s-final-stretch-from-worli-to-cuffe-parade-on-sept-30-announces-chief-minister-devendra-fadnavis/articleshow/123928132.cms</t>
         </is>
       </c>
     </row>
@@ -459,28 +459,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-devendra-fadnavis-says-govt-will-create-corpus-fund-for-medical-treatments-that-cost-more-than-rs-5-lakh/articleshow/123905737.cms</t>
+          <t>https://www.ndtv.com/india-news/on-rahul-gandhis-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-9306931</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/on-rahul-gandhis-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-9306931</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-devendra-fadnavis-says-govt-will-create-corpus-fund-for-medical-treatments-that-cost-more-than-rs-5-lakh/articleshow/123905737.cms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://indianmasterminds.com/news/cm-fadnavis-police-reform-technology-economy-ipf-2025-146277/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/next-mumbai-mayor-will-be-from-maha-yuti-says-devendra-fadnavis-as-bjp-launches-campaign-for-bmc-polls-3730927</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-move-supreme-court-if-karnataka-goes-ahead-with-plan-to-increase-almatti-dams-height-cm-devendra-fadnavis-3732808</t>
+          <t>https://www.ndtv.com/video/on-rahul-gandhi-s-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-996639</t>
         </is>
       </c>
     </row>
@@ -494,35 +494,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-devendra-fadnavis-to-launch-railway-project-for-marathwada-3730637</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-move-supreme-court-if-karnataka-goes-ahead-with-plan-to-increase-almatti-dams-height-cm-devendra-fadnavis-3732808</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/next-mumbai-mayor-will-be-from-maha-yuti-says-devendra-fadnavis-as-bjp-launches-campaign-for-bmc-polls-3730927</t>
+          <t>https://timesofindia.indiatimes.com/india/no-faith-in-constitution-fadnavis-targets-rahul-gandhi-over-gen-z-post-terms-him-urban-maoist/articleshow/123996897.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/remove-requirement-of-non-agricultural-land-certificate-for-micro-and-small-enterprises-says-maharashtra-chief-minister-devendra-fadnavis/articleshow/123979505.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-devendra-fadnavis-to-launch-railway-project-for-marathwada-3730637</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/acharya-devvrat-takes-oath-as-maha-governor-in-sanskrit-in-the-presence-of-cm-devendra-fadnavis/videoshow/123896080.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/congress-slams-maharashtra-cm-fadnavis-over-posters-featuring-shivaji-maharaj-pasted-at-train-station-with-filth-around-3732307</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-strengthen-it-department-for-better-citizen-services-cm-fadnavis-23595276</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/remove-requirement-of-non-agricultural-land-certificate-for-micro-and-small-enterprises-says-maharashtra-chief-minister-devendra-fadnavis/articleshow/123979505.cms</t>
         </is>
       </c>
     </row>
@@ -536,21 +536,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/109961/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-indias-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/wont-scrap-ladki-bahin-scheme-aim-to-create-1-crore-lakhpati-didis-fadnavis/article70061945.ece</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-to-come-out-with-bamboo-industry-policy-cm-devendra-fadnavis-3735818</t>
+          <t>https://www.ap7am.com/en/109961/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-indias-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-strenghten-it-dept-to-enhance-delivery-of-services-cm-fadnavis/articleshow/124053957.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-to-come-out-with-bamboo-industry-policy-cm-devendra-fadnavis-3735818</t>
         </is>
       </c>
     </row>
@@ -564,378 +564,378 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-fadnavis-reviews-security-and-preparedness-with-navy-and-army-officers/articleshow/124029075.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/pm-modi-to-inaugurate-mumbai-metro-3s-final-stretch-from-worli-to-cuffe-parade-on-sept-30-announces-chief-minister-devendra-fadnavis/articleshow/123928132.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-fadnavis-reviews-security-and-preparedness-with-navy-and-army-officers/articleshow/124029075.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-will-move-sc-if-karnataka-goes-ahead-with-plan-to-raise-almatti-dam-height-fadnavis-101758133395229.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-strenghten-it-dept-to-enhance-delivery-of-services-cm-fadnavis/articleshow/124053957.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3634846-strengthening-maritime-military-ties-fadnavis-meets-armed-forces-leaders</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-will-move-sc-if-karnataka-goes-ahead-with-plan-to-raise-almatti-dam-height-fadnavis-101758133395229.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3633329-fadnavis-accuses-rahul-gandhi-of-urban-maoist-rhetoric</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/acharya-devvrat-takes-oath-as-maha-governor-in-sanskrit-in-the-presence-of-cm-devendra-fadnavis/videoshow/123896080.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628667-fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir?amp</t>
+          <t>https://sundayguardianlive.com/news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-145995/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-pm-modi-a-visionary-global-statesman-on-his-75th-birthday-23594462</t>
+          <t>https://sundayguardianlive.com/news/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe20250918053517-141254/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maratha-quota-gr-will-not-affect-obc-rights-says-fadnavis-101757875654855.html</t>
+          <t>https://www.deccanherald.com/india/congress-accuses-bjp-of-coming-to-power-in-maharashtra-by-rigging-votes-asks-fadnavis-to-quit-3734523</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168537</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maratha-quota-gr-will-not-affect-obc-rights-says-fadnavis-101757875654855.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/congress-accuses-bjp-of-coming-to-power-in-maharashtra-by-rigging-votes-asks-fadnavis-to-quit-3734523</t>
+          <t>https://money.rediff.com/news/market/fadnavis-streamline-industry-approvals-in-maharashtra/33958120250919</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-signs-mou-with-cambridge-for-global-standard-education-cm-fadnavis/articleshow/123980116.cms</t>
+          <t>https://www.business-standard.com/industry/news/maha-govt-to-launch-skills-courses-for-gems-and-jewellery-sector-fadnavis-125091600501_1.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382/2</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168537</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-signs-mou-with-cambridge-for-global-standard-education-cm-fadnavis/articleshow/123980116.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/reduce-number-of-permissions-to-set-up-industries-speed-up-approval-time-fadnavis-to-officials/2930550</t>
+          <t>https://www.ptinews.com/editor-detail/Fadnavis-govt-apathetic-towards-farmers-woes-claims-Pawar;-warns-of-intensifying-stir/2916686</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/fadnavis-streamline-industry-approvals-in-maharashtra/33958120250919</t>
+          <t>https://www.telegraphindia.com/india/bad-devendra-fadnavis-marg-youth-congress-targets-cm-as-potholes-expose-bmcs-failure-on-mumbai-roads/cid/2124363</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/maha-govt-to-launch-skills-courses-for-gems-and-jewellery-sector-fadnavis-125091600501_1.html</t>
+          <t>https://www.thehansindia.com/news/national/fadnavis-govt-apathetic-towards-farmers-woes-1006773</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-on-marathwada-liberation-day-107384/1</t>
+          <t>https://m.economictimes.com/tech/information-tech/maharashtra-govt-to-strengthen-it-dept-to-enhance-delivery-of-services-fadnavis/articleshow/124049221.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/technology/3636540-maharashtra-pushes-digital-transformation-with-it-department-revamp</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/congress-slams-cm-fadnavis-over-shivaji-posters-pasted-in-unhygienic-surroundings-near-prabhadevi-railway-station-in-mumbai/articleshow/123948554.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Fadnavis-govt-apathetic-towards-farmers-woes-claims-Pawar;-warns-of-intensifying-stir/2916686</t>
+          <t>https://www.ptinews.com/story/business/chhatrapati-sambhajinagar-will-become-countrys-ev-capital-fadnavis/2922163</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-devendra-fadnavis-23594442</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.telegraphindia.com/india/bad-devendra-fadnavis-marg-youth-congress-targets-cm-as-potholes-expose-bmcs-failure-on-mumbai-roads/cid/2124363</t>
+          <t>https://www.cnbctv18.com/infrastructure/pm-modi-to-inaugurate-mumbai-metro-3-on-september-30-says-devendra-fadnavis-19677024.htm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/chhatrapati-sambhajinagar-will-become-countrys-ev-capital-fadnavis/2922163</t>
+          <t>https://www.heraldgoa.in/goa/mi-punha-yeyin-il-be-back-again-devendra-fadanvis-is-the-next-chief-minister-of-maharashtra/13454/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/tech/information-tech/maharashtra-govt-to-strengthen-it-dept-to-enhance-delivery-of-services-fadnavis/articleshow/124049221.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-lead-in-green-steel-manufacturing-cm-devendra-fadnavis-23594846</t>
+          <t>https://www.ptinews.com/editor-detail/using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level--fadnavis/2934307</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114</t>
+          <t>https://money.rediff.com/news/market/ev-capital-fadnavis-on-chhatrapati-sambhajinagar/33804020250917</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/ladki-bahin-scheme-to-continue-govt-committed-to-women-s-empowerment-devendra-fadnavis-13553696.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-fadnavis-3732054</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/sambhajinagar-becoming-ev-capital-of-country-fadnavis/articleshow/123952619.cms</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/congress-slams-cm-fadnavis-over-shivaji-posters-pasted-in-unhygienic-surroundings-near-prabhadevi-railway-station-in-mumbai/articleshow/123948554.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-govt-dept-websites-landing-pages-to-be-in-marathi-101757962665589.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/infrastructure/pm-modi-to-inaugurate-mumbai-metro-3-on-september-30-says-devendra-fadnavis-19677024.htm</t>
+          <t>https://bioenergytimes.com/maharashtra-to-launch-comprehensive-bamboo-industry-policy-cm-fadnavis-announces/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhi-speaks-like-an-urban-maoist-says-maharashtra-cm-fadnavis-on-congress-leaders-gen-z-post-23594827</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom41-mh-police-ld-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630398-bjps-enduring-commitment-fadnavis-recollects-2017-political-maneuverings-in-mumbai</t>
+          <t>https://infra.economictimes.indiatimes.com/news/railways/maharashtra-cm-fadnavis-inaugurates-new-amalner-beed-railway-line/123961961</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level--fadnavis/2934307</t>
+          <t>https://m.economictimes.com/industry/indl-goods/svs/steel/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/articleshow/123999573.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628555-vast-growth-opportunities-in-fisheries-animal-husbandry-sectors-says-fadnavis-cites-aps-example?amp</t>
+          <t>https://www.businessworld.in/article/hyundai-maharashtra-discuss-new-investments-jobs-571636</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-fadnavis-and-the-obcs-101757877151905.html</t>
+          <t>https://www.business-standard.com/india-news/next-phase-of-gst-reforms-will-boost-india-s-economic-growth-says-fadnavis-125092100781_1.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maratha-quota-row-obc-other-groups-turn-up-heat-cm-urges-restraint-125091500006_1.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-cabinet-clears-avgc-xr-policy-draws-up-a-25-year-roadmap-101758043978392.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
+          <t>https://www.ptinews.com/editor-detail/reduce-number-of-permissions-to-set-up-industries--speed-up-approval-time--fadnavis-to-officials/2930550</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modi-allocated-rs-21000-crore-for-rail-lines-in-marathwada-claims-cm-devendra-fadnavis-23594480</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-govt-to-strenghten-it-dept-to-enhance-delivery-of-services-fadnavis/2938775</t>
+          <t>https://www.aninews.in/news/entertainment/out-of-box/hindi-films-fail-to-depict-the-true-heroism-of-mumbai-police-says-maharashtra-cm-fadnavis20250920135931</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/acharya-devvrat-takes-oath-as-maharashtra-governor-101757915941969.html</t>
+          <t>https://www.ptinews.com/story/national/obc-other-groups-turn-up-heat-over-maratha-quota-gr-cm-cautions-against-politics-of-extreme/2915442</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/ev-capital-fadnavis-on-chhatrapati-sambhajinagar/33804020250917</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop-fadnavis/2927696</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/2930145</t>
+          <t>https://lokmat.news18.com/short-videos/trending/gopichand-padalkar-news-first-reaction-after-cm-devendra-fadnavis-call-jayant-patil-n18s-1075363.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-leads-maharashtra-in-greeting-pm-modi-on-birthday-calls-him-global-statesman-inspiration/2922857</t>
+          <t>https://www.business-standard.com/india-news/maratha-quota-row-obc-other-groups-turn-up-heat-cm-urges-restraint-125091500006_1.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/gopichand-padalkar-news-first-reaction-after-cm-devendra-fadnavis-call-jayant-patil-n18s-1075363.html</t>
+          <t>https://www.ptinews.com/editor-detail/maharashtra--all-files-to-be-vetted-by-shinde-before-being-sent-to-cm-fadnavis/2429371</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-cabinet-clears-avgc-xr-policy-draws-up-a-25-year-roadmap-101758043978392.html</t>
+          <t>https://www.ptinews.com/editor-detail/Western-Naval-Command-chief-meets-Maharashtra-CM-discusses-maritime-security-situation/2933686</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-govt-dept-websites-landing-pages-to-be-in-marathi-101757962665589.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-sign-mous-to-boost-steel-production-3736498</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/gst-reforms-to-speed-up-indias-economic-growth-says-fadnavis/2936669</t>
+          <t>https://www.hindustantimes.com/india-news/acharya-devvrat-takes-oath-as-maharashtra-governor-101757915941969.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-lays-foundation-stone-for-aws-data-centre-in-mumbai-part-of-usd-8-3-billion-investment/2941290</t>
+          <t>https://www.aninews.in/news/national/general-news/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm20250919232605</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/indl-goods/svs/steel/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/articleshow/123999573.cms</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-leads-maharashtra-in-greeting-pm-modi-on-birthday-calls-him-global-statesman-inspiration/2922857</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3636600-sanskriti-bachao-morcha-sparks-political-unrest-in-maharashtra</t>
+          <t>https://www.newsonair.gov.in/hyderabad-liberation-day-celebrated-with-flag-hoisting-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/next-phase-of-gst-reforms-will-boost-india-s-economic-growth-says-fadnavis-125092100781_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-to-storm-fadnavis-home-turf-rally-obcs-on-sept-18/articleshow/123929254.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/health/3628551-fadnavis-calls-for-inclusive-cancer-care-policy-for-maharashtra</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-calls-for-inclusive-cancer-care-policy-for-maharashtra/2917226</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/sharad-pawar-on-devendra-fadnavis-rain-damage-saying-devabhau-pawar-s-big-demand-to-cm-n18s-1075195.html</t>
+          <t>https://www.ptinews.com/story/national/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal/2926755</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/railways/maharashtra-cm-fadnavis-inaugurates-new-amalner-beed-railway-line/123961961</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-fadnavis-and-the-obcs-101757877151905.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/shiv-sena-ubt-targets-maharashtra-cm-devendra-for-not-unveiling-swami-ramanand-tirtha-statue-23594500</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-fadnavis-defends-obc-reservation-policy-says-no-threat-to-communitys-rights/articleshow/123886921.cms</t>
         </is>
       </c>
     </row>
@@ -949,322 +949,322 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3636632-maharashtra-cm-fadnavis-acts-on-marathwada-rainfall-crisis</t>
+          <t>https://lokmat.news18.com/short-videos/trending/sharad-pawar-on-devendra-fadnavis-rain-damage-saying-devabhau-pawar-s-big-demand-to-cm-n18s-1075195.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm20250919232605</t>
+          <t>https://inshorts.com/en/news/marathwada-got--21-000-cr-investment-in-past-10-years--fadnavis-1758179070896</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004?button=next</t>
+          <t>https://www.ptinews.com/editor-detail/gst-reforms-to-speed-up-india%E2%80%99s-economic-growth--says-fadnavis/2936669</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/drug-free-india-key-message-of-namo-yuva-run-bjp-mp-tejasvi-surya-3737765</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom28-mh-police-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hyderabad-liberation-day-celebrated-with-flag-hoisting-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/20/major-push-to-industry.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-to-storm-fadnavis-home-turf-rally-obcs-on-sept-18/articleshow/123929254.cms</t>
+          <t>https://www.ndtv.com/india-news/mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-cm-fadnavis-9322871</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/oppn-ruling-parties-spar-over-rahul-s-fresh-vote-chori-charges-cong-seeks-fadnavis-resignation/ar-AA1MOLDw</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-govt-will-create-corpus-fund-to-cover-treatments-costing-over-rs-5-lakh-fadnavis/2917336</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop--fadnavis/2927696</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/gst-reforms-to-speed-up-india%E2%80%99s-economic-growth--says-fadnavis/2936669</t>
+          <t>https://www.aninews.in/news/national/general-news/lifting-last-person-and-bringing-them-to-mainstream-development-reflects-pm-modis-working-approach-maharashtra-cm-fadnavis20250917223421</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal/2926755</t>
+          <t>https://www.ptinews.com/editor-detail/Oppn-ruling-parties-spar-over-Rahul-s-fresh-vote-chori-charges;-Cong-seeks-Fadnavis-resignation/2927028</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-should-step-up-to-bridge-differences-among-communities-pawar-on-quota-row/2940731</t>
+          <t>https://www.aninews.in/news/national/general-news/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address20250921195926</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe20250918053517</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row/articleshow/124004724.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
+          <t>https://www.ptinews.com/story/national/oppn-ruling-parties-spar-over-rahuls-fresh-vote-chori-charges-cong-seeks-fadnavis-resignation/2927511</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-cm-fadnavis-9322871</t>
+          <t>https://www.business-standard.com/industry/news/maharashtra-signs-mous-worth-80-962-cr-for-industrial-projects-40k-jobs-125091900956_1.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Oppn-ruling-parties-spar-over-Rahul-s-fresh-vote-chori-charges;-Cong-seeks-Fadnavis-resignation/2927028</t>
+          <t>https://zeenews.india.com/india/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-india-s-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt-2963047.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/oppn-ruling-parties-spar-over-rahul-s-fresh-vote-chori-charges;-cong-seeks-fadnavis-resignation/2927028</t>
+          <t>https://zeenews.india.com/india/residential-complex-for-muslims-in-mumbai-nhrc-issues-notice-to-fadnavis-govt-bjp-2957165.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Cong-slams-Fadnavis-over-posters-featuring-Shivaji-Maharaj-pasted-at-train-station-with-filth-around/2923386</t>
+          <t>https://www.aninews.in/news/national/general-news/mumbai-union-minister-pralhad-joshi-maharashtra-cm-fadnavis-inaugurate-steel-mahakumbh20250919211944</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/dycm-shivakumar-dismisses-meeting-amit-shah-rumours-says-i-am-not-mad-3739304</t>
+          <t>https://newsarenaindia.com/states/maharashtra-scraps-na-land-nod-for-msmes/56828</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/lifting-last-person-and-bringing-them-to-mainstream-development-reflects-pm-modis-working-approach-maharashtra-cm-fadnavis20250917223421</t>
+          <t>https://www.ptinews.com/story/national/trial-run-held-for-metro-lines-4-and-4a-in-thane-project-to-cut-travel-time-significantly/2937833</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address20250921195926</t>
+          <t>https://www.lokmattimes.com/maharashtra/rahul-gandhis-mind-has-been-stolen-maharashtra-cm-devendra-fadnavis-on-congress-mps-vote-theft-claims-a525/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/bjp-gave-up-claim-for-mumbai-mayor-s-post-in-2017-at-request-of-shinde--narvekar--says-cm-fadnavis/2921301</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-strengthen-it-department-for-better-citizen-services-cm-fadnavis-23595276</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal-23594647</t>
+          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3635703-gst-reforms-a-boost-to-indias-economic-growth-and-self-reliance</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-pm-modi-a-visionary-global-statesman-on-his-75th-birthday-23594462</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-india-s-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt-2963047.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modi-allocated-rs-21000-crore-for-rail-lines-in-marathwada-claims-cm-devendra-fadnavis-23594480</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/maharashtra-signs-mous-worth-80-962-cr-for-industrial-projects-40k-jobs-125091900956_1.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/football-legend-lionel-messi-to-visit-mumbai-in-december-will-train-with-young-footballers-cm-fadnavis-23595113</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/a-first-meeting-to-remember-for-a-lifetime-fadnavis-recalls-memory-on-pm-modis-75th-birthday/09171313</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-devendra-fadnavis-23594442</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/oppn--ruling-parties-spar-over-rahul-s-fresh--vote-chori--charges;-cong-seeks-fadnavis--resignation/2927511</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382/2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-announces-pod-taxi-plan-to-ease-traffic-congestion-in-mumbai-23595266</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/residential-complex-for-muslims-in-mumbai-nhrc-issues-notice-to-fadnavis-govt-bjp-2957165.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-for-tech-driven-policing-flags-ai-and-cybercrime-challenges-23594968</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-on-marathwada-liberation-day-107384/7</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-lead-in-green-steel-manufacturing-cm-devendra-fadnavis-23594846</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/mumbai-union-minister-pralhad-joshi-maharashtra-cm-fadnavis-inaugurate-steel-mahakumbh20250919211944</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mlas-remarks-about-ncp-sp-leader-23594821</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-CM-Fadnavis/2938730</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharastra-cm-fadnavis-pushes-for-faster-industrial-approvals-ai-based-reforms-to-boost-investments-23594849</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/heavy-rains-in-solapur-marathwada-cm-asks-water-resources-dept-to-coordinate-with-collectors/2939011</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhi-speaks-like-an-urban-maoist-says-maharashtra-cm-fadnavis-on-congress-leaders-gen-z-post-23594827</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/first-test-run-of-thane-metro-4-conducted-promises-to-ease-traffic-woes-23595193</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/delhi-cm-praises-pm-modi-for-gst-reforms-says-public-to-benefit-directly20250921223646</t>
+          <t>https://www.devdiscourse.com/article/business/3633546-streamlining-success-maharashtras-push-for-rapid-industrial-approvals</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
+          <t>https://www.mid-day.com/news/india-news/article/cm-fadnavis-says-chhatrapati-sambhajinagar-will-become-country-s-ev-capital-23594430?button=next</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/maharashtra-mahayuti-mva-war-of-words-erupts-rahul-gandhi-vote-theft-congress-demands-devendra-fadnavis-resignation-1801046</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal-23594647</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.footboom1.com/en/news/football/2752001-lionel-messi-s-confirmed-visit-to-maharashtra-sparks-excitement</t>
+          <t>https://www.sakshipost.com/news/condition-about-obtaining-non-agricultural-land-license-should-be-removed-msmes-cm-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/acharya-devvrat-sworn-in-as-governor-of-maharashtra-in-presence-of-cm-devendra-fadnavis-7112162.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-announces-pod-taxi-plan-to-ease-traffic-congestion-in-mumbai-23595266</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/zero-tolerance-important-curb-drug-related-crimes-says-cm-fadnavis-454693</t>
+          <t>https://news.abplive.com/cities/maharashtra-mahayuti-mva-war-of-words-erupts-rahul-gandhi-vote-theft-congress-demands-devendra-fadnavis-resignation-1801046</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/cm-devendra-fadnavis-dcm-ajit-pawar-to-inaugurate-amalner-beed-new-railway-line-in-pune-division-on-september-17/</t>
+          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/bureaucratic-delays-stall-pune-khadki-cantonment-merger-despite-maharashtra-cms-nod/</t>
+          <t>https://www.punekarnews.in/cm-devendra-fadnavis-dcm-ajit-pawar-to-inaugurate-amalner-beed-new-railway-line-in-pune-division-on-september-17/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/devendra-fadnavis-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane-7123779.html</t>
+          <t>https://www.devdiscourse.com/article/business/3633401-maharashtras-bold-step-towards-a-greener-steel-future</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
+          <t>https://www.newsdrum.in/national/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar-10478970</t>
         </is>
       </c>
     </row>
@@ -1278,161 +1278,161 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
+          <t>https://www.punekarnews.in/bureaucratic-delays-stall-pune-khadki-cantonment-merger-despite-maharashtra-cms-nod/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/mumbai-union-minister-pralhad-joshi-maharashtra-cm-fadnavis-inaugurate-steel-mahakumbh20250919211944</t>
+          <t>https://www.latestly.com/quickly/agency-news/devendra-fadnavis-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane-7123779.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/acharya-devvrat-sworn-in-as-new-governor-of-maharashtra-succeeding-cp-radhakrishnan/</t>
+          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-shocked-bjp-leader-haresh-keni-joins-congress-panvel-municipal-election-maharashtra-politics/articleshow/124016475.cms</t>
+          <t>https://english.varthabharati.in/india/mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-cm-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-sharad-pawar-devendra-fadnavis-engaged-in-a-war-of-words-over-maratha-obc-reservation-ws-l-9622419.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-shocked-bjp-leader-haresh-keni-joins-congress-panvel-municipal-election-maharashtra-politics/articleshow/124016475.cms</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mva-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%B0-%E0%A4%A8-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%AB%E0%A5%8D%E0%A4%A4-%E0%A4%B0-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%A5-sit-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%9C-%E0%A4%82%E0%A4%9A/ar-AA1ybCn1?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-government-constituted-a-ministerial-committee-for-simhastha-mahakumbh-2027-chhagan-bhujbal-named-3015468</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-big-attack-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava-bmc-election/articleshow/123926944.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-sharad-pawar-devendra-fadnavis-engaged-in-a-war-of-words-over-maratha-obc-reservation-ws-l-9622419.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%BF%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%A8-4/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AB-%E0%A4%B2%E0%A5%8D%E0%A4%AE-%E0%A4%9B-%E0%A4%B5-%E0%A4%95-%E0%A4%A4-%E0%A4%B0-%E0%A4%AB-%E0%A4%87%E0%A4%A4-%E0%A4%B9-%E0%A4%B8%E0%A4%95-%E0%A4%B0-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%89%E0%A4%A0-%E0%A4%8F-%E0%A4%B8%E0%A4%B5-%E0%A4%B2/ar-AA1AjRCP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-trouble-for-devendra-fadnavis-obc-banjara-protest-against-maratha-reservation-maharashtra-politics-ws-ln-9621475.html</t>
+          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-congratulates-indian-women-hockey-team-for-bronze-medal-amid-india-vs-pakistan-asia-cup-3012731</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-launched-various-csr-projects-of-hyundai-motor-india-ltd-in-mumbai-meeting-with-md-unsoo-kim-3013038</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-big-attack-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava-bmc-election/articleshow/123926944.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-devendra-fadnavis-compared-rahul-gandhi-to-hitlers-minister-saying-rahul-gandhis-hydrogen-bomb-is-a-dud/articleshow/123991146.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%B6-%E0%A4%B5-%E0%A4%9C-%E0%A4%95-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1MCKQS</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-devendra-fadnavis-shares-story-of-first-meeting-with-pm-narendra-modi-ws-kl-9629275.html</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-reacted-on-lop-rahul-gandhi-over-vote-theft-allegations-ann-3014991</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-shared-story-how-he-impressed-form-pm-narendra-modi-ahead-of-75th-birthday-rss-nagar-visit-know-all/articleshow/123913706.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-devendra-fadnavis-compared-rahul-gandhi-to-hitlers-minister-saying-rahul-gandhis-hydrogen-bomb-is-a-dud/articleshow/123991146.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-cm-devendra-fadnavis-wishi-pm-narendra-modi-on-75th-birthday-mumbai-3014251</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/cm-devendra-fadnavis-announces-metro-to-start-between-csmt-and-thane-date-announced/articleshow/124058765.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-chief-minister-devendra-fadnavis-on-mumbai-pod-taxi-services-ann-3016944</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sharad-pawar-ncp-sp-claims-devendra-fadnavis-govt-apathetic-towards-farmers-warned-to-intensify-protests-3013235</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-shared-story-how-he-impressed-form-pm-narendra-modi-ahead-of-75th-birthday-rss-nagar-visit-know-all/articleshow/123913706.cms</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-shiv-sena-ubt-responds-to-cm-devendra-fadnavis-song-ahead-bmc-election-2025-ann-3014169</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-cm-devendra-fadnavis-wishi-pm-narendra-modi-on-75th-birthday-mumbai-3014251</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AB-%E0%A4%B2%E0%A5%8D%E0%A4%AE-%E0%A4%9B-%E0%A4%B5-%E0%A4%95-%E0%A4%A4-%E0%A4%B0-%E0%A4%AB-%E0%A4%87%E0%A4%A4-%E0%A4%B9-%E0%A4%B8%E0%A4%95-%E0%A4%B0-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%89%E0%A4%A0-%E0%A4%8F-%E0%A4%B8%E0%A4%B5-%E0%A4%B2/ar-AA1AjRCP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-shiv-sena-ubt-responds-to-cm-devendra-fadnavis-song-ahead-bmc-election-2025-ann-3014169</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/india-news/maharashtra-cm-devendra-fadnavis-inaugurated-the-amalner-beed-railway-line-in-beed/</t>
+          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-says-bala-saheb-thackeray-was-a-brand-but-uddhav-thackeray-cheated-with-bjp-ann-3013935</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-says-bala-saheb-thackeray-was-a-brand-but-uddhav-thackeray-cheated-with-bjp-ann-3013935</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-trouble-for-devendra-fadnavis-obc-banjara-protest-against-maratha-reservation-maharashtra-politics-ws-ln-9621475.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AA-%E0%A4%8F%E0%A4%AE-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%A6-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%95-%E0%A4%AC%E0%A4%A7-%E0%A4%88-%E0%A4%AB-%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%AF%E0%A5%87-%E0%A4%AC-%E0%A4%A4/ar-AA1MFO9P</t>
+          <t>https://www.abplive.com/states/maharashtra/beed-amalner-railway-line-inauguration-by-maharashtra-cm-devendra-fadnavis-3014515</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
+          <t>https://www.punjabkesari.com/india-news/maharashtra-cm-devendra-fadnavis-inaugurated-the-amalner-beed-railway-line-in-beed/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/beed-amalner-railway-line-inauguration-by-maharashtra-cm-devendra-fadnavis-3014515</t>
+          <t>https://www.amarujala.com/india-news/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-hindi-news-2025-09-19</t>
         </is>
       </c>
     </row>
@@ -1446,28 +1446,28 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-hindi-news-2025-09-19</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/cm-fadnavis-joins-7000-people-in-namo-yuva-run-in-mumbai/articleshow/124030814.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-maharashtra-cm-on-trial-run-for-phase-i-of-metro-lines-4-and-4a-in-thane-also-attack-on-mva-3016842</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/videos/maharashtras-development-under-pm-modi-fadnavis-highlights-key-projects-3485056.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169178</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-maharashtra-cm-on-trial-run-for-phase-i-of-metro-lines-4-and-4a-in-thane-also-attack-on-mva-3016842</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-solapur-air-service-will-begin-from-15th-october-2025-cm-devendra-fadnavis-on-flight-service-3016029</t>
         </is>
       </c>
     </row>
@@ -1481,3722 +1481,2889 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-first-underground-metro-from-cuffe-parade-pm-narendra-modi-inugrate-cm-devendra-fadnavis-maharashtra-mmrc-3013836</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-nationalist-congress-party-ncp-president-ajit-pawar-cm-devendra-fadnavis-nitin-gadkari-maharashtra-local-poll-vidarbha-politics-9642156.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-nationalist-congress-party-ncp-president-ajit-pawar-cm-devendra-fadnavis-nitin-gadkari-maharashtra-local-poll-vidarbha-politics-9642156.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-fadnavis-announced-new-flight-between-solapur-to-mumbai-and-bengaluru-flight-from-15-october-know-all-details/articleshow/124016070.cms</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/devendra-fadnavis-%E0%A4%B5-%E0%A4%9F-%E0%A4%9A-%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A6-%E0%A4%AE-%E0%A4%97-%E0%A4%9A-%E0%A4%B0-%E0%A4%B9-%E0%A4%97%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%81%E0%A4%B0-%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%AF-%E0%A4%A4-%E0%A4%96-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1MTRZn?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.livehindustan.com/maharashtra/sharad-pawar-calls-to-devendra-fadnavis-on-bjp-mla-gopichand-statement-201758271903306.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%B8%E0%A4%A8%E0%A4%B2-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AB-%E0%A4%95-%E0%A4%9B%E0%A5%81%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%9C-%E0%A4%82%E0%A4%9A-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1zIR9b?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-baps-akshardham-temple-goyal-fadnavis-wish-mahant-swamiji-maharaj-on-92nd-birthday-9628582.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-fadnavis-announced-new-flight-between-solapur-to-mumbai-and-bengaluru-flight-from-15-october-know-all-details/articleshow/124016070.cms</t>
+          <t>https://www.lokmatnews.in/business/mumbai-financial-capital-chhatrapati-sambhajinagar-become-ev-electric-vehicle-capital-maharashtra-cm-devendra-fadnavis-said-14000-people-get-employment-latur-coach-factory-b507/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/sharad-pawar-calls-to-devendra-fadnavis-on-bjp-mla-gopichand-statement-201758271903306.html</t>
+          <t>https://www.amarujala.com/india-news/fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B5-%E0%A4%95-%E0%A4%AA-%E0%A4%A1-%E0%A4%AF-%E0%A4%AA%E0%A4%B0-%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%85%E0%A4%A8-%E0%A4%AA-%E0%A4%B6%E0%A4%A8-%E0%A4%AA-%E0%A4%95-%E0%A4%B8%E0%A4%A8%E0%A5%87-%E0%A4%B2-%E0%A4%96-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%AF-%E0%A4%B9%E0%A4%9F%E0%A4%B5-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1zhEO3?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-sharad-pawar-warn-devendra-fadnavis-over-farmers-suicide-said-look-what-happened-in-nepal-2025-09-16-1162916</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/bullet-train-project-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%85%E0%A4%B9%E0%A4%AE%E0%A4%A6-%E0%A4%AC-%E0%A4%A6-%E0%A4%AC%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%9F-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A4%AC-%E0%A4%B9-%E0%A4%97-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AC%E0%A5%9C-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1DPcCq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-and-deputy-cm-shinde-flagged-off-trial-run-of-thane-metro-line-4-from-gaimukh-to-cadbury-11720</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-baps-akshardham-temple-goyal-fadnavis-wish-mahant-swamiji-maharaj-on-92nd-birthday-9628582.html</t>
+          <t>https://www.etvbharat.com/hi/!bharat/maharashtra-to-launch-gems-jewellery-course-says-cm-devendra-fadnavis-hindi-news-hin25091603873</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/business/mumbai-financial-capital-chhatrapati-sambhajinagar-become-ev-electric-vehicle-capital-maharashtra-cm-devendra-fadnavis-said-14000-people-get-employment-latur-coach-factory-b507/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir-2025-09-15</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-news-congress-targets-devendra-fadnavis-government-over-broken-roads-in-mumbai-ann-3016304</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sharad-pawar-phone-call-to-cm-devendra-fadnavis-on-bjp-mla-gopichand-padalkar-remarks-3015443</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/rahul-gandhi-vote-chori-controversy-maharashtra-fadnavis-resignation-congress-bjp-ntc-dskc-2336442-2025-09-18</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AC-%E0%A4%A1-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%85%E0%A4%AE%E0%A4%B2%E0%A4%A8%E0%A5%87%E0%A4%B0-%E0%A4%AC-%E0%A4%A1-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A4%B5%E0%A5%87-%E0%A4%B2-%E0%A4%87%E0%A4%A8-%E0%A4%95-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%98-%E0%A4%9F%E0%A4%A8-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%96-%E0%A4%88-%E0%A4%B9%E0%A4%B0-%E0%A4%9D%E0%A4%82%E0%A4%A1/ar-AA1MMIJZ</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/pm-modi-75th-birthday-devendra-fadnavis-shared-how-he-was-impressed-with-narendra-modi-in-1st-meetin-1387117.html</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-s-politics-rises-due-to-rahul-s-claims-on-vote-theft-congress-says-fadnavis-should-resign-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-mla-gopichand-padalkar-statement-sparked-uproar-in-maharashtra-devendra-fadnavis-calling-for-restraint/articleshow/124002748.cms</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/fadnavis-promises-rehabilitation-plan-for-elphinstone-residents-11705</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/cm-fadnavis-joins-7000-people-in-namo-yuva-run-in-mumbai/articleshow/124030814.cms</t>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-cm-devendra-fadnavis-in-new-tension-over-quota-clash-maratha-vs-obc-banjara-vs-tribal-community-politics-201757910651491.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/ladki-behen-yojana-will-not-be-discontinued-committed-to-empowering-women-11648</t>
+          <t>https://www.aajtak.in/india/news/story/sharad-pawar-ncp-sp-responded-to-bjp-devabhau-campaign-with-deva-tuch-saang-aid-ntc-rpti-2334011-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-2025-09-15</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-mla-gopichand-padalkar-statement-sparked-uproar-in-maharashtra-devendra-fadnavis-calling-for-restraint/articleshow/124002748.cms</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/sharad-pawar-called-devendra-fadnavis-complained-about-bjp-mla-19958470</t>
+          <t>https://www.livehindustan.com/maharashtra/obc-activists-show-black-flags-to-cm-devendra-fadnavis-attempt-self-immolation-in-front-of-deputy-cm-ajit-pawar-convoy-201758158508899.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/pod-taxis-to-run-in-mumbai-fadnavis-announces-11728</t>
+          <t>https://www.amarujala.com/india-news/bjp-mla-s-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/story/sharad-pawar-ncp-sp-responded-to-bjp-devabhau-campaign-with-deva-tuch-saang-aid-ntc-rpti-2334011-2025-09-15</t>
+          <t>https://hindi.theprint.in/india/gst-reforms-will-accelerate-indias-economic-growth-fadnavis/871739/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B9-%E0%A4%AE%E0%A5%8D%E0%A4%AE%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%A4-%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%95-%E0%A4%95%E0%A4%AC%E0%A5%8D%E0%A4%B0-%E0%A4%B9%E0%A4%9F-%E0%A4%93-%E0%A4%95%E0%A4%B0-%E0%A4%A6-%E0%A4%96-%E0%A4%93-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B9%E0%A5%81%E0%A4%B8%E0%A5%88%E0%A4%A8-%E0%A4%A6%E0%A4%B2%E0%A4%B5%E0%A4%88-%E0%A4%A8%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%9A%E0%A5%88%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9C/ar-AA1BqMnJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/national-hindi-news/devendra-fadnavis-targeted-rahul-gandhi-125091900062_1.html</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/metro-4-corridor-trial-run-starts-today-ghodbunder-road-commute-to-be-easier/articleshow/124031334.cms</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%8F%E0%A4%B8%E0%A4%8F%E0%A4%AE%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%A0-%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%B9-%E0%A4%97-%E0%A4%AE%E0%A5%87%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%A4-%E0%A4%B0-%E0%A4%96-%E0%A4%AD-%E0%A4%AC%E0%A4%A4-%E0%A4%A6/ar-AA1N5LIg?ocid=finance-verthp-feeds</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/meena-tai-thackeray-memorial-vandalism-bmc-elections-frvd-2335927-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-s-politics-rises-due-to-rahul-s-claims-on-vote-theft-congress-says-fadnavis-should-resign-2025-09-18</t>
+          <t>https://hindi.theprint.in/india/rahul-gandhi-speaks-like-an-urban-naxal-fadnavis/870800/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%97-%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A4%97%E0%A5%87%E0%A4%97-%E0%A4%AE%E0%A4%95-%E0%A4%95-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%95%E0%A4%B9-%E0%A4%9C-%E0%A4%A8-%E0%A4%B2-%E0%A4%9C-%E0%A4%8F/ar-AA1BkgKd?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/lifestyle/fashion/maharashtra-cm-wife-amruta-fadnavis-beautiful-photos-in-peach-banarasi-tissue-silk-saree-at-screening/articleshow/124040076.cms</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/fadnavis-promises-rehabilitation-plan-for-elphinstone-residents-11705</t>
+          <t>https://mandalnews.com/amravati/dhangar-community-should-get-st-certificate-otherwise-hunger-strike/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/obc-activists-show-black-flags-to-cm-devendra-fadnavis-attempt-self-immolation-in-front-of-deputy-cm-ajit-pawar-convoy-201758158508899.html</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/namo-yuva-run-organised-across-the-country-to-mark-the-75th-birthday-of-prime-minister-modi-11704</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/law-and-order-effective-implementation-cm-fadanviphp/cid17447208.htm</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/maharashtra-govt-issued-kunbi-certificates-in-five-marathwada-districts-on-liberation-day/articleshow/123961774.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
+          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%A8-%E0%A4%B9-%E0%A4%97-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-cm-%E0%A4%9C-%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%9C-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A5%81%E0%A4%B2-%E0%A4%88-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%82-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95/ar-AA1uE4o5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/india-news/51-students-from-maharashtra-will-visit-nasa-students-who-win-the-science-competition-will-get-a-chance-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/bjp-mla-s-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm-2025-09-19</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-cm-devendra-fadnavis-pod-taxi-last-mile-connectivity-transport-update-ann-3017094</t>
+          <t>https://www.patrika.com/mumbai-news/uddhav-thackeray-mother-meenatai-statue-colour-thrown-accused-upendra-pawaskar-held-19954266</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
+          <t>https://mandalnews.com/amravati/banjara-community-should-be-included-in-st-category/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/dhangar-community-should-get-st-certificate-otherwise-hunger-strike/</t>
+          <t>https://hindi.theprint.in/india/opposition-and-ruling-parties-clash-over-rahuls-vote-stealing-allegations-demand-for-fadnavis-resignation/870465/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maharashtra-government-will-create-a-fund-for-treatment-costing-more-than-rs-5-lakh-fadnavis/869009/</t>
+          <t>https://navbharattimes.indiatimes.com/india/brahmin-faca-may-be-next-president-of-bjp-vp-poll-changed-maths-names-of-nadda-dinesh-sharma-and-fadnavis/articleshow/123935176.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/rahul-gandhi-speaks-like-an-urban-naxal-fadnavis/870800/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ima-doctors-threaten-to-go-on-24-hour-strike-in-maharashtra-including-mumbai-from-8-am-on-sep-18-devendra-cm-fadnavis-know-all/articleshow/123947629.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B2-%E0%A4%95%E0%A4%B2%E0%A5%81%E0%A4%AD-%E0%A4%B5%E0%A4%A8-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A5%82%E0%A4%82%E0%A4%9C-%E0%A4%A8-%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1Av3BQ?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.bhaskarhindi.com/state/maharashtra/maharashtra-news-fadnavis-government-bjp-government-government-vehicles-cm-vehicles-governor-vehicles-gst-vehicle-tax-registration-fee-1188430</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/metro-4-corridor-trial-run-starts-today-ghodbunder-road-commute-to-be-easier/articleshow/124031334.cms</t>
+          <t>https://24city.news/when-devendra-fadnavis-yaad-was-surprised-to-hear-this-of-narendra-modi-his-first-meeting/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-gopichand-padalkar-controversial-remark-on-jayant-patil-sharad-pawar-reaction-9642900.html</t>
+          <t>https://deshbandhump.com/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D-13/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/india-news/maharashtra/mumbai-people-will-get-relief-from-traffic-jam-soon-pod-taxi-service-will-start-id-473799</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/lifestyle/fashion/maharashtra-cm-wife-amruta-fadnavis-beautiful-photos-in-peach-banarasi-tissue-silk-saree-at-screening/articleshow/124040076.cms</t>
+          <t>https://www.agniban.com/protests-erupt-in-maharashtra-over-reservation-issue-obc-activists-show-black-flags-to-fadnavis-attempt-suicide/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/maharashtra-govt-issued-kunbi-certificates-in-five-marathwada-districts-on-liberation-day/articleshow/123961774.cms</t>
+          <t>https://www.hindisaamana.com/former-mla-exposes-fadnaviss-transparent-work/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-bombay-high-court-hyderabad-gazette-gr-plea-reject-obc-reservation-sharad-pawar-suicide-nanded-clash-know-all/articleshow/123999053.cms</t>
+          <t>https://www.hindisaamana.com/the-public-has-no-food-there-is-no-money-in-the-treasury-the-chief-minister-has-a-bed-worth-rs-20-lakh/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%95-%E0%A4%AC%E0%A4%A7-%E0%A4%88-%E0%A4%A6-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%A6%E0%A5%82%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AC%E0%A4%A4-%E0%A4%AF/ar-AA1MJ71H</t>
+          <t>https://www.raftaar.in/news/national/maharashtra-cm-devendra-fadnavis-took-a-dig-at-the-opposition-especially-the-shiv-sena-ubt-faction-by-singing-a-song</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/banjara-community-should-be-included-in-st-category/</t>
+          <t>https://www.prabhasakshi.com/national/rahul-gandhi-allegations-vote-theft-spark-debate-in-maharashtra-demands-fadnavis-resignation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/51-students-from-maharashtra-will-visit-nasa-students-who-win-the-science-competition-will-get-a-chance-2025-09-22</t>
+          <t>https://www.kisantak.in/news/trending/story/sharad-pawar-led-an-akrosh-morcha-in-nashik-demands-complete-loan-waiver-for-farmers-swm-1278008-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/uddhav-thackeray-mother-meenatai-statue-colour-thrown-accused-upendra-pawaskar-held-19954266</t>
+          <t>https://rashtrabaan.in/sharad-pawar-angry-bjp-mla-statement-called-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-government-changed-the-name-of-ahmednagar-railway-station-to-ahilyanagar-1387233.html</t>
+          <t>https://www.ibc24.in/business/chhatrapati-sambhajinagar-will-become-the-electric-vehicle-capital-of-the-country-fadnavis-3255721.html</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-doctors-strike-1-8-lakh-allopathic-doctors-protest-against-fadnavis-government-decision-1388823.html</t>
+          <t>https://indiagroundreport.com/mumbai-fadnavis-government-took-8-important-decisions-including-doubling-the-allowance-of-students/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-cm-devendra-fadnavis-in-new-tension-over-quota-clash-maratha-vs-obc-banjara-vs-tribal-community-politics-201757910651491.html</t>
+          <t>https://up18news.com/free-solar-power-to-every-farmer-by-2026-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/western-naval-command-chief-meets-fadnavis-discusses-maritime-security-situation/871381/?amp</t>
+          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/maratha-reservation-sharad-pawar-mahayuti-govt-maharashtra-cm-devendra-fadnavis-9622532.html</t>
+          <t>https://www.ptinews.com/story/national/using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level-fadnavis/2934307</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/maharashtra/maharashtra-news-fadnavis-government-bjp-government-government-vehicles-cm-vehicles-governor-vehicles-gst-vehicle-tax-registration-fee-1188430</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/pm-modi-allocated-rs-21000-crore-for-rail-lines-in-marathwada-claims-cm-devendra-fadnavis-23594480</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://24city.news/when-devendra-fadnavis-yaad-was-surprised-to-hear-this-of-narendra-modi-his-first-meeting/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-govt-signs-mou-with-cambridge-to-elevate-school-education-101758482430602.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-pm-modi-is-a-leader-who-prefers-simplicity-devendra-fadnavis-shared-a-special-video-news-hindi-1-753193-KKN.html</t>
+          <t>https://www.financialexpress.com/india-news/maharashtra-to-appoint-new-advocate-general-as-birendra-saraf-resigns-citing-personal-reasons/3979732/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
+          <t>https://www.projectsmonitor.com/daily-wire/aiifa-steelex-2025-maharashtra-chief-minister-devendra-fadnavis-and-union-minister-pralhad-joshi-inaugurate-the-steel-mahakumbh/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://raftaar.in/news/national/maharashtra-cm-devendra-fadnavis-took-a-dig-at-the-opposition-especially-the-shiv-sena-ubt-faction-by-singing-a-song</t>
+          <t>https://www.asianage.com/nation/maharashtra-government-approves-policy-to-boost-digital-content-sector-1904215</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/all-phases-of-the-metro-will-be-open-for-passengers-by-the-end-of-2026-devendra-fadnavis-4279721</t>
+          <t>https://www.mid-day.com/news/india-news/article/shiv-sena-ubt-targets-maharashtra-cm-devendra-for-not-unveiling-swami-ramanand-tirtha-statue-23594500</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://lalluram.com/sharad-pawar-reminded-cm-fadnavis-of-rajdharma-appealed-for-complete-loan-waiver-of-farmers-warned-and-said-the-situation-should-not-become-like-nepal/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004?holi-breakingnews</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-public-has-no-food-there-is-no-money-in-the-treasury-the-chief-minister-has-a-bed-worth-rs-20-lakh/</t>
+          <t>https://www.sakshipost.com/news/zero-tolerance-important-curb-drug-related-crimes-says-cm-fadnavis-454693</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/cm-fadnavis-expressed-gratitude-after-prime-minister-modis-speech-4277895</t>
+          <t>https://www.sakshipost.com/news/metro-line-connecting-thane-mumbai-be-operational-2026-end-says-cm-fadnavis-455400</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/quickly/india/devendra-fadnavis-on-pm-modi-pm-modi-is-a-leader-who-prefers-simplicity-devendra-fadnavis-shared-a-special-video-2755431.html</t>
+          <t>https://thenewsmill.com/2025/09/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.tarunmitra.in/state/maharashtra/sharad-pawar-raging-on-the-issue-of-maharashtra-farmers/article-105258</t>
+          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://joindia.co.in/news/sharad-pawar-calls-devendra-fadnavis-expresses-objection-to-controversial-statement/</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/maharashtra-cm-devendra-fadnavis-talk-on-obc-reservation/articleshow/123889715.cms</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-conflict-between-the-bjp-and-shinde-factions-escalates-in-thane-district/</t>
+          <t>http://marathi.factcrescendo.com/old-altered-video-viral-as-cm-fadnavis-did-not-believe-in-indian-constitution-democracy/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/video-ahead-of-bmc-polls-fadnavis-targets-uddhav-with-accha-sila-diya-jibe-2756036.html</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/fadnavis-praised-pm-modis-working-style-4271099</t>
+          <t>https://marathi.ndtv.com/cities/pm-modi-birthday-cm-fadnavis-reminisces-share-experienc-of-first-meeting-with-pm-modi-9291188</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/pm-modi-to-inaugurate-mumbai-metro-3-worli-cuffe-parade-stretch-on-sept-30-2755975.html</t>
+          <t>https://zeenews.india.com/marathi/video/cm-devendra-fadnavis-media-brief/941116</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-fadnavis-government-took-8-important-decisions-including-doubling-the-allowance-of-students/</t>
+          <t>https://www.loksatta.com/aurangabad/cm-devendra-fadnavis-said-announcements-made-for-marathwada-will-not-remain-on-paper-css-98-5378822/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://up18news.com/free-solar-power-to-every-farmer-by-2026-cm-devendra-fadnavis/</t>
+          <t>https://www.loksatta.com/pune/cm-fadnavis-said-no-complaints-on-kunbi-caste-certification-under-hyderabad-gazette-assures-maratha-caste-certificate-pune-print-news-rds-00-5380078/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://hindi.gyanhigyan.com/auto/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A4%B0%E0%A4%BF%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%A8%E0%A4%BE%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-21000-%E0%A4%95%E0%A4%B0%E0%A5%8B%E0%A4%A1%E0%A4%BC-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A4%BE/cid17430694.htm</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%B5-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97%E0%A4%B8-%E0%A4%A0-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1ME6vc</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114?news-breakingnews</t>
+          <t>https://marathi.ndtv.com/videos/cm-fadnavis-fadnavis-started-dreaming-of-becoming-prime-minister-bjp-strongly-criticizes-sapkal-s-cl-997453</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/health/news/maha-govt-approves-corpus-fund-for-health-treatment-of-over-rs-5-lakh-says-cm-fadnavis-297657</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/devendra-fadnavis-claim-that-milind-narvekar-phone-call-him-and-said-uddhav-thackeray-was-upset/articleshow/123927047.cms</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/sambhajinagar-becoming-ev-capital-of-country-fadnavis/articleshow/123952619.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/entertainment-news/hindi-films-fail-to-depict-the-true-heroism-of-mumbai-police-says-maharashtra-cm-fadnavis20250920135931-143844/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/devendra-fadnavis-slams-uddhav-and-raj-thackeray-over-thackeray-brand/articleshow/123927266.cms</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/india-news/maharashtra-to-appoint-new-advocate-general-as-birendra-saraf-resigns-citing-personal-reasons/3979732/</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-government-likely-to-increase-to-2399-available-under-the-mahatma-jyotirao-phule-jan-arogya-yojana-zws-70-5375201/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480/6</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/19/maharashtra-will-be-number-one-in-the-green-steel-sector-chief-minister-devendra-fadnavis-iifa-2025-steel-maha.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.dailypioneer.com/2025/india/congress-demands-apology-from-fadnavis-for-shivaji-poster.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/20/use-of-modern-technology-is-essential-for-combating-cyber-crimes-chief-minister-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address/</t>
+          <t>https://prahaar.in/2025/09/18/brand-vs-brandy-war-of-words-between-fadnavis-thackeray-faction-politics-heats-up/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava/amp_articleshow/123926617.cms</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/mumbai-balasaheb-thackeray-wife-meenatai-statue-defaced-1-arrested-1800879</t>
+          <t>https://maharashtratimes.com/maharashtra/chandrapur/shiv-sena-ubt-protest-in-chandrapur-over-place-of-banner-of-cm-devendra-fadnavis-and-chhatrapati-shivaji-maharaj/articleshow/124000637.cms</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/milind-soman-flags-off-namo-yuva-run-in-mumbai-says-its-pm-modis-dream-to-make-india-drug-free/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/21/mumbaikars-run-towards-a-drug-free-india-namo-yuva-run-receives-overwhelming-response-will-intoxicate-our-yout.html</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>http://marathi.factcrescendo.com/old-altered-video-viral-as-cm-fadnavis-did-not-believe-in-indian-constitution-democracy/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-kamboj-allegations-sakkale-accuses-devendra-fadnavis-of-pm-ambition-empowering-mohit-kamboj-and-giving-mumbai-to-adani-1385640</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashatra-news-live-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A4%B9-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%85%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8/ar-AA1MRBRN</t>
+          <t>https://marathi.abplive.com/news/maharashtra/rohit-pawar-criticizes-on-chief-minister-devendra-fadnavis-on-the-issue-of-mumbai-municipal-corporation-elections-1384659</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/pm-modi-birthday-cm-fadnavis-reminisces-share-experienc-of-first-meeting-with-pm-modi-9291188</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-talk-on-sharad-pawar-phone-call-about-gopchand-padalkar-statement/articleshow/123994142.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/cm-devendra-fadnavis-media-brief/941116</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-nashik-journalist-assault-cm-devendra-fadnavis-orders-strict-action-case-filing-process-initiated-against-assailants-1385488</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/kunbi-certificate-%E0%A4%96-%E0%A4%A1-%E0%A4%96-%E0%A4%A1-%E0%A4%95-%E0%A4%97%E0%A4%A6%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A7-%E0%A4%B0%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%A6-%E0%A4%96%E0%A4%B2%E0%A5%87-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A4%B0%E0%A4%A3/ar-AA1MMluT?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/22/the-next-step-in-the-transport-service-is-pod-taxi-chief-minister-devendra-fadnavis-instructions-to-accelerate.html</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%A7%E0%A4%A1-%E0%A4%95%E0%A5%87%E0%A4%AC-%E0%A4%9C-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MDXwL</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-for-giving-30-sara-projects-to-mohit-kamboj/921930/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/gopichand-padalkar-clarification-on-his-statement-about-jayant-patil-after-receiving-a-call-from-cm-devendra-fadnavis/articleshow/123994231.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/india-has-the-potential-to-become-a-global-leader-in-the-field-of-gems-and-jewellery-chief-minister-devendra-f.html</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%B5-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97%E0%A4%B8-%E0%A4%A0-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1ME6vc</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/thousands-of-rupees-were-laundered-during-the-corona-period-devendra-fadnavis-criticizes-thackeray/videoshow/123926314.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/aurangabad/beed/news/beed-railway-ignoration-cm-devendra-fadnavis-speech-135942485.html</t>
+          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-directed-that-guidelines-should-be-issued-by-amending-the-criteria-of-the-solar-agricultural-pump-scheme-as-per-the-demands-of-the-farmers-local18-1483770.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B2%E0%A4%9A-%E0%A4%B2-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9C%E0%A4%B5%E0%A4%B3%E0%A4%9A%E0%A5%87-3-%E0%A4%AC%E0%A4%A1%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%B2/ar-AA1yK0Ky?cvid=6B345CC548B8475D94F9EB8EE0C8C751&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/news/devendra-fadnavis-speech-at-chhatrapati-sambhajinagar-obc-activists-slogans-during-cm-speech-at-marathwada-mukti-sangram-din-program-marathi-news-1384714</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-slams-raj-uddhav-thackeray-mumbai-bmc-election-narendra-modi-brand-maharashtra-politics-1384645</t>
+          <t>https://marathi.abplive.com/photo-gallery/sports/lionel-messi-gives-cm-devendra-fadnavis-a-special-gift-of-signed-footbal-will-also-come-to-mumbai-for-a-visit-1385826</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-claim-that-milind-narvekar-phone-call-him-and-said-uddhav-thackeray-was-upset/articleshow/123927047.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-20-political-news-in-marathi-940632</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava/articleshow/123926617.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-advice-to-gopichand-padalkar-after-receiving-a-call-from-sharad-pawar-for-making-objectionable-comments-on-jayant-patil/923124/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sharad-pawar-called-devendra-fadnavis-and-complained-about-gopichand-padalkar-jayant-patil-maharashtra-politics-marathi-news-1385183</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/manoj-jarange-on-hyderabad-gadget-manoj-jarange-last-ultimatum-to-devendra-fadnavis-from-hyderabad-gazette/940846</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
+          <t>https://marathi.abplive.com/news/beed/devendra-fadnavis-beed-railway-inaguration-programme-train-dedicated-to-gopinath-munde-marathi-1384797</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-leader-manoj-jarange-patil-big-announcement-about-delhi-visit/articleshow/123945687.cms</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/cm-devendra-fadnavis-reaction-on-maratha-reservation-kunbi-certificates/articleshow/123993122.cms</t>
+          <t>https://www.mymahanagar.com/mahamumbai/uddhav-thackeray-in-power-the-mumbai-municipal-corporation-during-the-corona-period-committed-a-scam-in-the-body-bags-fadnavis-targets-thackeray/922227/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-slams-uddhav-and-raj-thackeray-over-thackeray-brand/articleshow/123927266.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/why-cant-they-be-removed-from-the-unruly-gopichand-padalkar-anjali-damania-lashed-out-at-cm-devendra-fadnavis-1385414</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/manoj-jarange-admire-maharashtra-cm-devendra-fadnavis-after-maratha-reservation-protest-1481999.html</t>
+          <t>https://maharashtratimes.com/maharashtra/sangli/gopichand-padalkar-clarification-on-his-statement-about-jayant-patil-after-receiving-a-call-from-cm-devendra-fadnavis/articleshow/123994231.cms</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
+          <t>https://maharashtratimes.com/maharashtra/nashik/nashik-nationalist-party-sharad-pawar-group-aakrosh-morcha-mla-rohit-pawar-criticizes-chief-minister-devendra-fadnavis/articleshow/123919393.cms</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/18/brand-vs-brandy-war-of-words-between-fadnavis-thackeray-faction-politics-heats-up/</t>
+          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-criticized-jayant-patil-in-dirty-words-devendra-fadnavis-phone-call-to-gopichand-padalkars-1385221</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-talk-on-sharad-pawar-phone-call-about-gopchand-padalkar-statement/articleshow/123994142.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/navi-mumbai/bjp-leader-haresh-keni-joins-congress-shocks-devendra-fadnavis-prashant-thakur-ahead-of-panvel-municipal-election/articleshow/124013605.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%A3%E0%A4%A4-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%AE%E0%A4%A6-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%B7-%E0%A4%B5%E0%A4%B0-%E0%A4%96%E0%A4%B2%E0%A4%AC%E0%A4%A4%E0%A4%82/ar-AA1IC7SW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AA-%E0%A4%9A%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%B8%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%B8%E0%A5%82%E0%A4%9A%E0%A4%A8-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AB-%E0%A4%A8/ar-AA1MSNkK</t>
+          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/rohit-pawar-recalled-the-demand-declaring-a-wet-drought-made-by-devendra-fadnavis-and-ajit-pawar-when-they-were-the-leader-of-opposition-1386183</t>
+          <t>https://www.loksatta.com/maharashtra/mumbai-rain-latest-updates-maharashtra-weather-news-political-devendra-fadnavis-sanjay-raut-asc-95-5375148/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/devendra-fadnavis-speech-at-chhatrapati-sambhajinagar-obc-activists-slogans-during-cm-speech-at-marathwada-mukti-sangram-din-program-marathi-news-1384714</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-chagan-bhujbal-sharad-pawar-obc-reservation-rain-update-friday-19-september-2025-1495763.html</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ncp-pune-city-president-prashant-jagtap-criticizes-bjp-mla-gopichand-padalkar/articleshow/123990567.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-prime-minister-narendra-modi-birthday-chhagan-bhujbal-obc-reservation-rain-alert-wednesday-17-september-2025-1494134.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-for-giving-30-sara-projects-to-mohit-kamboj/921930/</t>
+          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-criticizes-devendra-fadnavis-for-not-unveiling-the-statue-of-swami-ramanand-tirtha-despite-coming-to-chhatrapati-sambhajinagar/922378/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
+          <t>https://www.loksatta.com/pune/in-pune-city-water-supply-will-remain-suspended-on-thursday-pune-print-news-asj-82-5378829/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/beed/devendra-fadnavis-beed-railway-inaguration-programme-train-dedicated-to-gopinath-munde-marathi-1384797</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/sharad-pawar-called-cm-devendra-fadnavis-about-gopichand-padalkar-controversial-statement-on-jayant-patil-in-sangli/articleshow/123992055.cms</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-kamboj-allegations-sakkale-accuses-devendra-fadnavis-of-pm-ambition-empowering-mohit-kamboj-and-giving-mumbai-to-adani-1385640</t>
+          <t>https://news18marathi.com/maharashtra/chhatrapati-sambhaji-nagar/chhatrapati-sambhajinagar-80-year-old-sunanda-shinde-write-letter-to-cm-devendra-fadnavis-on-adarsh-bank-scam-local18-1481471.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/nashik-nationalist-party-sharad-pawar-group-aakrosh-morcha-mla-rohit-pawar-criticizes-chief-minister-devendra-fadnavis/articleshow/123919393.cms</t>
+          <t>https://www.loksatta.com/manoranjan/television/yeh-rishta-kya-kehlata-hai-fame-actor-rohit-purohit-sheena-bajaj-welcomes-baby-boy-hrc-97-5376440/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-said-that-devendra-fadnavis-does-not-know-history-has-no-social-knowledge-and-rss-was-not-involved-in-freedom-struggle-but-muslims-were-involved-and-they-were-part-of-the-social-fabric-mah/922681/</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-this-is-a-clove-cracker-chief-minister-devendra-fadnavis-reply/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/india-has-the-potential-to-become-a-global-leader-in-the-field-of-gems-and-jewellery-chief-minister-devendra-f.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-19-september-2025-125091900004_1.html</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/sports/lionel-messi-gives-cm-devendra-fadnavis-a-special-gift-of-signed-footbal-will-also-come-to-mumbai-for-a-visit-1385826</t>
+          <t>https://www.dainikprabhat.com/big-news-sudden-resignation-of-the-states-advocate-general-chief-minister-fadnavis-gave-information-in-the-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/cm-devendra-fadnavis-attacks-on-thackeray-brand-and-brothers-accuses-them-of-mishandling-best-elections-1495102.html</t>
+          <t>https://vishwanewsmarathi.com/sharad-pawars-main-indicator-but-wisdom-is-a-matter-of-learning/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/thousands-of-rupees-were-laundered-during-the-corona-period-devendra-fadnavis-criticizes-thackeray/videoshow/123926314.cms</t>
+          <t>https://www.dainikprabhat.com/nashik-news-sharad-pawar-aggressive-on-farmers-issues-targets-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-advice-to-gopichand-padalkar-after-receiving-a-call-from-sharad-pawar-for-making-objectionable-comments-on-jayant-patil/923124/</t>
+          <t>https://www.dainikprabhat.com/harshwardhan-sapkal-chief-minister-fadnavis-should-resign-congress-state-president-harshwardhan-sapkal-demanded/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://www.dainikprabhat.com/sharad-pawars-ncp-took-notice-of-padalkars-low-level-criticism-amol-kolhe-and-prashant-jagtaps-strong-response/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-leader-manoj-jarange-patil-big-announcement-about-delhi-visit/articleshow/123945687.cms</t>
+          <t>https://mahasamvad.in/179557/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-20-political-news-in-marathi-940632</t>
+          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-inspects-nashik-and-surrounding-areas-in-the-backdrop-of-kumbh-mela-gives-important-instructions-local18-1483785.html</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/22/indias-longest-elevated-metro-corridor-in-mumbai-information-from-chief-minister-devendra-fadnavis.html</t>
+          <t>https://www.msn.com/mr-in/news/other/kunbi-certificate-%E0%A4%96-%E0%A4%A1-%E0%A4%96-%E0%A4%A1-%E0%A4%95-%E0%A4%97%E0%A4%A6%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A7-%E0%A4%B0%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%A6-%E0%A4%96%E0%A4%B2%E0%A5%87-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A4%B0%E0%A4%A3/ar-AA1MMluT?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/uddhav-thackeray-in-power-the-mumbai-municipal-corporation-during-the-corona-period-committed-a-scam-in-the-body-bags-fadnavis-targets-thackeray/922227/</t>
+          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-attack-uddhav-thackeray-and-raj-thackeray-over-mumbai-mahapalika-bjp-vijay-melava-1481400.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/why-cant-they-be-removed-from-the-unruly-gopichand-padalkar-anjali-damania-lashed-out-at-cm-devendra-fadnavis-1385414</t>
+          <t>https://news18marathi.com/maharashtra/manoj-jarange-admire-maharashtra-cm-devendra-fadnavis-after-maratha-reservation-protest-1481999.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
+          <t>https://mahasamvad.in/178525/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AB-%E0%A4%A8%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%B8%E0%A5%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%82-%E0%A4%AB-%E0%A4%B0%E0%A4%B2-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AB%E0%A4%9F%E0%A4%95-%E0%A4%B0%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%AC%E0%A4%A6%E0%A4%B2%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MSIyN</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-thackeray-brand-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%A5%E0%A5%87%E0%A4%9F%E0%A4%9A-%E0%A4%9F-%E0%A4%B2%E0%A5%87%E0%A4%AC-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82-marathi-news/vi-AA1MI8n0?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-majhi-ladki-bahin-yojana-ekyc-update-women-beneficiaries-last-date-135957916.html</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-bmc-election-%E0%A4%B2-%E0%A4%B9%E0%A5%82%E0%A4%A3-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0-%E0%A4%B9-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%9A-bjp-melava/vi-AA1MFmSp?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-criticized-jayant-patil-in-dirty-words-devendra-fadnavis-phone-call-to-gopichand-padalkars-1385221</t>
+          <t>https://mahasamvad.in/178515/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/devendra-fadnavis-on-uddhav-thackeray-mumbai-municipal-corporation-will-have-a-mahayuti-mayor-write-it-down-fadnavis-sang-song-achha-sila-diya-tune-1384650</t>
+          <t>https://mahasamvad.in/179580/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-government-boosts-aid-for-organ-transplant-treatment-to-over-lakh-announces-cm-devendra-fadanvis-maharashtra-news-mhs25091505789</t>
+          <t>https://mahasamvad.in/179349/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/akola/buldhana/news/97-gram-panchayats-from-khamgaon-taluka-participate-in-samruddhi-panchayat-raj-abhiyan-135924229.html</t>
+          <t>https://news18marathi.com/maharashtra/obc-activist-shouting-slogans-during-cm-devendra-fadnavis-speech-at-chhatrapati-sambhaji-nagar-1481714.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-prime-minister-narendra-modi-birthday-chhagan-bhujbal-obc-reservation-rain-alert-wednesday-17-september-2025-1494134.html</t>
+          <t>https://news18marathi.com/mumbai/maharastra-cabinate-meeting-inside-story-ajit-pawar-makes-laughter-in-front-of-devendra-fadanvis-latest-marathi-news-1481676.html</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/</t>
+          <t>https://news18marathi.com/agriculture/when-will-river-linking-project-in-marathwada-start-chief-minister-fadnavis-has-given-information-about-this-1482614.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
+          <t>https://marathi.abplive.com/news/maharashtra/cm-devendra-fadnavis-directs-to-prepare-comprehensive-effective-policy-to-fight-cancer-maharashtra-health-marathi-news-1384411</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/the-role-of-the-state-government-in-creating-an-industry-friendly-environment-in-the-state.html</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
+          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/comforting-news-for-the-maratha-community-the-benefits-of-annasaheb-patil-corporations-schemes-will-reach-the-villages-directly-maharashtra-news-mhs25091901865</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/thane/thane-metro-railway-exciting-news-for-thane-residents-trial-run-date-announced-when-will-the-first-phase-begin-1385724</t>
+          <t>https://mahasamvad.in/178530/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-criticizes-devendra-fadnavis-for-not-unveiling-the-statue-of-swami-ramanand-tirtha-despite-coming-to-chhatrapati-sambhajinagar/922378/</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/harshwardhan-sapkal-accuses-maharashtra-cm-devendra-fadnavis-of-election-fraud-calls-him-thief-cm-during-press-conference/</t>
+          <t>https://news18marathi.com/agriculture/what-is-the-new-decision-of-the-state-government-regarding-making-agricultural-land-na-1484003.html</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chhatrapati-sambhaji-nagar/chhatrapati-sambhajinagar-80-year-old-sunanda-shinde-write-letter-to-cm-devendra-fadnavis-on-adarsh-bank-scam-local18-1481471.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/punepolice-force-1720-posts-will-soon-be-approved-by-the-high-powered-committee-headed-by-chief-minister-devendra-fadnavis/articleshow/124010529.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-19-september-2025-125091900004_1.html</t>
+          <t>https://agrowon.esakal.com/agro-special/8-important-decisions-in-the-cabinet-meeting-132-crores-of-funds-for-farmers-buildings-and-extension-of-the-deadline-for-the-construction-of-a-modern-orange-center-rat16</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-this-is-a-clove-cracker-chief-minister-devendra-fadnavis-reply/</t>
+          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-reaction-on-rahul-gandhi-allegations-bogus-voting-in-chandrapur-rajura-1483022.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-news-sudden-resignation-of-the-states-advocate-general-chief-minister-fadnavis-gave-information-in-the-cabinet-meeting/</t>
+          <t>https://mahasamvad.in/179466/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-22-september-2025-125092200004_1.html</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-at-bjp-vijay-sankalp-melava/videoshow/123937912.cms</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/implementation-of-law-and-order-will-lead-the-country-towards-becoming-a-superpower-chief-minister-devendra-fadnavis/</t>
+          <t>https://mahasamvad.in/178534/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/sharad-pawars-main-indicator-but-wisdom-is-a-matter-of-learning/</t>
+          <t>https://mahasamvad.in/179384/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/nashik-news-sharad-pawar-aggressive-on-farmers-issues-targets-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-cabinet-meeting-maharashtra-animation-gaming-policy-announced-government-takes-8-major-decisions-95140</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/harshwardhan-sapkal-chief-minister-fadnavis-should-resign-congress-state-president-harshwardhan-sapkal-demanded/</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-ias-officer-transfer-order-cabinet-meeting-devendra-fadanvis-ws-a-1481304.html</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://thodkyaat.com/maharashtra-cm-announces-%E2%82%B91-lakh-interest-free-loan-for-women-plans-to-make-1-crore-lakhpati-didis/</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-informed-that-the-states-advocate-general-birendra-saraf-has-resigned/922000/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%9A-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%B2-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%8A-%E0%A4%A8%E0%A4%AF%E0%A5%87-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8/ar-AA1MDxgy</t>
+          <t>https://news18marathi.com/maharashtra/sharad-pawar-attack-cm-devendra-fadanvis-over-farmer-loan-waiver-and-crop-rate-issue-ncp-nashik-melava-1480406.html</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-inspects-nashik-and-surrounding-areas-in-the-backdrop-of-kumbh-mela-gives-important-instructions-local18-1483785.html</t>
+          <t>https://www.mahasamvad.in/page/37/?m=0</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
+          <t>https://www.msn.com/mr-in/news/other/advocate-general-birendra-saraf-resigns-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%A7-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AC-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0-%E0%A4%AB-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE/ar-AA1MDN7q</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/political-news-file-a-case-against-sharad-pawar-gopichand-padalkar-demands-markadwadi-solapur-9294330</t>
+          <t>https://marathi.abplive.com/news/politics/sanjay-raut-on-maharashtra-debt-burden-slams-devendra-fadnavis-eknath-shinde-ajit-pawar-says-state-situation-is-similar-to-nepal-marathi-news-1384489</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-17-september-2025-pm-narendra-modi-75th-birthday-zp-presidentship-reservation-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-attack-uddhav-thackeray-and-raj-thackeray-over-mumbai-mahapalika-bjp-vijay-melava-1481400.html</t>
+          <t>https://news18marathi.com/maharashtra/manoj-jarange-patil-warning-cm-devendra-fadanvis-regarding-kunbi-certificate-1484509.html</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
+          <t>https://deshdoot.com/sharad-pawar-calls-cm-devendra-fadnavis-and-complained-about-gopichand-padalkar/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/obc-activist-shouting-slogans-during-cm-devendra-fadnavis-speech-at-chhatrapati-sambhaji-nagar-1481714.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/non-agricultural-land-certificates-compulsion-removed-for-micro-and-small-businesses/articleshow/123988928.cms</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-bmc-election-%E0%A4%B2-%E0%A4%B9%E0%A5%82%E0%A4%A3-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0-%E0%A4%B9-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%9A-bjp-melava/vi-AA1MFmSp?ocid=hpmsn</t>
+          <t>https://agrowon.esakal.com/agro-special/the-drought-history-of-marathwada-will-be-compiled-rat16</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-at-bjp-vijay-sankalp-melava/videoshow/123937912.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/sharad-pawar-says-farmer-lives-are-in-trouble-devevendra-fadnavis-taking-the-name-of-shivaji-maharaj-and-not-looking-at-baliraja-1384307</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-thackeray-brand-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%A5%E0%A5%87%E0%A4%9F%E0%A4%9A-%E0%A4%9F-%E0%A4%B2%E0%A5%87%E0%A4%AC-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82-marathi-news/vi-AA1MI8n0?ocid=hpmsn</t>
+          <t>https://maharashtratimes.com/entertainment/entertainment-news/television-news/devendra-fadnavis-watch-maharashtrachi-hasya-jatra-says-samir-choughule-in-mhj-unplugged/articleshow/123995979.cms</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8-%E0%A4%AE%E0%A5%82%E0%A4%B9-%E0%A4%95-%E0%A4%95-%E0%A4%AA-%E0%A4%86%E0%A4%A2%E0%A4%B3%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%A4-%E0%A4%B0%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%95%E0%A4%B0-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%95%E0%A4%A1%E0%A4%95-%E0%A4%95-%E0%A4%B0%E0%A4%B5-%E0%A4%88%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1yRhpX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178525/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AA-%E0%A4%9A%E0%A4%82%E0%A4%A6-%E0%A4%AA%E0%A4%A1%E0%A4%B3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A6%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%87-%E0%A4%8F%E0%A4%95-%E0%A4%A4%E0%A4%B0%E0%A5%82%E0%A4%A3/ar-AA1MSJPR</t>
+          <t>https://maharashtratimes.com/entertainment/entertainment-news/bollywood-news/kishor-kadam-exposes-bmc-fraud-of-engeineer-housing-society-scam-in-latest-post-to-cm-devendra-fadnavis/articleshow/123891023.cms</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-reaction-on-rahul-gandhi-allegations-bogus-voting-in-chandrapur-rajura-1483022.html</t>
+          <t>https://marathi.abplive.com/news/politics/pm-modi-birthday-special-cm-devendra-fadnavis-and-dcm-ekanth-shinde-wrote-articles-praises-modi-leadership-1384692</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-maharashtra-cm-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A4-%E0%A4%AA-%E0%A4%B5%E0%A4%B0%E0%A4%AB%E0%A5%81%E0%A4%B2-%E0%A4%96%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%B5%E0%A4%B0-%E0%A4%AC%E0%A4%B8%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%A4-%E0%A4%AA%E0%A4%97-%E0%A4%B0-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A7-%E0%A4%95-%E0%A4%AA%E0%A4%97-%E0%A4%B0/ar-AA1vigKI?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/maharashtra/sharad-pawar-criticizes-devendra-fadnavis-over-farmers-issues-from-aakrosh-morcha/921710/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/beed-news-chief-minister-devendra-fadnavis-and-deputy-chief-minister-ajit-pawar-visit-beed-dangerous-electrical-generator-covered-with-cloth-in-beed-1384811</t>
+          <t>https://www.saamana.com/shivsena-ubt-mp-sanjay-raut-press-conference-attack-on-bjp-on-corruption-and-debt-on-state-saamana-online-news/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/modi-is-the-biggest-brand-in-the-world-chief-minister-devendra-fadnavis-bjp-is-the-party-that-created-the-brand-of-its-workers-a-a941/</t>
+          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-targets-devendra-fadnavis-over-marathwada-flood-situation/921688/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178515/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/jayant-patil-heavy-rain-agriculture-news-declaring-a-wet-drought-in-the-state-jayant-patil-letter-to-chief-minister-devendra-fadnavis-in-sangli-1385048</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178649/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-flagged-off-the-first-train-service-from-beed-to-ahilyanagar-125091800006_1.html</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/when-will-river-linking-project-in-marathwada-start-chief-minister-fadnavis-has-given-information-about-this-1482614.html</t>
+          <t>https://www.dainikprabhat.com/pune-news-governments-make-and-break-on-reservation-continues-vijay-vadettiwar-hits-out-at-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/cm-devendra-fadnavis-directs-to-prepare-comprehensive-effective-policy-to-fight-cancer-maharashtra-health-marathi-news-1384411</t>
+          <t>https://www.newsdanka.com/vishesh/how-was-the-first-meeting-between-devendra-fadnavis-and-narendra-modi/167384/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178530/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-18-september-2025-125091800004_1.html</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ajit-pawar-in-nagpur-refusal-to-accept-that-vidarbha-is-the-stronghold-of-bjp-and-devendra-fadnavis-maharashtra-politics-marathi-news-1385133</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://www.business-standard.com/india-news/govt-committed-to-empowering-women-ladki-bahin-to-continue-cm-fadnavis-125091700582_1.html</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A4%B8%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8%E0%A4%B5-%E0%A4%A7%E0%A4%AE-%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%A6%E0%A4%B0-%E0%A4%AC-%E0%A4%A6-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F%E0%A4%B5%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B6%E0%A5%87%E0%A4%B5%E0%A4%9F%E0%A4%9A-%E0%A4%85%E0%A4%B2%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%87%E0%A4%9F/ar-AA1MXK2J</t>
+          <t>https://www.ptinews.com/detail/national/CM-Fadnavis-must-resign-after-Rahul-Gandhi-exposed-vote-theft-in-Maharashtra-Sapkal/2926755</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/cm-devendra-fadnavis-insured-maharashtra-state-government-to-introduce-new-bamboo-industry-policy-read-details/940426</t>
+          <t>https://thenewsmill.com/2025/09/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/india/top-marathi-news-today-live-marathi-news-breaking-news-live-update-national-news-live-news-992561.html</t>
+          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/maharashtra-devendra-fadnavis-pm-ambitions-rss-modi-resignation-claim-harshvardhan-sapkal-135967771.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-no-matter-what-happens-the-mayor-will-be-from-the-mahayuti-chief-minister-criticizes-thackeray-brothers-from-bjps-vijay-sankalp-rally/922208/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ncp-counters-devendra-fadnavis-devabhavu-campaign-1492671.html</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava/articleshow/123926617.cms</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/ahmednagar/rohit-pawar-reply-to-chhagan-bhujbal-on-jalna-antarwali-sarathi-lathicharge-on-maratha-protest-1385305</t>
+          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-and-bjp-stage-a-strong-show-of-strength-on-the-occasion-of-metro-trial-in-thane-cm-devendra-fadnavis-eknath-shinde-pratap-sarnaik/923787/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/maharastra-cabinate-meeting-inside-story-ajit-pawar-makes-laughter-in-front-of-devendra-fadanvis-latest-marathi-news-1481676.html</t>
+          <t>https://udayavani.com/national/injured-toddler-dies-on-way-to-hospital-as-ambulance-gets-stuck-in-traffic-jam-in-thane-001355?lang=en</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/thane/thane-metro-4-and-metro-4a-35-km-long-how-many-stations-trial-run-by-devendra-fadnavis-eknath-shinde-see-details-in-marathi-1385959</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-mandates-e-kyc-for-ladki-bahin-beneficiaries-sets-deadline-125091900196_1.html</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/punepolice-force-1720-posts-will-soon-be-approved-by-the-high-powered-committee-headed-by-chief-minister-devendra-fadnavis/articleshow/124010529.cms</t>
+          <t>https://udayavani.com/kerala-woman-goes-missing-after-losing-rs-11-lakh-in-cyber-scam-486240?lang=en</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-activist-waves-black-flag-and-raise-slogans-against-devendra-fadnavis/videoshow/123936572.cms</t>
+          <t>https://thenewsmill.com/2025/09/delhi-cm-praises-pm-modi-for-gst-reforms-says-public-to-benefit-directly/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-ias-officer-transfer-order-cabinet-meeting-devendra-fadanvis-ws-a-1481304.html</t>
+          <t>https://indiaeducationdiary.in/mahindra-tractors-and-maharashtra-govt-partner-to-launch-skill-development-centre-in-gadchiroli/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.etvbharat.com/mr/!state/no-question-of-pm-modis-retirement-increased-bjp-and-rss-bonding-ater-pm-modi-nagpur-visits-says-rss-researcher-dilip-devdhar-pm-modi-turns-75-today-75th-birthday-maharashtra-news-mhs25091700500</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179466/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-govt-to-launch-cleanliness-drive-in-750-villages-on-sep-17-to-mark-pm-modis-birthday-95099</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-to-introduce-certification-courses-in-gold-and-jewelry-sector-at-skill-development-university/articleshow/123967156.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-informed-that-the-states-advocate-general-birendra-saraf-has-resigned/922000/</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/loksatta-anvyarth-conflicts-continue-to-persist-even-after-prime-minister-narendra-modi-visit-to-manipur-amy-95-5380171/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-cm-bungalow-sofa-kitchen-renovation-40-lakh-expense-controversy-135949649.html</t>
+          <t>https://agrowon.esakal.com/agro-special/one-crore-women-in-maharashtra-will-be-made-millionaires-rat16</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/8-important-decisions-in-the-cabinet-meeting-132-crores-of-funds-for-farmers-buildings-and-extension-of-the-deadline-for-the-construction-of-a-modern-orange-center-rat16</t>
+          <t>https://www.loksatta.com/business/finance/know-where-has-pm-modi-invested-his-wealth-investment-options-marathi-news-rak-94-5379523/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/devendra-fadnavis-dreams-of-becoming-pm-claims-congress-state-president-harshvardhan-sapkal-135973533.html</t>
+          <t>https://www.loksatta.com/mumbai/centre-decision-crushes-pulse-farmers-in-india-ocd-94-5382837/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/beed-railway-inaugurate-by-ajit-pawar-and-cm-devendra-fadnavis-maharashtra-news-1481857.html</t>
+          <t>https://www.loksatta.com/business/finance/modi-government-issues-new-order-after-gst-rate-cut-print-eco-news-rds-00-5379506/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chagan-bhujbal-questions-kunbi-certificates-fadnavis-clarifies-135944637.html</t>
+          <t>https://www.loksatta.com/business/income-tax-return-filing-due-date-to-be-extended-again-today-as-login-issues-e-filing-glitches-persist-scj-81-5376367/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sanjay-raut-on-maharashtra-debt-burden-slams-devendra-fadnavis-eknath-shinde-ajit-pawar-says-state-situation-is-similar-to-nepal-marathi-news-1384489</t>
+          <t>https://www.loksatta.com/pune/sharad-pawar-questions-need-for-two-caste-subcommittees-pune-print-news-rds-00-5380029/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur/ajit-pawar-advise-to-bjp-mla-gopichand-padalkar-on-jayant-patil-statement-maharashtra-politics-marathi-news-1385092</t>
+          <t>https://www.navarashtra.com/india/top-marathi-news-today-live-marathi-news-breaking-news-live-update-national-news-live-news-992561.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-ajit-doval-criticism-anjali-damania-gopichand-padalkar-controversy-mcoca-removal-update-135966330.html</t>
+          <t>https://www.saamana.com/government-came-in-maharashtra-through-vote-theft-mahayuti-has-no-right-to-remain-in-power-harshvardhan-sapkal-criticism-saamana-online-news/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-9/923517/</t>
+          <t>https://marathi.webdunia.com/article/national-marathi-news/modi-government-to-distribute-25-lakh-free-lpg-connections-during-navratri-125092200056_1.html</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/desh/maharashtra-marathi-live-news-23-september-2025-navratri-festival-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.berartimes.com/vidarbha/216625/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/the-drought-history-of-marathwada-will-be-compiled-rat16</t>
+          <t>https://www.newsband.in/article_detail/controversy-eruptsover-naming-ofambernaththeatre</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/non-agricultural-land-certificates-compulsion-removed-for-micro-and-small-businesses/articleshow/123988928.cms</t>
+          <t>https://www.msn.com/en-in/news/India/nagpur-violence-chhaava-abu-azmi-effigy-burning-and-protest-here-is-the-chain-of-events-that-led-to-the-clashes/ar-AA1BcGe3?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/sharad-pawar-says-farmer-lives-are-in-trouble-devevendra-fadnavis-taking-the-name-of-shivaji-maharaj-and-not-looking-at-baliraja-1384307</t>
+          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/new-gst-reforms-will-give-new-impetus-to-indias-economic-development-chief-minister-devendra-fadnavis/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/padalkars-jibe-at-jayant-patil-sparks-protests-comment-inappropriate-says-cm/articleshow/124003830.cms</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/pm-modi-birthday-special-cm-devendra-fadnavis-and-dcm-ekanth-shinde-wrote-articles-praises-modi-leadership-1384692</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/thiruvananthapuram/concerned-over-controversies-surrounding-sabarimala-tdb-chief/articleshow/123928370.cms</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sharad-pawar-criticizes-devendra-fadnavis-over-farmers-issues-from-aakrosh-morcha/921710/</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/feeding-into-the-debate-pigeon-spots-near-sgnp-ruffle-feathers/articleshow/123906843.html</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/shivsena-ubt-mp-sanjay-raut-press-conference-attack-on-bjp-on-corruption-and-debt-on-state-saamana-online-news/</t>
+          <t>https://www.afternoonvoice.com/maharashtra-doctors-stage-strike-over-govt-nod-to-register-homeopaths.html</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-targets-devendra-fadnavis-over-marathwada-flood-situation/921688/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-tri-bhasha-samiti-also-meets-uddhav-thackeray-raj-thackeray-amid-hindi-vs-marathi-row-in-state-know-all/articleshow/123948973.cms</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-chaired-a-review-meeting-of-the-information-technology-department-125092200052_1.html</t>
+          <t>https://hindi.theprint.in/india/bjp-mlas-remarks-on-ncp-sp-leader-sparks-row-pawar-calls-cm/870777/</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://maharashtramirror.com/maharashtra-news-political-turmoil-in-the-state-differences-between-shinde-fadnavis-over-ias-appointment-to-d-class-municipalities/</t>
+          <t>https://www.indiatv.in/maharashtra/don-t-let-a-khan-become-mayor-bjp-mumbai-chief-ameet-satam-statament-ahead-of-polls-2025-09-17-1163297</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-flagged-off-the-first-train-service-from-beed-to-ahilyanagar-125091800006_1.html</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/sharad-pawar-raging-on-the-issue-of-maharashtra-farmers/article-105258</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-will-become-a-global-gaming-hub-fadnavis-cabinet-approves-125091700028_1.html</t>
+          <t>https://www.amarujala.com/video/india-news/rahul-gandhi-vote-theft-claim-cm-fond-of-rahul-gandhi-s-vote-theft-claims-gives-this-reply-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-governments-make-and-break-on-reservation-continues-vijay-vadettiwar-hits-out-at-fadnavis/</t>
+          <t>https://hindi.newsbytesapp.com/news/india/why-doctors-on-one-day-strike-in-maharashtra/story</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadanvis-pod-taxi-service-will-be-started-soon-in-mumbai-chief-minister-fadnavis-gave-information/</t>
+          <t>https://www.patrika.com/mumbai-news/thane-metro-dream-comes-true-after-20-year-new-lifelines-trial-run-begin-on-these-10-stations-19965341</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
+          <t>https://navbharatlive.com/maharashtra/wardha/teachers-strike-against-tet-decision-wrote-letter-to-cm-in-blood-ministers-degrees-1356071.html</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadanvis-provision-of-corpus-fund-for-treatment-worth-more-than-5-lakhs-chief-minister-fadnavis-announcement/</t>
+          <t>https://www.loksatta.com/nagpur/another-train-between-nagpur-pune-ssb-93-5379462/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://maharashtramirror.com/mumbai-local-train-news-megablock-on-harbour-line-from-midnight-today-local-services-closed-for-14-30-hours/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/demands-on-mulund-dumping-ground-land-grow-bjp-asks-for-golf-course-ubt-wants-hospital-and-now-dharavi-project-body-seeks-15-acres-for-casting-yard/articleshow/123904709.cms</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/mumbai-metro-4-project-inauguration-cm-fadnavis-blames-previous-mva-government-for-project-delay-037837.html</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-slams-thackeray-bjp-vijayi-sankalp-melava/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pimpri-news-devabhaus-poster-disfigures-the-city-allegations-that-chhatrapati-is-being-desecrated/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-approves-joint-venture-for-5000-mw-capacity-renewable-energy-project/articleshow/123925535.cms</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-now-the-chief-minister-has-a-complaint-about-potholes-roads-are-being-cleaned-complaints-are-pouring-in-fadnavis-is-upset-with-the-management-of-the-municipality/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/smart-solar-bench-installed-at-st-xaviers-college-in-mumbai/articleshow/123905895.cms</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/how-was-the-first-meeting-between-devendra-fadnavis-and-narendra-modi/167384/</t>
+          <t>https://www.msn.com/en-in/sports/cricket/bjp-mla-s-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm/ar-AA1MU0lT</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/new-shetkari-bhavans-in-79-market-committees-across-the-state-provision-of-rs-132-crore-48-lakhs/</t>
+          <t>https://www.ptinews.com/story/national/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm/2929801</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/fadnavis-made-a-big-announcement-saying-that-the-ladki-bahin-scheme-will-not-be-closed/</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-gopichand-padalkar-controversial-remark-on-jayant-patil-sharad-pawar-reaction-9642900.html</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
+          <t>https://www.livehindustan.com/maharashtra/shiv-sena-ubt-mp-sanjay-raut-says-many-mlas-because-of-vote-chori-in-maharashtra-201758358063004.html</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-18-september-2025-125091800004_1.html</t>
+          <t>https://www.loksatta.com/photos/todays-photo-3/5374798/why-did-sharad-pawar-get-angry-with-jitendra-awhad-at-the-ncp-program-what-happened-at-the-gathering-in-nashik-gkt-96/</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1-13/</t>
+          <t>https://www.loksatta.com/nagpur/hindutva-certificate-nagpur-rakesh-tikait-comment-amravati-ssb-93-5382390/</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-75th-birthday-retirement-rumors-dispelled-as-modi-continues-bjp-leadership-maharashtra-cm-dcm-praise-his-vision-for-development-and-national-interest-1384706</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%BE%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%80-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%9C%E0%A5%8D%E0%A4%9E%E0%A4%BE%E0%A4%A8-%E0%A4%B5%E0%A4%BF%E0%A4%AD%E0%A4%BE%E0%A4%97%E0%A4%BE/118336/</t>
+          <t>https://www.mymahanagar.com/maharashtra/bjp-gopichand-padalkar-on-being-apology-to-jayant-patil-on-controversial-statement/923126/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/no-faith-in-constitution-fadnavis-targets-rahul-gandhi-over-gen-z-post-terms-him-urban-maoist/articleshow/123996897.cms</t>
+          <t>https://www.loksatta.com/desh-videsh/bjp-fuming-on-shahid-afridis-positive-mindset-comment-on-rahul-gandhi-kvg-85-5377194/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
+          <t>https://www.marathiebatmya.com/political/ncp-leader-sharad-pawar-called-cm-fadnavis-to-express-his-displeasure/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/national/news/fadnavis-calls-rahul-gandhi-%E2%80%98urban-naxal-then-what-about-indias-foreign-policy-leaning-towards-%E2%80%98maoism-asks-shiv-se-299178</t>
+          <t>https://www.marathijagran.com/maharashtra/nashik/sharad-pawar-criticizes-the-cm-devendra-fadnavis-by-calling-him-devabhau-warns-the-government-94901</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/congress-slams-maharashtra-cm-fadnavis-over-posters-featuring-shivaji-maharaj-pasted-at-train-station-with-filth-around-3732307</t>
+          <t>https://agrowon.esakal.com/video/sharad-pawar-criticizes-devendra-fadnavis-farm-loan-waiver-protest</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe20250918053517-141254/</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/govt-committed-to-empowering-women-ladki-bahin-to-continue-cm-fadnavis-125091700582_1.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/obcs-disrupt-cm-s-speech-holds-huge-rally-in-hingoli-101758137116445.html</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharastra-cm-fadnavis-pushes-for-faster-industrial-approvals-ai-based-reforms-to-boost-investments-23594849</t>
+          <t>https://www.nagpurtoday.in/maratha-quota-maharashtra-gr-harmed-interests-of-obcs-wadettiwar/09191728</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-solapur-crime-ex-deputy-sarpanch-govind-burge-death-case-maratha-reservation-mumbai-rain-sharad-pawar-ajit-pawar-manoj-jarange-patil-rain-maratha-obc-rese-1492609.html</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-devendra-fadnavis-23594442?button=next</t>
+          <t>https://www.marathi.hindusthanpost.com/social/marathwada-mukti-sangram-din-2025-confusion-during-speech-cm-fadanvis/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-govt-signs-mou-with-cambridge-to-elevate-school-education-101758482430602.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-sign-mous-to-boost-steel-production-3736498</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/marathwada-got--21-000-cr-investment-in-past-10-years--fadnavis-1758179070896</t>
+          <t>https://www.business-standard.com/india-news/engineers-crucial-in-building-viksit-bharat-pm-modi-on-engineers-day-125091500111_1.html</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/hyundai-maharashtra-discuss-new-investments-jobs-571636</t>
+          <t>https://www.business-standard.com/india-news/pm-to-inaugurate-3-day-armed-forces-commanders-conference-in-kolkata-today-125091500085_1.html</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-fadnavis-defends-obc-reservation-policy-says-no-threat-to-communitys-rights/articleshow/123886921.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/nitin-gadkari-exclusive-on-mumbai-water-taxi-sea-planes-roro-rides-in-abp-reshaping-india-conclave-3013493</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop-Fadnavis/2927696</t>
+          <t>https://4pm.co.in/gadkaris-direct-challenge-to-shah-said-on-the-question-of-delay-on-bjp-president-ask-nadda/147016</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/CM-Fadnavis-must-resign-after-Rahul-Gandhi-exposed-vote-theft-in-Maharashtra-Sapkal/2926755</t>
+          <t>https://www.agniban.com/sharad-pawar-support-nitin-gadkari-facing-trolling-ethanol/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-reviews-pod-taxi-project-to-tackle-bkc-congestion-23595308</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maha-cong-chief-says-partys-symbol-didnt-reach-everywhere-after-joining-mva-rules-out-statewide-alliance-for-local-body-polls/articleshow/124019976.cms</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/drought-will-soon-be-a-thing-of-past-in-marathwada-cm/</t>
+          <t>https://www.hindisaamana.com/mahayutis-great-scam-200-forensic-labs-are-running-on-papers/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/mumbai-to-get-pod-taxi-service-for-seamless-last-mile-connectivity-says-cm-fadnavis/</t>
+          <t>https://www.greaterkashmir.com/latest-news/namo-yuva-run-sees-nationwide-participation-leaders-call-for-nasha-mukt-bharat/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/mou-cambridge-new-phase-world-class-education-maha-cm-fadnavis-454046</t>
+          <t>https://www.afternoonvoice.com/the-chronological-formation-and-political-evolution-of-maharashtra.html</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/awakened-feeling-of-patriotism-in-every-person-says-amruta-fadnavis-after-watching-mera-desh-pehle-the-untold-story-of-shri-narendra-modi/</t>
+          <t>https://maharashtratimes.com/india-news/bjp-likely-to-make-next-president-from-brahmin-community-as-vp-election-changes-social-arithmetic-three-names-in-the-race/articleshow/123940423.cms</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/varsha-bungalow-furniture-20-47-lakh-controversy-pwd-covers-multiple-bungalows-activists-point-to-crore-tenders-135952900.html</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/ajit-pawar-gets-shocker-as-pune-former-ncp-leader-bapu-bhegade-joins-bjp-bala-bhegade-vs-sunil-shelke/amp_articleshow/123892833.cms</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/cm-couldnt-spare-even-15-minutes-to-unveil-swami-ramanand-tirthas-statue-oppn-targets-fadnavis-10473538</t>
+          <t>https://www.saamana.com/bjp-leader-hate-statement-pollutes-the-atmosphere-mahavikas-aghadi-save-maharashtra-sankruti-march-in-sangli/</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/controversy-eruptsover-naming-ofambernaththeatre</t>
+          <t>https://www.animationxpress.com/latest-news/maharashtra-government-approves-states-avgc-xr-policy-with-rs-3000-crore-plan/</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/padalkars-jibe-at-jayant-patil-sparks-protests-comment-inappropriate-says-cm/articleshow/124003830.cms</t>
+          <t>https://www.electronicsforyou.biz/industry-buzz/rrp-electronics-gets-land-for-semiconductor-fab-in-navi-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://mumbaimirror.indiatimes.com/mumbai/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row/articleshow/124004724.html</t>
+          <t>https://m.economictimes.com/news/india/maharashtras-new-policy-to-promote-creative-tech-sector/articleshow/123928891.cms</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
+          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thiruvananthapuram/concerned-over-controversies-surrounding-sabarimala-tdb-chief/articleshow/123928370.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/hi-tech-media-park-in-nagpur-with-rs3000cr-nod-to-avgc-xr/articleshow/123928752.cms</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
+          <t>https://indianews.com.au/maharashtra-clears-avgc-xr-policy-2025-eyes-rs-50000-crore-investment-and-2-lakh-jobs/</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://mumbaimirror.indiatimes.com/mumbai/feeding-into-the-debate-pigeon-spots-near-sgnp-ruffle-feathers/articleshow/123906843.html</t>
+          <t>https://news18marathi.com/maharashtra/what-is-gaming-policy-of-maharashtra-cabinet-approval-1481423.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi/</t>
+          <t>https://marathi.indiatimes.com/e-paper/4000-cctvs-to-be-installed-for-nashik-trimbakeshwars-simhastha-kumbhmela/articleshow/123994347.cms</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/political-posters-without-permission-stir-controversy-in-pimpri-chinchwad/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/18/bom20-mh-rahul-ec-reax.html</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/maharashtra-doctors-stage-strike-over-govt-nod-to-register-homeopaths.html</t>
+          <t>https://thenewsmill.com/2025/09/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-tri-bhasha-samiti-also-meets-uddhav-thackeray-raj-thackeray-amid-hindi-vs-marathi-row-in-state-know-all/articleshow/123948973.cms</t>
+          <t>https://thenewsmill.com/2025/09/this-is-a-childish-statement-ncp-mp-sunil-tatkare-slams-rahul-gandhi-over-vote-theft-allegations/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/bjp-mlas-remarks-on-ncp-sp-leader-sparks-row-pawar-calls-cm/870777/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar-3735776</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/ajit-pawar-downplayed-the-controversy-with-the-woman-ips-officer/870095/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/perform-or-perish-ajit-pawar-warns-ncp-ministers-at-chintan-shivir/articleshow/124003932.cms</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/amit-shah-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B0-%E0%A4%AF%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%A6-%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5-%E0%A4%9C-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%AA-%E0%A4%A4-%E0%A4%95-%E0%A4%AA%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%AA-%E0%A4%82%E0%A4%9C%E0%A4%B2/ar-AA1CM0er?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/declare-wet-drought-in-maha-waive-loans-of-affected-farmers-supriya/articleshow/123955405.cms</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-investigation-going-on-hindi-news-1390995.html</t>
+          <t>https://money.rediff.com/news/market/maharashtra-green-steel-leader-fadnavis-announces/33951620250919</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/rahul-gandhi-vote-theft-claim-cm-fond-of-rahul-gandhi-s-vote-theft-claims-gives-this-reply-2025-09-19</t>
+          <t>https://money.rediff.com/news/market/maharashtra-govt-signs-rs-80-962-cr-investment-mous/33971920250919</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/wardha/teachers-strike-against-tet-decision-wrote-letter-to-cm-in-blood-ministers-degrees-1356071.html</t>
+          <t>https://www.devdiscourse.com/article/law-order/3629565-life-sentence-for-afghan-national-in-mannheim-stabbing?amp</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/another-train-between-nagpur-pune-ssb-93-5379462/</t>
+          <t>https://www.sakshipost.com/news/chhagan-bhujbal-takes-former-boss-sharad-pawar-ncp-sp-retaliates-454468</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/demands-on-mulund-dumping-ground-land-grow-bjp-asks-for-golf-course-ubt-wants-hospital-and-now-dharavi-project-body-seeks-15-acres-for-casting-yard/articleshow/123904709.cms</t>
+          <t>https://www.msn.com/en-in/news/india/amit-shah-visits-lalbaugcha-raja-ganesh-mandal-cm-s-house-in-mumbai-holds-meeting-with-dycm-shinde/ar-AA1Lxp5d?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/devendra-fadnavis-slams-thackeray-bjp-vijayi-sankalp-melava/</t>
+          <t>https://www.deccanherald.com/india/messi-set-to-dazzle-mumbai-with-his-magic-on-indian-turf-this-december-3738198</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cabinet-approves-joint-venture-for-5000-mw-capacity-renewable-energy-project/articleshow/123925535.cms</t>
+          <t>https://m.economictimes.com/news/sports/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-in-december/articleshow/124011925.cms</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/smart-solar-bench-installed-at-st-xaviers-college-in-mumbai/articleshow/123905895.cms</t>
+          <t>https://www.devdiscourse.com/article/sports-games/3634664-mumbais-first-fia-grade-night-street-race-a-new-era-in-indian-motorsports?amp</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3632920-election-integrity-dispute-shinde-dismisses-gandhis-claims-as-baseless</t>
+          <t>https://curlytales.com/india/trending/mumbai-metro-all-you-need-to-know-about-its-routes-features/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mlas-remarks-about-ncp-sp-leader-23594821</t>
+          <t>https://www.aninews.in/news/sports/others/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-indian-racing-festival-finale20250921191656</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm/2929801</t>
+          <t>https://www.devdiscourse.com/article/business/3636517-pod-taxis-to-revolutionize-mumbais-transport-landscape</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/sports/cricket/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm/ar-AA1MU0lT</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-lead-in-green-steel-manufacturing-cm-devendra-fadnavis-23594846?button=next</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%AA-%E0%A4%8F%E0%A4%B8%E0%A4%AA-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%95-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%AA%E0%A4%A3-%E0%A4%B8%E0%A5%87-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AB-%E0%A4%A8-%E0%A4%95-%E0%A4%AF/ar-AA1MTEtV</t>
+          <t>https://www.socialnews.xyz/2025/09/21/namo-yuva-run-in-mumbai-gallery/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/shiv-sena-ubt-mp-sanjay-raut-says-many-mlas-because-of-vote-chori-in-maharashtra-201758358063004.html</t>
+          <t>https://www.punjabnewsexpress.com/national/news/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi-297681</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/sharad-pawar-criticized-cm-devendra-fadnavis-at-nashik-baliraja-aakrosh-morcha/articleshow/123911615.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sharad-pawar-on-asking-pm-modi-to-retire-at-75-says-he-has-no-moral-right-watch-video-rak-94-5382190/</t>
+          <t>https://www.manufacturingtodayindia.com/maharashtra-seals-%E2%82%B980000-crore-mou-at-steelex-2025</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-news-scj-81-5380824/</t>
+          <t>https://www.timesnownews.com/mumbai/formula-race-in-navi-mumbai-first-fia-approved-street-racing-circuit-to-be-unveiled-know-when-where-article-152865232</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/nagpur-ajit-pawar-silent-on-chhagan-bhujbal-allegation-against-sharad-pawars-role-in-antarwali-sarati-lathi-charge-rds-00-5382824/</t>
+          <t>https://curlytales.com/india/trending/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-dates-venue-celeb-owners-more/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/trending-gallery/5382357/why-do-snakes-fight-with-mongooses-science-explained-spl-93/</t>
+          <t>https://currentaffairs.adda247.com/statue-of-chhatrapati-shivaji-honoured-at-pimpri%E2%80%91chinchwad/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/hindutva-certificate-nagpur-rakesh-tikait-comment-amravati-ssb-93-5382390/</t>
+          <t>https://marathi.abplive.com/news/latur/latur-news-marathwada-mahadev-koli-community-hunger-strike-postponed-important-assurance-from-shivendraraje-bhosale-maharashtra-marathi-update-1384929</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/desh-videsh/bjp-fuming-on-shahid-afridis-positive-mindset-comment-on-rahul-gandhi-kvg-85-5377194/</t>
+          <t>https://www.motoroids.com/news/hyundai-motor-india-foundation-pledges-%E2%82%B956-crore-csr-projects-in-maharashtra-for-sustainable-growth/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/bjp-gopichand-padalkar-on-being-apology-to-jayant-patil-on-controversial-statement/923126/</t>
+          <t>https://tathya.in/prabhakaran-on-green-steel/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/news/5382946/pomp-pageantry-and-politics-king-charles-royal-state-banquet-for-donlad-trump-in-photos-fehd-import-scj-81/</t>
+          <t>https://indiaeducationdiary.in/hyundai-motor-india-foundation-commits-%E2%82%B956-crore-to-csr-initiatives-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/truck-bike-accident-on-mumbai-nashik-highway-bhiwandi-ocd-94-5383014/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168588</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/entertainment-gallery/5380988/manasi-naik-shared-sakal-tar-hou-dya-movie-shoot-bts-photos-jahaz-mahal-mp-subodh-bhave-spl-93/</t>
+          <t>https://civicmirror.in/maharashtra/hyundai-should-invest-more-and-more-in-the-state-and-increase-employment-generation-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/cm-advises-padalkar-to-exercise-restraint-125092000048_1.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/18/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women.html</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/shivaji-wategaonkar-attack-on-gopichand-padalkar-jayant-patil-and-rajarambapu-patil-controversial-re-037671.html</t>
+          <t>https://www.studyiq.com/articles/mukhyamantri-majhi-ladki-bahin-yojana/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nashik/sharad-pawar-criticizes-the-cm-devendra-fadnavis-by-calling-him-devabhau-warns-the-government-94901</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ladki-bahin-yojana-update-beneficiary-women-will-do-e-kyc-when-last-date-of-process-maharashtra-govt-decision/articleshow/124001571.cms</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/sharad-pawar-attack-cm-devendra-fadanvis-over-farmer-loan-waiver-and-crop-rate-issue-ncp-nashik-melava-1480406.html</t>
+          <t>https://www.marathijagran.com/maharashtra/chhatrapati-sambhajinagar/ladki-bahin-yojana-will-be-closed-cm-devendra-fadnavis-gave-clarification-95422</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/video/sharad-pawar-criticizes-devendra-fadnavis-farm-loan-waiver-protest</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/chitra-wagh-slams-sharad-pawar-for-criticising-questioning-cm-devendra-fadnavis-over-farmers-issues-in-maharashtra/939621</t>
+          <t>https://news18marathi.com/photogallery/money/ladki-bahin-yojana-ekyc-government-makes-e-kyc-mandatory-check-details-in-marathi-1483416.html</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/sharad-pawar-criticizes-government-over-increase-in-farmer-suicides-amy-95-5374958/</t>
+          <t>https://www.mymahanagar.com/maharashtra/chief-minister-devendra-fadnavis-resolved-to-make-one-crore-women-in-the-state-lakhpati-didi-on-the-occasion-of-marathwada-mukti-din/922549/</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/jayant-patil-first-reaction-on-gopichand-padalkar-criticism-anger-from-sharad-pawar-ncp-group-maharashtra-politics-marathi-news-1385191</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/deva-bhau-you-take-the-name-of-shivaji-maharaj-but-you-dont-even-look-at-baliraja-what-sharad-pawar-said-in-his-speech-in-nashik-284196/amp/</t>
+          <t>https://www.dainikprabhat.com/fadnavis-made-a-big-announcement-saying-that-the-ladki-bahin-scheme-will-not-be-closed/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/bjp-slams-sharad-pawar-farmers-politics-284281/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-21-september-2025-125092100006_1.html</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/devendra-fadnavis-is-messiah-of-obc-community-praises-minister-chhagan-bhujbal/articleshow/123987624.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-will-get-1-lakh-rupees-loan-without-interest-read-how-it-works-cm-devendra-fadnavis-tells-calculation-article-152844483</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/sangli-ncp-sp-morcha-against-gopichand-padalkar-ddb79</t>
+          <t>https://marathi.asianetnews.com/maharashtra/cidco-lottery-2025-navi-mumbai-affordable-homes-22000-dream-houses/photoshow-s99l5v8</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/padalkars-criticism-has-a-strong-impact-sharad-pawar-directly-calls-cm-fadnavis-says-to-those-who-make-absurd-statements/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-govt-makes-e-kyc-mandatory-for-ladki-bahin-beneficiaries-sets-2-month-deadline-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
+          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/obcs-disrupt-cm-s-speech-holds-huge-rally-in-hingoli-101758137116445.html</t>
+          <t>https://civicmirror.in/maharashtra/e-kyc-facility-launched-on-the-website-for-the-chief-minister-my-beloved-sister-scheme-women-and-child-development-minister-aditi-tatkare/</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/wadettiwar-accuses-mahayuti-ministers-of-pushing-fake-obc-certificates/articleshow/124020428.cms</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-government-ekyc-mandatory-for-ladki-bahin-scheme-amid-rising-ineligible-beneficiaries-vsd-99-5383290/</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/chhatrapati-sambhajinagar/obc-activists-create-ruckus-during-devendra-fadnavis-speech-at-the-main-event-of-marathwada-liberation-day-95358</t>
+          <t>https://www.saamana.com/marathwada-mukti-sangram-din-2025-protest-in-front-of-devendra-fadnavis-ajit-pawar-pratap-sarnaik-saamana-online-news/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chhatrapati-sambhajinagar-cm-devendra-fadnavis-choas-police-arrested/922375/</t>
+          <t>https://hindi.latestly.com/india/maharashtra-ladki-bahen-yojana-e-kyc-is-mandatory-here-are-the-new-update-2757688.html</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-solapur-crime-ex-deputy-sarpanch-govind-burge-death-case-maratha-reservation-mumbai-rain-sharad-pawar-ajit-pawar-manoj-jarange-patil-rain-maratha-obc-rese-1492609.html</t>
+          <t>https://www.dainikprabhat.com/chief-minister-fadnavis-made-mohit-kamboj-rich-overnight-know-the-case-of-800-crores-varsha-gaikwads-serious-allegations/</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/marathwada-mukti-sangram-din-2025-confusion-during-speech-cm-fadanvis/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mla-s-remarks-on-ncp-sp-leader-kicks-up-row-101758309273108.html</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/pm-to-inaugurate-3-day-armed-forces-commanders-conference-in-kolkata-today-125091500085_1.html</t>
+          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/nitin-gadkari-exclusive-on-mumbai-water-taxi-sea-planes-roro-rides-in-abp-reshaping-india-conclave-3013493</t>
+          <t>https://www.punjabnewsexpress.com/national/news/maha-cabinet-clears-animation-policy-2025-renewable-energy-projects-297717</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/18/no-cap-on-prices-of-cars-for-guv-cm-and-judges-in-maharashtra-vehicle-policy</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/maha-cong-chief-says-partys-symbol-didnt-reach-everywhere-after-joining-mva-rules-out-statewide-alliance-for-local-body-polls/articleshow/124019976.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bom47-mh-almatti-dam-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/mahayutis-great-scam-200-forensic-labs-are-running-on-papers/</t>
+          <t>https://m.economictimes.com/news/india/maharashtras-new-policy-to-promote-creative-tech-sector/amp_articleshow/123928891.cms</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/mumbai-mahapalika-sahit-anya-nagarpalikaon-mein-mahayuti-ka-bhagwa-jhanda-lahraega-eknath-shinde/104161/</t>
+          <t>https://mahasamvad.in/178810/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/on-rahul-gandhi-s-message-to-gen-z-devendra-fadnavis-urban-naxal-jab-996639</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ncps-nagpur-declaration-speaks-about-strengthening-ties-with-bjp-hails-modis-leadership-3736829</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/steel-mahakumbh-investment-worth-rs-80962-crores-will-come-to-maharashtra-90300-jobs-will-be-created-95899</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://english.newstrack.com/uttar-pradesh/namo-yuva-run-inspires-india-youth-unite-for-a-drug-free-and-healthy-future-542936</t>
+          <t>https://www.etvbharat.com/mr/!state/namo-yuva-run-organized-in-mumbai-and-pune-to-promote-a-drug-free-india-on-pm-narendra-modi-birthday-maharashtra-news-mhs25092101073</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-gets-shocker-as-pune-former-ncp-leader-bapu-bhegade-joins-bjp-bala-bhegade-vs-sunil-shelke/articleshow/123892833.cms</t>
+          <t>https://maharashtratimes.com/career/career-news/maharashtra-to-introduce-certification-courses-in-gold-and-jewelry-sector-at-skill-development-university/articleshow/123967156.cms</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://ebatmidar.com/%E0%A4%9C%E0%A4%B3%E0%A4%97%E0%A4%BE%E0%A4%B5%E0%A4%BE%E0%A4%A4-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%AF%E0%A5%81%E0%A4%B5%E0%A4%BE-%E0%A4%B0%E0%A4%A8-%E0%A4%AD%E0%A4%B5%E0%A5%8D/</t>
+          <t>https://www.berartimes.com/maharashtra/216617/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/pm-modi-birthday-%E0%A4%AA%E0%A4%82%E0%A4%9A-%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%9D-%E0%A4%B2-%E0%A4%AA%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A4%82-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE-%E0%A4%A6-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87%E0%A4%9A-%E0%A4%B0-%E0%A4%B9%E0%A4%A3-%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A5%87%E0%A4%A4/ar-AA1MI1L2</t>
+          <t>https://civicmirror.in/maharashtra/will-change-criteria-for-solar-agricultural-pump-scheme-if-requested-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/bjp-leader-hate-statement-pollutes-the-atmosphere-mahavikas-aghadi-save-maharashtra-sankruti-march-in-sangli/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/acharya-devvrat-takes-oath-as-governor-of-maharashtra-94806</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://www.animationxpress.com/latest-news/maharashtra-government-approves-states-avgc-xr-policy-with-rs-3000-crore-plan/</t>
+          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.electronicsforyou.biz/industry-buzz/rrp-electronics-gets-land-for-semiconductor-fab-in-navi-mumbai/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtras-new-policy-to-promote-creative-tech-sector/articleshow/123928891.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/who-is-acharya-devvrat-took-oath-in-sanskrit-gujarat-governor-has-additional-charge-of-maharashtra-marathi-news-update-1384218</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/</t>
+          <t>https://www.etvbharat.com/mr/!state/preparations-for-installation-of-renuka-devi-mahur-ghatsthapana-2025-have-begun-devotees-from-all-over-the-country-and-abroad-come-for-darshan-maharashtra-news-mhs25092104230</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/hi-tech-media-park-in-nagpur-with-rs3000cr-nod-to-avgc-xr/articleshow/123928752.cms</t>
+          <t>https://www.etvbharat.com/mr/!politics/bmc-polls-50-50-seats-for-sena-ubt-mns-in-mumbai-strongholds-60-40-in-others-say-party-leaders-mhs25092103157</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/entertainment/maharashtra-cabinet-clears-animation-visual-effects-policy-with-roadmap-till-2050/2920262</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-cabinet-approves-8-key-decisions-announces-new-animation-vfx-gaming-policy-2025/</t>
+          <t>https://marathi.ndtv.com/videos/4-biggest-news-stories-from-the-state-and-abroad-watch-them-with-one-click-996961</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maharashtra-clears-avgc-xr-policy-2025-eyes-rs-50000-crore-investment-and-2-lakh-jobs-453114</t>
+          <t>https://dainikekmat.com/a-committee-of-eight-secretaries-headed-by-the-chief-secretary-to-prepare-a-vision-document-for-a-developed-maharashtra-2047/117284/</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-cabinet-meeting-maharashtra-animation-gaming-policy-announced-government-takes-8-major-decisions-95140</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/what-is-gaming-policy-of-maharashtra-cabinet-approval-1481423.html</t>
+          <t>https://www.heraldgoa.in/globe-nation/rohit-sharmas-retirement-decision-dependent-on-indias-champions-trophy-2025-result-potential-successors-revealed/15150/</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/4000-cctvs-to-be-installed-for-nashik-trimbakeshwars-simhastha-kumbhmela/articleshow/123994347.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/cabinet-approves-bhandara-to-gadchiroli-94-km-expressway.html</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cabinet-clears-animation-policy-2025-and-other-key-projects-23594299</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/maharashtra-has-great-opportunities-for-development-in-fisheries-and-animal-husbandry-sectors-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628572-krbl-shares-tank-nearly-10-pc?amp</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/18/bom20-mh-rahul-ec-reax.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/the-government-is-kind-to-devendra-fadnavis-builder-friend-juhu-800-crore-municipal-plot-is-in-the-builders-throat-congress-mp-varsha-gaikwad/924065/</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/this-is-a-childish-statement-ncp-mp-sunil-tatkare-slams-rahul-gandhi-over-vote-theft-allegations/</t>
+          <t>https://puneprimenews.com/state/marathwada/tuljai-kala-kendra-polices-big-decision-regarding-tuljai-kala-kendra-the-administration-of-the-art-center-is-being-violated-by-flouting-the-rules/</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar-3735776</t>
+          <t>https://hindi.latestly.com/india/politics/8-big-decisions-taken-in-the-maharashtra-cabinet-meeting-2755573.html</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/perform-or-perish-ajit-pawar-warns-ncp-ministers-at-chintan-shivir/articleshow/124003932.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/did-not-get-a-place-in-the-summit-committee-of-simhastha-kumbh-mela-saints-protest-against-the-mahayuti-government/</t>
+          <t>https://www.msn.com/mr-in/news/other/cancer-policy-%E0%A4%95%E0%A5%85%E0%A4%A8%E0%A5%8D%E0%A4%B8%E0%A4%B0%E0%A4%B6-%E0%A4%B2%E0%A4%A2%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A4%B8%E0%A4%AE-%E0%A4%B5%E0%A5%87%E0%A4%B6%E0%A4%95-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%A4%E0%A4%AF-%E0%A4%B0-%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1MBmW2</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/declare-wet-drought-in-maha-waive-loans-of-affected-farmers-supriya/articleshow/123955405.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/wet-drought-declaring-a-wet-drought-in-maharashtra-congress-leader-nana-patole-demands-to-government-95184</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
+          <t>https://www.timemaharashtra.com/maharashtra/cm-fadnavis-orders-to-build-a-cancer-hospital-on-behalf-of-the-sansthan-in-shirdi-prepare-a-policy-for-cancer-treatment/132544/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3629565-life-sentence-for-afghan-national-in-mannheim-stabbing?amp</t>
+          <t>https://www.manufacturingtodayindia.com/hyundai-rs-56-crore-csr-projects</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/pm-modi-s-75th-birthday-celebrations-live-politicians-celebs-share-their-modi-story-on-eve-of-birthday-liveblog-13550965.html</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3631029-empowering-women-maharashtras-push-for-one-crore-lakhpati-didis</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-mumbai/20250921/281668261136708</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/amit-shah-visits-lalbaugcha-raja-ganesh-mandal-cm-s-house-in-mumbai-holds-meeting-with-dycm-shinde/ar-AA1Lxp5d?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.mahasamvad.in/page/45/?m=0</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week/ar-AA1MYNtP</t>
+          <t>https://mahasamvad.in/178828/</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/mumbai-to-introduce-pod-taxi-services-for-last-mile-connectivity-maha-cm-1008907</t>
+          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/sports/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-in-december/articleshow/124011925.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/plan-to-concrete-51-key-roads-in-nashik-city-at-rs3000-crore/articleshow/123981854.cms</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/hindi-films-fail-to-show-real-mumbai-police--maharashtra-cm-1758365200271</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-cabinet-approves-rs931cr-for-bhandaragadchiroli-super-highway/articleshow/123928813.cms</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/acharya-devvrat-takes-additional-charge-as-maharashtra-governor-101757923599184-amp.html</t>
+          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/thane-metro-lines-4-and-4a-trial-run-revolutionizing-travel-in-mumbai-metropolitan-region/124060623</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://curlytales.com/india/trending/mumbai-metro-all-you-need-to-know-about-its-routes-features/</t>
+          <t>https://www.mypunepulse.com/pune-ajit-pawar-urges-no-overlap-between-flyover-and-metro-line-construction-works/</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/sports/others/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-indian-racing-festival-finale20250921191656</t>
+          <t>https://www.etvbharat.com/hi/!bharat/mumbai-first-fully-underground-metro-journey-will-be-comfortable-from-30-september-hindi-news-hin25092003486</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://curlytales.com/india/trending/pm-modi-to-inaugurate-mumbai-metro-three-final-stretch-on-sept-heres-all-about-it/</t>
+          <t>https://www.businessworld.in/article/maharashtra-unveils-policy-reforms-to-boost-msmes-social-welfare-572212</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-22-news-updates-live-updates-weather-update-mumbai-monsoon-18331430</t>
+          <t>https://www.indiaherald.com/Viral/Read/994848480/Maharashtras-Mega-Rs-Crore-Gamble-Igniting-Indias-Animation-Gaming-and-VFX-Revolution</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/pm-modi-to-inaugurate-mumbai-metro-3-s-final-stretch-on-sept-30-1758118163968</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/gjcs-8th-edition-of-india-gem-jewellery-show-gjs2025-opens-with-grand-inauguration-by-our-cm-shri-devendra-fadnavisji-at-jio-world-convention-centre-mumbai/</t>
+          <t>https://www.loksatta.com/mumbai/bombay-hc-grants-quashed-case-against-chamankar-brothers-in-maharashtra-sadan-scam-mumbai-print-news-zws-70-5378793/</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/metro-line-connecting-thane-mumbai-be-operational-2026-end-says-cm-fadnavis-455400</t>
+          <t>https://mahasamvad.in/179233/</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/21/namo-yuva-run-in-mumbai-gallery/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/pandit-deendayal-upadhyay-employment-fair-organized.html</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://gallinews.com/lodha-developers-mein-85-crore-ka-dhokhadhadi-rajendra-n-lodha-ko-mumbai-police-ne-pakda/</t>
+          <t>https://lokmanthan.com/a-comprehensive-policy-should-be-prepared-for-cancer-treatment-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%B5%E0%A4%B0-%E0%A4%B8%E0%A4%BE%E0%A4%A1%E0%A5%87%E0%A4%86%E0%A4%A0-%E0%A4%B2%E0%A4%BE%E0%A4%96-%E0%A4%95%E0%A5%8B%E0%A4%9F%E0%A5%80/117389/</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/video/news/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%88-%E0%A4%96-%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%9C-%E0%A4%8F-%E0%A4%A4-bjp-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%AF-%E0%A4%B5-%E0%A4%B5-%E0%A4%A6-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%A6-%E0%A4%AC%E0%A4%AF-%E0%A4%A8/vi-AA1MHnOc</t>
+          <t>https://www.thehindu.com/news/national/bihar/bihar-cm-nitish-kumar-assembly-elections-2025-unemployed-graduates-financial-assistance/article70064586.ece</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%B8%E0%A5%8D%E0%A4%A5-%E0%A4%AA-%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%85%E0%A4%A8%E0%A5%81%E0%A4%AE%E0%A4%A4-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%96%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%AE-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%95%E0%A4%B9/ar-AA1MUpqj?ocid=finance-verthp-feeds</t>
+          <t>https://indtoday.com/bjp-leader-slams-rahul-gandhi-for-remarks-on-gen-z-and-democracy/</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-no-matter-what-happens-the-mayor-will-be-from-the-mahayuti-chief-minister-criticizes-thackeray-brothers-from-bjps-vijay-sankalp-rally/922208/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/madc-approves-220acre-land-for-solar-grps-defence-aerospace-projects/articleshow/124004510.cms</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179340/</t>
+          <t>https://www.latestly.com/agency-news/india-news-govt-to-set-up-adi-seva-kendras-to-solve-issues-of-tribal-people-tripura-cm-7114924.html</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179233/</t>
+          <t>https://kiow.com/2025/09/16/gov-reynolds-returns-from-india-trade-and-investment-mission/</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%95%E0%A4%AC%E0%A5%81%E0%A4%A4%E0%A4%B0%E0%A4%96-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%86%E0%A4%A4-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%85%E0%A4%9F-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1JVxWD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/kozhikode/tribal-kids-from-remote-wayanad-settlement-begin-their-schooling/articleshow/123928460.cms</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
+          <t>https://www.financialexpress.com/india-news/pm-modi-75th-birthday-2025-wishes-live-updates-quotes-messages-greetings-tweets-on-x-facebook/3980159/</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-on-podtaxi-solution-to-mumbai-traffic-congestion-pod-taxis-will-come-last-mile-connectivity-for-mumbaikars-1386065</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178607/</t>
+          <t>https://mahasamvad.in/179074/</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-incident-of-throwing-paint-on-the-effigy-of-meenatai-thackeray-has-sparked-a-political-storm-uddhav-and-raj-thackeray-are-outraged-1188096</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/2-year-extension-granted-for-modern-orange-processing-centres-in-vidarbha/articleshow/123928870.cms</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/21/mumbaikars-run-towards-a-drug-free-india-namo-yuva-run-receives-overwhelming-response-will-intoxicate-our-yout.html</t>
+          <t>https://mahasamvad.in/179340/</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-slams-thackeray-bandhu-over-best-election-2025-result-and-brand-defeat-a-a719/</t>
+          <t>https://mahasamvad.in/179388/</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/pod-taxis-will-run-in-bandra-kurla-complex-chief-minister-devendra-fadnavis-has-instructed-9324651</t>
+          <t>https://www.msn.com/mr-in/news/other/magel-tyala-saur-krushi-pump-yojana-%E0%A4%AE-%E0%A4%97%E0%A5%87%E0%A4%B2-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%B8-%E0%A4%B0-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AA%E0%A4%82%E0%A4%AA-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%95%E0%A4%B7-%E0%A4%A4-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MUDTy</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/mohit-kamboj-special-for-bjp-and-sra-project-prof-mp-varsha-gaikwad-allegations-on-bjp-mohit-kamboj/921878/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/pm-suryaghar-yojana-443-mw-of-electricity-generated-in-vidarbha-1364448.html</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/mahayuti-cabinet-took-8-major-decisions-on-tuesday-mahayuti-cabinet-125091600058_1.html</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/18/brand-vs-brandy-war-of-words-between-fadnavis-thackeray-faction-politics-heats-up/amp/</t>
+          <t>https://www.marathi.hindusthanpost.com/social/cabinet-decision-projects-in-the-state-will-get-new-momentum-this-big-decision-taken-in-the-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/mumbai-ahmedabad-highway-traffic-dcm-shinde-s-order-was-reversed-by-cm-fadnavis-997414</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-congress-chief-harshawardhan-sapkal-attacks-state-govt-demands-special-package-for-rain-hit-farmers/articleshow/123904520.cms</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/varsha-gaikwad-big-statement-on-mohit-kamboj-sra-scam-mumbai-devendra-fadnavis-orders-to-exchange-juhu-land-reservation-bmc/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-demands-rs50k/ha-relief-for-farmers/articleshow/123907918.cms</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://www.tarunmitra.in/state/maharashtra/mumbai-on-september-30-pm-modi-will-give-underground-metro/article-105817</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/compensation-for-rain-hit-nanded-farmers-announced/articleshow/124018215.cms</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://lalluram.com/case-of-balasaheb-thackerays-wife-being-painted-uddhav-thackeray-says-conspiracy-to-incite-riots-in-mumbai-cm-fadnavis-orders-strict-action-against-the-culprits/</t>
+          <t>https://www.afternoonvoice.com/wadettiwar-urges-maharashtra-to-declare-wet-drought-seeks-rs-50000-aid-per-hectare-for-farmers.html</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
+          <t>https://maharashtratimes.com/maharashtra/parbhani/maharashtra-government-gives-128-crore-rupees-funds-to-parbhani-for-rainfall-affected-farmers/articleshow/123980989.cms</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/mumbai/varsha-gaikwad-alleges-the-government-is-kind-to-devendra-fadnavis-builder-friend/</t>
+          <t>https://agrowon.esakal.com/agro-special/nanded-farmers-to-receive-rs-553-crore-dbt-relief-sai29</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/mumbai/chief-minister-fadnavis-said-the-next-step-in-transport-service-is-pod-taxi/</t>
+          <t>https://www.loksatta.com/kolhapur/maharashtra-government-sanctions-over-88-lakh-rupees-aid-for-kolhapur-sangli-and-dharashiv-farmers-hit-by-june-july-rains-rds-00-5381688/</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/gems-and-jewellery-exhibition-inaugurated-courses-to-be-started-for-skilled-manpower-cm-devendra-fadnavis/132720/</t>
+          <t>https://mahasamvad.in/178713/</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/harshwardhan-sapkal-farmers-in-the-state-are-in-dire-straits-harshwardhan-sapkals-criticism/</t>
+          <t>https://agrowon.esakal.com/agro-special/heavy-rain-damages-crops-in-nanded-agriculture-minister-assures-support-sai29</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%95%E0%A4%BE%E0%A4%B9%E0%A5%80%E0%A4%B9%E0%A5%80-%E0%A4%9D%E0%A4%BE%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A4%B0%E0%A5%80-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%9A%E0%A4%BE-%E0%A4%AA/117487/</t>
+          <t>https://www.tv9marathi.com/videos/ncp-sharad-pawar-on-maharashtra-floods-farmers-distress-and-plea-for-government-aid-1495164.html</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/national/news/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi-297681</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bacchu-kadu-has-strongly-criticized-on-state-government-on-the-agricultural-issue-farmers-heavy-rain-in-solapur-1384615</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/kashmiri-pandit-student-alleges-harassment-at-book-event-in-pune/articleshow/123908215.cms</t>
+          <t>https://mahasamvad.in/179457/</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://www.manufacturingtodayindia.com/maharashtra-seals-%E2%82%B980000-crore-mou-at-steelex-2025</t>
+          <t>https://www.esakal.com/nanded/maharashtra-sanctions-553-crore-relief-for-flood-hit-farmers-in-nanded-vsb99</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/messi-set-to-dazzle-mumbai-with-his-magic-on-indian-turf-this-december-3738198</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-government-sanctions-128-crore-aid-for-flood-hit-farmers-in-parbhani-rds-00-5382862/</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/formula-race-in-navi-mumbai-first-fia-approved-street-racing-circuit-to-be-unveiled-know-when-where-article-152865232</t>
+          <t>https://www.loksatta.com/maharashtra/ahilyanagar-rain-damage-vikhe-patil-orders-ocd-94-5377488/</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/mla-abdul-sattar-%E0%A4%8F%E0%A4%95%E0%A4%B9-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%A6%E0%A4%A4-%E0%A4%AA-%E0%A4%B8%E0%A5%82%E0%A4%A8-%E0%A4%B5%E0%A4%82%E0%A4%9A-%E0%A4%A4-%E0%A4%B0-%E0%A4%B9%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%86%E0%A4%AE%E0%A4%A6-%E0%A4%B0-%E0%A4%85%E0%A4%AC%E0%A5%8D%E0%A4%A6%E0%A5%81%E0%A4%B2-%E0%A4%B8%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B0/ar-AA1MMWdn</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/amp/news/urban-transportation/maharashtra-deputy-cm-calls-for-enhanced-coordination-on-pune-metro-and-elevated-highway-projects/124040274</t>
+          <t>https://thefocusindia.com/maharashtra-news/maharashtra-agriculture-minister-dattatray-bharne-promises-aid-farmers-284717/amp/</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://curlytales.com/india/trending/navi-mumbai-to-host-maharashtras-first-formula-night-street-race-dates-venue-celeb-owners-more/</t>
+          <t>https://www.loksatta.com/maharashtra/parbhani-immediate-assistance-provided-to-farmers-affected-by-heavy-rains-says-meghna-sakore-bordikar-css-98-5379203/</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://everythingexperiential.com/article/stars-leaders-and-icons-unite-for-manoj-muntashir-shuklas-mera-desh-pahle-premiere-in-mumbai-572708</t>
+          <t>https://www.athawadavishesh.com/39369/</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://www.passionateinmarketing.com/navi-mumbai-to-host-maharashtras-first-ever-formula-night-street-race-as-part-of-the-indian-racing-festival-finale/</t>
+          <t>https://www.marathiebatmya.com/agriculture/dattatray-bharne-went-to-the-washim-district-to-inspect-the-affected-crop/</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/statue-of-chhatrapati-shivaji-honoured-at-pimpri%E2%80%91chinchwad/</t>
+          <t>https://www.marathi.hindusthanpost.com/social/agriculture-minister-dattatray-bharne-visits-washim-district-hoped-for-help-for-affected-farmers/</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/en-in/news/india/breaking-pm-modi-turns-75-nation-celebrates-with-prayers-art-global-greetings-and-tributes/vi-AA1MIflJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/latur/latur-news-marathwada-mahadev-koli-community-hunger-strike-postponed-important-assurance-from-shivendraraje-bhosale-maharashtra-marathi-update-1384929</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>https://indiaeducationdiary.in/hyundai-motor-india-foundation-commits-%E2%82%B956-crore-to-csr-initiatives-in-maharashtra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168588</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/hyundai-should-invest-more-and-more-in-the-state-and-increase-employment-generation-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/18/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/chhatrapati-sambhajinagar/ladki-bahin-yojana-will-be-closed-cm-devendra-fadnavis-gave-clarification-95422</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/business/ladki-bahin-yojana-scheme-1500-rs-stop-due-to-new-rules-e-kyc-women-get-angry-on-cm-devendra-fadnavis-at-hinogli-1386139</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/179428/</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>https://news18marathi.com/photogallery/money/ladki-bahin-yojana-ekyc-government-makes-e-kyc-mandatory-check-details-in-marathi-1483416.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
-        </is>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
-        </is>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/maharashtra/mumbai-rain-latest-updates-maharashtra-weather-news-political-devendra-fadnavis-sanjay-raut-asc-95-5375148/</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/chhatrapati-sambhajinagar/ladki-bahin-yojana-women-get-angry-on-mahayuti-government-at-hinogli-due-to-new-e-kyc-rules-96333</t>
-        </is>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/chief-minister-devendra-fadnavis-resolved-to-make-one-crore-women-in-the-state-lakhpati-didi-on-the-occasion-of-marathwada-mukti-din/922549/</t>
-        </is>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-will-get-1-lakh-rupees-loan-without-interest-read-how-it-works-cm-devendra-fadnavis-tells-calculation-article-152844483</t>
-        </is>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-21-september-2025-125092100006_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/ladki-bahin-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%9D%E0%A4%9F%E0%A4%95-%E0%A4%B5%E0%A4%AF-%E0%A4%9A-%E0%A4%B0%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A4%9F-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%98%E0%A4%B0-%E0%A4%A4-%E0%A4%B2-%E0%A4%A4-%E0%A4%A8-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%A4%E0%A4%B0/ar-AA1MWw0i</t>
-        </is>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>https://marathi.asianetnews.com/maharashtra/cidco-lottery-2025-navi-mumbai-affordable-homes-22000-dream-houses/photoshow-s99l5v8</t>
-        </is>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
-        </is>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/namo-yuva-run-2025-bjp-organizes-namo-yuva-run-marathon-in-navi-mumbai/133277/</t>
-        </is>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/18/no-cap-on-prices-of-cars-for-guv-cm-and-judges-in-maharashtra-vehicle-policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>https://m.thewire.in/article/ptiprnews/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon</t>
-        </is>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>https://www.adgully.com/post/6810/ficci-frames-2025-silver-jubilee-brings-stars-and-global-leaders-together</t>
-        </is>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bes3-mh-fadnavis-jewellery-sector.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/maharashtras-new-policy-to-promote-creative-tech-sector/amp_articleshow/123928891.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>https://startupnews.fyi/2025/09/22/maharashtra-govt-to-strengthen-it-dept-to-enhance-delivery-of-services-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>https://www.sakshipost.com/news/maha-cabinet-clears-animation-policy-2025-renewable-energy-projects-452983</t>
-        </is>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
-        </is>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/magel-tyala-saur-krushi-pump-yojana-%E0%A4%AE-%E0%A4%97%E0%A5%87%E0%A4%B2-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%B8-%E0%A4%B0-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AA%E0%A4%82%E0%A4%AA-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%95%E0%A4%B7-%E0%A4%A4-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MUDTy</t>
-        </is>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-advocate-general-birendra-saraf-resigns-will-continue-his-work-till-january/</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/the-countrys-path-towards-superpowerhood-is-being-paved-with-effective-implementation-of-law-and-order-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/career/career-news/mahatet-exam-2025-mandatory-exam-confusion-for-senior-teachers-application-process-begins-from-15-september/articleshow/123893618.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-mbbs-admissions-2025-new-schedule-released-for-second-round-what-is-the-date-for-the-third-round/articleshow/123914817.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-govt-to-launch-cleanliness-drive-in-750-villages-on-sep-17-to-mark-pm-modis-birthday-95099</t>
-        </is>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>https://marathi.oneindia.com/maharashtra/marathwada-muktisangram-din-2025-devendra-fadanvis-speech-chhatrapati-sambhajinagar-today-037431.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>https://www.berartimes.com/maharashtra/216617/</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>https://awajmaharashtracha.news/waff-bord/</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>https://ahmednagarlive24.com/spacial/maharashtra-railway-another-rs-150-crore-fund-approved-for-this-railway-line-in-maharashtra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>https://dainikekmat.com/a-committee-of-eight-secretaries-headed-by-the-chief-secretary-to-prepare-a-vision-document-for-a-developed-maharashtra-2047/117284/</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/will-change-criteria-for-solar-agricultural-pump-scheme-if-requested-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/acharya-devvrat-takes-oath-as-governor-of-maharashtra-94806</t>
-        </is>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/pahalgam-terror-attack-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%B2-500-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%9F%E0%A4%95-%E0%A4%86%E0%A4%A4-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%A6-%E0%A4%96%E0%A4%B2/ar-AA1Dy1rF?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.amp.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%AF%E0%A4%A8-%E0%A4%A7%E0%A4%B0%E0%A4%A3-%E0%A4%AA-%E0%A4%AF%E0%A4%A5-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A4%97%E0%A5%83%E0%A4%B9-%E0%A4%B8-%E0%A4%A0-862-29-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%9A-%E0%A4%A4%E0%A4%B0%E0%A4%A4%E0%A5%82%E0%A4%A6-%E0%A4%87%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%9C%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%9A%E0%A5%87-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF/ar-AA1HlaXX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
-        </is>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/law-order/3632182-maharashtra-unveils-industrial-and-social-policy-reforms</t>
-        </is>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>https://www.nagpurtoday.in/future-tech-hub-nagpur-to-host-dedicated-avgc-xr-park/09171239</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/cabinet-approves-bhandara-to-gadchiroli-94-km-expressway.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/mahamumbai/the-government-is-kind-to-devendra-fadnavis-builder-friend-juhu-800-crore-municipal-plot-is-in-the-builders-throat-congress-mp-varsha-gaikwad/924065/</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>https://puneprimenews.com/state/marathwada/tuljai-kala-kendra-polices-big-decision-regarding-tuljai-kala-kendra-the-administration-of-the-art-center-is-being-violated-by-flouting-the-rules/</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/ev-%E0%A4%98%E0%A5%87%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-5-%E0%A4%B2-%E0%A4%96-%E0%A4%82%E0%A4%9A-%E0%A4%85%E0%A4%A4-%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%A7-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-9000-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%B5%E0%A4%B0/ar-AA1MMJ2I?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/wet-drought-declaring-a-wet-drought-in-maharashtra-congress-leader-nana-patole-demands-to-government-95184</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/cm-fadnavis-orders-to-build-a-cancer-hospital-on-behalf-of-the-sansthan-in-shirdi-prepare-a-policy-for-cancer-treatment/132544/</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>https://www.manufacturingtodayindia.com/hyundai-rs-56-crore-csr-projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>https://indiaeducationdiary.in/mahindra-tractors-and-maharashtra-govt-partner-to-launch-skill-development-centre-in-gadchiroli/</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178604/</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178828/</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/plan-to-concrete-51-key-roads-in-nashik-city-at-rs3000-crore/articleshow/123981854.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-cabinet-approves-rs931cr-for-bhandaragadchiroli-super-highway/articleshow/123928813.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>https://infra.economictimes.indiatimes.com/news/urban-transportation/maharashtra-deputy-cm-calls-for-enhanced-coordination-on-pune-metro-and-elevated-highway-projects/124040274</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-unveil-golden-data-of-citizens-move-to-help-detect-bogus-beneficiaries/articleshow/124002889.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/parshuram-economic-development-corporation-chairman-ashish-damle-to-get-ministerial-status-says-maharashtra-govt-23594308?button=next</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>https://www.businessworld.in/article/maharashtra-unveils-policy-reforms-to-boost-msmes-social-welfare-572212</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
-        </is>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/mumbai/bombay-hc-grants-quashed-case-against-chamankar-brothers-in-maharashtra-sadan-scam-mumbai-print-news-zws-70-5378793/</t>
-        </is>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/pandit-deendayal-upadhyay-employment-fair-organized.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>https://lokmanthan.com/a-comprehensive-policy-should-be-prepared-for-cancer-treatment-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%B5%E0%A4%B0-%E0%A4%B8%E0%A4%BE%E0%A4%A1%E0%A5%87%E0%A4%86%E0%A4%A0-%E0%A4%B2%E0%A4%BE%E0%A4%96-%E0%A4%95%E0%A5%8B%E0%A4%9F%E0%A5%80/117389/</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>https://www.business-standard.com/india-news/maharashtra-mandates-e-kyc-for-ladki-bahin-beneficiaries-sets-deadline-125091900196_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>https://hindupost.in/society-culture/breaking-the-myth-of-equality-the-crisis-of-caste-in-bharatiya-christian-communities/</t>
-        </is>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom30-mh-obc-committee-certificates.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>https://www.studyiq.com/articles/mukhyamantri-majhi-ladki-bahin-yojana/</t>
-        </is>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>https://www.liveaaryaavart.com/2025/09/Bihar-state-para-sports.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/madc-approves-220acre-land-for-solar-grps-defence-aerospace-projects/articleshow/124004510.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>https://www.latestly.com/agency-news/india-news-govt-to-set-up-adi-seva-kendras-to-solve-issues-of-tribal-people-tripura-cm-7114924.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>https://kiow.com/2025/09/16/gov-reynolds-returns-from-india-trade-and-investment-mission/</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kozhikode/tribal-kids-from-remote-wayanad-settlement-begin-their-schooling/articleshow/123928460.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>https://www.financialexpress.com/india-news/pm-modi-75th-birthday-2025-wishes-live-updates-quotes-messages-greetings-tweets-on-x-facebook/3980159/</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/179074/</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178534/</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/2-year-extension-granted-for-modern-orange-processing-centres-in-vidarbha/articleshow/123928870.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>https://mandalnews.com/amravati/prime-minister-suryadhar-free-electricity-scheme/</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/mumbai/five-thousand-mw-renewable-energy-projects-in-maharashtra-state-mumbai-news-amy-95-5377726/</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/pm-suryaghar-yojana-443-mw-of-electricity-generated-in-vidarbha-1364448.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/mahayuti-cabinet-took-8-major-decisions-on-tuesday-mahayuti-cabinet-125091600058_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>https://www.theindiadaily.com/india/maharashtra-to-launch-cleanliness-drive-on-pm-narendra-modi-s-birthday-cm-devendra-fadnavis-mangal-prabhat-lodha-iti-students-join-swachh-bharat-initiative-news-94108</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-congress-chief-harshawardhan-sapkal-attacks-state-govt-demands-special-package-for-rain-hit-farmers/articleshow/123904520.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-rains-give-immediate-relief-of-rs-50k-per-hectare-to-affected-farmers-says-sapkal/2917276</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-demands-rs50k/ha-relief-for-farmers/articleshow/123907918.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/story/national/rain-havoc-in-marathwada-8-dead-houses-and-crops-damaged/2941151</t>
-        </is>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%93%E0%A4%B2-%E0%A4%A6%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%95-%E0%A4%B3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%95%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%B9%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-50-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7/ar-AA1MJhTF?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178713/</t>
-        </is>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>https://www.tv9marathi.com/videos/ncp-sharad-pawar-on-maharashtra-floods-farmers-distress-and-plea-for-government-aid-1495164.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/kolhapur/maharashtra-government-sanctions-over-88-lakh-rupees-aid-for-kolhapur-sangli-and-dharashiv-farmers-hit-by-june-july-rains-rds-00-5381688/</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/nanded-farmers-to-receive-rs-553-crore-dbt-relief-sai29</t>
-        </is>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/rohit-pawar-slams-devendra-fadnavis-no-funds-for-loan-waiver-yet-40-lakh-spent-on-cms-residence-renovation-1384979</t>
-        </is>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A%E0%A4%82-cm-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%AC%E0%A4%81%E0%A4%95-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%B8%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1MRkaw?cvid=68ccf74848e64225b263c6b454dae318&amp;ocid=hpmsn</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bacchu-kadu-has-strongly-criticized-on-state-government-on-the-agricultural-issue-farmers-heavy-rain-in-solapur-1384615</t>
-        </is>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/heavy-rain-damages-crops-in-nanded-agriculture-minister-assures-support-sai29</t>
-        </is>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/maharashtra/jayant-patil-heavy-rain-agriculture-news-declaring-a-wet-drought-in-the-state-jayant-patil-letter-to-chief-minister-devendra-fadnavis-in-sangli-1385048</t>
-        </is>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/maharashtra-farmers-crop-damage-relief-dattatray-bharne-announcement/41253</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-government-sanctions-128-crore-aid-for-flood-hit-farmers-in-parbhani-rds-00-5382862/</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-farmers-flood-compensation-2025-dattatray-bharane-statement-135991809.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/a-fund-of-689-crores-has-been-approved-to-help-farmers-affected-by-heavy-rainfall-996353.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/beed-farmers-worried-due-to-cloudburst-like-rain-in-ashti-taluka-farmers-demands-state-government-compensation-mla-suresh-dhas-says-government-with-you-watch-video-maharashtra-news-mhs25091803910</t>
-        </is>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/maharashtra/ahilyanagar-rain-damage-vikhe-patil-orders-ocd-94-5377488/</t>
-        </is>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/maharashtra/parbhani-immediate-assistance-provided-to-farmers-affected-by-heavy-rains-says-meghna-sakore-bordikar-css-98-5379203/</t>
-        </is>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>https://www.athawadavishesh.com/39369/</t>
-        </is>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>https://breakingmaharashtra.in/?p=40301</t>
-        </is>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/agriculture/dattatray-bharne-went-to-the-washim-district-to-inspect-the-affected-crop/</t>
-        </is>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/social/agriculture-minister-dattatray-bharne-visits-washim-district-hoped-for-help-for-affected-farmers/</t>
-        </is>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
         <is>
           <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%82%E0%A4%97%E0%A5%80/117572/</t>
         </is>

--- a/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
+++ b/Output/Devendra Fadnavis/extracted_links_Devendra Fadnavis_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A563"/>
+  <dimension ref="A1:A547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,14 +445,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/pm-modi-to-inaugurate-mumbai-metro-3s-final-stretch-from-worli-to-cuffe-parade-on-sept-30-announces-chief-minister-devendra-fadnavis/articleshow/123928132.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/unacceptable-sharad-pawar-dials-devendra-fadnavis-over-bjp-mla-gopichand-padalkars-remarks-on-jayant-patils-parents-3735796</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/unacceptable-sharad-pawar-dials-devendra-fadnavis-over-bjp-mla-gopichand-padalkars-remarks-on-jayant-patils-parents-3735796</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-devendra-fadnavis-says-govt-will-create-corpus-fund-for-medical-treatments-that-cost-more-than-rs-5-lakh/articleshow/123905737.cms</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-devendra-fadnavis-says-govt-will-create-corpus-fund-for-medical-treatments-that-cost-more-than-rs-5-lakh/articleshow/123905737.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
@@ -487,14 +487,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://www.heraldgoa.in/globe-nation/maharashtra-chief-minister-devendra-fadnavis-labels-pakistan-a-terrorist-nation-praises-indian-armed-forces-response-2/12107/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-move-supreme-court-if-karnataka-goes-ahead-with-plan-to-increase-almatti-dams-height-cm-devendra-fadnavis-3732808</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/pm-modi-to-inaugurate-mumbai-metro-3s-final-stretch-from-worli-to-cuffe-parade-on-sept-30-announces-chief-minister-devendra-fadnavis/articleshow/123928132.cms</t>
         </is>
       </c>
     </row>
@@ -508,266 +508,266 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-devendra-fadnavis-to-launch-railway-project-for-marathwada-3730637</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/wont-scrap-ladki-bahin-scheme-aim-to-create-1-crore-lakhpati-didis-fadnavis/article70061945.ece</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/congress-slams-maharashtra-cm-fadnavis-over-posters-featuring-shivaji-maharaj-pasted-at-train-station-with-filth-around-3732307</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-move-supreme-court-if-karnataka-goes-ahead-with-plan-to-increase-almatti-dams-height-cm-devendra-fadnavis-3732808</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/remove-requirement-of-non-agricultural-land-certificate-for-micro-and-small-enterprises-says-maharashtra-chief-minister-devendra-fadnavis/articleshow/123979505.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/congress-slams-maharashtra-cm-fadnavis-over-posters-featuring-shivaji-maharaj-pasted-at-train-station-with-filth-around-3732307</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/only-rahul-gandhi-has-art-of-continuously-lying-devendra-fadnavis-101758224439191.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-to-come-out-with-bamboo-industry-policy-cm-devendra-fadnavis-3735818</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/wont-scrap-ladki-bahin-scheme-aim-to-create-1-crore-lakhpati-didis-fadnavis/article70061945.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/remove-requirement-of-non-agricultural-land-certificate-for-micro-and-small-enterprises-says-maharashtra-chief-minister-devendra-fadnavis/articleshow/123979505.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/en/109961/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-indias-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-signs-mou-with-cambridge-for-global-standard-education-cm-fadnavis/articleshow/123980116.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-to-come-out-with-bamboo-industry-policy-cm-devendra-fadnavis-3735818</t>
+          <t>https://auto.economictimes.indiatimes.com/news/industry/chhatrapati-sambhajinagar-emerges-as-indias-ev-manufacturing-hub-declares-maharashtra-cm-fadnavis/123961856</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://auto.economictimes.indiatimes.com/news/industry/chhatrapati-sambhajinagar-emerges-as-indias-ev-manufacturing-hub-declares-maharashtra-cm-fadnavis/123961856</t>
+          <t>https://www.ap7am.com/en/109961/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-indias-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-strenghten-it-dept-to-enhance-delivery-of-services-cm-fadnavis/articleshow/124053957.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-fadnavis-reviews-security-and-preparedness-with-navy-and-army-officers/articleshow/124029075.cms</t>
+          <t>https://www.hindustantimes.com/india-news/only-rahul-gandhi-has-art-of-continuously-lying-devendra-fadnavis-101758224439191.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-strenghten-it-dept-to-enhance-delivery-of-services-cm-fadnavis/articleshow/124053957.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-devendra-fadnavis-to-launch-railway-project-for-marathwada-3730637</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-will-move-sc-if-karnataka-goes-ahead-with-plan-to-raise-almatti-dam-height-fadnavis-101758133395229.html</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/acharya-devvrat-takes-oath-as-maha-governor-in-sanskrit-in-the-presence-of-cm-devendra-fadnavis/videoshow/123896080.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/acharya-devvrat-takes-oath-as-maha-governor-in-sanskrit-in-the-presence-of-cm-devendra-fadnavis/videoshow/123896080.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-chief-minister-fadnavis-reviews-security-and-preparedness-with-navy-and-army-officers/articleshow/124029075.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-145995/</t>
+          <t>https://www.heraldgoa.in/globe-nation/devendra-fadnavis-responds-to-calls-for-removal-of-aurangzebs-grave-stresses-legal-protection/8262/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe20250918053517-141254/</t>
+          <t>https://www.ptinews.com/story/national/using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level-fadnavis/2934307</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/congress-accuses-bjp-of-coming-to-power-in-maharashtra-by-rigging-votes-asks-fadnavis-to-quit-3734523</t>
+          <t>https://www.telegraphindia.com/india/bad-devendra-fadnavis-marg-youth-congress-targets-cm-as-potholes-expose-bmcs-failure-on-mumbai-roads/cid/2124363</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maratha-quota-gr-will-not-affect-obc-rights-says-fadnavis-101757875654855.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/congress-slams-cm-fadnavis-over-shivaji-posters-pasted-in-unhygienic-surroundings-near-prabhadevi-railway-station-in-mumbai/articleshow/123948554.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/fadnavis-streamline-industry-approvals-in-maharashtra/33958120250919</t>
+          <t>https://www.deccanherald.com/india/congress-accuses-bjp-of-coming-to-power-in-maharashtra-by-rigging-votes-asks-fadnavis-to-quit-3734523</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/maha-govt-to-launch-skills-courses-for-gems-and-jewellery-sector-fadnavis-125091600501_1.html</t>
+          <t>https://www.indiatoday.in/india/story/ncp-sp-launches-deva-tuch-sang-campaign-challenging-bjp-devabhau-narrative-maharashtra-bmc-polls-2787760-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168537</t>
+          <t>https://www.business-standard.com/industry/news/maha-govt-to-launch-skills-courses-for-gems-and-jewellery-sector-fadnavis-125091600501_1.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-signs-mou-with-cambridge-for-global-standard-education-cm-fadnavis/articleshow/123980116.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-will-move-sc-if-karnataka-goes-ahead-with-plan-to-raise-almatti-dam-height-fadnavis-101758133395229.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Fadnavis-govt-apathetic-towards-farmers-woes-claims-Pawar;-warns-of-intensifying-stir/2916686</t>
+          <t>https://www.punjabnewsexpress.com/health/news/maha-govt-approves-corpus-fund-for-health-treatment-of-over-rs-5-lakh-says-cm-fadnavis-297657</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.telegraphindia.com/india/bad-devendra-fadnavis-marg-youth-congress-targets-cm-as-potholes-expose-bmcs-failure-on-mumbai-roads/cid/2124363</t>
+          <t>https://m.economictimes.com/tech/information-tech/maharashtra-govt-to-strengthen-it-dept-to-enhance-delivery-of-services-fadnavis/articleshow/124049221.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/fadnavis-govt-apathetic-towards-farmers-woes-1006773</t>
+          <t>https://www.ptinews.com/story/business/chhatrapati-sambhajinagar-will-become-countrys-ev-capital-fadnavis/2922163</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/tech/information-tech/maharashtra-govt-to-strengthen-it-dept-to-enhance-delivery-of-services-fadnavis/articleshow/124049221.cms</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir/2916686</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/congress-slams-cm-fadnavis-over-shivaji-posters-pasted-in-unhygienic-surroundings-near-prabhadevi-railway-station-in-mumbai/articleshow/123948554.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/chhatrapati-sambhajinagar-will-become-countrys-ev-capital-fadnavis/2922163</t>
+          <t>https://m.economictimes.com/industry/indl-goods/svs/steel/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/articleshow/123999573.cms</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/infrastructure/pm-modi-to-inaugurate-mumbai-metro-3-on-september-30-says-devendra-fadnavis-19677024.htm</t>
+          <t>https://www.ptinews.com/story/national/fadnavis-leads-maharashtra-in-greeting-pm-modi-on-birthday-calls-him-global-statesman-inspiration/2922857</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/goa/mi-punha-yeyin-il-be-back-again-devendra-fadanvis-is-the-next-chief-minister-of-maharashtra/13454/</t>
+          <t>https://www.cnbctv18.com/infrastructure/pm-modi-to-inaugurate-mumbai-metro-3-on-september-30-says-devendra-fadnavis-19677024.htm</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
+          <t>https://money.rediff.com/news/market/fadnavis-streamline-industry-approvals-in-maharashtra/33958120250919</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level--fadnavis/2934307</t>
+          <t>https://www.heraldgoa.in/globe-nation/6-organisations-active-in-maharashtra-already-banned-in-some-other-states-chief-minister-devendra-fadnavis-on-security-bill/4671/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/ev-capital-fadnavis-on-chhatrapati-sambhajinagar/33804020250917</t>
+          <t>https://www.business-standard.com/india-news/maratha-quota-row-obc-other-groups-turn-up-heat-cm-urges-restraint-125091500006_1.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-fadnavis-3732054</t>
+          <t>https://www.newsonair.gov.in/hyderabad-liberation-day-celebrated-with-flag-hoisting-by-maharashtra-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/sambhajinagar-becoming-ev-capital-of-country-fadnavis/articleshow/123952619.cms</t>
+          <t>https://money.rediff.com/news/market/ev-capital-fadnavis-on-chhatrapati-sambhajinagar/33804020250917</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-govt-dept-websites-landing-pages-to-be-in-marathi-101757962665589.html</t>
+          <t>https://www.aninews.in/news/entertainment/out-of-box/hindi-films-fail-to-depict-the-true-heroism-of-mumbai-police-says-maharashtra-cm-fadnavis20250920135931</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://bioenergytimes.com/maharashtra-to-launch-comprehensive-bamboo-industry-policy-cm-fadnavis-announces/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168537</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom41-mh-police-ld-fadnavis.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-sign-mous-to-boost-steel-production-3736498</t>
         </is>
       </c>
     </row>
@@ -781,14 +781,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/indl-goods/svs/steel/maharashtra-to-play-leading-role-in-green-steel-manufacturing-cm-fadnavis/articleshow/123999573.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-to-storm-fadnavis-home-turf-rally-obcs-on-sept-18/articleshow/123929254.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/hyundai-maharashtra-discuss-new-investments-jobs-571636</t>
+          <t>https://www.aninews.in/news/national/general-news/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm20250919232605</t>
         </is>
       </c>
     </row>
@@ -802,1666 +802,1666 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-cabinet-clears-avgc-xr-policy-draws-up-a-25-year-roadmap-101758043978392.html</t>
+          <t>https://www.ptinews.com/story/national/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal/2926755</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/reduce-number-of-permissions-to-set-up-industries--speed-up-approval-time--fadnavis-to-officials/2930550</t>
+          <t>https://lokmat.news18.com/short-videos/trending/gopichand-padalkar-news-first-reaction-after-cm-devendra-fadnavis-call-jayant-patil-n18s-1075363.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/out-of-box/hindi-films-fail-to-depict-the-true-heroism-of-mumbai-police-says-maharashtra-cm-fadnavis20250920135931</t>
+          <t>https://lokmat.news18.com/short-videos/trending/sharad-pawar-on-devendra-fadnavis-rain-damage-saying-devabhau-pawar-s-big-demand-to-cm-n18s-1075195.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/obc-other-groups-turn-up-heat-over-maratha-quota-gr-cm-cautions-against-politics-of-extreme/2915442</t>
+          <t>https://www.ptinews.com/editor-detail/gst-reforms-to-speed-up-india%E2%80%99s-economic-growth--says-fadnavis/2936669</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-govt-to-work-towards-developing-bamboo-as-sustainable-crop-fadnavis/2927696</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-govt-dept-websites-landing-pages-to-be-in-marathi-101757962665589.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/gopichand-padalkar-news-first-reaction-after-cm-devendra-fadnavis-call-jayant-patil-n18s-1075363.html</t>
+          <t>https://lokmat.news18.com/short-videos/trending/bajrang-sonawane-s-big-request-to-cm-devendra-fadnavis-directly-from-the-stage-n18s-1075017.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maratha-quota-row-obc-other-groups-turn-up-heat-cm-urges-restraint-125091500006_1.html</t>
+          <t>https://zeenews.india.com/india/residential-complex-for-muslims-in-mumbai-nhrc-issues-notice-to-fadnavis-govt-bjp-2957165.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maharashtra--all-files-to-be-vetted-by-shinde-before-being-sent-to-cm-fadnavis/2429371</t>
+          <t>https://www.aninews.in/news/national/general-news/lifting-last-person-and-bringing-them-to-mainstream-development-reflects-pm-modis-working-approach-maharashtra-cm-fadnavis20250917223421</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Western-Naval-Command-chief-meets-Maharashtra-CM-discusses-maritime-security-situation/2933686</t>
+          <t>https://www.aninews.in/news/national/general-news/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address20250921195926</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-sign-mous-to-boost-steel-production-3736498</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/obcs-disrupt-cm-s-speech-holds-huge-rally-in-hingoli-101758137116445.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/acharya-devvrat-takes-oath-as-maharashtra-governor-101757915941969.html</t>
+          <t>https://www.aninews.in/news/national/general-news/mumbai-union-minister-pralhad-joshi-maharashtra-cm-fadnavis-inaugurate-steel-mahakumbh20250919211944</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/not-a-matter-of-vote-chori-but-rahul-gandhi-suffering-a-brain-theft-maharashtra-cm20250919232605</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-cabinet-clears-avgc-xr-policy-draws-up-a-25-year-roadmap-101758043978392.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-leads-maharashtra-in-greeting-pm-modi-on-birthday-calls-him-global-statesman-inspiration/2922857</t>
+          <t>https://zeenews.india.com/india/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-india-s-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt-2963047.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hyderabad-liberation-day-celebrated-with-flag-hoisting-by-maharashtra-cm-devendra-fadnavis/</t>
+          <t>https://www.newsghana.com.gh/india-gem-show-opens-with-%E2%82%B932000-crore-business-target/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-to-storm-fadnavis-home-turf-rally-obcs-on-sept-18/articleshow/123929254.cms</t>
+          <t>https://www.business-standard.com/industry/news/maharashtra-signs-mous-worth-80-962-cr-for-industrial-projects-40k-jobs-125091900956_1.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/fadnavis-calls-for-inclusive-cancer-care-policy-for-maharashtra/2917226</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-mandates-e-kyc-for-ladki-bahin-beneficiaries-sets-deadline-125091900196_1.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal/2926755</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-fadnavis-and-the-obcs-101757877151905.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-strengthen-it-department-for-better-citizen-services-cm-fadnavis-23595276</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-fadnavis-defends-obc-reservation-policy-says-no-threat-to-communitys-rights/articleshow/123886921.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/bajrang-sonawane-s-big-request-to-cm-devendra-fadnavis-directly-from-the-stage-n18s-1075017.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/sharad-pawar-on-devendra-fadnavis-rain-damage-saying-devabhau-pawar-s-big-demand-to-cm-n18s-1075195.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-pm-modi-a-visionary-global-statesman-on-his-75th-birthday-23594462</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/marathwada-got--21-000-cr-investment-in-past-10-years--fadnavis-1758179070896</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-devendra-fadnavis-23594442</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/gst-reforms-to-speed-up-india%E2%80%99s-economic-growth--says-fadnavis/2936669</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-for-tech-driven-policing-flags-ai-and-cybercrime-challenges-23594968</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom28-mh-police-fadnavis.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/20/major-push-to-industry.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/football-legend-lionel-messi-to-visit-mumbai-in-december-will-train-with-young-footballers-cm-fadnavis-23595113</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-cm-fadnavis-9322871</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modi-allocated-rs-21000-crore-for-rail-lines-in-marathwada-claims-cm-devendra-fadnavis-23594480</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-govt-will-create-corpus-fund-to-cover-treatments-costing-over-rs-5-lakh-fadnavis/2917336</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-lead-in-green-steel-manufacturing-cm-devendra-fadnavis-23594846?button=next</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382/5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/lifting-last-person-and-bringing-them-to-mainstream-development-reflects-pm-modis-working-approach-maharashtra-cm-fadnavis20250917223421</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mlas-remarks-about-ncp-sp-leader-23594821</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Oppn-ruling-parties-spar-over-Rahul-s-fresh-vote-chori-charges;-Cong-seeks-Fadnavis-resignation/2927028</t>
+          <t>https://www.mid-day.com/news/india-news/article/shiv-sena-ubt-targets-maharashtra-cm-devendra-for-not-unveiling-swami-ramanand-tirtha-statue-23594500</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address20250921195926</t>
+          <t>https://www.mid-day.com/news/india-news/article/cm-fadnavis-says-chhatrapati-sambhajinagar-will-become-country-s-ev-capital-23594430</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://mumbaimirror.indiatimes.com/mumbai/bjp-mlas-remarks-on-ncp-sp-leader-triggers-row/articleshow/124004724.html</t>
+          <t>https://www.socialnews.xyz/2025/09/15/mumbai-acharya-devvrat-sworn-in-as-maharashtra-governor-gallery/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/oppn-ruling-parties-spar-over-rahuls-fresh-vote-chori-charges-cong-seeks-fadnavis-resignation/2927511</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal-23594647</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/maharashtra-signs-mous-worth-80-962-cr-for-industrial-projects-40k-jobs-125091900956_1.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-plans-cancer-care-units-in-every-district-23594213</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/fadnavis-calls-rahul-gandhi-urban-naxal-then-what-about-india-s-foreign-policy-leaning-towards-maoism-asks-shiv-sena-ubt-2963047.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-launch-skill-courses-to-boost-manpower-for-gems-and-jewellery-sector-devendra-fadnavis-23594288</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/residential-complex-for-muslims-in-mumbai-nhrc-issues-notice-to-fadnavis-govt-bjp-2957165.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/mumbai-union-minister-pralhad-joshi-maharashtra-cm-fadnavis-inaugurate-steel-mahakumbh20250919211944</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cabinet-clears-animation-policy-2025-and-other-key-projects-23594299</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/states/maharashtra-scraps-na-land-nod-for-msmes/56828</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-announces-pod-taxi-plan-to-ease-traffic-congestion-in-mumbai-23595266</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/trial-run-held-for-metro-lines-4-and-4a-in-thane-project-to-cut-travel-time-significantly/2937833</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-23594141</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/rahul-gandhis-mind-has-been-stolen-maharashtra-cm-devendra-fadnavis-on-congress-mps-vote-theft-claims-a525/</t>
+          <t>https://www.mid-day.com/news/india-news/article/maratha-quota-row-deepens-in-maharashtra-as-obc-sc-st-groups-protest-cm-fadnavis-urges-calm-23594029</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-strengthen-it-department-for-better-citizen-services-cm-fadnavis-23595276</t>
+          <t>https://www.punekarnews.in/cm-devendra-fadnavis-dcm-ajit-pawar-to-inaugurate-amalner-beed-new-railway-line-in-pune-division-on-september-17/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
+          <t>https://news.abplive.com/cities/maharashtra-mahayuti-mva-war-of-words-erupts-rahul-gandhi-vote-theft-congress-demands-devendra-fadnavis-resignation-1801046</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-pm-modi-a-visionary-global-statesman-on-his-75th-birthday-23594462</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modi-allocated-rs-21000-crore-for-rail-lines-in-marathwada-claims-cm-devendra-fadnavis-23594480</t>
+          <t>https://www.punekarnews.in/bureaucratic-delays-stall-pune-khadki-cantonment-merger-despite-maharashtra-cms-nod/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/football-legend-lionel-messi-to-visit-mumbai-in-december-will-train-with-young-footballers-cm-fadnavis-23595113</t>
+          <t>https://www.punekarnews.in/cm-fadnavis-flags-poor-road-conditions-in-pune-raises-alarm-over-potholes/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ladki-bahin-scheme-wont-be-scrapped-govt-committed-to-empowering-women-devendra-fadnavis-23594442</t>
+          <t>https://www.socialnews.xyz/2025/09/21/namo-yuva-run-in-mumbai-gallery/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382/2</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-shocked-bjp-leader-haresh-keni-joins-congress-panvel-municipal-election-maharashtra-politics/articleshow/124016475.cms</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-reacted-on-lop-rahul-gandhi-over-vote-theft-allegations-ann-3014991</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-devendra-fadnavis-calls-for-tech-driven-policing-flags-ai-and-cybercrime-challenges-23594968</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-sharad-pawar-devendra-fadnavis-engaged-in-a-war-of-words-over-maratha-obc-reservation-ws-l-9622419.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-lead-in-green-steel-manufacturing-cm-devendra-fadnavis-23594846</t>
+          <t>https://www.amarujala.com/india-news/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-hindi-news-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/pm-modis-address-to-nation-maharashtra-cm-fadnavis-calls-gst-reforms-historic-step-praises-pm-modi-23595114</t>
+          <t>https://www.livehindustan.com/maharashtra/sharad-pawar-calls-to-devendra-fadnavis-on-bjp-mla-gopichand-statement-201758271903306.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sharad-pawar-calls-cm-fadnavis-to-disapprove-of-bjp-mlas-remarks-about-ncp-sp-leader-23594821</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%B6-%E0%A4%B5-%E0%A4%9C-%E0%A4%95-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1MCKQS</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharastra-cm-fadnavis-pushes-for-faster-industrial-approvals-ai-based-reforms-to-boost-investments-23594849</t>
+          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-congratulates-indian-women-hockey-team-for-bronze-medal-amid-india-vs-pakistan-asia-cup-3012731</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhi-speaks-like-an-urban-maoist-says-maharashtra-cm-fadnavis-on-congress-leaders-gen-z-post-23594827</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-trouble-for-devendra-fadnavis-obc-banjara-protest-against-maratha-reservation-maharashtra-politics-ws-ln-9621475.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-shared-story-how-he-impressed-form-pm-narendra-modi-ahead-of-75th-birthday-rss-nagar-visit-know-all/articleshow/123913706.cms</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633546-streamlining-success-maharashtras-push-for-rapid-industrial-approvals</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-chief-minister-devendra-fadnavis-on-mumbai-pod-taxi-services-ann-3016944</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/cm-fadnavis-says-chhatrapati-sambhajinagar-will-become-country-s-ev-capital-23594430?button=next</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-big-attack-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava-bmc-election/articleshow/123926944.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-must-resign-after-rahul-gandhi-exposed-vote-theft-in-maharashtra-sapkal-23594647</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-cm-devendra-fadnavis-wishi-pm-narendra-modi-on-75th-birthday-mumbai-3014251</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/condition-about-obtaining-non-agricultural-land-license-should-be-removed-msmes-cm-fadnavis</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-devendra-fadnavis-compared-rahul-gandhi-to-hitlers-minister-saying-rahul-gandhis-hydrogen-bomb-is-a-dud/articleshow/123991146.cms</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-announces-pod-taxi-plan-to-ease-traffic-congestion-in-mumbai-23595266</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-nationalist-congress-party-ncp-president-ajit-pawar-cm-devendra-fadnavis-nitin-gadkari-maharashtra-local-poll-vidarbha-politics-9642156.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/maharashtra-mahayuti-mva-war-of-words-erupts-rahul-gandhi-vote-theft-congress-demands-devendra-fadnavis-resignation-1801046</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-launched-various-csr-projects-of-hyundai-motor-india-ltd-in-mumbai-meeting-with-md-unsoo-kim-3013038</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-government-constituted-a-ministerial-committee-for-simhastha-mahakumbh-2027-chhagan-bhujbal-named-3015468</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/cm-devendra-fadnavis-dcm-ajit-pawar-to-inaugurate-amalner-beed-new-railway-line-in-pune-division-on-september-17/</t>
+          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-shiv-sena-ubt-responds-to-cm-devendra-fadnavis-song-ahead-bmc-election-2025-ann-3014169</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633401-maharashtras-bold-step-towards-a-greener-steel-future</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-maharashtra-cm-reaction-on-pm-modi-address-to-nation-on-gst-reforms-3016450</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar-10478970</t>
+          <t>https://www.punjabkesari.com/india-news/maharashtra-cm-devendra-fadnavis-inaugurated-the-amalner-beed-railway-line-in-beed/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/cm-fadnavis-flags-poor-road-conditions-in-pune-raises-alarm-over-potholes/</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/cm-fadnavis-joins-7000-people-in-namo-yuva-run-in-mumbai/articleshow/124030814.cms</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/bureaucratic-delays-stall-pune-khadki-cantonment-merger-despite-maharashtra-cms-nod/</t>
+          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/devendra-fadnavis-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane-7123779.html</t>
+          <t>https://www.abplive.com/states/maharashtra/beed-amalner-railway-line-inauguration-by-maharashtra-cm-devendra-fadnavis-3014515</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-solapur-air-service-will-begin-from-15th-october-2025-cm-devendra-fadnavis-on-flight-service-3016029</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-cm-fadnavis</t>
+          <t>https://www.tv9hindi.com/videos/maharashtras-development-under-pm-modi-fadnavis-highlights-key-projects-3485056.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-shocked-bjp-leader-haresh-keni-joins-congress-panvel-municipal-election-maharashtra-politics/articleshow/124016475.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-maharashtra-cm-on-trial-run-for-phase-i-of-metro-lines-4-and-4a-in-thane-also-attack-on-mva-3016842</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-government-constituted-a-ministerial-committee-for-simhastha-mahakumbh-2027-chhagan-bhujbal-named-3015468</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-attacks-rahul-gandhi-accuses-him-of-being-urban-naxal-saying-his-brain-stolen/articleshow/123998386.cms</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-sharad-pawar-devendra-fadnavis-engaged-in-a-war-of-words-over-maratha-obc-reservation-ws-l-9622419.html</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-first-underground-metro-from-cuffe-parade-pm-narendra-modi-inugrate-cm-devendra-fadnavis-maharashtra-mmrc-3013836</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AB-%E0%A4%B2%E0%A5%8D%E0%A4%AE-%E0%A4%9B-%E0%A4%B5-%E0%A4%95-%E0%A4%A4-%E0%A4%B0-%E0%A4%AB-%E0%A4%87%E0%A4%A4-%E0%A4%B9-%E0%A4%B8%E0%A4%95-%E0%A4%B0-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%89%E0%A4%A0-%E0%A4%8F-%E0%A4%B8%E0%A4%B5-%E0%A4%B2/ar-AA1AjRCP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-baps-akshardham-temple-goyal-fadnavis-wish-mahant-swamiji-maharaj-on-92nd-birthday-9628582.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-congratulates-indian-women-hockey-team-for-bronze-medal-amid-india-vs-pakistan-asia-cup-3012731</t>
+          <t>https://www.amarujala.com/india-news/fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-big-attack-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava-bmc-election/articleshow/123926944.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-says-bala-saheb-thackeray-was-a-brand-but-uddhav-thackeray-cheated-with-bjp-ann-3013935</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%B6-%E0%A4%B5-%E0%A4%9C-%E0%A4%95-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%A6-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1MCKQS</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-fadnavis-announced-new-flight-between-solapur-to-mumbai-and-bengaluru-flight-from-15-october-know-all-details/articleshow/124016070.cms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-reacted-on-lop-rahul-gandhi-over-vote-theft-allegations-ann-3014991</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-sharad-pawar-warn-devendra-fadnavis-over-farmers-suicide-said-look-what-happened-in-nepal-2025-09-16-1162916</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/cm-devendra-fadnavis-compared-rahul-gandhi-to-hitlers-minister-saying-rahul-gandhis-hydrogen-bomb-is-a-dud/articleshow/123991146.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-news-congress-targets-devendra-fadnavis-government-over-broken-roads-in-mumbai-ann-3016304</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
+          <t>https://www.abplive.com/states/maharashtra/sharad-pawar-phone-call-to-cm-devendra-fadnavis-on-bjp-mla-gopichand-padalkar-remarks-3015443</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-chief-minister-devendra-fadnavis-on-mumbai-pod-taxi-services-ann-3016944</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-devendra-fadnavis-shared-story-how-he-impressed-form-pm-narendra-modi-ahead-of-75th-birthday-rss-nagar-visit-know-all/articleshow/123913706.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-cm-devendra-fadnavis-wishi-pm-narendra-modi-on-75th-birthday-mumbai-3014251</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-s-politics-rises-due-to-rahul-s-claims-on-vote-theft-congress-says-fadnavis-should-resign-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-shiv-sena-ubt-responds-to-cm-devendra-fadnavis-song-ahead-bmc-election-2025-ann-3014169</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/intensifying-verbal-conflict-in-maharashtra-pawars-complaint-to-the-cm-reprimanding-the-legislator-ytvd-2337563-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/cm-devendra-fadnavis-says-bala-saheb-thackeray-was-a-brand-but-uddhav-thackeray-cheated-with-bjp-ann-3013935</t>
+          <t>https://www.livehindustan.com/maharashtra/obc-activists-show-black-flags-to-cm-devendra-fadnavis-attempt-self-immolation-in-front-of-deputy-cm-ajit-pawar-convoy-201758158508899.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-trouble-for-devendra-fadnavis-obc-banjara-protest-against-maratha-reservation-maharashtra-politics-ws-ln-9621475.html</t>
+          <t>https://ndtv.in/maharashtra-news/we-will-ensure-that-not-even-a-single-fake-person-is-included-in-obc-cm-fadnavis-big-announcement-9277679</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/beed-amalner-railway-line-inauguration-by-maharashtra-cm-devendra-fadnavis-3014515</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/pod-taxis-to-run-in-mumbai-fadnavis-announces-11728</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/india-news/maharashtra-cm-devendra-fadnavis-inaugurated-the-amalner-beed-railway-line-in-beed/</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/ladki-behen-yojana-will-not-be-discontinued-committed-to-empowering-women-11648</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/rahul-gandhi-speaks-like-an-urban-maoist-fadnavis-on-his-gen-z-post-hindi-news-2025-09-19</t>
+          <t>https://www.amarujala.com/india-news/bjp-mla-s-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-maharashtra-cm-reaction-on-pm-modi-address-to-nation-on-gst-reforms-3016450</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-mla-gopichand-padalkar-statement-sparked-uproar-in-maharashtra-devendra-fadnavis-calling-for-restraint/articleshow/124002748.cms</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/cm-fadnavis-joins-7000-people-in-namo-yuva-run-in-mumbai/articleshow/124030814.cms</t>
+          <t>https://hindi.theprint.in/india/gst-reforms-will-accelerate-indias-economic-growth-fadnavis/871739/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-maharashtra-cm-on-trial-run-for-phase-i-of-metro-lines-4-and-4a-in-thane-also-attack-on-mva-3016842</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169178</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-solapur-air-service-will-begin-from-15th-october-2025-cm-devendra-fadnavis-on-flight-service-3016029</t>
+          <t>https://mandalnews.com/amravati/dhangar-community-should-get-st-certificate-otherwise-hunger-strike/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/devendra-fadnavis-attacks-rahul-gandhi-accuses-him-of-being-urban-naxal-saying-his-brain-stolen/articleshow/123998386.cms</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/metro-4-corridor-trial-run-starts-today-ghodbunder-road-commute-to-be-easier/articleshow/124031334.cms</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-nationalist-congress-party-ncp-president-ajit-pawar-cm-devendra-fadnavis-nitin-gadkari-maharashtra-local-poll-vidarbha-politics-9642156.html</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/fadnavis-promises-rehabilitation-plan-for-elphinstone-residents-11705</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-fadnavis-announced-new-flight-between-solapur-to-mumbai-and-bengaluru-flight-from-15-october-know-all-details/articleshow/124016070.cms</t>
+          <t>https://navbharattimes.indiatimes.com/lifestyle/fashion/maharashtra-cm-wife-amruta-fadnavis-beautiful-photos-in-peach-banarasi-tissue-silk-saree-at-screening/articleshow/124040076.cms</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/sharad-pawar-calls-to-devendra-fadnavis-on-bjp-mla-gopichand-statement-201758271903306.html</t>
+          <t>https://www.abplive.com/states/maharashtra/price-limit-on-government-vehicles-for-officials-increased-no-limit-for-governor-and-cm-ann-3014779</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-baps-akshardham-temple-goyal-fadnavis-wish-mahant-swamiji-maharaj-on-92nd-birthday-9628582.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/maharashtra-govt-issued-kunbi-certificates-in-five-marathwada-districts-on-liberation-day/articleshow/123961774.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/business/mumbai-financial-capital-chhatrapati-sambhajinagar-become-ev-electric-vehicle-capital-maharashtra-cm-devendra-fadnavis-said-14000-people-get-employment-latur-coach-factory-b507/</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/mumbai-metro-ameet-satam-controversial-statement-bmc-election-frvd-2335000-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/fadnavis-govt-apathetic-towards-farmers-woes-claims-pawar-warns-of-intensifying-stir-2025-09-15</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-sharad-pawar-warn-devendra-fadnavis-over-farmers-suicide-said-look-what-happened-in-nepal-2025-09-16-1162916</t>
+          <t>https://www.amarujala.com/india-news/51-students-from-maharashtra-will-visit-nasa-students-who-win-the-science-competition-will-get-a-chance-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-and-deputy-cm-shinde-flagged-off-trial-run-of-thane-metro-line-4-from-gaimukh-to-cadbury-11720</t>
+          <t>https://mandalnews.com/amravati/banjara-community-should-be-included-in-st-category/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/maharashtra-to-launch-gems-jewellery-course-says-cm-devendra-fadnavis-hindi-news-hin25091603873</t>
+          <t>https://zeenews.india.com/hindi/india/milk-shower-to-aurangzeb-poster-in-maharashtra-police-took-action/2922391</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ima-doctors-threaten-to-go-on-24-hour-strike-in-maharashtra-including-mumbai-from-8-am-on-sep-18-devendra-cm-fadnavis-know-all/articleshow/123947629.cms</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-news-congress-targets-devendra-fadnavis-government-over-broken-roads-in-mumbai-ann-3016304</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-govt-asks-ministries-depts-to-have-opening-page-of-websites-in-marathi-2025-09-15</t>
+          <t>https://navbharattimes.indiatimes.com/india/brahmin-faca-may-be-next-president-of-bjp-vp-poll-changed-maths-names-of-nadda-dinesh-sharma-and-fadnavis/articleshow/123935176.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AC-%E0%A4%A1-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%85%E0%A4%AE%E0%A4%B2%E0%A4%A8%E0%A5%87%E0%A4%B0-%E0%A4%AC-%E0%A4%A1-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A4%B5%E0%A5%87-%E0%A4%B2-%E0%A4%87%E0%A4%A8-%E0%A4%95-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%98-%E0%A4%9F%E0%A4%A8-cm-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%96-%E0%A4%88-%E0%A4%B9%E0%A4%B0-%E0%A4%9D%E0%A4%82%E0%A4%A1/ar-AA1MMIJZ</t>
+          <t>https://www.bhaskarhindi.com/state/maharashtra/maharashtra-news-fadnavis-government-bjp-government-government-vehicles-cm-vehicles-governor-vehicles-gst-vehicle-tax-registration-fee-1188430</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-s-politics-rises-due-to-rahul-s-claims-on-vote-theft-congress-says-fadnavis-should-resign-2025-09-18</t>
+          <t>https://24city.news/when-devendra-fadnavis-yaad-was-surprised-to-hear-this-of-narendra-modi-his-first-meeting/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/fadnavis-promises-rehabilitation-plan-for-elphinstone-residents-11705</t>
+          <t>https://hindi.latestly.com/india/will-maharashtras-ladki-bahin-yojana-be-scrapped-cm-devendra-fadnavis-breaks-silence-on-rumours-2756744.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/maharashtra-cm-devendra-fadnavis-in-new-tension-over-quota-clash-maratha-vs-obc-banjara-vs-tribal-community-politics-201757910651491.html</t>
+          <t>https://www.hindisaamana.com/former-mla-exposes-fadnaviss-transparent-work/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/story/sharad-pawar-ncp-sp-responded-to-bjp-devabhau-campaign-with-deva-tuch-saang-aid-ntc-rpti-2334011-2025-09-15</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
+          <t>https://navbharatlive.com/maharashtra/wardha/teachers-strike-against-tet-decision-wrote-letter-to-cm-in-blood-ministers-degrees-1356071.html</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-mla-gopichand-padalkar-statement-sparked-uproar-in-maharashtra-devendra-fadnavis-calling-for-restraint/articleshow/124002748.cms</t>
+          <t>https://hindi.latestly.com/quickly/india/devendra-fadnavis-on-pm-modi-pm-modi-is-a-leader-who-prefers-simplicity-devendra-fadnavis-shared-a-special-video-2755431.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/obc-activists-show-black-flags-to-cm-devendra-fadnavis-attempt-self-immolation-in-front-of-deputy-cm-ajit-pawar-convoy-201758158508899.html</t>
+          <t>https://www.ucnnews.live/politics/acharya-devvrat-took-oath-as-the-new-governor-of-maharashtra-chief-justice-of-bombay-high-court-administered-the-oath-1757924050723</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/bjp-mla-s-remarks-on-ncp-sp-leader-triggers-row-pawar-registers-objection-in-phone-call-to-cm-2025-09-19</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/sharad-pawar-raging-on-the-issue-of-maharashtra-farmers/article-105258</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/gst-reforms-will-accelerate-indias-economic-growth-fadnavis/871739/</t>
+          <t>https://www.hindisaamana.com/the-public-has-no-food-there-is-no-money-in-the-treasury-the-chief-minister-has-a-bed-worth-rs-20-lakh/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
+          <t>https://www.kisantak.in/news/trending/story/sharad-pawar-led-an-akrosh-morcha-in-nashik-demands-complete-loan-waiver-for-farmers-swm-1278008-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/metro-4-corridor-trial-run-starts-today-ghodbunder-road-commute-to-be-easier/articleshow/124031334.cms</t>
+          <t>https://raftaar.in/news/national/maharashtra-cm-devendra-fadnavis-took-a-dig-at-the-opposition-especially-the-shiv-sena-ubt-faction-by-singing-a-song</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/meena-tai-thackeray-memorial-vandalism-bmc-elections-frvd-2335927-2025-09-18</t>
+          <t>https://rashtrabaan.in/sharad-pawar-angry-bjp-mla-statement-called-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/rahul-gandhi-speaks-like-an-urban-naxal-fadnavis/870800/</t>
+          <t>https://www.ibc24.in/business/chhatrapati-sambhajinagar-will-become-the-electric-vehicle-capital-of-the-country-fadnavis-3255721.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/lifestyle/fashion/maharashtra-cm-wife-amruta-fadnavis-beautiful-photos-in-peach-banarasi-tissue-silk-saree-at-screening/articleshow/124040076.cms</t>
+          <t>https://www.ibc24.in/maharashtra/maharashtra-cm-fadnavis-should-resign-after-rahul-gandhis-revelation-on-vote-theft-3257842.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/dhangar-community-should-get-st-certificate-otherwise-hunger-strike/</t>
+          <t>https://indiagroundreport.com/mumbai-fadnavis-government-took-8-important-decisions-including-doubling-the-allowance-of-students/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/namo-yuva-run-organised-across-the-country-to-mark-the-75th-birthday-of-prime-minister-modi-11704</t>
+          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/pune/maharashtra-govt-issued-kunbi-certificates-in-five-marathwada-districts-on-liberation-day/articleshow/123961774.cms</t>
+          <t>https://hindi.gyanhigyan.com/auto/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A4%B0%E0%A4%BF%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%A8%E0%A4%BE%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-21000-%E0%A4%95%E0%A4%B0%E0%A5%8B%E0%A4%A1%E0%A4%BC-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A4%BE/cid17430694.htm</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
+          <t>https://www.punjabnewsexpress.com/national/news/saw-a-leader-who-valued-simplicity-over-luxury-devendra-fadnavis-recalls-first-meet-with-pm-modi-297681</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/51-students-from-maharashtra-will-visit-nasa-students-who-win-the-science-competition-will-get-a-chance-2025-09-22</t>
+          <t>https://www.ptinews.com/story/national/gst-reforms-to-speed-up-indias-economic-growth-says-fadnavis/2936669</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/sambhajinagar-becoming-ev-capital-of-country-fadnavis/articleshow/123952619.cms</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/uddhav-thackeray-mother-meenatai-statue-colour-thrown-accused-upendra-pawaskar-held-19954266</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/banjara-community-should-be-included-in-st-category/</t>
+          <t>https://www.ndtv.com/india-news/mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-cm-fadnavis-9322871</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/opposition-and-ruling-parties-clash-over-rahuls-vote-stealing-allegations-demand-for-fadnavis-resignation/870465/</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/awakened-feeling-of-patriotism-in-every-person-says-amruta-fadnavis-after-watching-mera-desh-pehle-the-untold-story-of-shri-narendra-modi20250921230151</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/brahmin-faca-may-be-next-president-of-bjp-vp-poll-changed-maths-names-of-nadda-dinesh-sharma-and-fadnavis/articleshow/123935176.cms</t>
+          <t>https://www.projectsmonitor.com/daily-wire/aiifa-steelex-2025-maharashtra-chief-minister-devendra-fadnavis-and-union-minister-pralhad-joshi-inaugurate-the-steel-mahakumbh/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/ima-doctors-threaten-to-go-on-24-hour-strike-in-maharashtra-including-mumbai-from-8-am-on-sep-18-devendra-cm-fadnavis-know-all/articleshow/123947629.cms</t>
+          <t>https://www.financialexpress.com/india-news/maharashtra-to-appoint-new-advocate-general-as-birendra-saraf-resigns-citing-personal-reasons/3979732/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/maharashtra/maharashtra-news-fadnavis-government-bjp-government-government-vehicles-cm-vehicles-governor-vehicles-gst-vehicle-tax-registration-fee-1188430</t>
+          <t>https://www.mid-day.com/news/india-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-hoists-tricolour-on-marathwada-liberation-day-107384</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://24city.news/when-devendra-fadnavis-yaad-was-surprised-to-hear-this-of-narendra-modi-his-first-meeting/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-lead-in-green-steel-manufacturing-cm-devendra-fadnavis-23594846</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D-13/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharastra-cm-fadnavis-pushes-for-faster-industrial-approvals-ai-based-reforms-to-boost-investments-23594849</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhi-speaks-like-an-urban-maoist-says-maharashtra-cm-fadnavis-on-congress-leaders-gen-z-post-23594827</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/protests-erupt-in-maharashtra-over-reservation-issue-obc-activists-show-black-flags-to-fadnavis-attempt-suicide/</t>
+          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/former-mla-exposes-fadnaviss-transparent-work/</t>
+          <t>https://thenewsmill.com/2025/09/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-public-has-no-food-there-is-no-money-in-the-treasury-the-chief-minister-has-a-bed-worth-rs-20-lakh/</t>
+          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.raftaar.in/news/national/maharashtra-cm-devendra-fadnavis-took-a-dig-at-the-opposition-especially-the-shiv-sena-ubt-faction-by-singing-a-song</t>
+          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/rahul-gandhi-allegations-vote-theft-spark-debate-in-maharashtra-demands-fadnavis-resignation</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/maharashtra-cm-devendra-fadnavis-talk-on-obc-reservation/articleshow/123889715.cms</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/sharad-pawar-led-an-akrosh-morcha-in-nashik-demands-complete-loan-waiver-for-farmers-swm-1278008-2025-09-15</t>
+          <t>https://marathi.abplive.com/news/mumbai/devendra-fadnavis-slams-raj-uddhav-thackeray-mumbai-bmc-election-narendra-modi-brand-maharashtra-politics-1384645</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://rashtrabaan.in/sharad-pawar-angry-bjp-mla-statement-called-cm-fadnavis/</t>
+          <t>http://marathi.factcrescendo.com/old-altered-video-viral-as-cm-fadnavis-did-not-believe-in-indian-constitution-democracy/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/chhatrapati-sambhajinagar-will-become-the-electric-vehicle-capital-of-the-country-fadnavis-3255721.html</t>
+          <t>https://marathi.ndtv.com/cities/pm-modi-birthday-cm-fadnavis-reminisces-share-experienc-of-first-meeting-with-pm-modi-9291188</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-fadnavis-government-took-8-important-decisions-including-doubling-the-allowance-of-students/</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://up18news.com/free-solar-power-to-every-farmer-by-2026-cm-devendra-fadnavis/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/devendra-fadnavis-claim-that-milind-narvekar-phone-call-him-and-said-uddhav-thackeray-was-upset/articleshow/123927047.cms</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
+          <t>https://marathi.abplive.com/news/politics/sharad-pawar-called-devendra-fadnavis-and-complained-about-gopichand-padalkar-jayant-patil-maharashtra-politics-marathi-news-1385183</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/using-technology-fearlessly-and-in-right-direction-can-take-policing-to-next-level-fadnavis/2934307</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/17/devendra-fadnavis-seva-pandharwada.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/pm-modi-allocated-rs-21000-crore-for-rail-lines-in-marathwada-claims-cm-devendra-fadnavis-23594480</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%B5-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97%E0%A4%B8-%E0%A4%A0-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1ME6vc</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-govt-signs-mou-with-cambridge-to-elevate-school-education-101758482430602.html</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava/articleshow/123926617.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/india-news/maharashtra-to-appoint-new-advocate-general-as-birendra-saraf-resigns-citing-personal-reasons/3979732/</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.projectsmonitor.com/daily-wire/aiifa-steelex-2025-maharashtra-chief-minister-devendra-fadnavis-and-union-minister-pralhad-joshi-inaugurate-the-steel-mahakumbh/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/devendra-fadnavis-slams-uddhav-and-raj-thackeray-over-thackeray-brand/articleshow/123927266.cms</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/nation/maharashtra-government-approves-policy-to-boost-digital-content-sector-1904215</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/cm-devendra-fadnavis-reaction-on-maratha-reservation-kunbi-certificates/articleshow/123993122.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/shiv-sena-ubt-targets-maharashtra-cm-devendra-for-not-unveiling-swami-ramanand-tirtha-statue-23594500</t>
+          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-inspects-nashik-and-surrounding-areas-in-the-backdrop-of-kumbh-mela-gives-important-instructions-local18-1483785.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-cm-fadnavis-promises-rehab-plan-for-elphinstone-residents-within-week-23595004?holi-breakingnews</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/19/maharashtra-will-be-number-one-in-the-green-steel-sector-chief-minister-devendra-fadnavis-iifa-2025-steel-maha.html</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/zero-tolerance-important-curb-drug-related-crimes-says-cm-fadnavis-454693</t>
+          <t>https://marathi.abplive.com/news/politics/devendra-fadnavis-has-advised-gopichand-padalkar-to-speak-carefully-jayant-patil-maharashtra-politics-1385209</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/metro-line-connecting-thane-mumbai-be-operational-2026-end-says-cm-fadnavis-455400</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackerays-bust-orders-probe/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/20/use-of-modern-technology-is-essential-for-combating-cyber-crimes-chief-minister-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-talk-on-sharad-pawar-phone-call-about-gopchand-padalkar-statement/articleshow/123994142.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/pune-news/maharashtra-cm-devendra-fadnavis-talk-on-obc-reservation/articleshow/123889715.cms</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-news-scj-81-5380824/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>http://marathi.factcrescendo.com/old-altered-video-viral-as-cm-fadnavis-did-not-believe-in-indian-constitution-democracy/</t>
+          <t>https://marathi.abplive.com/news/devendra-fadnavis-speech-at-chhatrapati-sambhajinagar-obc-activists-slogans-during-cm-speech-at-marathwada-mukti-sangram-din-program-marathi-news-1384714</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/pm-modi-birthday-cm-fadnavis-reminisces-share-experienc-of-first-meeting-with-pm-modi-9291188</t>
+          <t>https://prahaar.in/2025/09/18/brand-vs-brandy-war-of-words-between-fadnavis-thackeray-faction-politics-heats-up/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/cm-devendra-fadnavis-media-brief/941116</t>
+          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-attack-uddhav-thackeray-and-raj-thackeray-over-mumbai-mahapalika-bjp-vijay-melava-1481400.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/aurangabad/cm-devendra-fadnavis-said-announcements-made-for-marathwada-will-not-remain-on-paper-css-98-5378822/</t>
+          <t>https://maharashtratimes.com/maharashtra/chandrapur/shiv-sena-ubt-protest-in-chandrapur-over-place-of-banner-of-cm-devendra-fadnavis-and-chhatrapati-shivaji-maharaj/articleshow/124000637.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/cm-fadnavis-said-no-complaints-on-kunbi-caste-certification-under-hyderabad-gazette-assures-maratha-caste-certificate-pune-print-news-rds-00-5380078/</t>
+          <t>https://marathi.abplive.com/photo-gallery/sports/lionel-messi-gives-cm-devendra-fadnavis-a-special-gift-of-signed-footbal-will-also-come-to-mumbai-for-a-visit-1385826</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-meeting-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-8-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%B5-%E0%A4%97%E0%A5%87%E0%A4%AE-%E0%A4%82%E0%A4%97%E0%A4%B8-%E0%A4%A0-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1ME6vc</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/india-has-the-potential-to-become-a-global-leader-in-the-field-of-gems-and-jewellery-chief-minister-devendra-f.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/cm-fadnavis-fadnavis-started-dreaming-of-becoming-prime-minister-bjp-strongly-criticizes-sapkal-s-cl-997453</t>
+          <t>https://marathi.abplive.com/news/beed/devendra-fadnavis-beed-railway-inaguration-programme-train-dedicated-to-gopinath-munde-marathi-1384797</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/devendra-fadnavis-claim-that-milind-narvekar-phone-call-him-and-said-uddhav-thackeray-was-upset/articleshow/123927047.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/22/the-next-step-in-the-transport-service-is-pod-taxi-chief-minister-devendra-fadnavis-instructions-to-accelerate.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-for-giving-30-sara-projects-to-mohit-kamboj/921930/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/devendra-fadnavis-slams-uddhav-and-raj-thackeray-over-thackeray-brand/articleshow/123927266.cms</t>
+          <t>https://maharashtratimes.com/entertainment/entertainment-news/television-news/devendra-fadnavis-watch-maharashtrachi-hasya-jatra-says-samir-choughule-in-mhj-unplugged/articleshow/123995979.cms</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-government-likely-to-increase-to-2399-available-under-the-mahatma-jyotirao-phule-jan-arogya-yojana-zws-70-5375201/</t>
+          <t>https://marathi.abplive.com/news/politics/devendra-fadnavis-on-uddhav-thackeray-mumbai-municipal-corporation-will-have-a-mahayuti-mayor-write-it-down-fadnavis-sang-song-achha-sila-diya-tune-1384650</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/19/maharashtra-will-be-number-one-in-the-green-steel-sector-chief-minister-devendra-fadnavis-iifa-2025-steel-maha.html</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/thousands-of-rupees-were-laundered-during-the-corona-period-devendra-fadnavis-criticizes-thackeray/videoshow/123926314.cms</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/20/use-of-modern-technology-is-essential-for-combating-cyber-crimes-chief-minister-devendra-fadnavis.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-advice-to-gopichand-padalkar-after-receiving-a-call-from-sharad-pawar-for-making-objectionable-comments-on-jayant-patil/923124/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
+          <t>https://www.lokmat.com/maharashtra/cm-devendra-fadnavis-upset-over-controversial-statement-on-jayant-patil-by-bjp-mla-gopichand-padalkar-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/18/brand-vs-brandy-war-of-words-between-fadnavis-thackeray-faction-politics-heats-up/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava/amp_articleshow/123926617.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nashik/nashik-nationalist-party-sharad-pawar-group-aakrosh-morcha-mla-rohit-pawar-criticizes-chief-minister-devendra-fadnavis/articleshow/123919393.cms</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/chandrapur/shiv-sena-ubt-protest-in-chandrapur-over-place-of-banner-of-cm-devendra-fadnavis-and-chhatrapati-shivaji-maharaj/articleshow/124000637.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maratha-leader-manoj-jarange-patil-big-announcement-about-delhi-visit/articleshow/123945687.cms</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/21/mumbaikars-run-towards-a-drug-free-india-namo-yuva-run-receives-overwhelming-response-will-intoxicate-our-yout.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/why-cant-they-be-removed-from-the-unruly-gopichand-padalkar-anjali-damania-lashed-out-at-cm-devendra-fadnavis-1385414</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-kamboj-allegations-sakkale-accuses-devendra-fadnavis-of-pm-ambition-empowering-mohit-kamboj-and-giving-mumbai-to-adani-1385640</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/rohit-pawar-criticizes-on-chief-minister-devendra-fadnavis-on-the-issue-of-mumbai-municipal-corporation-elections-1384659</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/ncp-pune-city-president-prashant-jagtap-criticizes-bjp-mla-gopichand-padalkar/articleshow/123990567.cms</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-talk-on-sharad-pawar-phone-call-about-gopchand-padalkar-statement/articleshow/123994142.cms</t>
+          <t>https://www.mymahanagar.com/mahamumbai/uddhav-thackeray-in-power-the-mumbai-municipal-corporation-during-the-corona-period-committed-a-scam-in-the-body-bags-fadnavis-targets-thackeray/922227/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/sangli/gopichand-padalkar-clarification-on-his-statement-about-jayant-patil-after-receiving-a-call-from-cm-devendra-fadnavis/articleshow/123994231.cms</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-nashik-journalist-assault-cm-devendra-fadnavis-orders-strict-action-case-filing-process-initiated-against-assailants-1385488</t>
+          <t>https://news18marathi.com/agriculture/when-will-river-linking-project-in-marathwada-start-chief-minister-fadnavis-has-given-information-about-this-1482614.html</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/22/the-next-step-in-the-transport-service-is-pod-taxi-chief-minister-devendra-fadnavis-instructions-to-accelerate.html</t>
+          <t>https://maharashtratimes.com/maharashtra/navi-mumbai/bjp-leader-haresh-keni-joins-congress-shocks-devendra-fadnavis-prashant-thakur-ahead-of-panvel-municipal-election/articleshow/124013605.cms</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-for-giving-30-sara-projects-to-mohit-kamboj/921930/</t>
+          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-criticized-jayant-patil-in-dirty-words-devendra-fadnavis-phone-call-to-gopichand-padalkars-1385221</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/india-has-the-potential-to-become-a-global-leader-in-the-field-of-gems-and-jewellery-chief-minister-devendra-f.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-20-political-news-in-marathi-940632</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/thousands-of-rupees-were-laundered-during-the-corona-period-devendra-fadnavis-criticizes-thackeray/videoshow/123926314.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-directed-that-guidelines-should-be-issued-by-amending-the-criteria-of-the-solar-agricultural-pump-scheme-as-per-the-demands-of-the-farmers-local18-1483770.html</t>
+          <t>https://prahaar.in/2025/09/19/due-to-the-demand-of-farmers-the-criteria-of-this-scheme-will-now-be-changed/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/devendra-fadnavis-speech-at-chhatrapati-sambhajinagar-obc-activists-slogans-during-cm-speech-at-marathwada-mukti-sangram-din-program-marathi-news-1384714</t>
+          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/sports/lionel-messi-gives-cm-devendra-fadnavis-a-special-gift-of-signed-footbal-will-also-come-to-mumbai-for-a-visit-1385826</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-prime-minister-narendra-modi-birthday-chhagan-bhujbal-obc-reservation-rain-alert-wednesday-17-september-2025-1494134.html</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-20-political-news-in-marathi-940632</t>
+          <t>https://marathi.abplive.com/news/nagpur/chhagan-bhujbal-allegation-on-ncp-sharad-pawar-mla-for-antarwali-sarathi-protest-police-stone-pelting-jalna-1385055</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-advice-to-gopichand-padalkar-after-receiving-a-call-from-sharad-pawar-for-making-objectionable-comments-on-jayant-patil/923124/</t>
+          <t>https://www.loksatta.com/maharashtra/mumbai-rain-latest-updates-maharashtra-weather-news-political-devendra-fadnavis-sanjay-raut-asc-95-5375148/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/manoj-jarange-on-hyderabad-gadget-manoj-jarange-last-ultimatum-to-devendra-fadnavis-from-hyderabad-gazette/940846</t>
+          <t>https://www.saamana.com/harshwardhan-sapkal-accuses-maharashtra-cm-devendra-fadnavis-of-election-fraud-calls-him-thief-cm-during-press-conference/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/beed/devendra-fadnavis-beed-railway-inaguration-programme-train-dedicated-to-gopinath-munde-marathi-1384797</t>
+          <t>https://www.mumbaitak.in/city-news/mumbai/story/mumbai-news-mumbai-metro-4-trial-starts-from-today-these-passengers-will-benefit-more-3203440-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-leader-manoj-jarange-patil-big-announcement-about-delhi-visit/articleshow/123945687.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/uddhav-thackeray-in-power-the-mumbai-municipal-corporation-during-the-corona-period-committed-a-scam-in-the-body-bags-fadnavis-targets-thackeray/922227/</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-chagan-bhujbal-sharad-pawar-obc-reservation-rain-update-friday-19-september-2025-1495763.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/why-cant-they-be-removed-from-the-unruly-gopichand-padalkar-anjali-damania-lashed-out-at-cm-devendra-fadnavis-1385414</t>
+          <t>https://www.etvbharat.com/mr/!state/non-ac-local-trains-with-automatic-doors-to-run-in-mumbai-by-december-end-says-railway-minister-ashwini-vaishnav-maharashtra-news-mhs25092101481</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/sangli/gopichand-padalkar-clarification-on-his-statement-about-jayant-patil-after-receiving-a-call-from-cm-devendra-fadnavis/articleshow/123994231.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-criticizes-devendra-fadnavis-for-not-unveiling-the-statue-of-swami-ramanand-tirtha-despite-coming-to-chhatrapati-sambhajinagar/922378/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nashik/nashik-nationalist-party-sharad-pawar-group-aakrosh-morcha-mla-rohit-pawar-criticizes-chief-minister-devendra-fadnavis/articleshow/123919393.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/sharad-pawar-called-cm-devendra-fadnavis-about-gopichand-padalkar-controversial-statement-on-jayant-patil-in-sangli/articleshow/123992055.cms</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-criticized-jayant-patil-in-dirty-words-devendra-fadnavis-phone-call-to-gopichand-padalkars-1385221</t>
+          <t>https://www.loksatta.com/manoranjan/television/yeh-rishta-kya-kehlata-hai-fame-actor-rohit-purohit-sheena-bajaj-welcomes-baby-boy-hrc-97-5376440/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/navi-mumbai/bjp-leader-haresh-keni-joins-congress-shocks-devendra-fadnavis-prashant-thakur-ahead-of-panvel-municipal-election/articleshow/124013605.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-thackeray-brand-controversy-sanjay-raut-slams-devendra-fadnavis-over-balasaheb-thackeray-s-legacy-and-brand-remarks-1384959</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://www.dainikprabhat.com/devendra-fadnavis-this-is-a-clove-cracker-chief-minister-devendra-fadnavis-reply/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-criticizes-devendra-fadnavis-for-spending-on-varsha-his-official-residence/922751/</t>
+          <t>https://www.dainikprabhat.com/big-news-sudden-resignation-of-the-states-advocate-general-chief-minister-fadnavis-gave-information-in-the-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/mumbai-rain-latest-updates-maharashtra-weather-news-political-devendra-fadnavis-sanjay-raut-asc-95-5375148/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-19-september-2025-125091900004_1.html</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-chagan-bhujbal-sharad-pawar-obc-reservation-rain-update-friday-19-september-2025-1495763.html</t>
+          <t>https://vishwanewsmarathi.com/sharad-pawars-main-indicator-but-wisdom-is-a-matter-of-learning/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-prime-minister-narendra-modi-birthday-chhagan-bhujbal-obc-reservation-rain-alert-wednesday-17-september-2025-1494134.html</t>
+          <t>https://www.dainikprabhat.com/nashik-news-sharad-pawar-aggressive-on-farmers-issues-targets-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-criticizes-devendra-fadnavis-for-not-unveiling-the-statue-of-swami-ramanand-tirtha-despite-coming-to-chhatrapati-sambhajinagar/922378/</t>
+          <t>https://mahasamvad.in/179557/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/in-pune-city-water-supply-will-remain-suspended-on-thursday-pune-print-news-asj-82-5378829/</t>
+          <t>https://zeenews.india.com/marathi/video/cm-fadnavis-on-maharastra-crop-loss/940080</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/sharad-pawar-called-cm-devendra-fadnavis-about-gopichand-padalkar-controversial-statement-on-jayant-patil-in-sangli/articleshow/123992055.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-thackeray-brand-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%A5%E0%A5%87%E0%A4%9F%E0%A4%9A-%E0%A4%9F-%E0%A4%B2%E0%A5%87%E0%A4%AC-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82-marathi-news/vi-AA1MI8n0?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chhatrapati-sambhaji-nagar/chhatrapati-sambhajinagar-80-year-old-sunanda-shinde-write-letter-to-cm-devendra-fadnavis-on-adarsh-bank-scam-local18-1481471.html</t>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-bmc-election-%E0%A4%B2-%E0%A4%B9%E0%A5%82%E0%A4%A3-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0-%E0%A4%B9-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%9A-bjp-melava/vi-AA1MFmSp?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/manoranjan/television/yeh-rishta-kya-kehlata-hai-fame-actor-rohit-purohit-sheena-bajaj-welcomes-baby-boy-hrc-97-5376440/</t>
+          <t>https://marathi.ndtv.com/politics/political-news-file-a-case-against-sharad-pawar-gopichand-padalkar-demands-markadwadi-solapur-9294330</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/devendra-fadnavis-this-is-a-clove-cracker-chief-minister-devendra-fadnavis-reply/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-19-september-2025-125091900004_1.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-news-sudden-resignation-of-the-states-advocate-general-chief-minister-fadnavis-gave-information-in-the-cabinet-meeting/</t>
+          <t>https://mahasamvad.in/179349/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/sharad-pawars-main-indicator-but-wisdom-is-a-matter-of-learning/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/cm-devendra-fadnavis-directs-to-prepare-comprehensive-effective-policy-to-fight-cancer-maharashtra-health-marathi-news-1384411</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/nashik-news-sharad-pawar-aggressive-on-farmers-issues-targets-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.loksatta.com/mumbai/committee-of-eight-ias-to-draft-vision-of-vikasit-maharashtra-2047-zws-70-5375200/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/harshwardhan-sapkal-chief-minister-fadnavis-should-resign-congress-state-president-harshwardhan-sapkal-demanded/</t>
+          <t>https://news18marathi.com/mumbai/maharastra-cabinate-meeting-inside-story-ajit-pawar-makes-laughter-in-front-of-devendra-fadanvis-latest-marathi-news-1481676.html</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/sharad-pawars-ncp-took-notice-of-padalkars-low-level-criticism-amol-kolhe-and-prashant-jagtaps-strong-response/</t>
+          <t>https://marathi.abplive.com/news/politics/ajit-pawar-in-nagpur-refusal-to-accept-that-vidarbha-is-the-stronghold-of-bjp-and-devendra-fadnavis-maharashtra-politics-marathi-news-1385133</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179557/</t>
+          <t>https://mahasamvad.in/178649/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chief-minister-devendra-fadnavis-inspects-nashik-and-surrounding-areas-in-the-backdrop-of-kumbh-mela-gives-important-instructions-local18-1483785.html</t>
+          <t>https://agrowon.esakal.com/agro-special/8-important-decisions-in-the-cabinet-meeting-132-crores-of-funds-for-farmers-buildings-and-extension-of-the-deadline-for-the-construction-of-a-modern-orange-center-rat16</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/kunbi-certificate-%E0%A4%96-%E0%A4%A1-%E0%A4%96-%E0%A4%A1-%E0%A4%95-%E0%A4%97%E0%A4%A6%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A7-%E0%A4%B0%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%A6-%E0%A4%96%E0%A4%B2%E0%A5%87-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A4%B0%E0%A4%A3/ar-AA1MMluT?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-at-bjp-vijay-sankalp-melava/videoshow/123937912.cms</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/devendra-fadanvis-attack-uddhav-thackeray-and-raj-thackeray-over-mumbai-mahapalika-bjp-vijay-melava-1481400.html</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/manoj-jarange-admire-maharashtra-cm-devendra-fadnavis-after-maratha-reservation-protest-1481999.html</t>
+          <t>https://marathi.abplive.com/news/thane/thane-metro-4-and-metro-4a-35-km-long-how-many-stations-trial-run-by-devendra-fadnavis-eknath-shinde-see-details-in-marathi-1385959</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178525/</t>
+          <t>https://mahasamvad.in/179466/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-thackeray-brand-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%A5%E0%A5%87%E0%A4%9F%E0%A4%9A-%E0%A4%9F-%E0%A4%B2%E0%A5%87%E0%A4%AC-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82-marathi-news/vi-AA1MI8n0?ocid=hpmsn</t>
+          <t>https://marathi.abplive.com/news/maharashtra/nashik-kumbh-mela-news-government-forms-committee-of-ministers-for-kumbh-mela-to-be-held-in-nashik-cm-devendra-fadnavis-girish-mahajan-dadabhuse-1385300</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-bmc-election-%E0%A4%B2-%E0%A4%B9%E0%A5%82%E0%A4%A3-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0-%E0%A4%B9-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%9A-bjp-melava/vi-AA1MFmSp?ocid=hpmsn</t>
+          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-informed-that-the-states-advocate-general-birendra-saraf-has-resigned/922000/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178515/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-17-september-2025-pm-narendra-modi-75th-birthday-zp-presidentship-reservation-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179580/</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179349/</t>
+          <t>https://marathi.abplive.com/news/politics/sanjay-raut-on-maharashtra-debt-burden-slams-devendra-fadnavis-eknath-shinde-ajit-pawar-says-state-situation-is-similar-to-nepal-marathi-news-1384489</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/obc-activist-shouting-slogans-during-cm-devendra-fadnavis-speech-at-chhatrapati-sambhaji-nagar-1481714.html</t>
+          <t>https://marathi.abplive.com/news/nagpur/ajit-pawar-advise-to-bjp-mla-gopichand-padalkar-on-jayant-patil-statement-maharashtra-politics-marathi-news-1385092</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/maharastra-cabinate-meeting-inside-story-ajit-pawar-makes-laughter-in-front-of-devendra-fadanvis-latest-marathi-news-1481676.html</t>
+          <t>https://news18marathi.com/maharashtra/maharashtra-ias-officer-transfer-order-cabinet-meeting-devendra-fadanvis-ws-a-1481304.html</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/when-will-river-linking-project-in-marathwada-start-chief-minister-fadnavis-has-given-information-about-this-1482614.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-cabinet-meeting-maharashtra-animation-gaming-policy-announced-government-takes-8-major-decisions-95140</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/cm-devendra-fadnavis-directs-to-prepare-comprehensive-effective-policy-to-fight-cancer-maharashtra-health-marathi-news-1384411</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
@@ -2475,945 +2475,945 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/punepolice-force-1720-posts-will-soon-be-approved-by-the-high-powered-committee-headed-by-chief-minister-devendra-fadnavis/articleshow/124010529.cms</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://agrowon.esakal.com/agro-special/the-drought-history-of-marathwada-will-be-compiled-rat16</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178530/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/sharad-pawar-says-farmer-lives-are-in-trouble-devevendra-fadnavis-taking-the-name-of-shivaji-maharaj-and-not-looking-at-baliraja-1384307</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/what-is-the-new-decision-of-the-state-government-regarding-making-agricultural-land-na-1484003.html</t>
+          <t>https://maharashtratimes.com/e-paper/non-agricultural-land-certificates-compulsion-removed-for-micro-and-small-businesses/articleshow/123988928.cms</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/punepolice-force-1720-posts-will-soon-be-approved-by-the-high-powered-committee-headed-by-chief-minister-devendra-fadnavis/articleshow/124010529.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/congress-state-president-harshvardhan-sapkal-criticize-devendra-fadnavis-rss-narendra-modi/articleshow/124023628.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/8-important-decisions-in-the-cabinet-meeting-132-crores-of-funds-for-farmers-buildings-and-extension-of-the-deadline-for-the-construction-of-a-modern-orange-center-rat16</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-18-september-monsoon-maratha-reservation-obc-bmc-election-mumbai-local-train-weather-political-doctors-strike-tajya-batmya-in-marathi-940110</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadnavis-reaction-on-rahul-gandhi-allegations-bogus-voting-in-chandrapur-rajura-1483022.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/sharad-pawar-criticizes-devendra-fadnavis-over-farmers-issues-from-aakrosh-morcha/921710/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179466/</t>
+          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-targets-devendra-fadnavis-over-marathwada-flood-situation/921688/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-at-bjp-vijay-sankalp-melava/videoshow/123937912.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/jayant-patil-heavy-rain-agriculture-news-declaring-a-wet-drought-in-the-state-jayant-patil-letter-to-chief-minister-devendra-fadnavis-in-sangli-1385048</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178534/</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179384/</t>
+          <t>https://maharashtratimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-cabinet-meeting-maharashtra-animation-gaming-policy-announced-government-takes-8-major-decisions-95140</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/bjp-slams-sharad-pawar-for-criticising-questioning-cm-devendra-fadnavis-over-farmers-issues-in-state/939611</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/maharashtra-ias-officer-transfer-order-cabinet-meeting-devendra-fadanvis-ws-a-1481304.html</t>
+          <t>https://lokmanthan.com/a-comprehensive-policy-should-be-prepared-for-cancer-treatment-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/devendra-fadnavis-informed-that-the-states-advocate-general-birendra-saraf-has-resigned/922000/</t>
+          <t>https://lokmanthan.com/hyundai-should-invest-more-and-more-in-the-state-and-increase-employment-generation-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/sharad-pawar-attack-cm-devendra-fadanvis-over-farmer-loan-waiver-and-crop-rate-issue-ncp-nashik-melava-1480406.html</t>
+          <t>https://www.dainikprabhat.com/pune-news-governments-make-and-break-on-reservation-continues-vijay-vadettiwar-hits-out-at-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/37/?m=0</t>
+          <t>https://www.newsdanka.com/vishesh/how-was-the-first-meeting-between-devendra-fadnavis-and-narendra-modi/167384/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/advocate-general-birendra-saraf-resigns-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%A7-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AC-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0-%E0%A4%AB-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE/ar-AA1MDN7q</t>
+          <t>https://marathi.timesnownews.com/maharashtra/thane-metro-4-and-4a-span-35-km-with-32-stations-trial-run-inspected-by-devendra-fadnavis-and-eknath-shinde-full-details-in-marathi-article-152872624</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sanjay-raut-on-maharashtra-debt-burden-slams-devendra-fadnavis-eknath-shinde-ajit-pawar-says-state-situation-is-similar-to-nepal-marathi-news-1384489</t>
+          <t>https://www.newsdanka.com/videos/fadnavis-natwarlal-rohit-pawar-peoples-leader/167361/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-17-september-2025-pm-narendra-modi-75th-birthday-zp-presidentship-reservation-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://marathi.timesnownews.com/maharashtra/maharashtra-cm-devendra-fadnavis-says-will-make-changes-in-magel-tyala-saur-krushi-pump-yojana-article-152857154</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/manoj-jarange-patil-warning-cm-devendra-fadanvis-regarding-kunbi-certificate-1484509.html</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/sharad-pawar-calls-cm-devendra-fadnavis-and-complained-about-gopichand-padalkar/</t>
+          <t>https://www.punjabnewsexpress.com/national/news/fadnavis-calls-rahul-gandhi-%E2%80%98urban-naxal-then-what-about-indias-foreign-policy-leaning-towards-%E2%80%98maoism-asks-shiv-se-299178</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/non-agricultural-land-certificates-compulsion-removed-for-micro-and-small-businesses/articleshow/123988928.cms</t>
+          <t>https://www.business-standard.com/india-news/govt-committed-to-empowering-women-ladki-bahin-to-continue-cm-fadnavis-125091700582_1.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/the-drought-history-of-marathwada-will-be-compiled-rat16</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-govt-signs-mou-with-cambridge-to-elevate-school-education-101758482430602.html</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/sharad-pawar-says-farmer-lives-are-in-trouble-devevendra-fadnavis-taking-the-name-of-shivaji-maharaj-and-not-looking-at-baliraja-1384307</t>
+          <t>https://www.businessworld.in/article/hyundai-maharashtra-discuss-new-investments-jobs-571636</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/entertainment/entertainment-news/television-news/devendra-fadnavis-watch-maharashtrachi-hasya-jatra-says-samir-choughule-in-mhj-unplugged/articleshow/123995979.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/meenatai-thackeray-statue-smeared-with-red-paint-1-held-101758136336233.html</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-govt-will-create-corpus-fund-to-cover-treatments-costing-over-rs-5-lakh-fadnavis/2917336</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://www.ptinews.com/story/national/mumbai-to-get-pod-taxi-services-for-last-mile-connectivity-to-ease-traffic-woes-cm-fadnavis/2938730</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/entertainment/entertainment-news/bollywood-news/kishor-kadam-exposes-bmc-fraud-of-engeineer-housing-society-scam-in-latest-post-to-cm-devendra-fadnavis/articleshow/123891023.cms</t>
+          <t>https://www.bignewsnetwork.com/news/278584060/maharashtra-cm-condemns-alleged-vandalism-of-meenatai-thackeray-bust-orders-probe</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/pm-modi-birthday-special-cm-devendra-fadnavis-and-dcm-ekanth-shinde-wrote-articles-praises-modi-leadership-1384692</t>
+          <t>https://www.sakshipost.com/news/mou-cambridge-new-phase-world-class-education-maha-cm-fadnavis-454046</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sharad-pawar-criticizes-devendra-fadnavis-over-farmers-issues-from-aakrosh-morcha/921710/</t>
+          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/shivsena-ubt-mp-sanjay-raut-press-conference-attack-on-bjp-on-corruption-and-debt-on-state-saamana-online-news/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-no-matter-what-happens-the-mayor-will-be-from-the-mahayuti-chief-minister-criticizes-thackeray-brothers-from-bjps-vijay-sankalp-rally/922208/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ambadas-danve-targets-devendra-fadnavis-over-marathwada-flood-situation/921688/</t>
+          <t>https://agrowon.esakal.com/agro-special/40-year-wait-ends-as-261-km-beedahilyanagar-rail-line-opens-rat16</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/jayant-patil-heavy-rain-agriculture-news-declaring-a-wet-drought-in-the-state-jayant-patil-letter-to-chief-minister-devendra-fadnavis-in-sangli-1385048</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-live-breaking-news-17th-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-marathwada-vidarbha-rain-alert/liveblog/123933492.cms</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/fadnavis-flagged-off-the-first-train-service-from-beed-to-ahilyanagar-125091800006_1.html</t>
+          <t>https://vishwanewsmarathi.com/acharya-devvrat-takes-charge-as-governor-oath-taking-ceremony-held-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-governments-make-and-break-on-reservation-continues-vijay-vadettiwar-hits-out-at-fadnavis/</t>
+          <t>https://www.livehindustan.com/maharashtra/maharashtra-cm-devendra-fadnavis-in-new-tension-over-quota-clash-maratha-vs-obc-banjara-vs-tribal-community-politics-201757910651491.html</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/how-was-the-first-meeting-between-devendra-fadnavis-and-narendra-modi/167384/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-18-september-2025-125091800004_1.html</t>
+          <t>https://www.amarujala.com/video/india-news/rahul-gandhi-vote-theft-claim-cm-fond-of-rahul-gandhi-s-vote-theft-claims-gives-this-reply-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/govt-committed-to-empowering-women-ladki-bahin-to-continue-cm-fadnavis-125091700582_1.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/CM-Fadnavis-must-resign-after-Rahul-Gandhi-exposed-vote-theft-in-Maharashtra-Sapkal/2926755</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/gst-reforms-are-a-historic-initiative-maharashtra-cm-fadnavis-lauds-pm-modis-nation-address/</t>
+          <t>https://news18marathi.com/agriculture/what-is-the-new-decision-of-the-state-government-regarding-making-agricultural-land-na-1484003.html</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
+          <t>https://mahasamvad.in/179384/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/devendra-fadnavis-no-matter-what-happens-the-mayor-will-be-from-the-mahayuti-chief-minister-criticizes-thackeray-brothers-from-bjps-vijay-sankalp-rally/922208/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/mumbai/sra-how-is-aspect-realtys-board-on-bmcs-plot-varsha-gaikwads-question-mark-on-the-project-in-juhu-gali/922260/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-uddhav-thackeray-in-mumbai-bjp-vijay-sankalpa-melava/articleshow/123926617.cms</t>
+          <t>https://www.etvbharat.com/mr/!bharat/pm-narendra-modi-to-inaugurate-development-projects-worth-over-rs-34200-crore-in-gujarat-today-maharashtra-news-mhs25092001395</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-and-bjp-stage-a-strong-show-of-strength-on-the-occasion-of-metro-trial-in-thane-cm-devendra-fadnavis-eknath-shinde-pratap-sarnaik/923787/</t>
+          <t>https://www.loksatta.com/aurangabad/big-announcements-zero-ground-impact-maharashtra-cabinet-ambadas-danve-ocd-94-5373775/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://udayavani.com/national/injured-toddler-dies-on-way-to-hospital-as-ambulance-gets-stuck-in-traffic-jam-in-thane-001355?lang=en</t>
+          <t>https://www.loksatta.com/mumbai/bhandara-gadchiroli-expressway-project-cabinet-approval-ocd-94-5377349/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maharashtra-mandates-e-kyc-for-ladki-bahin-beneficiaries-sets-deadline-125091900196_1.html</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-airport-terminal-expansion-and-mihan-aerospace-project-updates-vsb99</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://udayavani.com/kerala-woman-goes-missing-after-losing-rs-11-lakh-in-cyber-scam-486240?lang=en</t>
+          <t>https://www.marathiebatmya.com/mumbai/varsha-gaikwad-alleges-the-government-is-kind-to-devendra-fadnavis-builder-friend/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/delhi-cm-praises-pm-modi-for-gst-reforms-says-public-to-benefit-directly/</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/mahindra-tractors-and-maharashtra-govt-partner-to-launch-skill-development-centre-in-gadchiroli/</t>
+          <t>https://www.animationxpress.com/latest-news/maharashtra-government-approves-states-avgc-xr-policy-with-rs-3000-crore-plan/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/no-question-of-pm-modis-retirement-increased-bjp-and-rss-bonding-ater-pm-modi-nagpur-visits-says-rss-researcher-dilip-devdhar-pm-modi-turns-75-today-75th-birthday-maharashtra-news-mhs25091700500</t>
+          <t>https://www.storyboard18.com/digital/maharashtra-cabinet-approves-%E2%82%B93268-cr-avgc-xr-policy-will-boost-creator-economy-81032.htm</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-govt-to-launch-cleanliness-drive-in-750-villages-on-sep-17-to-mark-pm-modis-birthday-95099</t>
+          <t>https://m.economictimes.com/news/india/maharashtras-new-policy-to-promote-creative-tech-sector/articleshow/123928891.cms</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://thelivenagpur.com/2025/09/17/maharashtra-unveils-rs-3268-cr-policy-to-boost-avgc-xr-approves-key-welfare-projects/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/sampadkiya/columns/loksatta-anvyarth-conflicts-continue-to-persist-even-after-prime-minister-narendra-modi-visit-to-manipur-amy-95-5380171/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/hi-tech-media-park-in-nagpur-with-rs3000cr-nod-to-avgc-xr/articleshow/123928752.cms</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/one-crore-women-in-maharashtra-will-be-made-millionaires-rat16</t>
+          <t>https://scanx.trade/stock-market-news/stocks/hudco-re-appoints-baldeo-purushartha-as-government-nominee-director/19487527</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/business/finance/know-where-has-pm-modi-invested-his-wealth-investment-options-marathi-news-rak-94-5379523/</t>
+          <t>https://www.ahmedabadmirror.com/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/81899457.html</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/centre-decision-crushes-pulse-farmers-in-india-ocd-94-5382837/</t>
+          <t>https://www.mypunepulse.com/maharashtra-cabinet-approves-8-key-decisions-announces-new-animation-vfx-gaming-policy-2025/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>